--- a/Übungen/Online_Shop.xlsx
+++ b/Übungen/Online_Shop.xlsx
@@ -20,18 +20,115 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="46">
+  <si>
+    <t xml:space="preserve">Beispiel: Funktionsorientierter Projektstrukturplan</t>
+  </si>
   <si>
     <t xml:space="preserve">Online-Shop</t>
   </si>
   <si>
-    <t xml:space="preserve">PSP ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">verantwortl.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teilprojekt</t>
+    <t xml:space="preserve">Fr. Claire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Produkt-Katalogisierung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entwicklung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dokumentation, Tests,
+Kundenbetreuung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hr. Karl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fr. Groß</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hr. Nguyen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Produkte kategorisieren</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Datenbank erstellen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Handbücher erstellen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Produkte erfassen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seitenstruktur einrichten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Produktfotos erstellen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auftraggeber-Präsentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Produktfotos bearbeiten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Template auswählen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zahlungsdienste einbinden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bewertungssystem anpassen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2.6</t>
   </si>
   <si>
     <t xml:space="preserve">PSP-ID</t>
@@ -40,49 +137,25 @@
     <t xml:space="preserve">Arbeitspaket</t>
   </si>
   <si>
-    <t xml:space="preserve">Datenbank erstellen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Produkte kategorisieren</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Produkte erfassen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Produktfotos erstellen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Produktfotos bearbeiten</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Template auswählen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seitenstruktur einrichten</t>
+    <t xml:space="preserve">Korrekturen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eventuelle Korrekturen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2.4</t>
   </si>
   <si>
     <t xml:space="preserve">Datenbank einbinden</t>
   </si>
   <si>
-    <t xml:space="preserve">Zahlungsdienste einbinden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bewertungssystem anpassen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Handbücher erstellen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tests</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Korrekturen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auftraggeber-Präsentation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eventuelle Korrekturen</t>
+    <t xml:space="preserve">1.2.9</t>
   </si>
   <si>
     <t xml:space="preserve">Onlinestellung</t>
@@ -92,9 +165,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="@"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
+    <numFmt numFmtId="166" formatCode="@"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -301,7 +375,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="23">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -338,6 +412,14 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -346,7 +428,11 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -354,7 +440,11 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -362,12 +452,20 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -445,52 +543,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>906840</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>720</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>906840</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>8640</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp>
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="0" name=""/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5483160" y="488160"/>
-          <a:ext cx="0" cy="170640"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="0">
-          <a:solidFill>
-            <a:srgbClr val="3465a4"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
-        <a:fontRef idx="minor"/>
-      </xdr:style>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
@@ -503,7 +555,9 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2"/>
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -512,7 +566,7 @@
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
       <c r="I1" s="4" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1" s="4"/>
       <c r="K1" s="3"/>
@@ -523,7 +577,7 @@
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="5" t="n">
         <v>1</v>
       </c>
       <c r="J2" s="5" t="s">
@@ -560,190 +614,486 @@
       <c r="G5" s="4"/>
       <c r="H5" s="3"/>
       <c r="I5" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J5" s="4"/>
       <c r="K5" s="3"/>
-      <c r="L5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="M5" s="4"/>
+      <c r="L5" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="M5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="0"/>
       <c r="F6" s="5" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="5" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="5" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>2</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="0"/>
+      <c r="G7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="M7" s="6"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="I8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="4"/>
+      <c r="L8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M8" s="4"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="L9" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="M9" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="M10" s="6"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F11" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="I11" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J11" s="4"/>
+      <c r="L11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M11" s="4"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F12" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="L12" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="M13" s="6"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F14" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="I14" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J14" s="4"/>
+      <c r="L14" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="M14" s="4"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F15" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="L15" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="M15" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G16" s="6"/>
+      <c r="J16" s="6"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F17" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="I17" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J17" s="4"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F18" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J19" s="6"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I20" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J20" s="4"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I21" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J22" s="6"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I23" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J23" s="4"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I24" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
+      <c r="A25" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="J25" s="6"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="11"/>
-      <c r="B26" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
+      <c r="A26" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="I26" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J26" s="4"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
+      <c r="A27" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="I27" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
+      <c r="A28" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B28" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="J28" s="6"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14" t="s">
+      <c r="A29" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="I29" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J29" s="4"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="I30" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="J30" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
+      <c r="A31" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="J31" s="6"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
+      <c r="A32" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="I32" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J32" s="4"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
+      <c r="A33" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="I33" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14" t="s">
+      <c r="A34" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="B34" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-    </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-    </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
+      <c r="A37" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B37" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
+      <c r="A38" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
+      <c r="A39" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B39" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
+      <c r="A40" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="15"/>
-      <c r="B41" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C41" s="16"/>
-      <c r="D41" s="16"/>
+      <c r="A41" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="38">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="L5:M5"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="I23:J23"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="I26:J26"/>
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="B29:D29"/>
+    <mergeCell ref="I29:J29"/>
     <mergeCell ref="B30:D30"/>
     <mergeCell ref="B31:D31"/>
     <mergeCell ref="B32:D32"/>
+    <mergeCell ref="I32:J32"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="B35:D35"/>
@@ -761,6 +1111,5 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>
   </headerFooter>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Übungen/Online_Shop.xlsx
+++ b/Übungen/Online_Shop.xlsx
@@ -20,18 +20,115 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="46">
+  <si>
+    <t xml:space="preserve">Beispiel: Funktionsorientierter Projektstrukturplan</t>
+  </si>
   <si>
     <t xml:space="preserve">Online-Shop</t>
   </si>
   <si>
-    <t xml:space="preserve">PSP ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">verantwortl.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teilprojekt</t>
+    <t xml:space="preserve">Fr. Claire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Produkt-Katalogisierung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entwicklung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dokumentation, Tests,
+Kundenbetreuung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hr. Karl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fr. Groß</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hr. Nguyen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Produkte kategorisieren</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Datenbank erstellen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Handbücher erstellen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Produkte erfassen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seitenstruktur einrichten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Produktfotos erstellen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auftraggeber-Präsentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Produktfotos bearbeiten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Template auswählen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zahlungsdienste einbinden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bewertungssystem anpassen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2.6</t>
   </si>
   <si>
     <t xml:space="preserve">PSP-ID</t>
@@ -40,49 +137,25 @@
     <t xml:space="preserve">Arbeitspaket</t>
   </si>
   <si>
-    <t xml:space="preserve">Datenbank erstellen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Produkte kategorisieren</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Produkte erfassen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Produktfotos erstellen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Produktfotos bearbeiten</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Template auswählen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seitenstruktur einrichten</t>
+    <t xml:space="preserve">Korrekturen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eventuelle Korrekturen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2.4</t>
   </si>
   <si>
     <t xml:space="preserve">Datenbank einbinden</t>
   </si>
   <si>
-    <t xml:space="preserve">Zahlungsdienste einbinden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bewertungssystem anpassen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Handbücher erstellen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tests</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Korrekturen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auftraggeber-Präsentation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eventuelle Korrekturen</t>
+    <t xml:space="preserve">1.2.9</t>
   </si>
   <si>
     <t xml:space="preserve">Onlinestellung</t>
@@ -92,9 +165,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="@"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
+    <numFmt numFmtId="166" formatCode="@"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -301,7 +375,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="23">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -338,6 +412,14 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -346,7 +428,11 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -354,7 +440,11 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -362,12 +452,20 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -445,65 +543,21 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>906840</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>720</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>906840</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>8640</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp>
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="0" name=""/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5483160" y="488160"/>
-          <a:ext cx="0" cy="170640"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="0">
-          <a:solidFill>
-            <a:srgbClr val="3465a4"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
-        <a:fontRef idx="minor"/>
-      </xdr:style>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M41"/>
-  <sheetFormatPr defaultColWidth="13.0390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="13.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.77"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2"/>
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -512,7 +566,7 @@
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
       <c r="I1" s="4" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1" s="4"/>
       <c r="K1" s="3"/>
@@ -523,7 +577,7 @@
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="5" t="n">
         <v>1</v>
       </c>
       <c r="J2" s="5" t="s">
@@ -560,190 +614,486 @@
       <c r="G5" s="4"/>
       <c r="H5" s="3"/>
       <c r="I5" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J5" s="4"/>
       <c r="K5" s="3"/>
-      <c r="L5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="M5" s="4"/>
+      <c r="L5" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="M5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="0"/>
       <c r="F6" s="5" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="5" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="5" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>2</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="0"/>
+      <c r="G7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="M7" s="6"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="I8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="4"/>
+      <c r="L8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M8" s="4"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="L9" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="M9" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="M10" s="6"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F11" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="I11" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J11" s="4"/>
+      <c r="L11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M11" s="4"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F12" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="L12" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="M13" s="6"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F14" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="I14" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J14" s="4"/>
+      <c r="L14" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="M14" s="4"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F15" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="L15" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="M15" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G16" s="6"/>
+      <c r="J16" s="6"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F17" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="I17" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J17" s="4"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F18" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J19" s="6"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I20" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J20" s="4"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I21" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J22" s="6"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I23" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J23" s="4"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I24" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
+      <c r="A25" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="J25" s="6"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="11"/>
-      <c r="B26" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
+      <c r="A26" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="I26" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J26" s="4"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
+      <c r="A27" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="I27" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
+      <c r="A28" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B28" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="J28" s="6"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14" t="s">
+      <c r="A29" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="I29" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J29" s="4"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="I30" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="J30" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
+      <c r="A31" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="J31" s="6"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
+      <c r="A32" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="I32" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J32" s="4"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
+      <c r="A33" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="I33" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14" t="s">
+      <c r="A34" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="B34" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-    </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-    </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
+      <c r="A37" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B37" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
+      <c r="A38" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
+      <c r="A39" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B39" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
+      <c r="A40" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="15"/>
-      <c r="B41" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C41" s="16"/>
-      <c r="D41" s="16"/>
+      <c r="A41" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="38">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="L5:M5"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="I23:J23"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="I26:J26"/>
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="B29:D29"/>
+    <mergeCell ref="I29:J29"/>
     <mergeCell ref="B30:D30"/>
     <mergeCell ref="B31:D31"/>
     <mergeCell ref="B32:D32"/>
+    <mergeCell ref="I32:J32"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="B35:D35"/>
@@ -761,6 +1111,5 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>
   </headerFooter>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Übungen/Online_Shop.xlsx
+++ b/Übungen/Online_Shop.xlsx
@@ -20,139 +20,108 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="46">
-  <si>
-    <t xml:space="preserve">Beispiel: Funktionsorientierter Projektstrukturplan</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="36">
   <si>
     <t xml:space="preserve">Online-Shop</t>
   </si>
   <si>
-    <t xml:space="preserve">Fr. Claire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Produkt-Katalogisierung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entwicklung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dokumentation, Tests,
-Kundenbetreuung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hr. Karl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fr. Groß</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hr. Nguyen</t>
+    <t xml:space="preserve">PSP-ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">verantw.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teilprojekt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arbeitspaket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Datenbank erstellen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1.1</t>
   </si>
   <si>
     <t xml:space="preserve">Produkte kategorisieren</t>
   </si>
   <si>
-    <t xml:space="preserve">Datenbank erstellen</t>
+    <t xml:space="preserve">1.1.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Produkte erfassen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Produktfotos erstellen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Produktfotos bearbeiten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Template auswählen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seitenstruktur einrichten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Datenbank einbinden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zahlungsdienste einbinden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bewertungssystem anpassen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3.1</t>
   </si>
   <si>
     <t xml:space="preserve">Handbücher erstellen</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Produkte erfassen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seitenstruktur einrichten</t>
+    <t xml:space="preserve">1.3.2</t>
   </si>
   <si>
     <t xml:space="preserve">Tests</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Produktfotos erstellen</t>
+    <t xml:space="preserve">1.2.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Korrekturen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3.3</t>
   </si>
   <si>
     <t xml:space="preserve">Auftraggeber-Präsentation</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Produktfotos bearbeiten</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Template auswählen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zahlungsdienste einbinden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bewertungssystem anpassen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSP-ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arbeitspaket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Korrekturen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2.7</t>
+    <t xml:space="preserve">1.2.8</t>
   </si>
   <si>
     <t xml:space="preserve">eventuelle Korrekturen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Datenbank einbinden</t>
   </si>
   <si>
     <t xml:space="preserve">1.2.9</t>
@@ -165,10 +134,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
-    <numFmt numFmtId="166" formatCode="@"/>
+    <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -375,7 +343,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -412,14 +380,6 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -428,11 +388,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -440,11 +396,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -452,20 +404,12 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -549,15 +493,13 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M41"/>
-  <sheetFormatPr defaultColWidth="13.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="13.07421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.77"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
+      <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -566,7 +508,7 @@
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
       <c r="I1" s="4" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J1" s="4"/>
       <c r="K1" s="3"/>
@@ -577,7 +519,7 @@
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="5" t="n">
+      <c r="I2" s="5" t="s">
         <v>1</v>
       </c>
       <c r="J2" s="5" t="s">
@@ -614,36 +556,36 @@
       <c r="G5" s="4"/>
       <c r="H5" s="3"/>
       <c r="I5" s="4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J5" s="4"/>
       <c r="K5" s="3"/>
-      <c r="L5" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="M5" s="9"/>
+      <c r="L5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="M5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="0"/>
       <c r="F6" s="5" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="5" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="5" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -652,448 +594,191 @@
       <c r="J7" s="6"/>
       <c r="M7" s="6"/>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F8" s="4" t="s">
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="4"/>
-      <c r="I8" s="4" t="s">
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="J8" s="4"/>
-      <c r="L8" s="4" t="s">
+      <c r="B30" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="M8" s="4"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F9" s="5" t="s">
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I9" s="5" t="s">
+      <c r="B31" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="J9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="L9" s="10" t="s">
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="M9" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="M10" s="6"/>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F11" s="4" t="s">
+      <c r="B32" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="G11" s="4"/>
-      <c r="I11" s="4" t="s">
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="J11" s="4"/>
-      <c r="L11" s="4" t="s">
+      <c r="B33" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="M11" s="4"/>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F12" s="5" t="s">
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B34" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="G12" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I12" s="5" t="s">
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="J12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="L12" s="10" t="s">
+      <c r="B35" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="M12" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="M13" s="6"/>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F14" s="4" t="s">
+      <c r="C35" s="14"/>
+      <c r="D35" s="14"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="G14" s="4"/>
-      <c r="I14" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J14" s="4"/>
-      <c r="L14" s="4" t="s">
+      <c r="B36" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="M14" s="4"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F15" s="5" t="s">
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="L15" s="10" t="s">
+      <c r="B37" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="M15" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G16" s="6"/>
-      <c r="J16" s="6"/>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F17" s="4" t="s">
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="G17" s="4"/>
-      <c r="I17" s="4" t="s">
+      <c r="B38" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="J17" s="4"/>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F18" s="5" t="s">
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="G18" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I18" s="5" t="s">
+      <c r="B39" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="J18" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J19" s="6"/>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I20" s="4" t="s">
+      <c r="C39" s="14"/>
+      <c r="D39" s="14"/>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="J20" s="4"/>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I21" s="5" t="s">
+      <c r="B40" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="J21" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J22" s="6"/>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I23" s="4" t="s">
+      <c r="C40" s="14"/>
+      <c r="D40" s="14"/>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="J23" s="4"/>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I24" s="5" t="s">
+      <c r="B41" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="J24" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="J25" s="6"/>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B26" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-      <c r="I26" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="J26" s="4"/>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="I27" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="J27" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="B28" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="J28" s="6"/>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="B29" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="I29" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J29" s="4"/>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
-      <c r="I30" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J30" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="B31" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="J31" s="6"/>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="B32" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="I32" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J32" s="4"/>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="B33" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
-      <c r="I33" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="J33" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="B34" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
-    </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="B35" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="C35" s="18"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="18"/>
-    </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B36" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
-    </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B37" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="C37" s="18"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="18"/>
-      <c r="F37" s="18"/>
-    </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="18"/>
-    </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="B39" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="C39" s="18"/>
-      <c r="D39" s="18"/>
-      <c r="E39" s="18"/>
-      <c r="F39" s="18"/>
-    </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="B40" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="C40" s="18"/>
-      <c r="D40" s="18"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="18"/>
-    </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="C41" s="21"/>
-      <c r="D41" s="21"/>
-      <c r="E41" s="22"/>
-      <c r="F41" s="22"/>
+      <c r="C41" s="16"/>
+      <c r="D41" s="16"/>
     </row>
   </sheetData>
-  <mergeCells count="38">
+  <mergeCells count="22">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="L5:M5"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="L14:M14"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="I23:J23"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="B26:D26"/>
-    <mergeCell ref="I26:J26"/>
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="B29:D29"/>
-    <mergeCell ref="I29:J29"/>
     <mergeCell ref="B30:D30"/>
     <mergeCell ref="B31:D31"/>
     <mergeCell ref="B32:D32"/>
-    <mergeCell ref="I32:J32"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="B35:D35"/>

--- a/Übungen/Online_Shop.xlsx
+++ b/Übungen/Online_Shop.xlsx
@@ -20,108 +20,139 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="46">
+  <si>
+    <t xml:space="preserve">Beispiel: Funktionsorientierter Projektstrukturplan</t>
+  </si>
   <si>
     <t xml:space="preserve">Online-Shop</t>
   </si>
   <si>
+    <t xml:space="preserve">Fr. Claire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Produkt-Katalogisierung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entwicklung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dokumentation, Tests,
+Kundenbetreuung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hr. Karl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fr. Groß</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hr. Nguyen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Produkte kategorisieren</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Datenbank erstellen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Handbücher erstellen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Produkte erfassen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seitenstruktur einrichten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Produktfotos erstellen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auftraggeber-Präsentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Produktfotos bearbeiten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Template auswählen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zahlungsdienste einbinden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bewertungssystem anpassen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2.6</t>
+  </si>
+  <si>
     <t xml:space="preserve">PSP-ID</t>
   </si>
   <si>
-    <t xml:space="preserve">verantw.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teilprojekt</t>
-  </si>
-  <si>
     <t xml:space="preserve">Arbeitspaket</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Datenbank erstellen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Produkte kategorisieren</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Produkte erfassen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Produktfotos erstellen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Produktfotos bearbeiten</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Template auswählen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seitenstruktur einrichten</t>
+    <t xml:space="preserve">Korrekturen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eventuelle Korrekturen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2.8</t>
   </si>
   <si>
     <t xml:space="preserve">1.2.4</t>
   </si>
   <si>
     <t xml:space="preserve">Datenbank einbinden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zahlungsdienste einbinden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bewertungssystem anpassen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Handbücher erstellen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tests</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Korrekturen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auftraggeber-Präsentation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eventuelle Korrekturen</t>
   </si>
   <si>
     <t xml:space="preserve">1.2.9</t>
@@ -134,9 +165,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="@"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
+    <numFmt numFmtId="166" formatCode="@"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -343,7 +375,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="23">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -380,6 +412,14 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -388,7 +428,11 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -396,7 +440,11 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -404,12 +452,20 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -493,13 +549,15 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M41"/>
-  <sheetFormatPr defaultColWidth="13.07421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="13.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.77"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2"/>
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -508,7 +566,7 @@
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
       <c r="I1" s="4" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1" s="4"/>
       <c r="K1" s="3"/>
@@ -519,7 +577,7 @@
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="5" t="n">
         <v>1</v>
       </c>
       <c r="J2" s="5" t="s">
@@ -556,36 +614,36 @@
       <c r="G5" s="4"/>
       <c r="H5" s="3"/>
       <c r="I5" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J5" s="4"/>
       <c r="K5" s="3"/>
-      <c r="L5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="M5" s="4"/>
+      <c r="L5" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="M5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="0"/>
       <c r="F6" s="5" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="5" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="5" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -594,191 +652,448 @@
       <c r="J7" s="6"/>
       <c r="M7" s="6"/>
     </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="I8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="4"/>
+      <c r="L8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M8" s="4"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="L9" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="M9" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="M10" s="6"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F11" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="I11" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J11" s="4"/>
+      <c r="L11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M11" s="4"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F12" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="L12" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="M13" s="6"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F14" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="I14" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J14" s="4"/>
+      <c r="L14" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="M14" s="4"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F15" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="L15" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="M15" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G16" s="6"/>
+      <c r="J16" s="6"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F17" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="I17" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J17" s="4"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F18" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J19" s="6"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I20" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J20" s="4"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I21" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J22" s="6"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I23" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J23" s="4"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I24" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
+      <c r="A25" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="J25" s="6"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
+      <c r="A26" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="I26" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J26" s="4"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B27" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
+      <c r="A27" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="I27" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="13" t="s">
+      <c r="A28" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B28" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="J28" s="6"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="I29" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J29" s="4"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="I30" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="J30" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B28" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B29" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B30" s="14" t="s">
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="J31" s="6"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="I32" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J32" s="4"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="I33" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="B34" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B32" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="B33" s="14" t="s">
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B37" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="B34" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-    </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B35" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-    </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B36" s="14" t="s">
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B39" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-    </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B37" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-    </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B38" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-    </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B39" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="B40" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
+      <c r="A40" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="B41" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="C41" s="16"/>
-      <c r="D41" s="16"/>
+      <c r="A41" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="38">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="L5:M5"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="I23:J23"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="I26:J26"/>
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="B29:D29"/>
+    <mergeCell ref="I29:J29"/>
     <mergeCell ref="B30:D30"/>
     <mergeCell ref="B31:D31"/>
     <mergeCell ref="B32:D32"/>
+    <mergeCell ref="I32:J32"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="B35:D35"/>

--- a/Übungen/Online_Shop.xlsx
+++ b/Übungen/Online_Shop.xlsx
@@ -5,10 +5,11 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="PSP" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Netzplan" sheetId="2" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -20,125 +21,236 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="72">
+  <si>
+    <t xml:space="preserve">Beispiel: Funktionsorientierter Projektstrukturplan</t>
+  </si>
   <si>
     <t xml:space="preserve">Online-Shop</t>
   </si>
   <si>
+    <t xml:space="preserve">Fr. Claire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Produkt-Katalogisierung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entwicklung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dokumentation, Tests,
+Kundenbetreuung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hr. Karl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fr. Groß</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hr. Nguyen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Produkte kategorisieren</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Datenbank erstellen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Handbücher erstellen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Produkte erfassen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Template auswählen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Produktfotos erstellen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seitenstruktur einrichten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auftraggeber-Präsentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Produktfotos bearbeiten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Datenbank einbinden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zahlungsdienste einbinden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bewertungssystem anpassen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2.6</t>
+  </si>
+  <si>
     <t xml:space="preserve">PSP-ID</t>
   </si>
   <si>
-    <t xml:space="preserve">verantw.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teilprojekt</t>
-  </si>
-  <si>
     <t xml:space="preserve">Arbeitspaket</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Datenbank erstellen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Produkte kategorisieren</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Produkte erfassen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Produktfotos erstellen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Produktfotos bearbeiten</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Template auswählen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seitenstruktur einrichten</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Datenbank einbinden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zahlungsdienste einbinden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bewertungssystem anpassen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Handbücher erstellen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tests</t>
+    <t xml:space="preserve">Korrekturen</t>
   </si>
   <si>
     <t xml:space="preserve">1.2.7</t>
   </si>
   <si>
-    <t xml:space="preserve">Korrekturen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auftraggeber-Präsentation</t>
+    <t xml:space="preserve">eventuelle Korrekturen</t>
   </si>
   <si>
     <t xml:space="preserve">1.2.8</t>
   </si>
   <si>
-    <t xml:space="preserve">eventuelle Korrekturen</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.2.9</t>
   </si>
   <si>
     <t xml:space="preserve">Onlinestellung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vorgänger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nachfolger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dauer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1.1, 1.2.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1.2, 1.1.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2.4, 1.3.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1.2, 1.1.4, 1.2.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Onlinehilfe erstellen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3.1, 1.2.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Früheste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anfangszeit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Endzeit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gesamtpuffer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freier Puffer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Späteste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FEZ_Vorgänger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAZ + D</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="@"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
+    <numFmt numFmtId="166" formatCode="@"/>
+    <numFmt numFmtId="167" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -189,8 +301,16 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -200,7 +320,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFBF00"/>
-        <bgColor rgb="FFFF9900"/>
+        <bgColor rgb="FFFF8000"/>
       </patternFill>
     </fill>
     <fill>
@@ -212,13 +332,31 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEEEEEE"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFE8E8E8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFAADCF7"/>
         <bgColor rgb="FFCCCCFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8E8E8"/>
+        <bgColor rgb="FFEEEEEE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00A933"/>
+        <bgColor rgb="FF008000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF8000"/>
+        <bgColor rgb="FFFF6600"/>
       </patternFill>
     </fill>
   </fills>
@@ -235,35 +373,6 @@
       <right style="hair"/>
       <top style="hair"/>
       <bottom style="hair"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thick">
-        <color rgb="FF2A6099"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thick">
-        <color rgb="FF2A6099"/>
-      </left>
-      <right/>
-      <top style="thick">
-        <color rgb="FF2A6099"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right/>
-      <top style="thick">
-        <color rgb="FF2A6099"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
@@ -308,6 +417,27 @@
       <bottom style="hair"/>
       <diagonal/>
     </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="thick"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thick"/>
+      <right/>
+      <top style="thick"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thick"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="23">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -343,7 +473,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="57">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -368,15 +498,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -384,11 +510,39 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -396,19 +550,155 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -424,6 +714,17 @@
     <cellStyle name="KritischerPfad" xfId="21"/>
     <cellStyle name="Wochenende" xfId="22"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="2"/>
+        <b val="1"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -445,10 +746,10 @@
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFEEEEEE"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFE8E8E8"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF2A6099"/>
+      <rgbColor rgb="FF0066CC"/>
       <rgbColor rgb="FFCCCCFF"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
@@ -470,12 +771,12 @@
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFBF00"/>
-      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF8000"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666666"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF00A933"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
@@ -487,19 +788,949 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>907200</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>154440</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>11520</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>154440</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="0" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="5483520" y="479520"/>
+          <a:ext cx="5536080" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>906840</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>906840</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>8640</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5483160" y="488160"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>906120</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>906120</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>8640</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5482440" y="488160"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>4680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>12960</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5495040" y="1125360"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>4680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>12600</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5495040" y="1612800"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>3960</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>11880</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5495040" y="2099880"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>3600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>11880</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5495040" y="2587320"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>-360</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>7920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8251560" y="324720"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>7920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8251560" y="487440"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>4680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>12960</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8251560" y="1125360"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>4680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>12600</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8251560" y="1612800"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>3600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>11880</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8251560" y="2587320"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>3240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>11160</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8251560" y="3074400"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>2160</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>10440</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8251560" y="4048920"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>1440</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>9360</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8251560" y="5023440"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>360</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>360</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>7920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11008440" y="487440"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>360</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>4680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>360</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>12960</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11008440" y="1125360"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>360</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>4680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>360</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>12600</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11008440" y="1612800"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>360</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>3960</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>360</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>11880</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11008440" y="2099880"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>911160</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>160920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>911160</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>6480</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8244000" y="3557520"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>911160</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>161640</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>911160</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>7200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8244000" y="4533480"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>911160</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>160200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>911160</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>5760</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8244000" y="2093760"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M41"/>
-  <sheetFormatPr defaultColWidth="13.109375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="13.0390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.77"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2"/>
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -508,7 +1739,7 @@
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
       <c r="I1" s="4" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1" s="4"/>
       <c r="K1" s="3"/>
@@ -519,7 +1750,7 @@
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="5" t="n">
         <v>1</v>
       </c>
       <c r="J2" s="5" t="s">
@@ -534,20 +1765,20 @@
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
-      <c r="J3" s="6"/>
+      <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F4" s="3"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="6"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="24.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F5" s="4" t="s">
@@ -556,229 +1787,456 @@
       <c r="G5" s="4"/>
       <c r="H5" s="3"/>
       <c r="I5" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J5" s="4"/>
       <c r="K5" s="3"/>
-      <c r="L5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="M5" s="4"/>
+      <c r="L5" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="M5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="0"/>
       <c r="F6" s="5" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="5" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="5" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="0"/>
-      <c r="G7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="M7" s="6"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="I8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="4"/>
+      <c r="L8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M8" s="4"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="M9" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F11" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="I11" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J11" s="4"/>
+      <c r="L11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M11" s="4"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F12" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F14" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="I14" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="J14" s="4"/>
+      <c r="L14" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M14" s="4"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F15" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="M15" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F17" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="I17" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J17" s="4"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F18" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I20" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J20" s="4"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I21" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I23" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="J23" s="4"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I24" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
+      <c r="A25" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="12"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="I26" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J26" s="4"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B27" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
+      <c r="A27" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="I27" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="13" t="s">
+      <c r="A28" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="I29" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J29" s="4"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="I30" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="J30" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B28" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B29" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B30" s="14" t="s">
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="I32" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J32" s="4"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="I33" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C34" s="15"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C35" s="15"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B32" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="B33" s="14" t="s">
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B37" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="B34" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-    </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B35" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-    </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B36" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-    </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="13" t="s">
+      <c r="C37" s="15"/>
+      <c r="D37" s="15"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="15"/>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C38" s="15"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="15"/>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B39" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="B37" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-    </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B38" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-    </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B39" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
+      <c r="C39" s="15"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="15"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="B40" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
+      <c r="A40" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C40" s="15"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="15"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="B41" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="C41" s="16"/>
-      <c r="D41" s="16"/>
+      <c r="A41" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="19"/>
+      <c r="F41" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="38">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="L5:M5"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="I23:J23"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="I26:J26"/>
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="B29:D29"/>
+    <mergeCell ref="I29:J29"/>
     <mergeCell ref="B30:D30"/>
     <mergeCell ref="B31:D31"/>
     <mergeCell ref="B32:D32"/>
+    <mergeCell ref="I32:J32"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="B35:D35"/>
@@ -796,5 +2254,999 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:BT35"/>
+  <sheetFormatPr defaultColWidth="11.78515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="20" width="11.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="16.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="3" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="104" min="8" style="0" width="3.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1022" style="0" width="11.52"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" s="22" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="28"/>
+      <c r="K2" s="27"/>
+      <c r="N2" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="28"/>
+      <c r="P2" s="27"/>
+      <c r="S2" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" s="28"/>
+      <c r="U2" s="27"/>
+      <c r="AI2" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" s="28"/>
+      <c r="AK2" s="27"/>
+      <c r="AN2" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" s="28"/>
+      <c r="AP2" s="27"/>
+      <c r="AS2" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" s="28"/>
+      <c r="AU2" s="27"/>
+      <c r="AX2" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" s="28"/>
+      <c r="AZ2" s="27"/>
+      <c r="BC2" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD2" s="28"/>
+      <c r="BE2" s="27"/>
+      <c r="BH2" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI2" s="28"/>
+      <c r="BJ2" s="27"/>
+      <c r="BM2" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN2" s="28"/>
+      <c r="BO2" s="27"/>
+      <c r="BR2" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS2" s="28"/>
+      <c r="BT2" s="27"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="G3" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="N3" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="O3" s="32"/>
+      <c r="P3" s="32"/>
+      <c r="S3" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="T3" s="32"/>
+      <c r="U3" s="32"/>
+      <c r="AI3" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="AJ3" s="32"/>
+      <c r="AK3" s="32"/>
+      <c r="AN3" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="AO3" s="32"/>
+      <c r="AP3" s="32"/>
+      <c r="AS3" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="AT3" s="32"/>
+      <c r="AU3" s="32"/>
+      <c r="AX3" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="AY3" s="32"/>
+      <c r="AZ3" s="32"/>
+      <c r="BC3" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="BD3" s="32"/>
+      <c r="BE3" s="32"/>
+      <c r="BH3" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="BI3" s="32"/>
+      <c r="BJ3" s="32"/>
+      <c r="BM3" s="32" t="s">
+        <v>43</v>
+      </c>
+      <c r="BN3" s="32"/>
+      <c r="BO3" s="32"/>
+      <c r="BR3" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="BS3" s="32"/>
+      <c r="BT3" s="32"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" s="33" t="n">
+        <f aca="false">G2</f>
+        <v>5</v>
+      </c>
+      <c r="J4" s="34"/>
+      <c r="K4" s="33"/>
+      <c r="L4" s="35"/>
+      <c r="M4" s="36"/>
+      <c r="N4" s="33" t="n">
+        <f aca="false">G3</f>
+        <v>1</v>
+      </c>
+      <c r="O4" s="34"/>
+      <c r="P4" s="33"/>
+      <c r="Q4" s="35"/>
+      <c r="R4" s="36"/>
+      <c r="S4" s="33" t="n">
+        <f aca="false">G4</f>
+        <v>4</v>
+      </c>
+      <c r="T4" s="34"/>
+      <c r="U4" s="33"/>
+      <c r="V4" s="35"/>
+      <c r="W4" s="35"/>
+      <c r="X4" s="35"/>
+      <c r="Y4" s="35"/>
+      <c r="Z4" s="35"/>
+      <c r="AA4" s="35"/>
+      <c r="AB4" s="35"/>
+      <c r="AC4" s="35"/>
+      <c r="AD4" s="35"/>
+      <c r="AE4" s="35"/>
+      <c r="AF4" s="35"/>
+      <c r="AG4" s="35"/>
+      <c r="AH4" s="36"/>
+      <c r="AI4" s="33" t="n">
+        <f aca="false">G9</f>
+        <v>2</v>
+      </c>
+      <c r="AJ4" s="34"/>
+      <c r="AK4" s="33"/>
+      <c r="AL4" s="35"/>
+      <c r="AM4" s="35"/>
+      <c r="AN4" s="33" t="n">
+        <f aca="false">G10</f>
+        <v>2</v>
+      </c>
+      <c r="AO4" s="34"/>
+      <c r="AP4" s="33"/>
+      <c r="AQ4" s="35"/>
+      <c r="AR4" s="35"/>
+      <c r="AS4" s="33" t="n">
+        <f aca="false">G11</f>
+        <v>2</v>
+      </c>
+      <c r="AT4" s="34"/>
+      <c r="AU4" s="33"/>
+      <c r="AV4" s="35"/>
+      <c r="AW4" s="35"/>
+      <c r="AX4" s="33" t="n">
+        <f aca="false">G13</f>
+        <v>3</v>
+      </c>
+      <c r="AY4" s="34"/>
+      <c r="AZ4" s="33"/>
+      <c r="BA4" s="35"/>
+      <c r="BB4" s="35"/>
+      <c r="BC4" s="33" t="n">
+        <f aca="false">G14</f>
+        <v>3</v>
+      </c>
+      <c r="BD4" s="34"/>
+      <c r="BE4" s="33"/>
+      <c r="BF4" s="35"/>
+      <c r="BG4" s="35"/>
+      <c r="BH4" s="33" t="n">
+        <f aca="false">G15</f>
+        <v>1</v>
+      </c>
+      <c r="BI4" s="34"/>
+      <c r="BJ4" s="33"/>
+      <c r="BK4" s="35"/>
+      <c r="BL4" s="35"/>
+      <c r="BM4" s="33" t="n">
+        <f aca="false">G16</f>
+        <v>5</v>
+      </c>
+      <c r="BN4" s="34"/>
+      <c r="BO4" s="33"/>
+      <c r="BP4" s="35"/>
+      <c r="BQ4" s="36"/>
+      <c r="BR4" s="33" t="n">
+        <f aca="false">G17</f>
+        <v>1</v>
+      </c>
+      <c r="BS4" s="34"/>
+      <c r="BT4" s="33"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="28"/>
+      <c r="K5" s="27"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="28"/>
+      <c r="P5" s="27"/>
+      <c r="R5" s="37"/>
+      <c r="S5" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="28"/>
+      <c r="U5" s="27"/>
+      <c r="AH5" s="37"/>
+      <c r="AI5" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="28"/>
+      <c r="AK5" s="27"/>
+      <c r="AN5" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" s="28"/>
+      <c r="AP5" s="27"/>
+      <c r="AS5" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" s="28"/>
+      <c r="AU5" s="27"/>
+      <c r="AX5" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" s="28"/>
+      <c r="AZ5" s="27"/>
+      <c r="BC5" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" s="28"/>
+      <c r="BE5" s="27"/>
+      <c r="BH5" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI5" s="28"/>
+      <c r="BJ5" s="27"/>
+      <c r="BM5" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN5" s="28"/>
+      <c r="BO5" s="27"/>
+      <c r="BQ5" s="37"/>
+      <c r="BR5" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS5" s="28"/>
+      <c r="BT5" s="27"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="39" t="n">
+        <v>7</v>
+      </c>
+      <c r="M6" s="37"/>
+      <c r="R6" s="37"/>
+      <c r="AH6" s="37"/>
+      <c r="BQ6" s="37"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="29"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="37"/>
+      <c r="R7" s="37"/>
+      <c r="AH7" s="37"/>
+      <c r="BQ7" s="37"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" s="37"/>
+      <c r="R8" s="37"/>
+      <c r="S8" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="28"/>
+      <c r="U8" s="27"/>
+      <c r="X8" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="28"/>
+      <c r="Z8" s="27"/>
+      <c r="AH8" s="37"/>
+      <c r="BQ8" s="37"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" s="37"/>
+      <c r="R9" s="37"/>
+      <c r="S9" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="T9" s="32"/>
+      <c r="U9" s="32"/>
+      <c r="X9" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y9" s="32"/>
+      <c r="Z9" s="32"/>
+      <c r="AH9" s="37"/>
+      <c r="BQ9" s="37"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" s="37"/>
+      <c r="R10" s="35"/>
+      <c r="S10" s="33" t="n">
+        <f aca="false">G5</f>
+        <v>3</v>
+      </c>
+      <c r="T10" s="34"/>
+      <c r="U10" s="33"/>
+      <c r="V10" s="35"/>
+      <c r="W10" s="35"/>
+      <c r="X10" s="33" t="n">
+        <f aca="false">G6</f>
+        <v>7</v>
+      </c>
+      <c r="Y10" s="34"/>
+      <c r="Z10" s="40"/>
+      <c r="AA10" s="35"/>
+      <c r="AB10" s="35"/>
+      <c r="AC10" s="35"/>
+      <c r="AD10" s="35"/>
+      <c r="AE10" s="35"/>
+      <c r="AF10" s="35"/>
+      <c r="AG10" s="35"/>
+      <c r="AH10" s="37"/>
+      <c r="BQ10" s="37"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" s="37"/>
+      <c r="S11" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="28"/>
+      <c r="U11" s="27"/>
+      <c r="X11" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="28"/>
+      <c r="Z11" s="27"/>
+      <c r="AH11" s="37"/>
+      <c r="BQ11" s="37"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="39" t="n">
+        <v>10</v>
+      </c>
+      <c r="M12" s="37"/>
+      <c r="X12" s="41"/>
+      <c r="AH12" s="37"/>
+      <c r="BQ12" s="37"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" s="37"/>
+      <c r="X13" s="41"/>
+      <c r="AH13" s="37"/>
+      <c r="BQ13" s="37"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="G14" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="M14" s="37"/>
+      <c r="N14" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="28"/>
+      <c r="P14" s="27"/>
+      <c r="S14" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="28"/>
+      <c r="U14" s="27"/>
+      <c r="X14" s="41"/>
+      <c r="AH14" s="37"/>
+      <c r="AI14" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="28"/>
+      <c r="AK14" s="27"/>
+      <c r="BQ14" s="37"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G15" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="37"/>
+      <c r="N15" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="S15" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="T15" s="32"/>
+      <c r="U15" s="32"/>
+      <c r="X15" s="41"/>
+      <c r="AH15" s="37"/>
+      <c r="AI15" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ15" s="32"/>
+      <c r="AK15" s="32"/>
+      <c r="BQ15" s="37"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="G16" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="M16" s="35"/>
+      <c r="N16" s="33" t="n">
+        <f aca="false">G7</f>
+        <v>1</v>
+      </c>
+      <c r="O16" s="34"/>
+      <c r="P16" s="33"/>
+      <c r="Q16" s="35"/>
+      <c r="R16" s="35"/>
+      <c r="S16" s="33" t="n">
+        <f aca="false">G8</f>
+        <v>3</v>
+      </c>
+      <c r="T16" s="34"/>
+      <c r="U16" s="33"/>
+      <c r="V16" s="35"/>
+      <c r="W16" s="35"/>
+      <c r="X16" s="35"/>
+      <c r="Y16" s="35"/>
+      <c r="Z16" s="35"/>
+      <c r="AA16" s="35"/>
+      <c r="AB16" s="35"/>
+      <c r="AC16" s="35"/>
+      <c r="AD16" s="35"/>
+      <c r="AE16" s="35"/>
+      <c r="AF16" s="35"/>
+      <c r="AG16" s="35"/>
+      <c r="AH16" s="35"/>
+      <c r="AI16" s="33" t="n">
+        <f aca="false">G12</f>
+        <v>10</v>
+      </c>
+      <c r="AJ16" s="34"/>
+      <c r="AK16" s="40"/>
+      <c r="AL16" s="35"/>
+      <c r="AM16" s="35"/>
+      <c r="AN16" s="35"/>
+      <c r="AO16" s="35"/>
+      <c r="AP16" s="35"/>
+      <c r="AQ16" s="35"/>
+      <c r="AR16" s="35"/>
+      <c r="AS16" s="35"/>
+      <c r="AT16" s="35"/>
+      <c r="AU16" s="35"/>
+      <c r="AV16" s="35"/>
+      <c r="AW16" s="35"/>
+      <c r="AX16" s="35"/>
+      <c r="AY16" s="35"/>
+      <c r="AZ16" s="35"/>
+      <c r="BA16" s="35"/>
+      <c r="BB16" s="35"/>
+      <c r="BC16" s="35"/>
+      <c r="BD16" s="35"/>
+      <c r="BE16" s="35"/>
+      <c r="BF16" s="35"/>
+      <c r="BG16" s="35"/>
+      <c r="BH16" s="35"/>
+      <c r="BI16" s="35"/>
+      <c r="BJ16" s="35"/>
+      <c r="BK16" s="35"/>
+      <c r="BL16" s="35"/>
+      <c r="BM16" s="35"/>
+      <c r="BN16" s="35"/>
+      <c r="BO16" s="35"/>
+      <c r="BP16" s="35"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17" s="44"/>
+      <c r="G17" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="28"/>
+      <c r="P17" s="27"/>
+      <c r="S17" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="28"/>
+      <c r="U17" s="27"/>
+      <c r="AI17" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="28"/>
+      <c r="AK17" s="27"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="B19" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" s="48"/>
+      <c r="D19" s="49" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="33" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="B22" s="51" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="52"/>
+      <c r="D22" s="53" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="28"/>
+      <c r="D24" s="27" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" s="32"/>
+      <c r="D25" s="32"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="C26" s="34" t="s">
+        <v>65</v>
+      </c>
+      <c r="D26" s="33" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="54" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" s="28"/>
+      <c r="D27" s="27" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="B29" s="55" t="s">
+        <v>69</v>
+      </c>
+      <c r="C29" s="56" t="s">
+        <v>70</v>
+      </c>
+      <c r="D29" s="56"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="B30" s="55" t="s">
+        <v>69</v>
+      </c>
+      <c r="C30" s="56" t="s">
+        <v>71</v>
+      </c>
+      <c r="D30" s="56"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="55"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" s="55" t="s">
+        <v>69</v>
+      </c>
+      <c r="C32" s="56" t="s">
+        <v>71</v>
+      </c>
+      <c r="D32" s="56"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="B33" s="55" t="s">
+        <v>69</v>
+      </c>
+      <c r="C33" s="56" t="s">
+        <v>70</v>
+      </c>
+      <c r="D33" s="56"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="55"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="55"/>
+    </row>
+  </sheetData>
+  <mergeCells count="39">
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="S3:U3"/>
+    <mergeCell ref="AI3:AK3"/>
+    <mergeCell ref="AN3:AP3"/>
+    <mergeCell ref="AS3:AU3"/>
+    <mergeCell ref="AX3:AZ3"/>
+    <mergeCell ref="BC3:BE3"/>
+    <mergeCell ref="BH3:BJ3"/>
+    <mergeCell ref="BM3:BO3"/>
+    <mergeCell ref="BR3:BT3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="S9:U9"/>
+    <mergeCell ref="X9:Z9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="S15:U15"/>
+    <mergeCell ref="AI15:AK15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+  </mergeCells>
+  <conditionalFormatting sqref="J4 C21 C26 O4 T4 O16 U16 AJ4 AO4 AT4 AY4 S10:T10 AK16 BD4 BI4 BN4 BS4">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
--- a/Übungen/Online_Shop.xlsx
+++ b/Übungen/Online_Shop.xlsx
@@ -5,10 +5,11 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="PSP" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Netzplan" sheetId="2" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="72">
   <si>
     <t xml:space="preserve">Beispiel: Funktionsorientierter Projektstrukturplan</t>
   </si>
@@ -80,43 +81,49 @@
     <t xml:space="preserve">Produkte erfassen</t>
   </si>
   <si>
+    <t xml:space="preserve">Template auswählen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Produktfotos erstellen</t>
+  </si>
+  <si>
     <t xml:space="preserve">Seitenstruktur einrichten</t>
   </si>
   <si>
-    <t xml:space="preserve">Tests</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1.2</t>
+    <t xml:space="preserve">Auftraggeber-Präsentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1.3</t>
   </si>
   <si>
     <t xml:space="preserve">1.2.3</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Produktfotos erstellen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auftraggeber-Präsentation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1.3</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.3.3</t>
   </si>
   <si>
     <t xml:space="preserve">Produktfotos bearbeiten</t>
   </si>
   <si>
-    <t xml:space="preserve">Template auswählen</t>
+    <t xml:space="preserve">Datenbank einbinden</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.4</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2.2</t>
+    <t xml:space="preserve">1.2.4</t>
   </si>
   <si>
     <t xml:space="preserve">Zahlungsdienste einbinden</t>
@@ -149,28 +156,101 @@
     <t xml:space="preserve">1.2.8</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Datenbank einbinden</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.2.9</t>
   </si>
   <si>
     <t xml:space="preserve">Onlinestellung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vorgänger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nachfolger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dauer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1.1, 1.2.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1.2, 1.1.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2.4, 1.3.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1.2, 1.1.4, 1.2.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Onlinehilfe erstellen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3.1, 1.2.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Früheste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anfangszeit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Endzeit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gesamtpuffer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freier Puffer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Späteste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FEZ_Vorgänger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAZ + D</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
     <numFmt numFmtId="166" formatCode="@"/>
+    <numFmt numFmtId="167" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -221,8 +301,16 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -232,7 +320,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFBF00"/>
-        <bgColor rgb="FFFF9900"/>
+        <bgColor rgb="FFFF8000"/>
       </patternFill>
     </fill>
     <fill>
@@ -244,13 +332,31 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEEEEEE"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFE8E8E8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFAADCF7"/>
         <bgColor rgb="FFCCCCFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8E8E8"/>
+        <bgColor rgb="FFEEEEEE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00A933"/>
+        <bgColor rgb="FF008000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF8000"/>
+        <bgColor rgb="FFFF6600"/>
       </patternFill>
     </fill>
   </fills>
@@ -267,35 +373,6 @@
       <right style="hair"/>
       <top style="hair"/>
       <bottom style="hair"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thick">
-        <color rgb="FF2A6099"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thick">
-        <color rgb="FF2A6099"/>
-      </left>
-      <right/>
-      <top style="thick">
-        <color rgb="FF2A6099"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right/>
-      <top style="thick">
-        <color rgb="FF2A6099"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
@@ -340,6 +417,27 @@
       <bottom style="hair"/>
       <diagonal/>
     </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="thick"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thick"/>
+      <right/>
+      <top style="thick"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thick"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="23">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -375,7 +473,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="57">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -400,18 +498,6 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -424,11 +510,35 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -444,28 +554,152 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -480,6 +714,17 @@
     <cellStyle name="KritischerPfad" xfId="21"/>
     <cellStyle name="Wochenende" xfId="22"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="2"/>
+        <b val="1"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -501,10 +746,10 @@
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFEEEEEE"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFE8E8E8"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF2A6099"/>
+      <rgbColor rgb="FF0066CC"/>
       <rgbColor rgb="FFCCCCFF"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
@@ -526,12 +771,12 @@
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFBF00"/>
-      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF8000"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666666"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF00A933"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
@@ -543,13 +788,941 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>907560</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>154440</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>11880</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>154440</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="0" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="5488560" y="479520"/>
+          <a:ext cx="5545080" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>906840</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>906840</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>8640</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5488200" y="488160"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>906120</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>906120</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>8640</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5487480" y="488160"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>4680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>12960</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5501520" y="1125360"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>4680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>12600</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5501520" y="1612800"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>3960</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>11880</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5501520" y="2099880"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>3600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>11880</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5501520" y="2587320"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>-360</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>7920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8261640" y="324720"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>7920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8261640" y="487440"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>4680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>12960</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8261640" y="1125360"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>4680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>12600</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8261640" y="1612800"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>3600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>11880</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8261640" y="2587320"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>3240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>11160</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8261640" y="3074400"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>2160</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>10440</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8261640" y="4048920"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>1440</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>9360</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8261640" y="5023440"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>360</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>360</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>7920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11022480" y="487440"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>360</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>4680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>360</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>12960</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11022480" y="1125360"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>360</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>4680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>360</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>12600</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11022480" y="1612800"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>360</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>3960</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>360</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>11880</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11022480" y="2099880"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>911160</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>160920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>911160</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>6480</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8253000" y="3557520"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>911160</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>161640</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>911160</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>7200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8253000" y="4533480"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>911160</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>160200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>911160</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>5760</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8253000" y="2093760"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M41"/>
-  <sheetFormatPr defaultColWidth="13.0390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="13.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.77"/>
   </cols>
@@ -592,20 +1765,20 @@
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
-      <c r="J3" s="6"/>
+      <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F4" s="3"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="6"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="24.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F5" s="4" t="s">
@@ -618,13 +1791,12 @@
       </c>
       <c r="J5" s="4"/>
       <c r="K5" s="3"/>
-      <c r="L5" s="9" t="s">
+      <c r="L5" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="M5" s="9"/>
+      <c r="M5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="0"/>
       <c r="F6" s="5" t="s">
         <v>6</v>
       </c>
@@ -646,12 +1818,6 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="0"/>
-      <c r="G7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="M7" s="6"/>
-    </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F8" s="4" t="s">
         <v>12</v>
@@ -679,17 +1845,12 @@
       <c r="J9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="L9" s="10" t="s">
+      <c r="L9" s="7" t="s">
         <v>17</v>
       </c>
       <c r="M9" s="5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="M10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F11" s="4" t="s">
@@ -718,17 +1879,12 @@
       <c r="J12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="L12" s="10" t="s">
+      <c r="L12" s="7" t="s">
         <v>23</v>
       </c>
       <c r="M12" s="5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="M13" s="6"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F14" s="4" t="s">
@@ -736,230 +1892,217 @@
       </c>
       <c r="G14" s="4"/>
       <c r="I14" s="4" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J14" s="4"/>
       <c r="L14" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F15" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>7</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="L15" s="10" t="s">
-        <v>27</v>
+      <c r="L15" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G16" s="6"/>
-      <c r="J16" s="6"/>
-    </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F17" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G17" s="4"/>
       <c r="I17" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F18" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>7</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J19" s="6"/>
-    </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I20" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J20" s="4"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I21" s="5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J22" s="6"/>
-    </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I23" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J23" s="4"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I24" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J24" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="J25" s="6"/>
+      <c r="A25" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="14" t="s">
+      <c r="A26" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
       <c r="I26" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J26" s="4"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
       <c r="I27" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J27" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="17" t="s">
+      <c r="A28" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B28" s="18" t="s">
+      <c r="B28" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="J28" s="6"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="B29" s="18" t="s">
+      <c r="A29" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
       <c r="I29" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J29" s="4"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="17" t="s">
+      <c r="A30" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="B30" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
       <c r="I30" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J30" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="17" t="s">
+      <c r="A31" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B31" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="J31" s="6"/>
+      <c r="B31" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="17" t="s">
+      <c r="A32" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="I32" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J32" s="4"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="I32" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J32" s="4"/>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="B33" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
       <c r="I33" s="5" t="s">
         <v>44</v>
       </c>
@@ -968,100 +2111,100 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="17" t="s">
+      <c r="A34" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C34" s="15"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C35" s="15"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="15"/>
+      <c r="D37" s="15"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="15"/>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C38" s="15"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="15"/>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C39" s="15"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="15"/>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
-    </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="B35" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="C35" s="18"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="18"/>
-    </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B36" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
-    </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B37" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="C37" s="18"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="18"/>
-      <c r="F37" s="18"/>
-    </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="18"/>
-    </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="B39" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="C39" s="18"/>
-      <c r="D39" s="18"/>
-      <c r="E39" s="18"/>
-      <c r="F39" s="18"/>
-    </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="B40" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="C40" s="18"/>
-      <c r="D40" s="18"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="18"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="15"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="20" t="s">
+      <c r="A41" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B41" s="21" t="s">
+      <c r="B41" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="C41" s="21"/>
-      <c r="D41" s="21"/>
-      <c r="E41" s="22"/>
-      <c r="F41" s="22"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="19"/>
+      <c r="F41" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="38">
@@ -1111,5 +2254,999 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:BT35"/>
+  <sheetFormatPr defaultColWidth="11.8046875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="20" width="11.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="16.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="3" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="104" min="8" style="0" width="3.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1022" style="0" width="11.52"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" s="22" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="28"/>
+      <c r="K2" s="27"/>
+      <c r="N2" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="28"/>
+      <c r="P2" s="27"/>
+      <c r="S2" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" s="28"/>
+      <c r="U2" s="27"/>
+      <c r="AI2" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" s="28"/>
+      <c r="AK2" s="27"/>
+      <c r="AN2" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" s="28"/>
+      <c r="AP2" s="27"/>
+      <c r="AS2" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" s="28"/>
+      <c r="AU2" s="27"/>
+      <c r="AX2" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" s="28"/>
+      <c r="AZ2" s="27"/>
+      <c r="BC2" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD2" s="28"/>
+      <c r="BE2" s="27"/>
+      <c r="BH2" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI2" s="28"/>
+      <c r="BJ2" s="27"/>
+      <c r="BM2" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN2" s="28"/>
+      <c r="BO2" s="27"/>
+      <c r="BR2" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS2" s="28"/>
+      <c r="BT2" s="27"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="G3" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="N3" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="O3" s="32"/>
+      <c r="P3" s="32"/>
+      <c r="S3" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="T3" s="32"/>
+      <c r="U3" s="32"/>
+      <c r="AI3" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="AJ3" s="32"/>
+      <c r="AK3" s="32"/>
+      <c r="AN3" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="AO3" s="32"/>
+      <c r="AP3" s="32"/>
+      <c r="AS3" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="AT3" s="32"/>
+      <c r="AU3" s="32"/>
+      <c r="AX3" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="AY3" s="32"/>
+      <c r="AZ3" s="32"/>
+      <c r="BC3" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="BD3" s="32"/>
+      <c r="BE3" s="32"/>
+      <c r="BH3" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="BI3" s="32"/>
+      <c r="BJ3" s="32"/>
+      <c r="BM3" s="32" t="s">
+        <v>43</v>
+      </c>
+      <c r="BN3" s="32"/>
+      <c r="BO3" s="32"/>
+      <c r="BR3" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="BS3" s="32"/>
+      <c r="BT3" s="32"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" s="33" t="n">
+        <f aca="false">G2</f>
+        <v>5</v>
+      </c>
+      <c r="J4" s="34"/>
+      <c r="K4" s="33"/>
+      <c r="L4" s="35"/>
+      <c r="M4" s="36"/>
+      <c r="N4" s="33" t="n">
+        <f aca="false">G3</f>
+        <v>1</v>
+      </c>
+      <c r="O4" s="34"/>
+      <c r="P4" s="33"/>
+      <c r="Q4" s="35"/>
+      <c r="R4" s="36"/>
+      <c r="S4" s="33" t="n">
+        <f aca="false">G4</f>
+        <v>4</v>
+      </c>
+      <c r="T4" s="34"/>
+      <c r="U4" s="33"/>
+      <c r="V4" s="35"/>
+      <c r="W4" s="35"/>
+      <c r="X4" s="35"/>
+      <c r="Y4" s="35"/>
+      <c r="Z4" s="35"/>
+      <c r="AA4" s="35"/>
+      <c r="AB4" s="35"/>
+      <c r="AC4" s="35"/>
+      <c r="AD4" s="35"/>
+      <c r="AE4" s="35"/>
+      <c r="AF4" s="35"/>
+      <c r="AG4" s="35"/>
+      <c r="AH4" s="36"/>
+      <c r="AI4" s="33" t="n">
+        <f aca="false">G9</f>
+        <v>2</v>
+      </c>
+      <c r="AJ4" s="34"/>
+      <c r="AK4" s="33"/>
+      <c r="AL4" s="35"/>
+      <c r="AM4" s="35"/>
+      <c r="AN4" s="33" t="n">
+        <f aca="false">G10</f>
+        <v>2</v>
+      </c>
+      <c r="AO4" s="34"/>
+      <c r="AP4" s="33"/>
+      <c r="AQ4" s="35"/>
+      <c r="AR4" s="35"/>
+      <c r="AS4" s="33" t="n">
+        <f aca="false">G11</f>
+        <v>2</v>
+      </c>
+      <c r="AT4" s="34"/>
+      <c r="AU4" s="33"/>
+      <c r="AV4" s="35"/>
+      <c r="AW4" s="35"/>
+      <c r="AX4" s="33" t="n">
+        <f aca="false">G13</f>
+        <v>3</v>
+      </c>
+      <c r="AY4" s="34"/>
+      <c r="AZ4" s="33"/>
+      <c r="BA4" s="35"/>
+      <c r="BB4" s="35"/>
+      <c r="BC4" s="33" t="n">
+        <f aca="false">G14</f>
+        <v>3</v>
+      </c>
+      <c r="BD4" s="34"/>
+      <c r="BE4" s="33"/>
+      <c r="BF4" s="35"/>
+      <c r="BG4" s="35"/>
+      <c r="BH4" s="33" t="n">
+        <f aca="false">G15</f>
+        <v>1</v>
+      </c>
+      <c r="BI4" s="34"/>
+      <c r="BJ4" s="33"/>
+      <c r="BK4" s="35"/>
+      <c r="BL4" s="35"/>
+      <c r="BM4" s="33" t="n">
+        <f aca="false">G16</f>
+        <v>5</v>
+      </c>
+      <c r="BN4" s="34"/>
+      <c r="BO4" s="33"/>
+      <c r="BP4" s="35"/>
+      <c r="BQ4" s="36"/>
+      <c r="BR4" s="33" t="n">
+        <f aca="false">G17</f>
+        <v>1</v>
+      </c>
+      <c r="BS4" s="34"/>
+      <c r="BT4" s="33"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="28"/>
+      <c r="K5" s="27"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="28"/>
+      <c r="P5" s="27"/>
+      <c r="R5" s="37"/>
+      <c r="S5" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="28"/>
+      <c r="U5" s="27"/>
+      <c r="AH5" s="37"/>
+      <c r="AI5" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="28"/>
+      <c r="AK5" s="27"/>
+      <c r="AN5" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" s="28"/>
+      <c r="AP5" s="27"/>
+      <c r="AS5" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" s="28"/>
+      <c r="AU5" s="27"/>
+      <c r="AX5" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" s="28"/>
+      <c r="AZ5" s="27"/>
+      <c r="BC5" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" s="28"/>
+      <c r="BE5" s="27"/>
+      <c r="BH5" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI5" s="28"/>
+      <c r="BJ5" s="27"/>
+      <c r="BM5" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN5" s="28"/>
+      <c r="BO5" s="27"/>
+      <c r="BQ5" s="37"/>
+      <c r="BR5" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS5" s="28"/>
+      <c r="BT5" s="27"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="39" t="n">
+        <v>7</v>
+      </c>
+      <c r="M6" s="37"/>
+      <c r="R6" s="37"/>
+      <c r="AH6" s="37"/>
+      <c r="BQ6" s="37"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="29"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="37"/>
+      <c r="R7" s="37"/>
+      <c r="AH7" s="37"/>
+      <c r="BQ7" s="37"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" s="37"/>
+      <c r="R8" s="37"/>
+      <c r="S8" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="28"/>
+      <c r="U8" s="27"/>
+      <c r="X8" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="28"/>
+      <c r="Z8" s="27"/>
+      <c r="AH8" s="37"/>
+      <c r="BQ8" s="37"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" s="37"/>
+      <c r="R9" s="37"/>
+      <c r="S9" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="T9" s="32"/>
+      <c r="U9" s="32"/>
+      <c r="X9" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y9" s="32"/>
+      <c r="Z9" s="32"/>
+      <c r="AH9" s="37"/>
+      <c r="BQ9" s="37"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" s="37"/>
+      <c r="R10" s="35"/>
+      <c r="S10" s="33" t="n">
+        <f aca="false">G5</f>
+        <v>3</v>
+      </c>
+      <c r="T10" s="34"/>
+      <c r="U10" s="33"/>
+      <c r="V10" s="35"/>
+      <c r="W10" s="35"/>
+      <c r="X10" s="33" t="n">
+        <f aca="false">G6</f>
+        <v>7</v>
+      </c>
+      <c r="Y10" s="34"/>
+      <c r="Z10" s="40"/>
+      <c r="AA10" s="35"/>
+      <c r="AB10" s="35"/>
+      <c r="AC10" s="35"/>
+      <c r="AD10" s="35"/>
+      <c r="AE10" s="35"/>
+      <c r="AF10" s="35"/>
+      <c r="AG10" s="35"/>
+      <c r="AH10" s="37"/>
+      <c r="BQ10" s="37"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" s="37"/>
+      <c r="S11" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="28"/>
+      <c r="U11" s="27"/>
+      <c r="X11" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="28"/>
+      <c r="Z11" s="27"/>
+      <c r="AH11" s="37"/>
+      <c r="BQ11" s="37"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="39" t="n">
+        <v>10</v>
+      </c>
+      <c r="M12" s="37"/>
+      <c r="X12" s="41"/>
+      <c r="AH12" s="37"/>
+      <c r="BQ12" s="37"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" s="37"/>
+      <c r="X13" s="41"/>
+      <c r="AH13" s="37"/>
+      <c r="BQ13" s="37"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="G14" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="M14" s="37"/>
+      <c r="N14" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="28"/>
+      <c r="P14" s="27"/>
+      <c r="S14" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="28"/>
+      <c r="U14" s="27"/>
+      <c r="X14" s="41"/>
+      <c r="AH14" s="37"/>
+      <c r="AI14" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="28"/>
+      <c r="AK14" s="27"/>
+      <c r="BQ14" s="37"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G15" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="37"/>
+      <c r="N15" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="S15" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="T15" s="32"/>
+      <c r="U15" s="32"/>
+      <c r="X15" s="41"/>
+      <c r="AH15" s="37"/>
+      <c r="AI15" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ15" s="32"/>
+      <c r="AK15" s="32"/>
+      <c r="BQ15" s="37"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="G16" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="M16" s="35"/>
+      <c r="N16" s="33" t="n">
+        <f aca="false">G7</f>
+        <v>1</v>
+      </c>
+      <c r="O16" s="34"/>
+      <c r="P16" s="33"/>
+      <c r="Q16" s="35"/>
+      <c r="R16" s="35"/>
+      <c r="S16" s="33" t="n">
+        <f aca="false">G8</f>
+        <v>3</v>
+      </c>
+      <c r="T16" s="34"/>
+      <c r="U16" s="33"/>
+      <c r="V16" s="35"/>
+      <c r="W16" s="35"/>
+      <c r="X16" s="35"/>
+      <c r="Y16" s="35"/>
+      <c r="Z16" s="35"/>
+      <c r="AA16" s="35"/>
+      <c r="AB16" s="35"/>
+      <c r="AC16" s="35"/>
+      <c r="AD16" s="35"/>
+      <c r="AE16" s="35"/>
+      <c r="AF16" s="35"/>
+      <c r="AG16" s="35"/>
+      <c r="AH16" s="35"/>
+      <c r="AI16" s="33" t="n">
+        <f aca="false">G12</f>
+        <v>10</v>
+      </c>
+      <c r="AJ16" s="34"/>
+      <c r="AK16" s="40"/>
+      <c r="AL16" s="35"/>
+      <c r="AM16" s="35"/>
+      <c r="AN16" s="35"/>
+      <c r="AO16" s="35"/>
+      <c r="AP16" s="35"/>
+      <c r="AQ16" s="35"/>
+      <c r="AR16" s="35"/>
+      <c r="AS16" s="35"/>
+      <c r="AT16" s="35"/>
+      <c r="AU16" s="35"/>
+      <c r="AV16" s="35"/>
+      <c r="AW16" s="35"/>
+      <c r="AX16" s="35"/>
+      <c r="AY16" s="35"/>
+      <c r="AZ16" s="35"/>
+      <c r="BA16" s="35"/>
+      <c r="BB16" s="35"/>
+      <c r="BC16" s="35"/>
+      <c r="BD16" s="35"/>
+      <c r="BE16" s="35"/>
+      <c r="BF16" s="35"/>
+      <c r="BG16" s="35"/>
+      <c r="BH16" s="35"/>
+      <c r="BI16" s="35"/>
+      <c r="BJ16" s="35"/>
+      <c r="BK16" s="35"/>
+      <c r="BL16" s="35"/>
+      <c r="BM16" s="35"/>
+      <c r="BN16" s="35"/>
+      <c r="BO16" s="35"/>
+      <c r="BP16" s="35"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17" s="44"/>
+      <c r="G17" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="28"/>
+      <c r="P17" s="27"/>
+      <c r="S17" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="28"/>
+      <c r="U17" s="27"/>
+      <c r="AI17" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="28"/>
+      <c r="AK17" s="27"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="B19" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" s="48"/>
+      <c r="D19" s="49" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="33" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="B22" s="51" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="52"/>
+      <c r="D22" s="53" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="28"/>
+      <c r="D24" s="27" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" s="32"/>
+      <c r="D25" s="32"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="C26" s="34" t="s">
+        <v>65</v>
+      </c>
+      <c r="D26" s="33" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="54" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" s="28"/>
+      <c r="D27" s="27" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="B29" s="55" t="s">
+        <v>69</v>
+      </c>
+      <c r="C29" s="56" t="s">
+        <v>70</v>
+      </c>
+      <c r="D29" s="56"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="B30" s="55" t="s">
+        <v>69</v>
+      </c>
+      <c r="C30" s="56" t="s">
+        <v>71</v>
+      </c>
+      <c r="D30" s="56"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="55"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" s="55" t="s">
+        <v>69</v>
+      </c>
+      <c r="C32" s="56" t="s">
+        <v>71</v>
+      </c>
+      <c r="D32" s="56"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="B33" s="55" t="s">
+        <v>69</v>
+      </c>
+      <c r="C33" s="56" t="s">
+        <v>70</v>
+      </c>
+      <c r="D33" s="56"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="55"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="55"/>
+    </row>
+  </sheetData>
+  <mergeCells count="39">
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="S3:U3"/>
+    <mergeCell ref="AI3:AK3"/>
+    <mergeCell ref="AN3:AP3"/>
+    <mergeCell ref="AS3:AU3"/>
+    <mergeCell ref="AX3:AZ3"/>
+    <mergeCell ref="BC3:BE3"/>
+    <mergeCell ref="BH3:BJ3"/>
+    <mergeCell ref="BM3:BO3"/>
+    <mergeCell ref="BR3:BT3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="S9:U9"/>
+    <mergeCell ref="X9:Z9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="S15:U15"/>
+    <mergeCell ref="AI15:AK15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+  </mergeCells>
+  <conditionalFormatting sqref="J4 C21 C26 O4 T4 O16 U16 AJ4 AO4 AT4 AY4 S10:T10 AK16 BD4 BI4 BN4 BS4">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
--- a/Übungen/Online_Shop.xlsx
+++ b/Übungen/Online_Shop.xlsx
@@ -610,7 +610,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -634,7 +634,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2313,57 +2313,100 @@
         <v>0</v>
       </c>
       <c r="J2" s="28"/>
-      <c r="K2" s="27"/>
+      <c r="K2" s="27" t="n">
+        <f aca="false">I2+I4</f>
+        <v>5</v>
+      </c>
       <c r="N2" s="27" t="n">
-        <v>0</v>
+        <f aca="false">K2</f>
+        <v>5</v>
       </c>
       <c r="O2" s="28"/>
-      <c r="P2" s="27"/>
+      <c r="P2" s="27" t="n">
+        <f aca="false">N2+N4</f>
+        <v>6</v>
+      </c>
       <c r="S2" s="27" t="n">
-        <v>0</v>
+        <f aca="false">P2</f>
+        <v>6</v>
       </c>
       <c r="T2" s="28"/>
-      <c r="U2" s="27"/>
+      <c r="U2" s="27" t="n">
+        <f aca="false">S2+S4</f>
+        <v>10</v>
+      </c>
       <c r="AI2" s="27" t="n">
-        <v>0</v>
+        <f aca="false">MAX(U2,Z8,U14)</f>
+        <v>16</v>
       </c>
       <c r="AJ2" s="28"/>
-      <c r="AK2" s="27"/>
+      <c r="AK2" s="27" t="n">
+        <f aca="false">AI2+AI4</f>
+        <v>18</v>
+      </c>
       <c r="AN2" s="27" t="n">
-        <v>0</v>
+        <f aca="false">AK2</f>
+        <v>18</v>
       </c>
       <c r="AO2" s="28"/>
-      <c r="AP2" s="27"/>
+      <c r="AP2" s="27" t="n">
+        <f aca="false">AN2+AN4</f>
+        <v>20</v>
+      </c>
       <c r="AS2" s="27" t="n">
-        <v>0</v>
+        <f aca="false">AP2</f>
+        <v>20</v>
       </c>
       <c r="AT2" s="28"/>
-      <c r="AU2" s="27"/>
+      <c r="AU2" s="27" t="n">
+        <f aca="false">AS2+AS4</f>
+        <v>22</v>
+      </c>
       <c r="AX2" s="27" t="n">
-        <v>0</v>
+        <f aca="false">AU2</f>
+        <v>22</v>
       </c>
       <c r="AY2" s="28"/>
-      <c r="AZ2" s="27"/>
+      <c r="AZ2" s="27" t="n">
+        <f aca="false">AX2+AX4</f>
+        <v>25</v>
+      </c>
       <c r="BC2" s="27" t="n">
-        <v>0</v>
+        <f aca="false">AZ2</f>
+        <v>25</v>
       </c>
       <c r="BD2" s="28"/>
-      <c r="BE2" s="27"/>
+      <c r="BE2" s="27" t="n">
+        <f aca="false">BC2+BC4</f>
+        <v>28</v>
+      </c>
       <c r="BH2" s="27" t="n">
-        <v>0</v>
+        <f aca="false">BE2</f>
+        <v>28</v>
       </c>
       <c r="BI2" s="28"/>
-      <c r="BJ2" s="27"/>
+      <c r="BJ2" s="27" t="n">
+        <f aca="false">BH2+BH4</f>
+        <v>29</v>
+      </c>
       <c r="BM2" s="27" t="n">
-        <v>0</v>
+        <f aca="false">BJ2</f>
+        <v>29</v>
       </c>
       <c r="BN2" s="28"/>
-      <c r="BO2" s="27"/>
+      <c r="BO2" s="27" t="n">
+        <f aca="false">BM2+BM4</f>
+        <v>34</v>
+      </c>
       <c r="BR2" s="27" t="n">
-        <v>0</v>
+        <f aca="false">MAX(BO2,AK14)</f>
+        <v>34</v>
       </c>
       <c r="BS2" s="28"/>
-      <c r="BT2" s="27"/>
+      <c r="BT2" s="27" t="n">
+        <f aca="false">BR2+BR4</f>
+        <v>35</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
@@ -2461,24 +2504,42 @@
         <f aca="false">G2</f>
         <v>5</v>
       </c>
-      <c r="J4" s="34"/>
-      <c r="K4" s="33"/>
+      <c r="J4" s="34" t="n">
+        <f aca="false">K5-K2</f>
+        <v>0</v>
+      </c>
+      <c r="K4" s="33" t="n">
+        <f aca="false">MIN(N2,N14)-K2</f>
+        <v>0</v>
+      </c>
       <c r="L4" s="35"/>
       <c r="M4" s="36"/>
       <c r="N4" s="33" t="n">
         <f aca="false">G3</f>
         <v>1</v>
       </c>
-      <c r="O4" s="34"/>
-      <c r="P4" s="33"/>
+      <c r="O4" s="34" t="n">
+        <f aca="false">P5-P2</f>
+        <v>0</v>
+      </c>
+      <c r="P4" s="33" t="n">
+        <f aca="false">MIN(S2,S8)-P2</f>
+        <v>0</v>
+      </c>
       <c r="Q4" s="35"/>
       <c r="R4" s="36"/>
       <c r="S4" s="33" t="n">
         <f aca="false">G4</f>
         <v>4</v>
       </c>
-      <c r="T4" s="34"/>
-      <c r="U4" s="33"/>
+      <c r="T4" s="34" t="n">
+        <f aca="false">U5-U2</f>
+        <v>6</v>
+      </c>
+      <c r="U4" s="33" t="n">
+        <f aca="false">AI2-U2</f>
+        <v>6</v>
+      </c>
       <c r="V4" s="35"/>
       <c r="W4" s="35"/>
       <c r="X4" s="35"/>
@@ -2496,63 +2557,108 @@
         <f aca="false">G9</f>
         <v>2</v>
       </c>
-      <c r="AJ4" s="34"/>
-      <c r="AK4" s="33"/>
+      <c r="AJ4" s="34" t="n">
+        <f aca="false">AK5-AK2</f>
+        <v>0</v>
+      </c>
+      <c r="AK4" s="33" t="n">
+        <f aca="false">AN2-AK2</f>
+        <v>0</v>
+      </c>
       <c r="AL4" s="35"/>
       <c r="AM4" s="35"/>
       <c r="AN4" s="33" t="n">
         <f aca="false">G10</f>
         <v>2</v>
       </c>
-      <c r="AO4" s="34"/>
-      <c r="AP4" s="33"/>
+      <c r="AO4" s="34" t="n">
+        <f aca="false">AP5-AP2</f>
+        <v>0</v>
+      </c>
+      <c r="AP4" s="33" t="n">
+        <f aca="false">AS2-AP2</f>
+        <v>0</v>
+      </c>
       <c r="AQ4" s="35"/>
       <c r="AR4" s="35"/>
       <c r="AS4" s="33" t="n">
         <f aca="false">G11</f>
         <v>2</v>
       </c>
-      <c r="AT4" s="34"/>
-      <c r="AU4" s="33"/>
+      <c r="AT4" s="34" t="n">
+        <f aca="false">AU5-AU2</f>
+        <v>0</v>
+      </c>
+      <c r="AU4" s="33" t="n">
+        <f aca="false">AX2-AU2</f>
+        <v>0</v>
+      </c>
       <c r="AV4" s="35"/>
       <c r="AW4" s="35"/>
       <c r="AX4" s="33" t="n">
         <f aca="false">G13</f>
         <v>3</v>
       </c>
-      <c r="AY4" s="34"/>
-      <c r="AZ4" s="33"/>
+      <c r="AY4" s="34" t="n">
+        <f aca="false">AZ5-AZ2</f>
+        <v>0</v>
+      </c>
+      <c r="AZ4" s="33" t="n">
+        <f aca="false">BC2-AZ2</f>
+        <v>0</v>
+      </c>
       <c r="BA4" s="35"/>
       <c r="BB4" s="35"/>
       <c r="BC4" s="33" t="n">
         <f aca="false">G14</f>
         <v>3</v>
       </c>
-      <c r="BD4" s="34"/>
-      <c r="BE4" s="33"/>
+      <c r="BD4" s="34" t="n">
+        <f aca="false">BE5-BE2</f>
+        <v>0</v>
+      </c>
+      <c r="BE4" s="33" t="n">
+        <f aca="false">BH2-BE2</f>
+        <v>0</v>
+      </c>
       <c r="BF4" s="35"/>
       <c r="BG4" s="35"/>
       <c r="BH4" s="33" t="n">
         <f aca="false">G15</f>
         <v>1</v>
       </c>
-      <c r="BI4" s="34"/>
-      <c r="BJ4" s="33"/>
+      <c r="BI4" s="34" t="n">
+        <f aca="false">BJ5-BJ2</f>
+        <v>0</v>
+      </c>
+      <c r="BJ4" s="33" t="n">
+        <f aca="false">BM2-BJ2</f>
+        <v>0</v>
+      </c>
       <c r="BK4" s="35"/>
       <c r="BL4" s="35"/>
       <c r="BM4" s="33" t="n">
         <f aca="false">G16</f>
         <v>5</v>
       </c>
-      <c r="BN4" s="34"/>
-      <c r="BO4" s="33"/>
+      <c r="BN4" s="34" t="n">
+        <f aca="false">BO5-BO2</f>
+        <v>0</v>
+      </c>
+      <c r="BO4" s="33" t="n">
+        <f aca="false">BR2-BO2</f>
+        <v>0</v>
+      </c>
       <c r="BP4" s="35"/>
       <c r="BQ4" s="36"/>
       <c r="BR4" s="33" t="n">
         <f aca="false">G17</f>
         <v>1</v>
       </c>
-      <c r="BS4" s="34"/>
+      <c r="BS4" s="34" t="n">
+        <f aca="false">BT5-BT2</f>
+        <v>0</v>
+      </c>
       <c r="BT4" s="33"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2577,61 +2683,104 @@
         <v>0</v>
       </c>
       <c r="J5" s="28"/>
-      <c r="K5" s="27"/>
+      <c r="K5" s="27" t="n">
+        <f aca="false">MIN(N5,N17)</f>
+        <v>5</v>
+      </c>
       <c r="M5" s="37"/>
       <c r="N5" s="27" t="n">
-        <v>0</v>
+        <f aca="false">P5-N4</f>
+        <v>5</v>
       </c>
       <c r="O5" s="28"/>
-      <c r="P5" s="27"/>
+      <c r="P5" s="27" t="n">
+        <f aca="false">MIN(S5,S11)</f>
+        <v>6</v>
+      </c>
       <c r="R5" s="37"/>
       <c r="S5" s="27" t="n">
-        <v>0</v>
+        <f aca="false">U5-S4</f>
+        <v>12</v>
       </c>
       <c r="T5" s="28"/>
-      <c r="U5" s="27"/>
+      <c r="U5" s="27" t="n">
+        <f aca="false">AI5</f>
+        <v>16</v>
+      </c>
       <c r="AH5" s="37"/>
       <c r="AI5" s="27" t="n">
-        <v>0</v>
+        <f aca="false">AK5-AI4</f>
+        <v>16</v>
       </c>
       <c r="AJ5" s="28"/>
-      <c r="AK5" s="27"/>
+      <c r="AK5" s="27" t="n">
+        <f aca="false">AN5</f>
+        <v>18</v>
+      </c>
       <c r="AN5" s="27" t="n">
-        <v>0</v>
+        <f aca="false">AP5-AN4</f>
+        <v>18</v>
       </c>
       <c r="AO5" s="28"/>
-      <c r="AP5" s="27"/>
+      <c r="AP5" s="27" t="n">
+        <f aca="false">AS5</f>
+        <v>20</v>
+      </c>
       <c r="AS5" s="27" t="n">
-        <v>0</v>
+        <f aca="false">AU5-AS4</f>
+        <v>20</v>
       </c>
       <c r="AT5" s="28"/>
-      <c r="AU5" s="27"/>
+      <c r="AU5" s="27" t="n">
+        <f aca="false">AX5</f>
+        <v>22</v>
+      </c>
       <c r="AX5" s="27" t="n">
-        <v>0</v>
+        <f aca="false">AZ5-AX4</f>
+        <v>22</v>
       </c>
       <c r="AY5" s="28"/>
-      <c r="AZ5" s="27"/>
+      <c r="AZ5" s="27" t="n">
+        <f aca="false">BC5</f>
+        <v>25</v>
+      </c>
       <c r="BC5" s="27" t="n">
-        <v>0</v>
+        <f aca="false">BE5-BC4</f>
+        <v>25</v>
       </c>
       <c r="BD5" s="28"/>
-      <c r="BE5" s="27"/>
+      <c r="BE5" s="27" t="n">
+        <f aca="false">BH5</f>
+        <v>28</v>
+      </c>
       <c r="BH5" s="27" t="n">
-        <v>0</v>
+        <f aca="false">BJ5-BH4</f>
+        <v>28</v>
       </c>
       <c r="BI5" s="28"/>
-      <c r="BJ5" s="27"/>
+      <c r="BJ5" s="27" t="n">
+        <f aca="false">BM5</f>
+        <v>29</v>
+      </c>
       <c r="BM5" s="27" t="n">
-        <v>0</v>
+        <f aca="false">BO5-BM4</f>
+        <v>29</v>
       </c>
       <c r="BN5" s="28"/>
-      <c r="BO5" s="27"/>
+      <c r="BO5" s="27" t="n">
+        <f aca="false">BR5</f>
+        <v>34</v>
+      </c>
       <c r="BQ5" s="37"/>
       <c r="BR5" s="27" t="n">
-        <v>0</v>
+        <f aca="false">BT5-BR4</f>
+        <v>34</v>
       </c>
       <c r="BS5" s="28"/>
-      <c r="BT5" s="27"/>
+      <c r="BT5" s="27" t="n">
+        <f aca="false">BT2</f>
+        <v>35</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
@@ -2700,15 +2849,23 @@
       <c r="M8" s="37"/>
       <c r="R8" s="37"/>
       <c r="S8" s="27" t="n">
-        <v>0</v>
+        <f aca="false">P2</f>
+        <v>6</v>
       </c>
       <c r="T8" s="28"/>
-      <c r="U8" s="27"/>
+      <c r="U8" s="27" t="n">
+        <f aca="false">S8+S10</f>
+        <v>9</v>
+      </c>
       <c r="X8" s="27" t="n">
-        <v>0</v>
+        <f aca="false">U8</f>
+        <v>9</v>
       </c>
       <c r="Y8" s="28"/>
-      <c r="Z8" s="27"/>
+      <c r="Z8" s="27" t="n">
+        <f aca="false">X8+X10</f>
+        <v>16</v>
+      </c>
       <c r="AH8" s="37"/>
       <c r="BQ8" s="37"/>
     </row>
@@ -2769,16 +2926,28 @@
         <f aca="false">G5</f>
         <v>3</v>
       </c>
-      <c r="T10" s="34"/>
-      <c r="U10" s="33"/>
+      <c r="T10" s="34" t="n">
+        <f aca="false">U11-U8</f>
+        <v>0</v>
+      </c>
+      <c r="U10" s="33" t="n">
+        <f aca="false">X8-U8</f>
+        <v>0</v>
+      </c>
       <c r="V10" s="35"/>
       <c r="W10" s="35"/>
       <c r="X10" s="33" t="n">
         <f aca="false">G6</f>
         <v>7</v>
       </c>
-      <c r="Y10" s="34"/>
-      <c r="Z10" s="40"/>
+      <c r="Y10" s="34" t="n">
+        <f aca="false">Z11-Z8</f>
+        <v>0</v>
+      </c>
+      <c r="Z10" s="40" t="n">
+        <f aca="false">AI2-Z8</f>
+        <v>0</v>
+      </c>
       <c r="AA10" s="35"/>
       <c r="AB10" s="35"/>
       <c r="AC10" s="35"/>
@@ -2809,15 +2978,23 @@
       </c>
       <c r="M11" s="37"/>
       <c r="S11" s="27" t="n">
-        <v>0</v>
+        <f aca="false">U11-S10</f>
+        <v>6</v>
       </c>
       <c r="T11" s="28"/>
-      <c r="U11" s="27"/>
+      <c r="U11" s="27" t="n">
+        <f aca="false">X11</f>
+        <v>9</v>
+      </c>
       <c r="X11" s="27" t="n">
-        <v>0</v>
+        <f aca="false">Z11-X10</f>
+        <v>9</v>
       </c>
       <c r="Y11" s="28"/>
-      <c r="Z11" s="27"/>
+      <c r="Z11" s="27" t="n">
+        <f aca="false">AI5</f>
+        <v>16</v>
+      </c>
       <c r="AH11" s="37"/>
       <c r="BQ11" s="37"/>
     </row>
@@ -2887,22 +3064,33 @@
       </c>
       <c r="M14" s="37"/>
       <c r="N14" s="27" t="n">
-        <v>0</v>
+        <f aca="false">K2</f>
+        <v>5</v>
       </c>
       <c r="O14" s="28"/>
-      <c r="P14" s="27"/>
+      <c r="P14" s="27" t="n">
+        <f aca="false">N14+N16</f>
+        <v>6</v>
+      </c>
       <c r="S14" s="27" t="n">
-        <v>0</v>
+        <f aca="false">P14</f>
+        <v>6</v>
       </c>
       <c r="T14" s="28"/>
-      <c r="U14" s="27"/>
-      <c r="X14" s="41"/>
+      <c r="U14" s="27" t="n">
+        <f aca="false">S14+S16</f>
+        <v>9</v>
+      </c>
       <c r="AH14" s="37"/>
       <c r="AI14" s="27" t="n">
-        <v>0</v>
+        <f aca="false">U14</f>
+        <v>9</v>
       </c>
       <c r="AJ14" s="28"/>
-      <c r="AK14" s="27"/>
+      <c r="AK14" s="27" t="n">
+        <f aca="false">AI14+AI16</f>
+        <v>19</v>
+      </c>
       <c r="BQ14" s="37"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2934,8 +3122,19 @@
       </c>
       <c r="T15" s="32"/>
       <c r="U15" s="32"/>
-      <c r="X15" s="41"/>
-      <c r="AH15" s="37"/>
+      <c r="V15" s="35"/>
+      <c r="W15" s="35"/>
+      <c r="X15" s="35"/>
+      <c r="Y15" s="35"/>
+      <c r="Z15" s="35"/>
+      <c r="AA15" s="35"/>
+      <c r="AB15" s="35"/>
+      <c r="AC15" s="35"/>
+      <c r="AD15" s="35"/>
+      <c r="AE15" s="35"/>
+      <c r="AF15" s="35"/>
+      <c r="AG15" s="35"/>
+      <c r="AH15" s="41"/>
       <c r="AI15" s="32" t="s">
         <v>17</v>
       </c>
@@ -2966,16 +3165,28 @@
         <f aca="false">G7</f>
         <v>1</v>
       </c>
-      <c r="O16" s="34"/>
-      <c r="P16" s="33"/>
+      <c r="O16" s="34" t="n">
+        <f aca="false">P17-P14</f>
+        <v>7</v>
+      </c>
+      <c r="P16" s="33" t="n">
+        <f aca="false">S14-P14</f>
+        <v>0</v>
+      </c>
       <c r="Q16" s="35"/>
       <c r="R16" s="35"/>
       <c r="S16" s="33" t="n">
         <f aca="false">G8</f>
         <v>3</v>
       </c>
-      <c r="T16" s="34"/>
-      <c r="U16" s="33"/>
+      <c r="T16" s="34" t="n">
+        <f aca="false">U17-U14</f>
+        <v>7</v>
+      </c>
+      <c r="U16" s="33" t="n">
+        <f aca="false">MIN(AI2,AI14)-U14</f>
+        <v>0</v>
+      </c>
       <c r="V16" s="35"/>
       <c r="W16" s="35"/>
       <c r="X16" s="35"/>
@@ -2993,8 +3204,14 @@
         <f aca="false">G12</f>
         <v>10</v>
       </c>
-      <c r="AJ16" s="34"/>
-      <c r="AK16" s="40"/>
+      <c r="AJ16" s="34" t="n">
+        <f aca="false">AK17-AK14</f>
+        <v>15</v>
+      </c>
+      <c r="AK16" s="40" t="n">
+        <f aca="false">BR2-AK14</f>
+        <v>15</v>
+      </c>
       <c r="AL16" s="35"/>
       <c r="AM16" s="35"/>
       <c r="AN16" s="35"/>
@@ -3044,20 +3261,32 @@
         <v>1</v>
       </c>
       <c r="N17" s="27" t="n">
-        <v>0</v>
+        <f aca="false">P17-N16</f>
+        <v>12</v>
       </c>
       <c r="O17" s="28"/>
-      <c r="P17" s="27"/>
+      <c r="P17" s="27" t="n">
+        <f aca="false">S17</f>
+        <v>13</v>
+      </c>
       <c r="S17" s="27" t="n">
-        <v>0</v>
+        <f aca="false">U17-S16</f>
+        <v>13</v>
       </c>
       <c r="T17" s="28"/>
-      <c r="U17" s="27"/>
+      <c r="U17" s="27" t="n">
+        <f aca="false">MIN(AI5,AI17)</f>
+        <v>16</v>
+      </c>
       <c r="AI17" s="27" t="n">
-        <v>0</v>
+        <f aca="false">AK17-AI16</f>
+        <v>24</v>
       </c>
       <c r="AJ17" s="28"/>
-      <c r="AK17" s="27"/>
+      <c r="AK17" s="27" t="n">
+        <f aca="false">BR5</f>
+        <v>34</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="46" t="s">
@@ -3236,7 +3465,7 @@
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="C33:D33"/>
   </mergeCells>
-  <conditionalFormatting sqref="J4 C21 C26 O4 T4 O16 U16 AJ4 AO4 AT4 AY4 S10:T10 AK16 BD4 BI4 BN4 BS4">
+  <conditionalFormatting sqref="C21 C26 T16:U16 S10:T10 AJ16:AK16 BS4 BN4 BI4 BD4 AY4 AT4 AO4 AJ4 Y10 T4 O4 O16 J4">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>

--- a/Übungen/Online_Shop.xlsx
+++ b/Übungen/Online_Shop.xlsx
@@ -5,10 +5,11 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="PSP" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Netzplan" sheetId="2" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="72">
   <si>
     <t xml:space="preserve">Beispiel: Funktionsorientierter Projektstrukturplan</t>
   </si>
@@ -80,43 +81,49 @@
     <t xml:space="preserve">Produkte erfassen</t>
   </si>
   <si>
+    <t xml:space="preserve">Template auswählen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Produktfotos erstellen</t>
+  </si>
+  <si>
     <t xml:space="preserve">Seitenstruktur einrichten</t>
   </si>
   <si>
-    <t xml:space="preserve">Tests</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1.2</t>
+    <t xml:space="preserve">Auftraggeber-Präsentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1.3</t>
   </si>
   <si>
     <t xml:space="preserve">1.2.3</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Produktfotos erstellen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auftraggeber-Präsentation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1.3</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.3.3</t>
   </si>
   <si>
     <t xml:space="preserve">Produktfotos bearbeiten</t>
   </si>
   <si>
-    <t xml:space="preserve">Template auswählen</t>
+    <t xml:space="preserve">Datenbank einbinden</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.4</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2.2</t>
+    <t xml:space="preserve">1.2.4</t>
   </si>
   <si>
     <t xml:space="preserve">Zahlungsdienste einbinden</t>
@@ -149,28 +156,101 @@
     <t xml:space="preserve">1.2.8</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Datenbank einbinden</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.2.9</t>
   </si>
   <si>
     <t xml:space="preserve">Onlinestellung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vorgänger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nachfolger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dauer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1.1, 1.2.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1.2, 1.1.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2.4, 1.3.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1.2, 1.1.4, 1.2.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Onlinehilfe erstellen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3.1, 1.2.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Früheste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anfangszeit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Endzeit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gesamtpuffer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freier Puffer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Späteste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FEZ_Vorgänger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAZ + D</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
     <numFmt numFmtId="166" formatCode="@"/>
+    <numFmt numFmtId="167" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -221,8 +301,16 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -232,7 +320,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFBF00"/>
-        <bgColor rgb="FFFF9900"/>
+        <bgColor rgb="FFFF8000"/>
       </patternFill>
     </fill>
     <fill>
@@ -244,13 +332,31 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEEEEEE"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFE8E8E8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFAADCF7"/>
         <bgColor rgb="FFCCCCFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8E8E8"/>
+        <bgColor rgb="FFEEEEEE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00A933"/>
+        <bgColor rgb="FF008000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF8000"/>
+        <bgColor rgb="FFFF6600"/>
       </patternFill>
     </fill>
   </fills>
@@ -267,35 +373,6 @@
       <right style="hair"/>
       <top style="hair"/>
       <bottom style="hair"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thick">
-        <color rgb="FF2A6099"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thick">
-        <color rgb="FF2A6099"/>
-      </left>
-      <right/>
-      <top style="thick">
-        <color rgb="FF2A6099"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right/>
-      <top style="thick">
-        <color rgb="FF2A6099"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
@@ -340,6 +417,27 @@
       <bottom style="hair"/>
       <diagonal/>
     </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="thick"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thick"/>
+      <right/>
+      <top style="thick"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thick"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="23">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -375,7 +473,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="56">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -400,18 +498,6 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -424,11 +510,35 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -444,28 +554,148 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -480,6 +710,17 @@
     <cellStyle name="KritischerPfad" xfId="21"/>
     <cellStyle name="Wochenende" xfId="22"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="2"/>
+        <b val="1"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -501,10 +742,10 @@
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFEEEEEE"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFE8E8E8"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF2A6099"/>
+      <rgbColor rgb="FF0066CC"/>
       <rgbColor rgb="FFCCCCFF"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
@@ -526,12 +767,12 @@
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFBF00"/>
-      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF8000"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666666"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF00A933"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
@@ -543,13 +784,941 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>907560</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>154440</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>11880</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>154440</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="0" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="5493960" y="479520"/>
+          <a:ext cx="5554080" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>906840</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>906840</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>8640</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5493240" y="488160"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>906120</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>906120</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>8640</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5492520" y="488160"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>4680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>12960</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5507640" y="1125360"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>4680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>12600</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5507640" y="1612800"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>3960</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>11880</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5507640" y="2099880"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>3600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>11880</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5507640" y="2587320"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>-360</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>7920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8272080" y="324720"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>7920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8272080" y="487440"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>4680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>12960</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8272080" y="1125360"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>4680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>12600</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8272080" y="1612800"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>3600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>11880</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8272080" y="2587320"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>3240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>11160</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8272080" y="3074400"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>2160</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>10440</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8272080" y="4048920"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>1440</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>9360</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8272080" y="5023440"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>360</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>360</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>7920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11036520" y="487440"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>360</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>4680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>360</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>12960</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11036520" y="1125360"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>360</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>4680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>360</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>12600</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11036520" y="1612800"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>360</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>3960</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>360</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>11880</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11036520" y="2099880"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>911160</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>160920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>911160</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>6480</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8261640" y="3557520"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>911160</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>161640</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>911160</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>7200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8261640" y="4533480"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>911160</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>160200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>911160</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>5760</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8261640" y="2093760"/>
+          <a:ext cx="0" cy="170640"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18000">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M41"/>
-  <sheetFormatPr defaultColWidth="13.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="13.07421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.77"/>
   </cols>
@@ -592,20 +1761,20 @@
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
-      <c r="J3" s="6"/>
+      <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F4" s="3"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="6"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="24.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F5" s="4" t="s">
@@ -618,13 +1787,12 @@
       </c>
       <c r="J5" s="4"/>
       <c r="K5" s="3"/>
-      <c r="L5" s="9" t="s">
+      <c r="L5" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="M5" s="9"/>
+      <c r="M5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="0"/>
       <c r="F6" s="5" t="s">
         <v>6</v>
       </c>
@@ -646,12 +1814,6 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="0"/>
-      <c r="G7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="M7" s="6"/>
-    </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F8" s="4" t="s">
         <v>12</v>
@@ -679,17 +1841,12 @@
       <c r="J9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="L9" s="10" t="s">
+      <c r="L9" s="7" t="s">
         <v>17</v>
       </c>
       <c r="M9" s="5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="M10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F11" s="4" t="s">
@@ -718,17 +1875,12 @@
       <c r="J12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="L12" s="10" t="s">
+      <c r="L12" s="7" t="s">
         <v>23</v>
       </c>
       <c r="M12" s="5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="M13" s="6"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F14" s="4" t="s">
@@ -736,230 +1888,217 @@
       </c>
       <c r="G14" s="4"/>
       <c r="I14" s="4" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J14" s="4"/>
       <c r="L14" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F15" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>7</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="L15" s="10" t="s">
-        <v>27</v>
+      <c r="L15" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G16" s="6"/>
-      <c r="J16" s="6"/>
-    </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F17" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G17" s="4"/>
       <c r="I17" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F18" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>7</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J19" s="6"/>
-    </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I20" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J20" s="4"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I21" s="5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J22" s="6"/>
-    </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I23" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J23" s="4"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I24" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J24" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="J25" s="6"/>
+      <c r="A25" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="14" t="s">
+      <c r="A26" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
       <c r="I26" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J26" s="4"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
       <c r="I27" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J27" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="17" t="s">
+      <c r="A28" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B28" s="18" t="s">
+      <c r="B28" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="J28" s="6"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="B29" s="18" t="s">
+      <c r="A29" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
       <c r="I29" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J29" s="4"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="17" t="s">
+      <c r="A30" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="B30" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
       <c r="I30" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J30" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="17" t="s">
+      <c r="A31" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B31" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="J31" s="6"/>
+      <c r="B31" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="17" t="s">
+      <c r="A32" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="I32" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J32" s="4"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="I32" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J32" s="4"/>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="B33" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
       <c r="I33" s="5" t="s">
         <v>44</v>
       </c>
@@ -968,100 +2107,100 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="17" t="s">
+      <c r="A34" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C34" s="15"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C35" s="15"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="15"/>
+      <c r="D37" s="15"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="15"/>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C38" s="15"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="15"/>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C39" s="15"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="15"/>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
-    </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="B35" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="C35" s="18"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="18"/>
-    </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B36" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
-    </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B37" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="C37" s="18"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="18"/>
-      <c r="F37" s="18"/>
-    </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="18"/>
-    </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="B39" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="C39" s="18"/>
-      <c r="D39" s="18"/>
-      <c r="E39" s="18"/>
-      <c r="F39" s="18"/>
-    </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="B40" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="C40" s="18"/>
-      <c r="D40" s="18"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="18"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="15"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="20" t="s">
+      <c r="A41" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B41" s="21" t="s">
+      <c r="B41" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="C41" s="21"/>
-      <c r="D41" s="21"/>
-      <c r="E41" s="22"/>
-      <c r="F41" s="22"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="19"/>
+      <c r="F41" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="38">
@@ -1111,5 +2250,949 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:BT35"/>
+  <sheetFormatPr defaultColWidth="11.82421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="20" width="11.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="16.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="3" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="104" min="8" style="0" width="3.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1022" style="0" width="11.52"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" s="22" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="28"/>
+      <c r="K2" s="27"/>
+      <c r="N2" s="27"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="27"/>
+      <c r="S2" s="27"/>
+      <c r="T2" s="28"/>
+      <c r="U2" s="27"/>
+      <c r="AI2" s="27"/>
+      <c r="AJ2" s="28"/>
+      <c r="AK2" s="27"/>
+      <c r="AN2" s="27"/>
+      <c r="AO2" s="28"/>
+      <c r="AP2" s="27"/>
+      <c r="AS2" s="27"/>
+      <c r="AT2" s="28"/>
+      <c r="AU2" s="27"/>
+      <c r="AX2" s="27"/>
+      <c r="AY2" s="28"/>
+      <c r="AZ2" s="27"/>
+      <c r="BC2" s="27"/>
+      <c r="BD2" s="28"/>
+      <c r="BE2" s="27"/>
+      <c r="BH2" s="27"/>
+      <c r="BI2" s="28"/>
+      <c r="BJ2" s="27"/>
+      <c r="BM2" s="27"/>
+      <c r="BN2" s="28"/>
+      <c r="BO2" s="27"/>
+      <c r="BR2" s="27"/>
+      <c r="BS2" s="28"/>
+      <c r="BT2" s="27"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="G3" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="N3" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="O3" s="32"/>
+      <c r="P3" s="32"/>
+      <c r="S3" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="T3" s="32"/>
+      <c r="U3" s="32"/>
+      <c r="AI3" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="AJ3" s="32"/>
+      <c r="AK3" s="32"/>
+      <c r="AN3" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="AO3" s="32"/>
+      <c r="AP3" s="32"/>
+      <c r="AS3" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="AT3" s="32"/>
+      <c r="AU3" s="32"/>
+      <c r="AX3" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="AY3" s="32"/>
+      <c r="AZ3" s="32"/>
+      <c r="BC3" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="BD3" s="32"/>
+      <c r="BE3" s="32"/>
+      <c r="BH3" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="BI3" s="32"/>
+      <c r="BJ3" s="32"/>
+      <c r="BM3" s="32" t="s">
+        <v>43</v>
+      </c>
+      <c r="BN3" s="32"/>
+      <c r="BO3" s="32"/>
+      <c r="BR3" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="BS3" s="32"/>
+      <c r="BT3" s="32"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" s="33" t="n">
+        <f aca="false">G2</f>
+        <v>5</v>
+      </c>
+      <c r="J4" s="34"/>
+      <c r="K4" s="33"/>
+      <c r="L4" s="35"/>
+      <c r="M4" s="36"/>
+      <c r="N4" s="33" t="n">
+        <f aca="false">G3</f>
+        <v>1</v>
+      </c>
+      <c r="O4" s="34"/>
+      <c r="P4" s="33"/>
+      <c r="Q4" s="35"/>
+      <c r="R4" s="36"/>
+      <c r="S4" s="33" t="n">
+        <f aca="false">G4</f>
+        <v>4</v>
+      </c>
+      <c r="T4" s="34"/>
+      <c r="U4" s="33"/>
+      <c r="V4" s="35"/>
+      <c r="W4" s="35"/>
+      <c r="X4" s="35"/>
+      <c r="Y4" s="35"/>
+      <c r="Z4" s="35"/>
+      <c r="AA4" s="35"/>
+      <c r="AB4" s="35"/>
+      <c r="AC4" s="35"/>
+      <c r="AD4" s="35"/>
+      <c r="AE4" s="35"/>
+      <c r="AF4" s="35"/>
+      <c r="AG4" s="35"/>
+      <c r="AH4" s="36"/>
+      <c r="AI4" s="33" t="n">
+        <f aca="false">G9</f>
+        <v>2</v>
+      </c>
+      <c r="AJ4" s="34"/>
+      <c r="AK4" s="33"/>
+      <c r="AL4" s="35"/>
+      <c r="AM4" s="35"/>
+      <c r="AN4" s="33" t="n">
+        <f aca="false">G10</f>
+        <v>2</v>
+      </c>
+      <c r="AO4" s="34"/>
+      <c r="AP4" s="33"/>
+      <c r="AQ4" s="35"/>
+      <c r="AR4" s="35"/>
+      <c r="AS4" s="33" t="n">
+        <f aca="false">G11</f>
+        <v>2</v>
+      </c>
+      <c r="AT4" s="34"/>
+      <c r="AU4" s="33"/>
+      <c r="AV4" s="35"/>
+      <c r="AW4" s="35"/>
+      <c r="AX4" s="33" t="n">
+        <f aca="false">G13</f>
+        <v>3</v>
+      </c>
+      <c r="AY4" s="34"/>
+      <c r="AZ4" s="33"/>
+      <c r="BA4" s="35"/>
+      <c r="BB4" s="35"/>
+      <c r="BC4" s="33" t="n">
+        <f aca="false">G14</f>
+        <v>3</v>
+      </c>
+      <c r="BD4" s="34"/>
+      <c r="BE4" s="33"/>
+      <c r="BF4" s="35"/>
+      <c r="BG4" s="35"/>
+      <c r="BH4" s="33" t="n">
+        <f aca="false">G15</f>
+        <v>1</v>
+      </c>
+      <c r="BI4" s="34"/>
+      <c r="BJ4" s="33"/>
+      <c r="BK4" s="35"/>
+      <c r="BL4" s="35"/>
+      <c r="BM4" s="33" t="n">
+        <f aca="false">G16</f>
+        <v>5</v>
+      </c>
+      <c r="BN4" s="34"/>
+      <c r="BO4" s="33"/>
+      <c r="BP4" s="35"/>
+      <c r="BQ4" s="36"/>
+      <c r="BR4" s="33" t="n">
+        <f aca="false">G17</f>
+        <v>1</v>
+      </c>
+      <c r="BS4" s="34"/>
+      <c r="BT4" s="33"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="28"/>
+      <c r="K5" s="27"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="27"/>
+      <c r="O5" s="28"/>
+      <c r="P5" s="27"/>
+      <c r="R5" s="37"/>
+      <c r="S5" s="27"/>
+      <c r="T5" s="28"/>
+      <c r="U5" s="27"/>
+      <c r="AH5" s="37"/>
+      <c r="AI5" s="27"/>
+      <c r="AJ5" s="28"/>
+      <c r="AK5" s="27"/>
+      <c r="AN5" s="27"/>
+      <c r="AO5" s="28"/>
+      <c r="AP5" s="27"/>
+      <c r="AS5" s="27"/>
+      <c r="AT5" s="28"/>
+      <c r="AU5" s="27"/>
+      <c r="AX5" s="27"/>
+      <c r="AY5" s="28"/>
+      <c r="AZ5" s="27"/>
+      <c r="BC5" s="27"/>
+      <c r="BD5" s="28"/>
+      <c r="BE5" s="27"/>
+      <c r="BH5" s="27"/>
+      <c r="BI5" s="28"/>
+      <c r="BJ5" s="27"/>
+      <c r="BM5" s="27"/>
+      <c r="BN5" s="28"/>
+      <c r="BO5" s="27"/>
+      <c r="BQ5" s="37"/>
+      <c r="BR5" s="27"/>
+      <c r="BS5" s="28"/>
+      <c r="BT5" s="27"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="39" t="n">
+        <v>7</v>
+      </c>
+      <c r="M6" s="37"/>
+      <c r="R6" s="37"/>
+      <c r="AH6" s="37"/>
+      <c r="BQ6" s="37"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="29"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="37"/>
+      <c r="R7" s="37"/>
+      <c r="AH7" s="37"/>
+      <c r="BQ7" s="37"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" s="37"/>
+      <c r="R8" s="37"/>
+      <c r="S8" s="27"/>
+      <c r="T8" s="28"/>
+      <c r="U8" s="27"/>
+      <c r="X8" s="27"/>
+      <c r="Y8" s="28"/>
+      <c r="Z8" s="27"/>
+      <c r="AH8" s="37"/>
+      <c r="BQ8" s="37"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" s="37"/>
+      <c r="R9" s="37"/>
+      <c r="S9" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="T9" s="32"/>
+      <c r="U9" s="32"/>
+      <c r="X9" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y9" s="32"/>
+      <c r="Z9" s="32"/>
+      <c r="AH9" s="37"/>
+      <c r="BQ9" s="37"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" s="37"/>
+      <c r="R10" s="35"/>
+      <c r="S10" s="33" t="n">
+        <f aca="false">G5</f>
+        <v>3</v>
+      </c>
+      <c r="T10" s="34"/>
+      <c r="U10" s="33"/>
+      <c r="V10" s="35"/>
+      <c r="W10" s="35"/>
+      <c r="X10" s="33" t="n">
+        <f aca="false">G6</f>
+        <v>7</v>
+      </c>
+      <c r="Y10" s="34"/>
+      <c r="Z10" s="33"/>
+      <c r="AA10" s="35"/>
+      <c r="AB10" s="35"/>
+      <c r="AC10" s="35"/>
+      <c r="AD10" s="35"/>
+      <c r="AE10" s="35"/>
+      <c r="AF10" s="35"/>
+      <c r="AG10" s="35"/>
+      <c r="AH10" s="37"/>
+      <c r="BQ10" s="37"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" s="37"/>
+      <c r="S11" s="27"/>
+      <c r="T11" s="28"/>
+      <c r="U11" s="27"/>
+      <c r="X11" s="27"/>
+      <c r="Y11" s="28"/>
+      <c r="Z11" s="27"/>
+      <c r="AH11" s="37"/>
+      <c r="BQ11" s="37"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="39" t="n">
+        <v>10</v>
+      </c>
+      <c r="M12" s="37"/>
+      <c r="X12" s="40"/>
+      <c r="AH12" s="37"/>
+      <c r="BQ12" s="37"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" s="37"/>
+      <c r="X13" s="40"/>
+      <c r="AH13" s="37"/>
+      <c r="BQ13" s="37"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="G14" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="M14" s="37"/>
+      <c r="N14" s="27"/>
+      <c r="O14" s="28"/>
+      <c r="P14" s="27"/>
+      <c r="S14" s="27"/>
+      <c r="T14" s="28"/>
+      <c r="U14" s="27"/>
+      <c r="AH14" s="37"/>
+      <c r="AI14" s="27"/>
+      <c r="AJ14" s="28"/>
+      <c r="AK14" s="27"/>
+      <c r="BQ14" s="37"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G15" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="37"/>
+      <c r="N15" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="S15" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="T15" s="32"/>
+      <c r="U15" s="32"/>
+      <c r="V15" s="35"/>
+      <c r="W15" s="35"/>
+      <c r="X15" s="35"/>
+      <c r="Y15" s="35"/>
+      <c r="Z15" s="35"/>
+      <c r="AA15" s="35"/>
+      <c r="AB15" s="35"/>
+      <c r="AC15" s="35"/>
+      <c r="AD15" s="35"/>
+      <c r="AE15" s="35"/>
+      <c r="AF15" s="35"/>
+      <c r="AG15" s="35"/>
+      <c r="AH15" s="40"/>
+      <c r="AI15" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ15" s="32"/>
+      <c r="AK15" s="32"/>
+      <c r="BQ15" s="37"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="G16" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="M16" s="35"/>
+      <c r="N16" s="33" t="n">
+        <f aca="false">G7</f>
+        <v>1</v>
+      </c>
+      <c r="O16" s="34"/>
+      <c r="P16" s="33"/>
+      <c r="Q16" s="35"/>
+      <c r="R16" s="35"/>
+      <c r="S16" s="33" t="n">
+        <f aca="false">G8</f>
+        <v>3</v>
+      </c>
+      <c r="T16" s="34"/>
+      <c r="U16" s="33"/>
+      <c r="V16" s="35"/>
+      <c r="W16" s="35"/>
+      <c r="X16" s="35"/>
+      <c r="Y16" s="35"/>
+      <c r="Z16" s="35"/>
+      <c r="AA16" s="35"/>
+      <c r="AB16" s="35"/>
+      <c r="AC16" s="35"/>
+      <c r="AD16" s="35"/>
+      <c r="AE16" s="35"/>
+      <c r="AF16" s="35"/>
+      <c r="AG16" s="35"/>
+      <c r="AH16" s="35"/>
+      <c r="AI16" s="33" t="n">
+        <f aca="false">G12</f>
+        <v>10</v>
+      </c>
+      <c r="AJ16" s="34"/>
+      <c r="AK16" s="33"/>
+      <c r="AL16" s="35"/>
+      <c r="AM16" s="35"/>
+      <c r="AN16" s="35"/>
+      <c r="AO16" s="35"/>
+      <c r="AP16" s="35"/>
+      <c r="AQ16" s="35"/>
+      <c r="AR16" s="35"/>
+      <c r="AS16" s="35"/>
+      <c r="AT16" s="35"/>
+      <c r="AU16" s="35"/>
+      <c r="AV16" s="35"/>
+      <c r="AW16" s="35"/>
+      <c r="AX16" s="35"/>
+      <c r="AY16" s="35"/>
+      <c r="AZ16" s="35"/>
+      <c r="BA16" s="35"/>
+      <c r="BB16" s="35"/>
+      <c r="BC16" s="35"/>
+      <c r="BD16" s="35"/>
+      <c r="BE16" s="35"/>
+      <c r="BF16" s="35"/>
+      <c r="BG16" s="35"/>
+      <c r="BH16" s="35"/>
+      <c r="BI16" s="35"/>
+      <c r="BJ16" s="35"/>
+      <c r="BK16" s="35"/>
+      <c r="BL16" s="35"/>
+      <c r="BM16" s="35"/>
+      <c r="BN16" s="35"/>
+      <c r="BO16" s="35"/>
+      <c r="BP16" s="35"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="41"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="42" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17" s="43"/>
+      <c r="G17" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" s="27"/>
+      <c r="O17" s="28"/>
+      <c r="P17" s="27"/>
+      <c r="S17" s="27"/>
+      <c r="T17" s="28"/>
+      <c r="U17" s="27"/>
+      <c r="AI17" s="27"/>
+      <c r="AJ17" s="28"/>
+      <c r="AK17" s="27"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="45" t="s">
+        <v>55</v>
+      </c>
+      <c r="B19" s="46" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" s="47"/>
+      <c r="D19" s="48" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="33" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="49" t="s">
+        <v>60</v>
+      </c>
+      <c r="B22" s="50" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="51"/>
+      <c r="D22" s="52" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="28"/>
+      <c r="D24" s="27" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" s="32"/>
+      <c r="D25" s="32"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="C26" s="34" t="s">
+        <v>65</v>
+      </c>
+      <c r="D26" s="33" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="53" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" s="28"/>
+      <c r="D27" s="27" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="B29" s="54" t="s">
+        <v>69</v>
+      </c>
+      <c r="C29" s="55" t="s">
+        <v>70</v>
+      </c>
+      <c r="D29" s="55"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="B30" s="54" t="s">
+        <v>69</v>
+      </c>
+      <c r="C30" s="55" t="s">
+        <v>71</v>
+      </c>
+      <c r="D30" s="55"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="54"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" s="54" t="s">
+        <v>69</v>
+      </c>
+      <c r="C32" s="55" t="s">
+        <v>71</v>
+      </c>
+      <c r="D32" s="55"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="B33" s="54" t="s">
+        <v>69</v>
+      </c>
+      <c r="C33" s="55" t="s">
+        <v>70</v>
+      </c>
+      <c r="D33" s="55"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="54"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="54"/>
+    </row>
+  </sheetData>
+  <mergeCells count="39">
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="S3:U3"/>
+    <mergeCell ref="AI3:AK3"/>
+    <mergeCell ref="AN3:AP3"/>
+    <mergeCell ref="AS3:AU3"/>
+    <mergeCell ref="AX3:AZ3"/>
+    <mergeCell ref="BC3:BE3"/>
+    <mergeCell ref="BH3:BJ3"/>
+    <mergeCell ref="BM3:BO3"/>
+    <mergeCell ref="BR3:BT3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="S9:U9"/>
+    <mergeCell ref="X9:Z9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="S15:U15"/>
+    <mergeCell ref="AI15:AK15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C21 C26 S10:T10 T4 O4 J4 O16 T16 AJ16 Y10 AJ4 AO4 AT4 AY4 BD4 BI4 BN4 BS4">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
--- a/Übungen/Online_Shop.xlsx
+++ b/Übungen/Online_Shop.xlsx
@@ -610,7 +610,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2309,37 +2309,100 @@
         <v>0</v>
       </c>
       <c r="J2" s="28"/>
-      <c r="K2" s="27"/>
-      <c r="N2" s="27"/>
+      <c r="K2" s="27" t="n">
+        <f aca="false">I2+I4</f>
+        <v>5</v>
+      </c>
+      <c r="N2" s="27" t="n">
+        <f aca="false">K2</f>
+        <v>5</v>
+      </c>
       <c r="O2" s="28"/>
-      <c r="P2" s="27"/>
-      <c r="S2" s="27"/>
+      <c r="P2" s="27" t="n">
+        <f aca="false">N2+N4</f>
+        <v>6</v>
+      </c>
+      <c r="S2" s="27" t="n">
+        <f aca="false">P2</f>
+        <v>6</v>
+      </c>
       <c r="T2" s="28"/>
-      <c r="U2" s="27"/>
-      <c r="AI2" s="27"/>
+      <c r="U2" s="27" t="n">
+        <f aca="false">S2+S4</f>
+        <v>10</v>
+      </c>
+      <c r="AI2" s="27" t="n">
+        <f aca="false">MAX(U2,Z8,U14)</f>
+        <v>16</v>
+      </c>
       <c r="AJ2" s="28"/>
-      <c r="AK2" s="27"/>
-      <c r="AN2" s="27"/>
+      <c r="AK2" s="27" t="n">
+        <f aca="false">AI2+AI4</f>
+        <v>18</v>
+      </c>
+      <c r="AN2" s="27" t="n">
+        <f aca="false">AK2</f>
+        <v>18</v>
+      </c>
       <c r="AO2" s="28"/>
-      <c r="AP2" s="27"/>
-      <c r="AS2" s="27"/>
+      <c r="AP2" s="27" t="n">
+        <f aca="false">AN2+AN4</f>
+        <v>20</v>
+      </c>
+      <c r="AS2" s="27" t="n">
+        <f aca="false">AP2</f>
+        <v>20</v>
+      </c>
       <c r="AT2" s="28"/>
-      <c r="AU2" s="27"/>
-      <c r="AX2" s="27"/>
+      <c r="AU2" s="27" t="n">
+        <f aca="false">AS2+AS4</f>
+        <v>22</v>
+      </c>
+      <c r="AX2" s="27" t="n">
+        <f aca="false">AU2</f>
+        <v>22</v>
+      </c>
       <c r="AY2" s="28"/>
-      <c r="AZ2" s="27"/>
-      <c r="BC2" s="27"/>
+      <c r="AZ2" s="27" t="n">
+        <f aca="false">AX2+AX4</f>
+        <v>25</v>
+      </c>
+      <c r="BC2" s="27" t="n">
+        <f aca="false">AZ2</f>
+        <v>25</v>
+      </c>
       <c r="BD2" s="28"/>
-      <c r="BE2" s="27"/>
-      <c r="BH2" s="27"/>
+      <c r="BE2" s="27" t="n">
+        <f aca="false">BC2+BC4</f>
+        <v>28</v>
+      </c>
+      <c r="BH2" s="27" t="n">
+        <f aca="false">BE2</f>
+        <v>28</v>
+      </c>
       <c r="BI2" s="28"/>
-      <c r="BJ2" s="27"/>
-      <c r="BM2" s="27"/>
+      <c r="BJ2" s="27" t="n">
+        <f aca="false">BH2+BH4</f>
+        <v>29</v>
+      </c>
+      <c r="BM2" s="27" t="n">
+        <f aca="false">BJ2</f>
+        <v>29</v>
+      </c>
       <c r="BN2" s="28"/>
-      <c r="BO2" s="27"/>
-      <c r="BR2" s="27"/>
+      <c r="BO2" s="27" t="n">
+        <f aca="false">BM2+BM4</f>
+        <v>34</v>
+      </c>
+      <c r="BR2" s="27" t="n">
+        <f aca="false">MAX(BO2,AK14)</f>
+        <v>34</v>
+      </c>
       <c r="BS2" s="28"/>
-      <c r="BT2" s="27"/>
+      <c r="BT2" s="27" t="n">
+        <f aca="false">BR2+BR4</f>
+        <v>35</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
@@ -2437,24 +2500,42 @@
         <f aca="false">G2</f>
         <v>5</v>
       </c>
-      <c r="J4" s="34"/>
-      <c r="K4" s="33"/>
+      <c r="J4" s="34" t="n">
+        <f aca="false">K5-K2</f>
+        <v>0</v>
+      </c>
+      <c r="K4" s="33" t="n">
+        <f aca="false">MIN(N2,N14)-K2</f>
+        <v>0</v>
+      </c>
       <c r="L4" s="35"/>
       <c r="M4" s="36"/>
       <c r="N4" s="33" t="n">
         <f aca="false">G3</f>
         <v>1</v>
       </c>
-      <c r="O4" s="34"/>
-      <c r="P4" s="33"/>
+      <c r="O4" s="34" t="n">
+        <f aca="false">P5-P2</f>
+        <v>0</v>
+      </c>
+      <c r="P4" s="33" t="n">
+        <f aca="false">S2-P2</f>
+        <v>0</v>
+      </c>
       <c r="Q4" s="35"/>
       <c r="R4" s="36"/>
       <c r="S4" s="33" t="n">
         <f aca="false">G4</f>
         <v>4</v>
       </c>
-      <c r="T4" s="34"/>
-      <c r="U4" s="33"/>
+      <c r="T4" s="34" t="n">
+        <f aca="false">U5-U2</f>
+        <v>6</v>
+      </c>
+      <c r="U4" s="33" t="n">
+        <f aca="false">AI2-U2</f>
+        <v>6</v>
+      </c>
       <c r="V4" s="35"/>
       <c r="W4" s="35"/>
       <c r="X4" s="35"/>
@@ -2472,63 +2553,108 @@
         <f aca="false">G9</f>
         <v>2</v>
       </c>
-      <c r="AJ4" s="34"/>
-      <c r="AK4" s="33"/>
+      <c r="AJ4" s="34" t="n">
+        <f aca="false">AK5-AK2</f>
+        <v>0</v>
+      </c>
+      <c r="AK4" s="34" t="n">
+        <f aca="false">AL5-AL2</f>
+        <v>0</v>
+      </c>
       <c r="AL4" s="35"/>
       <c r="AM4" s="35"/>
       <c r="AN4" s="33" t="n">
         <f aca="false">G10</f>
         <v>2</v>
       </c>
-      <c r="AO4" s="34"/>
-      <c r="AP4" s="33"/>
+      <c r="AO4" s="34" t="n">
+        <f aca="false">AP5-AP2</f>
+        <v>0</v>
+      </c>
+      <c r="AP4" s="34" t="n">
+        <f aca="false">AQ5-AQ2</f>
+        <v>0</v>
+      </c>
       <c r="AQ4" s="35"/>
       <c r="AR4" s="35"/>
       <c r="AS4" s="33" t="n">
         <f aca="false">G11</f>
         <v>2</v>
       </c>
-      <c r="AT4" s="34"/>
-      <c r="AU4" s="33"/>
+      <c r="AT4" s="34" t="n">
+        <f aca="false">AU5-AU2</f>
+        <v>0</v>
+      </c>
+      <c r="AU4" s="34" t="n">
+        <f aca="false">AV5-AV2</f>
+        <v>0</v>
+      </c>
       <c r="AV4" s="35"/>
       <c r="AW4" s="35"/>
       <c r="AX4" s="33" t="n">
         <f aca="false">G13</f>
         <v>3</v>
       </c>
-      <c r="AY4" s="34"/>
-      <c r="AZ4" s="33"/>
+      <c r="AY4" s="34" t="n">
+        <f aca="false">AZ5-AZ2</f>
+        <v>0</v>
+      </c>
+      <c r="AZ4" s="34" t="n">
+        <f aca="false">BA5-BA2</f>
+        <v>0</v>
+      </c>
       <c r="BA4" s="35"/>
       <c r="BB4" s="35"/>
       <c r="BC4" s="33" t="n">
         <f aca="false">G14</f>
         <v>3</v>
       </c>
-      <c r="BD4" s="34"/>
-      <c r="BE4" s="33"/>
+      <c r="BD4" s="34" t="n">
+        <f aca="false">BE5-BE2</f>
+        <v>0</v>
+      </c>
+      <c r="BE4" s="34" t="n">
+        <f aca="false">BF5-BF2</f>
+        <v>0</v>
+      </c>
       <c r="BF4" s="35"/>
       <c r="BG4" s="35"/>
       <c r="BH4" s="33" t="n">
         <f aca="false">G15</f>
         <v>1</v>
       </c>
-      <c r="BI4" s="34"/>
-      <c r="BJ4" s="33"/>
+      <c r="BI4" s="34" t="n">
+        <f aca="false">BJ5-BJ2</f>
+        <v>0</v>
+      </c>
+      <c r="BJ4" s="34" t="n">
+        <f aca="false">BK5-BK2</f>
+        <v>0</v>
+      </c>
       <c r="BK4" s="35"/>
       <c r="BL4" s="35"/>
       <c r="BM4" s="33" t="n">
         <f aca="false">G16</f>
         <v>5</v>
       </c>
-      <c r="BN4" s="34"/>
-      <c r="BO4" s="33"/>
+      <c r="BN4" s="34" t="n">
+        <f aca="false">BO5-BO2</f>
+        <v>0</v>
+      </c>
+      <c r="BO4" s="33" t="n">
+        <f aca="false">BR2-BO2</f>
+        <v>0</v>
+      </c>
       <c r="BP4" s="35"/>
       <c r="BQ4" s="36"/>
       <c r="BR4" s="33" t="n">
         <f aca="false">G17</f>
         <v>1</v>
       </c>
-      <c r="BS4" s="34"/>
+      <c r="BS4" s="34" t="n">
+        <f aca="false">BT5-BT2</f>
+        <v>0</v>
+      </c>
       <c r="BT4" s="33"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2553,41 +2679,104 @@
         <v>0</v>
       </c>
       <c r="J5" s="28"/>
-      <c r="K5" s="27"/>
+      <c r="K5" s="27" t="n">
+        <f aca="false">MIN(N5,N17)</f>
+        <v>5</v>
+      </c>
       <c r="M5" s="37"/>
-      <c r="N5" s="27"/>
+      <c r="N5" s="27" t="n">
+        <f aca="false">P5-N4</f>
+        <v>5</v>
+      </c>
       <c r="O5" s="28"/>
-      <c r="P5" s="27"/>
+      <c r="P5" s="27" t="n">
+        <f aca="false">MIN(S11,S5)</f>
+        <v>6</v>
+      </c>
       <c r="R5" s="37"/>
-      <c r="S5" s="27"/>
+      <c r="S5" s="27" t="n">
+        <f aca="false">U5-S4</f>
+        <v>12</v>
+      </c>
       <c r="T5" s="28"/>
-      <c r="U5" s="27"/>
+      <c r="U5" s="27" t="n">
+        <f aca="false">AI5</f>
+        <v>16</v>
+      </c>
       <c r="AH5" s="37"/>
-      <c r="AI5" s="27"/>
+      <c r="AI5" s="27" t="n">
+        <f aca="false">AK5-AI4</f>
+        <v>16</v>
+      </c>
       <c r="AJ5" s="28"/>
-      <c r="AK5" s="27"/>
-      <c r="AN5" s="27"/>
+      <c r="AK5" s="27" t="n">
+        <f aca="false">AN5</f>
+        <v>18</v>
+      </c>
+      <c r="AN5" s="27" t="n">
+        <f aca="false">AP5-AN4</f>
+        <v>18</v>
+      </c>
       <c r="AO5" s="28"/>
-      <c r="AP5" s="27"/>
-      <c r="AS5" s="27"/>
+      <c r="AP5" s="27" t="n">
+        <f aca="false">AS5</f>
+        <v>20</v>
+      </c>
+      <c r="AS5" s="27" t="n">
+        <f aca="false">AU5-AS4</f>
+        <v>20</v>
+      </c>
       <c r="AT5" s="28"/>
-      <c r="AU5" s="27"/>
-      <c r="AX5" s="27"/>
+      <c r="AU5" s="27" t="n">
+        <f aca="false">AX5</f>
+        <v>22</v>
+      </c>
+      <c r="AX5" s="27" t="n">
+        <f aca="false">AZ5-AX4</f>
+        <v>22</v>
+      </c>
       <c r="AY5" s="28"/>
-      <c r="AZ5" s="27"/>
-      <c r="BC5" s="27"/>
+      <c r="AZ5" s="27" t="n">
+        <f aca="false">BC5</f>
+        <v>25</v>
+      </c>
+      <c r="BC5" s="27" t="n">
+        <f aca="false">BE5-BC4</f>
+        <v>25</v>
+      </c>
       <c r="BD5" s="28"/>
-      <c r="BE5" s="27"/>
-      <c r="BH5" s="27"/>
+      <c r="BE5" s="27" t="n">
+        <f aca="false">BH5</f>
+        <v>28</v>
+      </c>
+      <c r="BH5" s="27" t="n">
+        <f aca="false">BJ5-BH4</f>
+        <v>28</v>
+      </c>
       <c r="BI5" s="28"/>
-      <c r="BJ5" s="27"/>
-      <c r="BM5" s="27"/>
+      <c r="BJ5" s="27" t="n">
+        <f aca="false">BM5</f>
+        <v>29</v>
+      </c>
+      <c r="BM5" s="27" t="n">
+        <f aca="false">BO5-BM4</f>
+        <v>29</v>
+      </c>
       <c r="BN5" s="28"/>
-      <c r="BO5" s="27"/>
+      <c r="BO5" s="27" t="n">
+        <f aca="false">BR5</f>
+        <v>34</v>
+      </c>
       <c r="BQ5" s="37"/>
-      <c r="BR5" s="27"/>
+      <c r="BR5" s="27" t="n">
+        <f aca="false">BT5-BR4</f>
+        <v>34</v>
+      </c>
       <c r="BS5" s="28"/>
-      <c r="BT5" s="27"/>
+      <c r="BT5" s="27" t="n">
+        <f aca="false">BT2</f>
+        <v>35</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
@@ -2655,12 +2844,24 @@
       </c>
       <c r="M8" s="37"/>
       <c r="R8" s="37"/>
-      <c r="S8" s="27"/>
+      <c r="S8" s="27" t="n">
+        <f aca="false">P2</f>
+        <v>6</v>
+      </c>
       <c r="T8" s="28"/>
-      <c r="U8" s="27"/>
-      <c r="X8" s="27"/>
+      <c r="U8" s="27" t="n">
+        <f aca="false">S8+S10</f>
+        <v>9</v>
+      </c>
+      <c r="X8" s="27" t="n">
+        <f aca="false">U8</f>
+        <v>9</v>
+      </c>
       <c r="Y8" s="28"/>
-      <c r="Z8" s="27"/>
+      <c r="Z8" s="27" t="n">
+        <f aca="false">X8+X10</f>
+        <v>16</v>
+      </c>
       <c r="AH8" s="37"/>
       <c r="BQ8" s="37"/>
     </row>
@@ -2721,16 +2922,28 @@
         <f aca="false">G5</f>
         <v>3</v>
       </c>
-      <c r="T10" s="34"/>
-      <c r="U10" s="33"/>
+      <c r="T10" s="34" t="n">
+        <f aca="false">U11-U8</f>
+        <v>0</v>
+      </c>
+      <c r="U10" s="33" t="n">
+        <f aca="false">X8-U8</f>
+        <v>0</v>
+      </c>
       <c r="V10" s="35"/>
       <c r="W10" s="35"/>
       <c r="X10" s="33" t="n">
         <f aca="false">G6</f>
         <v>7</v>
       </c>
-      <c r="Y10" s="34"/>
-      <c r="Z10" s="33"/>
+      <c r="Y10" s="34" t="n">
+        <f aca="false">Z11-Z8</f>
+        <v>0</v>
+      </c>
+      <c r="Z10" s="33" t="n">
+        <f aca="false">AI2-Z8</f>
+        <v>0</v>
+      </c>
       <c r="AA10" s="35"/>
       <c r="AB10" s="35"/>
       <c r="AC10" s="35"/>
@@ -2760,12 +2973,24 @@
         <v>2</v>
       </c>
       <c r="M11" s="37"/>
-      <c r="S11" s="27"/>
+      <c r="S11" s="27" t="n">
+        <f aca="false">U11-S10</f>
+        <v>6</v>
+      </c>
       <c r="T11" s="28"/>
-      <c r="U11" s="27"/>
-      <c r="X11" s="27"/>
+      <c r="U11" s="27" t="n">
+        <f aca="false">X11</f>
+        <v>9</v>
+      </c>
+      <c r="X11" s="27" t="n">
+        <f aca="false">Z11-X10</f>
+        <v>9</v>
+      </c>
       <c r="Y11" s="28"/>
-      <c r="Z11" s="27"/>
+      <c r="Z11" s="27" t="n">
+        <f aca="false">AI5</f>
+        <v>16</v>
+      </c>
       <c r="AH11" s="37"/>
       <c r="BQ11" s="37"/>
     </row>
@@ -2834,16 +3059,34 @@
         <v>3</v>
       </c>
       <c r="M14" s="37"/>
-      <c r="N14" s="27"/>
+      <c r="N14" s="27" t="n">
+        <f aca="false">K2</f>
+        <v>5</v>
+      </c>
       <c r="O14" s="28"/>
-      <c r="P14" s="27"/>
-      <c r="S14" s="27"/>
+      <c r="P14" s="27" t="n">
+        <f aca="false">N14+N16</f>
+        <v>6</v>
+      </c>
+      <c r="S14" s="27" t="n">
+        <f aca="false">P14</f>
+        <v>6</v>
+      </c>
       <c r="T14" s="28"/>
-      <c r="U14" s="27"/>
+      <c r="U14" s="27" t="n">
+        <f aca="false">S14+S16</f>
+        <v>9</v>
+      </c>
       <c r="AH14" s="37"/>
-      <c r="AI14" s="27"/>
+      <c r="AI14" s="27" t="n">
+        <f aca="false">U14</f>
+        <v>9</v>
+      </c>
       <c r="AJ14" s="28"/>
-      <c r="AK14" s="27"/>
+      <c r="AK14" s="27" t="n">
+        <f aca="false">AI14+AI16</f>
+        <v>19</v>
+      </c>
       <c r="BQ14" s="37"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2918,16 +3161,28 @@
         <f aca="false">G7</f>
         <v>1</v>
       </c>
-      <c r="O16" s="34"/>
-      <c r="P16" s="33"/>
+      <c r="O16" s="34" t="n">
+        <f aca="false">P17-P14</f>
+        <v>7</v>
+      </c>
+      <c r="P16" s="33" t="n">
+        <f aca="false">S14-P14</f>
+        <v>0</v>
+      </c>
       <c r="Q16" s="35"/>
       <c r="R16" s="35"/>
       <c r="S16" s="33" t="n">
         <f aca="false">G8</f>
         <v>3</v>
       </c>
-      <c r="T16" s="34"/>
-      <c r="U16" s="33"/>
+      <c r="T16" s="34" t="n">
+        <f aca="false">U17-U14</f>
+        <v>7</v>
+      </c>
+      <c r="U16" s="33" t="n">
+        <f aca="false">MIN(AI14,AI2)-U14</f>
+        <v>0</v>
+      </c>
       <c r="V16" s="35"/>
       <c r="W16" s="35"/>
       <c r="X16" s="35"/>
@@ -2945,8 +3200,14 @@
         <f aca="false">G12</f>
         <v>10</v>
       </c>
-      <c r="AJ16" s="34"/>
-      <c r="AK16" s="33"/>
+      <c r="AJ16" s="34" t="n">
+        <f aca="false">AK17-AK14</f>
+        <v>15</v>
+      </c>
+      <c r="AK16" s="33" t="n">
+        <f aca="false">BR2-AK14</f>
+        <v>15</v>
+      </c>
       <c r="AL16" s="35"/>
       <c r="AM16" s="35"/>
       <c r="AN16" s="35"/>
@@ -2995,15 +3256,33 @@
       <c r="G17" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="N17" s="27"/>
+      <c r="N17" s="27" t="n">
+        <f aca="false">P17-N16</f>
+        <v>12</v>
+      </c>
       <c r="O17" s="28"/>
-      <c r="P17" s="27"/>
-      <c r="S17" s="27"/>
+      <c r="P17" s="27" t="n">
+        <f aca="false">S17</f>
+        <v>13</v>
+      </c>
+      <c r="S17" s="27" t="n">
+        <f aca="false">U17-S16</f>
+        <v>13</v>
+      </c>
       <c r="T17" s="28"/>
-      <c r="U17" s="27"/>
-      <c r="AI17" s="27"/>
+      <c r="U17" s="27" t="n">
+        <f aca="false">MIN(AI5,AI17)</f>
+        <v>16</v>
+      </c>
+      <c r="AI17" s="27" t="n">
+        <f aca="false">AK17-AI16</f>
+        <v>24</v>
+      </c>
       <c r="AJ17" s="28"/>
-      <c r="AK17" s="27"/>
+      <c r="AK17" s="27" t="n">
+        <f aca="false">BR5</f>
+        <v>34</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="45" t="s">
@@ -3182,7 +3461,7 @@
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="C33:D33"/>
   </mergeCells>
-  <conditionalFormatting sqref="C21 C26 S10:T10 T4 O4 J4 O16 T16 AJ16 Y10 AJ4 AO4 AT4 AY4 BD4 BI4 BN4 BS4">
+  <conditionalFormatting sqref="C21 C26 S10:T10 BS4 BN4 BI4:BJ4 BD4:BE4 AY4:AZ4 AT4:AU4 AO4:AP4 AJ4:AK4 AJ16 Y10 T16 T4 O16 O4 J4">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>

--- a/Übungen/Online_Shop.xlsx
+++ b/Übungen/Online_Shop.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="75">
   <si>
     <t xml:space="preserve">Beispiel: Funktionsorientierter Projektstrukturplan</t>
   </si>
@@ -166,6 +166,15 @@
   </si>
   <si>
     <t xml:space="preserve">Nachfolger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aufwand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kapazität</t>
   </si>
   <si>
     <t xml:space="preserve">Dauer</t>
@@ -2259,15 +2268,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BT35"/>
+  <dimension ref="A1:BW35"/>
   <sheetFormatPr defaultColWidth="11.82421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="20" width="11.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="16.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="3" width="11.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="104" min="8" style="0" width="3.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1022" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="6" style="3" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="107" min="11" style="0" width="3.83"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2288,6 +2296,15 @@
       <c r="G1" s="22" t="s">
         <v>48</v>
       </c>
+      <c r="H1" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="I1" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" s="22" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
@@ -2300,107 +2317,112 @@
       <c r="D2" s="23"/>
       <c r="E2" s="24"/>
       <c r="F2" s="25" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G2" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="I2" s="27" t="n">
+      <c r="H2" s="26"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="L2" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="28"/>
-      <c r="K2" s="27" t="n">
-        <f aca="false">I2+I4</f>
+      <c r="M2" s="28"/>
+      <c r="N2" s="27" t="n">
+        <f aca="false">L2+L4</f>
         <v>5</v>
       </c>
-      <c r="N2" s="27" t="n">
-        <f aca="false">K2</f>
+      <c r="Q2" s="27" t="n">
+        <f aca="false">N2</f>
         <v>5</v>
       </c>
-      <c r="O2" s="28"/>
-      <c r="P2" s="27" t="n">
-        <f aca="false">N2+N4</f>
+      <c r="R2" s="28"/>
+      <c r="S2" s="27" t="n">
+        <f aca="false">Q2+Q4</f>
         <v>6</v>
       </c>
-      <c r="S2" s="27" t="n">
-        <f aca="false">P2</f>
+      <c r="V2" s="27" t="n">
+        <f aca="false">S2</f>
         <v>6</v>
       </c>
-      <c r="T2" s="28"/>
-      <c r="U2" s="27" t="n">
-        <f aca="false">S2+S4</f>
+      <c r="W2" s="28"/>
+      <c r="X2" s="27" t="n">
+        <f aca="false">V2+V4</f>
         <v>10</v>
       </c>
-      <c r="AI2" s="27" t="n">
-        <f aca="false">MAX(U2,Z8,U14)</f>
+      <c r="AL2" s="27" t="n">
+        <f aca="false">MAX(X2,AC8,X14)</f>
         <v>16</v>
       </c>
-      <c r="AJ2" s="28"/>
-      <c r="AK2" s="27" t="n">
-        <f aca="false">AI2+AI4</f>
+      <c r="AM2" s="28"/>
+      <c r="AN2" s="27" t="n">
+        <f aca="false">AL2+AL4</f>
         <v>18</v>
       </c>
-      <c r="AN2" s="27" t="n">
-        <f aca="false">AK2</f>
+      <c r="AQ2" s="27" t="n">
+        <f aca="false">AN2</f>
         <v>18</v>
       </c>
-      <c r="AO2" s="28"/>
-      <c r="AP2" s="27" t="n">
-        <f aca="false">AN2+AN4</f>
+      <c r="AR2" s="28"/>
+      <c r="AS2" s="27" t="n">
+        <f aca="false">AQ2+AQ4</f>
         <v>20</v>
       </c>
-      <c r="AS2" s="27" t="n">
-        <f aca="false">AP2</f>
+      <c r="AV2" s="27" t="n">
+        <f aca="false">AS2</f>
         <v>20</v>
       </c>
-      <c r="AT2" s="28"/>
-      <c r="AU2" s="27" t="n">
-        <f aca="false">AS2+AS4</f>
+      <c r="AW2" s="28"/>
+      <c r="AX2" s="27" t="n">
+        <f aca="false">AV2+AV4</f>
         <v>22</v>
       </c>
-      <c r="AX2" s="27" t="n">
-        <f aca="false">AU2</f>
+      <c r="BA2" s="27" t="n">
+        <f aca="false">AX2</f>
         <v>22</v>
       </c>
-      <c r="AY2" s="28"/>
-      <c r="AZ2" s="27" t="n">
-        <f aca="false">AX2+AX4</f>
+      <c r="BB2" s="28"/>
+      <c r="BC2" s="27" t="n">
+        <f aca="false">BA2+BA4</f>
         <v>25</v>
       </c>
-      <c r="BC2" s="27" t="n">
-        <f aca="false">AZ2</f>
+      <c r="BF2" s="27" t="n">
+        <f aca="false">BC2</f>
         <v>25</v>
       </c>
-      <c r="BD2" s="28"/>
-      <c r="BE2" s="27" t="n">
-        <f aca="false">BC2+BC4</f>
+      <c r="BG2" s="28"/>
+      <c r="BH2" s="27" t="n">
+        <f aca="false">BF2+BF4</f>
         <v>28</v>
       </c>
-      <c r="BH2" s="27" t="n">
-        <f aca="false">BE2</f>
+      <c r="BK2" s="27" t="n">
+        <f aca="false">BH2</f>
         <v>28</v>
       </c>
-      <c r="BI2" s="28"/>
-      <c r="BJ2" s="27" t="n">
-        <f aca="false">BH2+BH4</f>
+      <c r="BL2" s="28"/>
+      <c r="BM2" s="27" t="n">
+        <f aca="false">BK2+BK4</f>
         <v>29</v>
       </c>
-      <c r="BM2" s="27" t="n">
-        <f aca="false">BJ2</f>
+      <c r="BP2" s="27" t="n">
+        <f aca="false">BM2</f>
         <v>29</v>
       </c>
-      <c r="BN2" s="28"/>
-      <c r="BO2" s="27" t="n">
-        <f aca="false">BM2+BM4</f>
+      <c r="BQ2" s="28"/>
+      <c r="BR2" s="27" t="n">
+        <f aca="false">BP2+BP4</f>
         <v>34</v>
       </c>
-      <c r="BR2" s="27" t="n">
-        <f aca="false">MAX(BO2,AK14)</f>
+      <c r="BU2" s="27" t="n">
+        <f aca="false">MAX(BR2,AN14)</f>
         <v>34</v>
       </c>
-      <c r="BS2" s="28"/>
-      <c r="BT2" s="27" t="n">
-        <f aca="false">BR2+BR4</f>
+      <c r="BV2" s="28"/>
+      <c r="BW2" s="27" t="n">
+        <f aca="false">BU2+BU4</f>
         <v>35</v>
       </c>
     </row>
@@ -2417,66 +2439,71 @@
         <v>16</v>
       </c>
       <c r="F3" s="30" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G3" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="I3" s="32" t="s">
+      <c r="H3" s="31"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="32"/>
-      <c r="K3" s="32"/>
-      <c r="N3" s="32" t="s">
+      <c r="M3" s="32"/>
+      <c r="N3" s="32"/>
+      <c r="Q3" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="O3" s="32"/>
-      <c r="P3" s="32"/>
-      <c r="S3" s="32" t="s">
+      <c r="R3" s="32"/>
+      <c r="S3" s="32"/>
+      <c r="V3" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="T3" s="32"/>
-      <c r="U3" s="32"/>
-      <c r="AI3" s="32" t="s">
+      <c r="W3" s="32"/>
+      <c r="X3" s="32"/>
+      <c r="AL3" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="AJ3" s="32"/>
-      <c r="AK3" s="32"/>
-      <c r="AN3" s="32" t="s">
+      <c r="AM3" s="32"/>
+      <c r="AN3" s="32"/>
+      <c r="AQ3" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="AO3" s="32"/>
-      <c r="AP3" s="32"/>
-      <c r="AS3" s="32" t="s">
+      <c r="AR3" s="32"/>
+      <c r="AS3" s="32"/>
+      <c r="AV3" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="AT3" s="32"/>
-      <c r="AU3" s="32"/>
-      <c r="AX3" s="32" t="s">
+      <c r="AW3" s="32"/>
+      <c r="AX3" s="32"/>
+      <c r="BA3" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="AY3" s="32"/>
-      <c r="AZ3" s="32"/>
-      <c r="BC3" s="32" t="s">
+      <c r="BB3" s="32"/>
+      <c r="BC3" s="32"/>
+      <c r="BF3" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="BD3" s="32"/>
-      <c r="BE3" s="32"/>
-      <c r="BH3" s="32" t="s">
+      <c r="BG3" s="32"/>
+      <c r="BH3" s="32"/>
+      <c r="BK3" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="BI3" s="32"/>
-      <c r="BJ3" s="32"/>
-      <c r="BM3" s="32" t="s">
+      <c r="BL3" s="32"/>
+      <c r="BM3" s="32"/>
+      <c r="BP3" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="BN3" s="32"/>
-      <c r="BO3" s="32"/>
-      <c r="BR3" s="32" t="s">
+      <c r="BQ3" s="32"/>
+      <c r="BR3" s="32"/>
+      <c r="BU3" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="BS3" s="32"/>
-      <c r="BT3" s="32"/>
+      <c r="BV3" s="32"/>
+      <c r="BW3" s="32"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
@@ -2496,49 +2523,51 @@
       <c r="G4" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="I4" s="33" t="n">
-        <f aca="false">G2</f>
+      <c r="H4" s="31"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="L4" s="33" t="n">
+        <f aca="false">J2</f>
         <v>5</v>
       </c>
-      <c r="J4" s="34" t="n">
-        <f aca="false">K5-K2</f>
+      <c r="M4" s="34" t="n">
+        <f aca="false">N5-N2</f>
         <v>0</v>
       </c>
-      <c r="K4" s="33" t="n">
-        <f aca="false">MIN(N2,N14)-K2</f>
+      <c r="N4" s="33" t="n">
+        <f aca="false">MIN(Q2,Q14)-N2</f>
         <v>0</v>
       </c>
-      <c r="L4" s="35"/>
-      <c r="M4" s="36"/>
-      <c r="N4" s="33" t="n">
-        <f aca="false">G3</f>
+      <c r="O4" s="35"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="33" t="n">
+        <f aca="false">J3</f>
         <v>1</v>
       </c>
-      <c r="O4" s="34" t="n">
-        <f aca="false">P5-P2</f>
+      <c r="R4" s="34" t="n">
+        <f aca="false">S5-S2</f>
         <v>0</v>
       </c>
-      <c r="P4" s="33" t="n">
-        <f aca="false">S2-P2</f>
+      <c r="S4" s="33" t="n">
+        <f aca="false">V2-S2</f>
         <v>0</v>
       </c>
-      <c r="Q4" s="35"/>
-      <c r="R4" s="36"/>
-      <c r="S4" s="33" t="n">
-        <f aca="false">G4</f>
+      <c r="T4" s="35"/>
+      <c r="U4" s="36"/>
+      <c r="V4" s="33" t="n">
+        <f aca="false">J4</f>
         <v>4</v>
       </c>
-      <c r="T4" s="34" t="n">
-        <f aca="false">U5-U2</f>
+      <c r="W4" s="34" t="n">
+        <f aca="false">X5-X2</f>
         <v>6</v>
       </c>
-      <c r="U4" s="33" t="n">
-        <f aca="false">AI2-U2</f>
+      <c r="X4" s="33" t="n">
+        <f aca="false">AL2-X2</f>
         <v>6</v>
       </c>
-      <c r="V4" s="35"/>
-      <c r="W4" s="35"/>
-      <c r="X4" s="35"/>
       <c r="Y4" s="35"/>
       <c r="Z4" s="35"/>
       <c r="AA4" s="35"/>
@@ -2548,114 +2577,117 @@
       <c r="AE4" s="35"/>
       <c r="AF4" s="35"/>
       <c r="AG4" s="35"/>
-      <c r="AH4" s="36"/>
-      <c r="AI4" s="33" t="n">
-        <f aca="false">G9</f>
+      <c r="AH4" s="35"/>
+      <c r="AI4" s="35"/>
+      <c r="AJ4" s="35"/>
+      <c r="AK4" s="36"/>
+      <c r="AL4" s="33" t="n">
+        <f aca="false">J9</f>
         <v>2</v>
       </c>
-      <c r="AJ4" s="34" t="n">
-        <f aca="false">AK5-AK2</f>
+      <c r="AM4" s="34" t="n">
+        <f aca="false">AN5-AN2</f>
         <v>0</v>
       </c>
-      <c r="AK4" s="34" t="n">
-        <f aca="false">AL5-AL2</f>
+      <c r="AN4" s="34" t="n">
+        <f aca="false">AO5-AO2</f>
         <v>0</v>
       </c>
-      <c r="AL4" s="35"/>
-      <c r="AM4" s="35"/>
-      <c r="AN4" s="33" t="n">
-        <f aca="false">G10</f>
+      <c r="AO4" s="35"/>
+      <c r="AP4" s="35"/>
+      <c r="AQ4" s="33" t="n">
+        <f aca="false">J10</f>
         <v>2</v>
       </c>
-      <c r="AO4" s="34" t="n">
-        <f aca="false">AP5-AP2</f>
+      <c r="AR4" s="34" t="n">
+        <f aca="false">AS5-AS2</f>
         <v>0</v>
       </c>
-      <c r="AP4" s="34" t="n">
-        <f aca="false">AQ5-AQ2</f>
+      <c r="AS4" s="34" t="n">
+        <f aca="false">AT5-AT2</f>
         <v>0</v>
       </c>
-      <c r="AQ4" s="35"/>
-      <c r="AR4" s="35"/>
-      <c r="AS4" s="33" t="n">
-        <f aca="false">G11</f>
+      <c r="AT4" s="35"/>
+      <c r="AU4" s="35"/>
+      <c r="AV4" s="33" t="n">
+        <f aca="false">J11</f>
         <v>2</v>
       </c>
-      <c r="AT4" s="34" t="n">
-        <f aca="false">AU5-AU2</f>
+      <c r="AW4" s="34" t="n">
+        <f aca="false">AX5-AX2</f>
         <v>0</v>
       </c>
-      <c r="AU4" s="34" t="n">
-        <f aca="false">AV5-AV2</f>
+      <c r="AX4" s="34" t="n">
+        <f aca="false">AY5-AY2</f>
         <v>0</v>
       </c>
-      <c r="AV4" s="35"/>
-      <c r="AW4" s="35"/>
-      <c r="AX4" s="33" t="n">
-        <f aca="false">G13</f>
+      <c r="AY4" s="35"/>
+      <c r="AZ4" s="35"/>
+      <c r="BA4" s="33" t="n">
+        <f aca="false">J13</f>
         <v>3</v>
       </c>
-      <c r="AY4" s="34" t="n">
-        <f aca="false">AZ5-AZ2</f>
+      <c r="BB4" s="34" t="n">
+        <f aca="false">BC5-BC2</f>
         <v>0</v>
       </c>
-      <c r="AZ4" s="34" t="n">
-        <f aca="false">BA5-BA2</f>
+      <c r="BC4" s="34" t="n">
+        <f aca="false">BD5-BD2</f>
         <v>0</v>
       </c>
-      <c r="BA4" s="35"/>
-      <c r="BB4" s="35"/>
-      <c r="BC4" s="33" t="n">
-        <f aca="false">G14</f>
+      <c r="BD4" s="35"/>
+      <c r="BE4" s="35"/>
+      <c r="BF4" s="33" t="n">
+        <f aca="false">J14</f>
         <v>3</v>
       </c>
-      <c r="BD4" s="34" t="n">
-        <f aca="false">BE5-BE2</f>
+      <c r="BG4" s="34" t="n">
+        <f aca="false">BH5-BH2</f>
         <v>0</v>
       </c>
-      <c r="BE4" s="34" t="n">
-        <f aca="false">BF5-BF2</f>
+      <c r="BH4" s="34" t="n">
+        <f aca="false">BI5-BI2</f>
         <v>0</v>
       </c>
-      <c r="BF4" s="35"/>
-      <c r="BG4" s="35"/>
-      <c r="BH4" s="33" t="n">
-        <f aca="false">G15</f>
+      <c r="BI4" s="35"/>
+      <c r="BJ4" s="35"/>
+      <c r="BK4" s="33" t="n">
+        <f aca="false">J15</f>
         <v>1</v>
       </c>
-      <c r="BI4" s="34" t="n">
-        <f aca="false">BJ5-BJ2</f>
+      <c r="BL4" s="34" t="n">
+        <f aca="false">BM5-BM2</f>
         <v>0</v>
       </c>
-      <c r="BJ4" s="34" t="n">
-        <f aca="false">BK5-BK2</f>
+      <c r="BM4" s="34" t="n">
+        <f aca="false">BN5-BN2</f>
         <v>0</v>
       </c>
-      <c r="BK4" s="35"/>
-      <c r="BL4" s="35"/>
-      <c r="BM4" s="33" t="n">
-        <f aca="false">G16</f>
+      <c r="BN4" s="35"/>
+      <c r="BO4" s="35"/>
+      <c r="BP4" s="33" t="n">
+        <f aca="false">J16</f>
         <v>5</v>
       </c>
-      <c r="BN4" s="34" t="n">
-        <f aca="false">BO5-BO2</f>
+      <c r="BQ4" s="34" t="n">
+        <f aca="false">BR5-BR2</f>
         <v>0</v>
       </c>
-      <c r="BO4" s="33" t="n">
-        <f aca="false">BR2-BO2</f>
+      <c r="BR4" s="33" t="n">
+        <f aca="false">BU2-BR2</f>
         <v>0</v>
       </c>
-      <c r="BP4" s="35"/>
-      <c r="BQ4" s="36"/>
-      <c r="BR4" s="33" t="n">
-        <f aca="false">G17</f>
+      <c r="BS4" s="35"/>
+      <c r="BT4" s="36"/>
+      <c r="BU4" s="33" t="n">
+        <f aca="false">J17</f>
         <v>1</v>
       </c>
-      <c r="BS4" s="34" t="n">
-        <f aca="false">BT5-BT2</f>
+      <c r="BV4" s="34" t="n">
+        <f aca="false">BW5-BW2</f>
         <v>0</v>
       </c>
-      <c r="BT4" s="33"/>
+      <c r="BW4" s="33"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
@@ -2675,106 +2707,111 @@
       <c r="G5" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="I5" s="27" t="n">
+      <c r="H5" s="31"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="28"/>
-      <c r="K5" s="27" t="n">
-        <f aca="false">MIN(N5,N17)</f>
+      <c r="M5" s="28"/>
+      <c r="N5" s="27" t="n">
+        <f aca="false">MIN(Q5,Q17)</f>
         <v>5</v>
       </c>
-      <c r="M5" s="37"/>
-      <c r="N5" s="27" t="n">
-        <f aca="false">P5-N4</f>
+      <c r="P5" s="37"/>
+      <c r="Q5" s="27" t="n">
+        <f aca="false">S5-Q4</f>
         <v>5</v>
       </c>
-      <c r="O5" s="28"/>
-      <c r="P5" s="27" t="n">
-        <f aca="false">MIN(S11,S5)</f>
+      <c r="R5" s="28"/>
+      <c r="S5" s="27" t="n">
+        <f aca="false">MIN(V11,V5)</f>
         <v>6</v>
       </c>
-      <c r="R5" s="37"/>
-      <c r="S5" s="27" t="n">
-        <f aca="false">U5-S4</f>
+      <c r="U5" s="37"/>
+      <c r="V5" s="27" t="n">
+        <f aca="false">X5-V4</f>
         <v>12</v>
       </c>
-      <c r="T5" s="28"/>
-      <c r="U5" s="27" t="n">
-        <f aca="false">AI5</f>
+      <c r="W5" s="28"/>
+      <c r="X5" s="27" t="n">
+        <f aca="false">AL5</f>
         <v>16</v>
       </c>
-      <c r="AH5" s="37"/>
-      <c r="AI5" s="27" t="n">
-        <f aca="false">AK5-AI4</f>
+      <c r="AK5" s="37"/>
+      <c r="AL5" s="27" t="n">
+        <f aca="false">AN5-AL4</f>
         <v>16</v>
       </c>
-      <c r="AJ5" s="28"/>
-      <c r="AK5" s="27" t="n">
-        <f aca="false">AN5</f>
+      <c r="AM5" s="28"/>
+      <c r="AN5" s="27" t="n">
+        <f aca="false">AQ5</f>
         <v>18</v>
       </c>
-      <c r="AN5" s="27" t="n">
-        <f aca="false">AP5-AN4</f>
+      <c r="AQ5" s="27" t="n">
+        <f aca="false">AS5-AQ4</f>
         <v>18</v>
       </c>
-      <c r="AO5" s="28"/>
-      <c r="AP5" s="27" t="n">
-        <f aca="false">AS5</f>
+      <c r="AR5" s="28"/>
+      <c r="AS5" s="27" t="n">
+        <f aca="false">AV5</f>
         <v>20</v>
       </c>
-      <c r="AS5" s="27" t="n">
-        <f aca="false">AU5-AS4</f>
+      <c r="AV5" s="27" t="n">
+        <f aca="false">AX5-AV4</f>
         <v>20</v>
       </c>
-      <c r="AT5" s="28"/>
-      <c r="AU5" s="27" t="n">
-        <f aca="false">AX5</f>
+      <c r="AW5" s="28"/>
+      <c r="AX5" s="27" t="n">
+        <f aca="false">BA5</f>
         <v>22</v>
       </c>
-      <c r="AX5" s="27" t="n">
-        <f aca="false">AZ5-AX4</f>
+      <c r="BA5" s="27" t="n">
+        <f aca="false">BC5-BA4</f>
         <v>22</v>
       </c>
-      <c r="AY5" s="28"/>
-      <c r="AZ5" s="27" t="n">
-        <f aca="false">BC5</f>
+      <c r="BB5" s="28"/>
+      <c r="BC5" s="27" t="n">
+        <f aca="false">BF5</f>
         <v>25</v>
       </c>
-      <c r="BC5" s="27" t="n">
-        <f aca="false">BE5-BC4</f>
+      <c r="BF5" s="27" t="n">
+        <f aca="false">BH5-BF4</f>
         <v>25</v>
       </c>
-      <c r="BD5" s="28"/>
-      <c r="BE5" s="27" t="n">
-        <f aca="false">BH5</f>
+      <c r="BG5" s="28"/>
+      <c r="BH5" s="27" t="n">
+        <f aca="false">BK5</f>
         <v>28</v>
       </c>
-      <c r="BH5" s="27" t="n">
-        <f aca="false">BJ5-BH4</f>
+      <c r="BK5" s="27" t="n">
+        <f aca="false">BM5-BK4</f>
         <v>28</v>
       </c>
-      <c r="BI5" s="28"/>
-      <c r="BJ5" s="27" t="n">
-        <f aca="false">BM5</f>
+      <c r="BL5" s="28"/>
+      <c r="BM5" s="27" t="n">
+        <f aca="false">BP5</f>
         <v>29</v>
       </c>
-      <c r="BM5" s="27" t="n">
-        <f aca="false">BO5-BM4</f>
+      <c r="BP5" s="27" t="n">
+        <f aca="false">BR5-BP4</f>
         <v>29</v>
       </c>
-      <c r="BN5" s="28"/>
-      <c r="BO5" s="27" t="n">
-        <f aca="false">BR5</f>
+      <c r="BQ5" s="28"/>
+      <c r="BR5" s="27" t="n">
+        <f aca="false">BU5</f>
         <v>34</v>
       </c>
-      <c r="BQ5" s="37"/>
-      <c r="BR5" s="27" t="n">
-        <f aca="false">BT5-BR4</f>
+      <c r="BT5" s="37"/>
+      <c r="BU5" s="27" t="n">
+        <f aca="false">BW5-BU4</f>
         <v>34</v>
       </c>
-      <c r="BS5" s="28"/>
-      <c r="BT5" s="27" t="n">
-        <f aca="false">BT2</f>
+      <c r="BV5" s="28"/>
+      <c r="BW5" s="27" t="n">
+        <f aca="false">BW2</f>
         <v>35</v>
       </c>
     </row>
@@ -2796,10 +2833,15 @@
       <c r="G6" s="39" t="n">
         <v>7</v>
       </c>
-      <c r="M6" s="37"/>
-      <c r="R6" s="37"/>
-      <c r="AH6" s="37"/>
-      <c r="BQ6" s="37"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="38"/>
+      <c r="J6" s="39" t="n">
+        <v>7</v>
+      </c>
+      <c r="P6" s="37"/>
+      <c r="U6" s="37"/>
+      <c r="AK6" s="37"/>
+      <c r="BT6" s="37"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
@@ -2819,10 +2861,15 @@
       <c r="G7" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="M7" s="37"/>
-      <c r="R7" s="37"/>
-      <c r="AH7" s="37"/>
-      <c r="BQ7" s="37"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" s="37"/>
+      <c r="U7" s="37"/>
+      <c r="AK7" s="37"/>
+      <c r="BT7" s="37"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
@@ -2837,33 +2884,38 @@
         <v>22</v>
       </c>
       <c r="F8" s="38" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G8" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="M8" s="37"/>
-      <c r="R8" s="37"/>
-      <c r="S8" s="27" t="n">
-        <f aca="false">P2</f>
+      <c r="H8" s="39"/>
+      <c r="I8" s="38"/>
+      <c r="J8" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="P8" s="37"/>
+      <c r="U8" s="37"/>
+      <c r="V8" s="27" t="n">
+        <f aca="false">S2</f>
         <v>6</v>
       </c>
-      <c r="T8" s="28"/>
-      <c r="U8" s="27" t="n">
-        <f aca="false">S8+S10</f>
+      <c r="W8" s="28"/>
+      <c r="X8" s="27" t="n">
+        <f aca="false">V8+V10</f>
         <v>9</v>
       </c>
-      <c r="X8" s="27" t="n">
-        <f aca="false">U8</f>
+      <c r="AA8" s="27" t="n">
+        <f aca="false">X8</f>
         <v>9</v>
       </c>
-      <c r="Y8" s="28"/>
-      <c r="Z8" s="27" t="n">
-        <f aca="false">X8+X10</f>
+      <c r="AB8" s="28"/>
+      <c r="AC8" s="27" t="n">
+        <f aca="false">AA8+AA10</f>
         <v>16</v>
       </c>
-      <c r="AH8" s="37"/>
-      <c r="BQ8" s="37"/>
+      <c r="AK8" s="37"/>
+      <c r="BT8" s="37"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
@@ -2875,7 +2927,7 @@
       <c r="C9" s="29"/>
       <c r="D9" s="29"/>
       <c r="E9" s="38" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F9" s="38" t="s">
         <v>35</v>
@@ -2883,20 +2935,25 @@
       <c r="G9" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="M9" s="37"/>
-      <c r="R9" s="37"/>
-      <c r="S9" s="32" t="s">
+      <c r="H9" s="39"/>
+      <c r="I9" s="38"/>
+      <c r="J9" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="P9" s="37"/>
+      <c r="U9" s="37"/>
+      <c r="V9" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="T9" s="32"/>
-      <c r="U9" s="32"/>
-      <c r="X9" s="32" t="s">
+      <c r="W9" s="32"/>
+      <c r="X9" s="32"/>
+      <c r="AA9" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="Y9" s="32"/>
-      <c r="Z9" s="32"/>
-      <c r="AH9" s="37"/>
-      <c r="BQ9" s="37"/>
+      <c r="AB9" s="32"/>
+      <c r="AC9" s="32"/>
+      <c r="AK9" s="37"/>
+      <c r="BT9" s="37"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
@@ -2916,43 +2973,48 @@
       <c r="G10" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="M10" s="37"/>
-      <c r="R10" s="35"/>
-      <c r="S10" s="33" t="n">
-        <f aca="false">G5</f>
+      <c r="H10" s="39"/>
+      <c r="I10" s="38"/>
+      <c r="J10" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="P10" s="37"/>
+      <c r="U10" s="35"/>
+      <c r="V10" s="33" t="n">
+        <f aca="false">J5</f>
         <v>3</v>
       </c>
-      <c r="T10" s="34" t="n">
-        <f aca="false">U11-U8</f>
+      <c r="W10" s="34" t="n">
+        <f aca="false">X11-X8</f>
         <v>0</v>
       </c>
-      <c r="U10" s="33" t="n">
-        <f aca="false">X8-U8</f>
+      <c r="X10" s="33" t="n">
+        <f aca="false">AA8-X8</f>
         <v>0</v>
       </c>
-      <c r="V10" s="35"/>
-      <c r="W10" s="35"/>
-      <c r="X10" s="33" t="n">
-        <f aca="false">G6</f>
+      <c r="Y10" s="35"/>
+      <c r="Z10" s="35"/>
+      <c r="AA10" s="33" t="n">
+        <f aca="false">J6</f>
         <v>7</v>
       </c>
-      <c r="Y10" s="34" t="n">
-        <f aca="false">Z11-Z8</f>
+      <c r="AB10" s="34" t="n">
+        <f aca="false">AC11-AC8</f>
         <v>0</v>
       </c>
-      <c r="Z10" s="33" t="n">
-        <f aca="false">AI2-Z8</f>
+      <c r="AC10" s="33" t="n">
+        <f aca="false">AL2-AC8</f>
         <v>0</v>
       </c>
-      <c r="AA10" s="35"/>
-      <c r="AB10" s="35"/>
-      <c r="AC10" s="35"/>
       <c r="AD10" s="35"/>
       <c r="AE10" s="35"/>
       <c r="AF10" s="35"/>
       <c r="AG10" s="35"/>
-      <c r="AH10" s="37"/>
-      <c r="BQ10" s="37"/>
+      <c r="AH10" s="35"/>
+      <c r="AI10" s="35"/>
+      <c r="AJ10" s="35"/>
+      <c r="AK10" s="37"/>
+      <c r="BT10" s="37"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
@@ -2972,34 +3034,39 @@
       <c r="G11" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="M11" s="37"/>
-      <c r="S11" s="27" t="n">
-        <f aca="false">U11-S10</f>
+      <c r="H11" s="39"/>
+      <c r="I11" s="38"/>
+      <c r="J11" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="P11" s="37"/>
+      <c r="V11" s="27" t="n">
+        <f aca="false">X11-V10</f>
         <v>6</v>
       </c>
-      <c r="T11" s="28"/>
-      <c r="U11" s="27" t="n">
-        <f aca="false">X11</f>
+      <c r="W11" s="28"/>
+      <c r="X11" s="27" t="n">
+        <f aca="false">AA11</f>
         <v>9</v>
       </c>
-      <c r="X11" s="27" t="n">
-        <f aca="false">Z11-X10</f>
+      <c r="AA11" s="27" t="n">
+        <f aca="false">AC11-AA10</f>
         <v>9</v>
       </c>
-      <c r="Y11" s="28"/>
-      <c r="Z11" s="27" t="n">
-        <f aca="false">AI5</f>
+      <c r="AB11" s="28"/>
+      <c r="AC11" s="27" t="n">
+        <f aca="false">AL5</f>
         <v>16</v>
       </c>
-      <c r="AH11" s="37"/>
-      <c r="BQ11" s="37"/>
+      <c r="AK11" s="37"/>
+      <c r="BT11" s="37"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
         <v>17</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C12" s="29"/>
       <c r="D12" s="29"/>
@@ -3012,10 +3079,15 @@
       <c r="G12" s="39" t="n">
         <v>10</v>
       </c>
-      <c r="M12" s="37"/>
-      <c r="X12" s="40"/>
-      <c r="AH12" s="37"/>
-      <c r="BQ12" s="37"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="38"/>
+      <c r="J12" s="39" t="n">
+        <v>10</v>
+      </c>
+      <c r="P12" s="37"/>
+      <c r="AA12" s="40"/>
+      <c r="AK12" s="37"/>
+      <c r="BT12" s="37"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
@@ -3035,10 +3107,15 @@
       <c r="G13" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="M13" s="37"/>
-      <c r="X13" s="40"/>
-      <c r="AH13" s="37"/>
-      <c r="BQ13" s="37"/>
+      <c r="H13" s="39"/>
+      <c r="I13" s="38"/>
+      <c r="J13" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="P13" s="37"/>
+      <c r="AA13" s="40"/>
+      <c r="AK13" s="37"/>
+      <c r="BT13" s="37"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
@@ -3058,36 +3135,41 @@
       <c r="G14" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="M14" s="37"/>
-      <c r="N14" s="27" t="n">
-        <f aca="false">K2</f>
+      <c r="H14" s="39"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="P14" s="37"/>
+      <c r="Q14" s="27" t="n">
+        <f aca="false">N2</f>
         <v>5</v>
       </c>
-      <c r="O14" s="28"/>
-      <c r="P14" s="27" t="n">
-        <f aca="false">N14+N16</f>
+      <c r="R14" s="28"/>
+      <c r="S14" s="27" t="n">
+        <f aca="false">Q14+Q16</f>
         <v>6</v>
       </c>
-      <c r="S14" s="27" t="n">
-        <f aca="false">P14</f>
+      <c r="V14" s="27" t="n">
+        <f aca="false">S14</f>
         <v>6</v>
       </c>
-      <c r="T14" s="28"/>
-      <c r="U14" s="27" t="n">
-        <f aca="false">S14+S16</f>
+      <c r="W14" s="28"/>
+      <c r="X14" s="27" t="n">
+        <f aca="false">V14+V16</f>
         <v>9</v>
       </c>
-      <c r="AH14" s="37"/>
-      <c r="AI14" s="27" t="n">
-        <f aca="false">U14</f>
+      <c r="AK14" s="37"/>
+      <c r="AL14" s="27" t="n">
+        <f aca="false">X14</f>
         <v>9</v>
       </c>
-      <c r="AJ14" s="28"/>
-      <c r="AK14" s="27" t="n">
-        <f aca="false">AI14+AI16</f>
+      <c r="AM14" s="28"/>
+      <c r="AN14" s="27" t="n">
+        <f aca="false">AL14+AL16</f>
         <v>19</v>
       </c>
-      <c r="BQ14" s="37"/>
+      <c r="BT14" s="37"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
@@ -3107,20 +3189,22 @@
       <c r="G15" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="M15" s="37"/>
-      <c r="N15" s="32" t="s">
+      <c r="H15" s="39"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" s="37"/>
+      <c r="Q15" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="O15" s="32"/>
-      <c r="P15" s="32"/>
-      <c r="S15" s="32" t="s">
+      <c r="R15" s="32"/>
+      <c r="S15" s="32"/>
+      <c r="V15" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="T15" s="32"/>
-      <c r="U15" s="32"/>
-      <c r="V15" s="35"/>
-      <c r="W15" s="35"/>
-      <c r="X15" s="35"/>
+      <c r="W15" s="32"/>
+      <c r="X15" s="32"/>
       <c r="Y15" s="35"/>
       <c r="Z15" s="35"/>
       <c r="AA15" s="35"/>
@@ -3130,13 +3214,16 @@
       <c r="AE15" s="35"/>
       <c r="AF15" s="35"/>
       <c r="AG15" s="35"/>
-      <c r="AH15" s="40"/>
-      <c r="AI15" s="32" t="s">
+      <c r="AH15" s="35"/>
+      <c r="AI15" s="35"/>
+      <c r="AJ15" s="35"/>
+      <c r="AK15" s="40"/>
+      <c r="AL15" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="AJ15" s="32"/>
-      <c r="AK15" s="32"/>
-      <c r="BQ15" s="37"/>
+      <c r="AM15" s="32"/>
+      <c r="AN15" s="32"/>
+      <c r="BT15" s="37"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
@@ -3156,36 +3243,38 @@
       <c r="G16" s="39" t="n">
         <v>5</v>
       </c>
-      <c r="M16" s="35"/>
-      <c r="N16" s="33" t="n">
-        <f aca="false">G7</f>
+      <c r="H16" s="39"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="P16" s="35"/>
+      <c r="Q16" s="33" t="n">
+        <f aca="false">J7</f>
         <v>1</v>
       </c>
-      <c r="O16" s="34" t="n">
-        <f aca="false">P17-P14</f>
+      <c r="R16" s="34" t="n">
+        <f aca="false">S17-S14</f>
         <v>7</v>
       </c>
-      <c r="P16" s="33" t="n">
-        <f aca="false">S14-P14</f>
+      <c r="S16" s="33" t="n">
+        <f aca="false">V14-S14</f>
         <v>0</v>
       </c>
-      <c r="Q16" s="35"/>
-      <c r="R16" s="35"/>
-      <c r="S16" s="33" t="n">
-        <f aca="false">G8</f>
+      <c r="T16" s="35"/>
+      <c r="U16" s="35"/>
+      <c r="V16" s="33" t="n">
+        <f aca="false">J8</f>
         <v>3</v>
       </c>
-      <c r="T16" s="34" t="n">
-        <f aca="false">U17-U14</f>
+      <c r="W16" s="34" t="n">
+        <f aca="false">X17-X14</f>
         <v>7</v>
       </c>
-      <c r="U16" s="33" t="n">
-        <f aca="false">MIN(AI14,AI2)-U14</f>
+      <c r="X16" s="33" t="n">
+        <f aca="false">MIN(AL14,AL2)-X14</f>
         <v>0</v>
       </c>
-      <c r="V16" s="35"/>
-      <c r="W16" s="35"/>
-      <c r="X16" s="35"/>
       <c r="Y16" s="35"/>
       <c r="Z16" s="35"/>
       <c r="AA16" s="35"/>
@@ -3196,21 +3285,21 @@
       <c r="AF16" s="35"/>
       <c r="AG16" s="35"/>
       <c r="AH16" s="35"/>
-      <c r="AI16" s="33" t="n">
-        <f aca="false">G12</f>
+      <c r="AI16" s="35"/>
+      <c r="AJ16" s="35"/>
+      <c r="AK16" s="35"/>
+      <c r="AL16" s="33" t="n">
+        <f aca="false">J12</f>
         <v>10</v>
       </c>
-      <c r="AJ16" s="34" t="n">
-        <f aca="false">AK17-AK14</f>
+      <c r="AM16" s="34" t="n">
+        <f aca="false">AN17-AN14</f>
         <v>15</v>
       </c>
-      <c r="AK16" s="33" t="n">
-        <f aca="false">BR2-AK14</f>
+      <c r="AN16" s="33" t="n">
+        <f aca="false">BU2-AN14</f>
         <v>15</v>
       </c>
-      <c r="AL16" s="35"/>
-      <c r="AM16" s="35"/>
-      <c r="AN16" s="35"/>
       <c r="AO16" s="35"/>
       <c r="AP16" s="35"/>
       <c r="AQ16" s="35"/>
@@ -3239,6 +3328,9 @@
       <c r="BN16" s="35"/>
       <c r="BO16" s="35"/>
       <c r="BP16" s="35"/>
+      <c r="BQ16" s="35"/>
+      <c r="BR16" s="35"/>
+      <c r="BS16" s="35"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="17" t="s">
@@ -3250,50 +3342,55 @@
       <c r="C17" s="41"/>
       <c r="D17" s="41"/>
       <c r="E17" s="42" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F17" s="43"/>
       <c r="G17" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="N17" s="27" t="n">
-        <f aca="false">P17-N16</f>
+      <c r="H17" s="44"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="27" t="n">
+        <f aca="false">S17-Q16</f>
         <v>12</v>
       </c>
-      <c r="O17" s="28"/>
-      <c r="P17" s="27" t="n">
-        <f aca="false">S17</f>
+      <c r="R17" s="28"/>
+      <c r="S17" s="27" t="n">
+        <f aca="false">V17</f>
         <v>13</v>
       </c>
-      <c r="S17" s="27" t="n">
-        <f aca="false">U17-S16</f>
+      <c r="V17" s="27" t="n">
+        <f aca="false">X17-V16</f>
         <v>13</v>
       </c>
-      <c r="T17" s="28"/>
-      <c r="U17" s="27" t="n">
-        <f aca="false">MIN(AI5,AI17)</f>
+      <c r="W17" s="28"/>
+      <c r="X17" s="27" t="n">
+        <f aca="false">MIN(AL5,AL17)</f>
         <v>16</v>
       </c>
-      <c r="AI17" s="27" t="n">
-        <f aca="false">AK17-AI16</f>
+      <c r="AL17" s="27" t="n">
+        <f aca="false">AN17-AL16</f>
         <v>24</v>
       </c>
-      <c r="AJ17" s="28"/>
-      <c r="AK17" s="27" t="n">
-        <f aca="false">BR5</f>
+      <c r="AM17" s="28"/>
+      <c r="AN17" s="27" t="n">
+        <f aca="false">BU5</f>
         <v>34</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="45" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B19" s="46" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C19" s="47"/>
       <c r="D19" s="48" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3305,84 +3402,84 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="32" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C21" s="34" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D21" s="33" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="49" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B22" s="50" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C22" s="51"/>
       <c r="D22" s="52" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="53" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C24" s="28"/>
       <c r="D24" s="27" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="32" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="32" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C26" s="34" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D26" s="33" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="53" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C27" s="28"/>
       <c r="D27" s="27" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B29" s="54" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C29" s="55" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D29" s="55"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B30" s="54" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C30" s="55" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D30" s="55"/>
     </row>
@@ -3391,25 +3488,25 @@
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B32" s="54" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C32" s="55" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D32" s="55"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B33" s="54" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C33" s="55" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D33" s="55"/>
     </row>
@@ -3424,34 +3521,34 @@
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B3:D3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="S3:U3"/>
-    <mergeCell ref="AI3:AK3"/>
-    <mergeCell ref="AN3:AP3"/>
-    <mergeCell ref="AS3:AU3"/>
-    <mergeCell ref="AX3:AZ3"/>
-    <mergeCell ref="BC3:BE3"/>
-    <mergeCell ref="BH3:BJ3"/>
-    <mergeCell ref="BM3:BO3"/>
-    <mergeCell ref="BR3:BT3"/>
+    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="Q3:S3"/>
+    <mergeCell ref="V3:X3"/>
+    <mergeCell ref="AL3:AN3"/>
+    <mergeCell ref="AQ3:AS3"/>
+    <mergeCell ref="AV3:AX3"/>
+    <mergeCell ref="BA3:BC3"/>
+    <mergeCell ref="BF3:BH3"/>
+    <mergeCell ref="BK3:BM3"/>
+    <mergeCell ref="BP3:BR3"/>
+    <mergeCell ref="BU3:BW3"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B9:D9"/>
-    <mergeCell ref="S9:U9"/>
-    <mergeCell ref="X9:Z9"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="AA9:AC9"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B15:D15"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="S15:U15"/>
-    <mergeCell ref="AI15:AK15"/>
+    <mergeCell ref="Q15:S15"/>
+    <mergeCell ref="V15:X15"/>
+    <mergeCell ref="AL15:AN15"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="B20:D20"/>
@@ -3461,7 +3558,7 @@
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="C33:D33"/>
   </mergeCells>
-  <conditionalFormatting sqref="C21 C26 S10:T10 BS4 BN4 BI4:BJ4 BD4:BE4 AY4:AZ4 AT4:AU4 AO4:AP4 AJ4:AK4 AJ16 Y10 T16 T4 O16 O4 J4">
+  <conditionalFormatting sqref="C21 C26 V10:W10 BV4 BQ4 BL4:BM4 BG4:BH4 BB4:BC4 AW4:AX4 AR4:AS4 AM4:AN4 AM16 AB10 W16 W4 R16 R4 M4">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>

--- a/Übungen/Online_Shop.xlsx
+++ b/Übungen/Online_Shop.xlsx
@@ -253,11 +253,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
     <numFmt numFmtId="166" formatCode="@"/>
-    <numFmt numFmtId="167" formatCode="General"/>
+    <numFmt numFmtId="167" formatCode="0.00\ %"/>
+    <numFmt numFmtId="168" formatCode="General"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -482,7 +483,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="62">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -567,6 +568,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -575,6 +580,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="167" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -591,6 +600,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -611,15 +624,19 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -643,6 +660,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -660,6 +681,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="6" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1721,6 +1746,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
@@ -2274,7 +2303,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="20" width="11.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="16.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="6" style="3" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="3" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="21" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="3" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="107" min="11" style="0" width="3.83"/>
   </cols>
   <sheetData>
@@ -2282,27 +2313,27 @@
       <c r="A1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="22" t="s">
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="G1" s="22" t="s">
+      <c r="G1" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="H1" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="I1" s="22" t="s">
+      <c r="I1" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="J1" s="22" t="s">
+      <c r="J1" s="23" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2310,1152 +2341,1231 @@
       <c r="A2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="25" t="s">
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="G2" s="26" t="n">
+      <c r="G2" s="28" t="n">
         <v>5</v>
       </c>
-      <c r="H2" s="26"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="L2" s="27" t="n">
+      <c r="H2" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" s="28" t="n">
+        <f aca="false">ROUNDUP(G2/(H2*I2),0)</f>
+        <v>2</v>
+      </c>
+      <c r="L2" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="M2" s="28"/>
-      <c r="N2" s="27" t="n">
+      <c r="M2" s="31"/>
+      <c r="N2" s="30" t="n">
         <f aca="false">L2+L4</f>
-        <v>5</v>
-      </c>
-      <c r="Q2" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q2" s="30" t="n">
         <f aca="false">N2</f>
-        <v>5</v>
-      </c>
-      <c r="R2" s="28"/>
-      <c r="S2" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="R2" s="31"/>
+      <c r="S2" s="30" t="n">
         <f aca="false">Q2+Q4</f>
-        <v>6</v>
-      </c>
-      <c r="V2" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="V2" s="30" t="n">
         <f aca="false">S2</f>
-        <v>6</v>
-      </c>
-      <c r="W2" s="28"/>
-      <c r="X2" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="W2" s="31"/>
+      <c r="X2" s="30" t="n">
         <f aca="false">V2+V4</f>
-        <v>10</v>
-      </c>
-      <c r="AL2" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AL2" s="30" t="n">
         <f aca="false">MAX(X2,AC8,X14)</f>
-        <v>16</v>
-      </c>
-      <c r="AM2" s="28"/>
-      <c r="AN2" s="27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AM2" s="31"/>
+      <c r="AN2" s="30" t="n">
         <f aca="false">AL2+AL4</f>
-        <v>18</v>
-      </c>
-      <c r="AQ2" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ2" s="30" t="n">
         <f aca="false">AN2</f>
-        <v>18</v>
-      </c>
-      <c r="AR2" s="28"/>
-      <c r="AS2" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR2" s="31"/>
+      <c r="AS2" s="30" t="n">
         <f aca="false">AQ2+AQ4</f>
-        <v>20</v>
-      </c>
-      <c r="AV2" s="27" t="n">
+        <v>17</v>
+      </c>
+      <c r="AV2" s="30" t="n">
         <f aca="false">AS2</f>
-        <v>20</v>
-      </c>
-      <c r="AW2" s="28"/>
-      <c r="AX2" s="27" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW2" s="31"/>
+      <c r="AX2" s="30" t="n">
         <f aca="false">AV2+AV4</f>
+        <v>19</v>
+      </c>
+      <c r="BA2" s="30" t="n">
+        <f aca="false">AX2</f>
+        <v>19</v>
+      </c>
+      <c r="BB2" s="31"/>
+      <c r="BC2" s="30" t="n">
+        <f aca="false">BA2+BA4</f>
         <v>22</v>
       </c>
-      <c r="BA2" s="27" t="n">
-        <f aca="false">AX2</f>
+      <c r="BF2" s="30" t="n">
+        <f aca="false">BC2</f>
         <v>22</v>
       </c>
-      <c r="BB2" s="28"/>
-      <c r="BC2" s="27" t="n">
-        <f aca="false">BA2+BA4</f>
+      <c r="BG2" s="31"/>
+      <c r="BH2" s="30" t="n">
+        <f aca="false">BF2+BF4</f>
         <v>25</v>
       </c>
-      <c r="BF2" s="27" t="n">
-        <f aca="false">BC2</f>
+      <c r="BK2" s="30" t="n">
+        <f aca="false">BH2</f>
         <v>25</v>
       </c>
-      <c r="BG2" s="28"/>
-      <c r="BH2" s="27" t="n">
-        <f aca="false">BF2+BF4</f>
-        <v>28</v>
-      </c>
-      <c r="BK2" s="27" t="n">
-        <f aca="false">BH2</f>
-        <v>28</v>
-      </c>
-      <c r="BL2" s="28"/>
-      <c r="BM2" s="27" t="n">
+      <c r="BL2" s="31"/>
+      <c r="BM2" s="30" t="n">
         <f aca="false">BK2+BK4</f>
-        <v>29</v>
-      </c>
-      <c r="BP2" s="27" t="n">
+        <v>26</v>
+      </c>
+      <c r="BP2" s="30" t="n">
         <f aca="false">BM2</f>
-        <v>29</v>
-      </c>
-      <c r="BQ2" s="28"/>
-      <c r="BR2" s="27" t="n">
+        <v>26</v>
+      </c>
+      <c r="BQ2" s="31"/>
+      <c r="BR2" s="30" t="n">
         <f aca="false">BP2+BP4</f>
-        <v>34</v>
-      </c>
-      <c r="BU2" s="27" t="n">
+        <v>31</v>
+      </c>
+      <c r="BU2" s="30" t="n">
         <f aca="false">MAX(BR2,AN14)</f>
-        <v>34</v>
-      </c>
-      <c r="BV2" s="28"/>
-      <c r="BW2" s="27" t="n">
+        <v>35</v>
+      </c>
+      <c r="BV2" s="31"/>
+      <c r="BW2" s="30" t="n">
         <f aca="false">BU2+BU4</f>
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="30" t="s">
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="30" t="s">
+      <c r="F3" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="G3" s="31" t="n">
+      <c r="G3" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="H3" s="31"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="31" t="n">
+      <c r="H3" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="L3" s="32" t="s">
+      <c r="J3" s="28" t="n">
+        <f aca="false">ROUNDUP(G3/(H3*I3),0)</f>
+        <v>1</v>
+      </c>
+      <c r="L3" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="M3" s="32"/>
-      <c r="N3" s="32"/>
-      <c r="Q3" s="32" t="s">
+      <c r="M3" s="36"/>
+      <c r="N3" s="36"/>
+      <c r="Q3" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="R3" s="32"/>
-      <c r="S3" s="32"/>
-      <c r="V3" s="32" t="s">
+      <c r="R3" s="36"/>
+      <c r="S3" s="36"/>
+      <c r="V3" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="W3" s="32"/>
-      <c r="X3" s="32"/>
-      <c r="AL3" s="32" t="s">
+      <c r="W3" s="36"/>
+      <c r="X3" s="36"/>
+      <c r="AL3" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="AM3" s="32"/>
-      <c r="AN3" s="32"/>
-      <c r="AQ3" s="32" t="s">
+      <c r="AM3" s="36"/>
+      <c r="AN3" s="36"/>
+      <c r="AQ3" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="AR3" s="32"/>
-      <c r="AS3" s="32"/>
-      <c r="AV3" s="32" t="s">
+      <c r="AR3" s="36"/>
+      <c r="AS3" s="36"/>
+      <c r="AV3" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="AW3" s="32"/>
-      <c r="AX3" s="32"/>
-      <c r="BA3" s="32" t="s">
+      <c r="AW3" s="36"/>
+      <c r="AX3" s="36"/>
+      <c r="BA3" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="BB3" s="32"/>
-      <c r="BC3" s="32"/>
-      <c r="BF3" s="32" t="s">
+      <c r="BB3" s="36"/>
+      <c r="BC3" s="36"/>
+      <c r="BF3" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="BG3" s="32"/>
-      <c r="BH3" s="32"/>
-      <c r="BK3" s="32" t="s">
+      <c r="BG3" s="36"/>
+      <c r="BH3" s="36"/>
+      <c r="BK3" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="BL3" s="32"/>
-      <c r="BM3" s="32"/>
-      <c r="BP3" s="32" t="s">
+      <c r="BL3" s="36"/>
+      <c r="BM3" s="36"/>
+      <c r="BP3" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="BQ3" s="32"/>
-      <c r="BR3" s="32"/>
-      <c r="BU3" s="32" t="s">
+      <c r="BQ3" s="36"/>
+      <c r="BR3" s="36"/>
+      <c r="BU3" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="BV3" s="32"/>
-      <c r="BW3" s="32"/>
+      <c r="BV3" s="36"/>
+      <c r="BW3" s="36"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="30" t="s">
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="30" t="s">
+      <c r="F4" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="31" t="n">
+      <c r="G4" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="H4" s="31"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="31" t="n">
+      <c r="H4" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="28" t="n">
+        <f aca="false">ROUNDUP(G4/(H4*I4),0)</f>
         <v>4</v>
       </c>
-      <c r="L4" s="33" t="n">
+      <c r="L4" s="37" t="n">
         <f aca="false">J2</f>
-        <v>5</v>
-      </c>
-      <c r="M4" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" s="38" t="n">
         <f aca="false">N5-N2</f>
         <v>0</v>
       </c>
-      <c r="N4" s="33" t="n">
+      <c r="N4" s="37" t="n">
         <f aca="false">MIN(Q2,Q14)-N2</f>
         <v>0</v>
       </c>
-      <c r="O4" s="35"/>
-      <c r="P4" s="36"/>
-      <c r="Q4" s="33" t="n">
+      <c r="O4" s="39"/>
+      <c r="P4" s="40"/>
+      <c r="Q4" s="37" t="n">
         <f aca="false">J3</f>
         <v>1</v>
       </c>
-      <c r="R4" s="34" t="n">
+      <c r="R4" s="38" t="n">
         <f aca="false">S5-S2</f>
-        <v>0</v>
-      </c>
-      <c r="S4" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="S4" s="37" t="n">
         <f aca="false">V2-S2</f>
         <v>0</v>
       </c>
-      <c r="T4" s="35"/>
-      <c r="U4" s="36"/>
-      <c r="V4" s="33" t="n">
+      <c r="T4" s="39"/>
+      <c r="U4" s="40"/>
+      <c r="V4" s="37" t="n">
         <f aca="false">J4</f>
         <v>4</v>
       </c>
-      <c r="W4" s="34" t="n">
+      <c r="W4" s="38" t="n">
         <f aca="false">X5-X2</f>
-        <v>6</v>
-      </c>
-      <c r="X4" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="X4" s="37" t="n">
         <f aca="false">AL2-X2</f>
         <v>6</v>
       </c>
-      <c r="Y4" s="35"/>
-      <c r="Z4" s="35"/>
-      <c r="AA4" s="35"/>
-      <c r="AB4" s="35"/>
-      <c r="AC4" s="35"/>
-      <c r="AD4" s="35"/>
-      <c r="AE4" s="35"/>
-      <c r="AF4" s="35"/>
-      <c r="AG4" s="35"/>
-      <c r="AH4" s="35"/>
-      <c r="AI4" s="35"/>
-      <c r="AJ4" s="35"/>
-      <c r="AK4" s="36"/>
-      <c r="AL4" s="33" t="n">
+      <c r="Y4" s="39"/>
+      <c r="Z4" s="39"/>
+      <c r="AA4" s="39"/>
+      <c r="AB4" s="39"/>
+      <c r="AC4" s="39"/>
+      <c r="AD4" s="39"/>
+      <c r="AE4" s="39"/>
+      <c r="AF4" s="39"/>
+      <c r="AG4" s="39"/>
+      <c r="AH4" s="39"/>
+      <c r="AI4" s="39"/>
+      <c r="AJ4" s="39"/>
+      <c r="AK4" s="40"/>
+      <c r="AL4" s="37" t="n">
         <f aca="false">J9</f>
         <v>2</v>
       </c>
-      <c r="AM4" s="34" t="n">
+      <c r="AM4" s="38" t="n">
         <f aca="false">AN5-AN2</f>
-        <v>0</v>
-      </c>
-      <c r="AN4" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN4" s="38" t="n">
         <f aca="false">AO5-AO2</f>
         <v>0</v>
       </c>
-      <c r="AO4" s="35"/>
-      <c r="AP4" s="35"/>
-      <c r="AQ4" s="33" t="n">
+      <c r="AO4" s="39"/>
+      <c r="AP4" s="39"/>
+      <c r="AQ4" s="37" t="n">
         <f aca="false">J10</f>
         <v>2</v>
       </c>
-      <c r="AR4" s="34" t="n">
+      <c r="AR4" s="38" t="n">
         <f aca="false">AS5-AS2</f>
-        <v>0</v>
-      </c>
-      <c r="AS4" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS4" s="38" t="n">
         <f aca="false">AT5-AT2</f>
         <v>0</v>
       </c>
-      <c r="AT4" s="35"/>
-      <c r="AU4" s="35"/>
-      <c r="AV4" s="33" t="n">
+      <c r="AT4" s="39"/>
+      <c r="AU4" s="39"/>
+      <c r="AV4" s="37" t="n">
         <f aca="false">J11</f>
         <v>2</v>
       </c>
-      <c r="AW4" s="34" t="n">
+      <c r="AW4" s="38" t="n">
         <f aca="false">AX5-AX2</f>
-        <v>0</v>
-      </c>
-      <c r="AX4" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX4" s="38" t="n">
         <f aca="false">AY5-AY2</f>
         <v>0</v>
       </c>
-      <c r="AY4" s="35"/>
-      <c r="AZ4" s="35"/>
-      <c r="BA4" s="33" t="n">
+      <c r="AY4" s="39"/>
+      <c r="AZ4" s="39"/>
+      <c r="BA4" s="37" t="n">
         <f aca="false">J13</f>
         <v>3</v>
       </c>
-      <c r="BB4" s="34" t="n">
+      <c r="BB4" s="38" t="n">
         <f aca="false">BC5-BC2</f>
-        <v>0</v>
-      </c>
-      <c r="BC4" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC4" s="38" t="n">
         <f aca="false">BD5-BD2</f>
         <v>0</v>
       </c>
-      <c r="BD4" s="35"/>
-      <c r="BE4" s="35"/>
-      <c r="BF4" s="33" t="n">
+      <c r="BD4" s="39"/>
+      <c r="BE4" s="39"/>
+      <c r="BF4" s="37" t="n">
         <f aca="false">J14</f>
         <v>3</v>
       </c>
-      <c r="BG4" s="34" t="n">
+      <c r="BG4" s="38" t="n">
         <f aca="false">BH5-BH2</f>
-        <v>0</v>
-      </c>
-      <c r="BH4" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH4" s="38" t="n">
         <f aca="false">BI5-BI2</f>
         <v>0</v>
       </c>
-      <c r="BI4" s="35"/>
-      <c r="BJ4" s="35"/>
-      <c r="BK4" s="33" t="n">
+      <c r="BI4" s="39"/>
+      <c r="BJ4" s="39"/>
+      <c r="BK4" s="37" t="n">
         <f aca="false">J15</f>
         <v>1</v>
       </c>
-      <c r="BL4" s="34" t="n">
+      <c r="BL4" s="38" t="n">
         <f aca="false">BM5-BM2</f>
-        <v>0</v>
-      </c>
-      <c r="BM4" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM4" s="38" t="n">
         <f aca="false">BN5-BN2</f>
         <v>0</v>
       </c>
-      <c r="BN4" s="35"/>
-      <c r="BO4" s="35"/>
-      <c r="BP4" s="33" t="n">
+      <c r="BN4" s="39"/>
+      <c r="BO4" s="39"/>
+      <c r="BP4" s="37" t="n">
         <f aca="false">J16</f>
         <v>5</v>
       </c>
-      <c r="BQ4" s="34" t="n">
+      <c r="BQ4" s="38" t="n">
         <f aca="false">BR5-BR2</f>
-        <v>0</v>
-      </c>
-      <c r="BR4" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR4" s="37" t="n">
         <f aca="false">BU2-BR2</f>
-        <v>0</v>
-      </c>
-      <c r="BS4" s="35"/>
-      <c r="BT4" s="36"/>
-      <c r="BU4" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS4" s="39"/>
+      <c r="BT4" s="40"/>
+      <c r="BU4" s="37" t="n">
         <f aca="false">J17</f>
         <v>1</v>
       </c>
-      <c r="BV4" s="34" t="n">
+      <c r="BV4" s="38" t="n">
         <f aca="false">BW5-BW2</f>
         <v>0</v>
       </c>
-      <c r="BW4" s="33"/>
+      <c r="BW4" s="37"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="30" t="s">
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="30" t="s">
+      <c r="F5" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="31" t="n">
+      <c r="G5" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="H5" s="31"/>
-      <c r="I5" s="30"/>
-      <c r="J5" s="31" t="n">
+      <c r="H5" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="28" t="n">
+        <f aca="false">ROUNDUP(G5/(H5*I5),0)</f>
         <v>3</v>
       </c>
-      <c r="L5" s="27" t="n">
+      <c r="L5" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="M5" s="28"/>
-      <c r="N5" s="27" t="n">
+      <c r="M5" s="31"/>
+      <c r="N5" s="30" t="n">
         <f aca="false">MIN(Q5,Q17)</f>
-        <v>5</v>
-      </c>
-      <c r="P5" s="37"/>
-      <c r="Q5" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="P5" s="41"/>
+      <c r="Q5" s="30" t="n">
         <f aca="false">S5-Q4</f>
-        <v>5</v>
-      </c>
-      <c r="R5" s="28"/>
-      <c r="S5" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="R5" s="31"/>
+      <c r="S5" s="30" t="n">
         <f aca="false">MIN(V11,V5)</f>
-        <v>6</v>
-      </c>
-      <c r="U5" s="37"/>
-      <c r="V5" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="U5" s="41"/>
+      <c r="V5" s="30" t="n">
         <f aca="false">X5-V4</f>
-        <v>12</v>
-      </c>
-      <c r="W5" s="28"/>
-      <c r="X5" s="27" t="n">
+        <v>13</v>
+      </c>
+      <c r="W5" s="31"/>
+      <c r="X5" s="30" t="n">
         <f aca="false">AL5</f>
-        <v>16</v>
-      </c>
-      <c r="AK5" s="37"/>
-      <c r="AL5" s="27" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK5" s="41"/>
+      <c r="AL5" s="30" t="n">
         <f aca="false">AN5-AL4</f>
-        <v>16</v>
-      </c>
-      <c r="AM5" s="28"/>
-      <c r="AN5" s="27" t="n">
+        <v>17</v>
+      </c>
+      <c r="AM5" s="31"/>
+      <c r="AN5" s="30" t="n">
         <f aca="false">AQ5</f>
-        <v>18</v>
-      </c>
-      <c r="AQ5" s="27" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ5" s="30" t="n">
         <f aca="false">AS5-AQ4</f>
-        <v>18</v>
-      </c>
-      <c r="AR5" s="28"/>
-      <c r="AS5" s="27" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR5" s="31"/>
+      <c r="AS5" s="30" t="n">
         <f aca="false">AV5</f>
-        <v>20</v>
-      </c>
-      <c r="AV5" s="27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AV5" s="30" t="n">
         <f aca="false">AX5-AV4</f>
-        <v>20</v>
-      </c>
-      <c r="AW5" s="28"/>
-      <c r="AX5" s="27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW5" s="31"/>
+      <c r="AX5" s="30" t="n">
         <f aca="false">BA5</f>
-        <v>22</v>
-      </c>
-      <c r="BA5" s="27" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA5" s="30" t="n">
         <f aca="false">BC5-BA4</f>
-        <v>22</v>
-      </c>
-      <c r="BB5" s="28"/>
-      <c r="BC5" s="27" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB5" s="31"/>
+      <c r="BC5" s="30" t="n">
         <f aca="false">BF5</f>
-        <v>25</v>
-      </c>
-      <c r="BF5" s="27" t="n">
+        <v>26</v>
+      </c>
+      <c r="BF5" s="30" t="n">
         <f aca="false">BH5-BF4</f>
-        <v>25</v>
-      </c>
-      <c r="BG5" s="28"/>
-      <c r="BH5" s="27" t="n">
+        <v>26</v>
+      </c>
+      <c r="BG5" s="31"/>
+      <c r="BH5" s="30" t="n">
         <f aca="false">BK5</f>
-        <v>28</v>
-      </c>
-      <c r="BK5" s="27" t="n">
+        <v>29</v>
+      </c>
+      <c r="BK5" s="30" t="n">
         <f aca="false">BM5-BK4</f>
-        <v>28</v>
-      </c>
-      <c r="BL5" s="28"/>
-      <c r="BM5" s="27" t="n">
+        <v>29</v>
+      </c>
+      <c r="BL5" s="31"/>
+      <c r="BM5" s="30" t="n">
         <f aca="false">BP5</f>
-        <v>29</v>
-      </c>
-      <c r="BP5" s="27" t="n">
+        <v>30</v>
+      </c>
+      <c r="BP5" s="30" t="n">
         <f aca="false">BR5-BP4</f>
-        <v>29</v>
-      </c>
-      <c r="BQ5" s="28"/>
-      <c r="BR5" s="27" t="n">
+        <v>30</v>
+      </c>
+      <c r="BQ5" s="31"/>
+      <c r="BR5" s="30" t="n">
         <f aca="false">BU5</f>
-        <v>34</v>
-      </c>
-      <c r="BT5" s="37"/>
-      <c r="BU5" s="27" t="n">
+        <v>35</v>
+      </c>
+      <c r="BT5" s="41"/>
+      <c r="BU5" s="30" t="n">
         <f aca="false">BW5-BU4</f>
-        <v>34</v>
-      </c>
-      <c r="BV5" s="28"/>
-      <c r="BW5" s="27" t="n">
+        <v>35</v>
+      </c>
+      <c r="BV5" s="31"/>
+      <c r="BW5" s="30" t="n">
         <f aca="false">BW2</f>
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="29" t="s">
+      <c r="B6" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="38" t="s">
+      <c r="C6" s="32"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="38" t="s">
+      <c r="F6" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="39" t="n">
+      <c r="G6" s="43" t="n">
         <v>7</v>
       </c>
-      <c r="H6" s="39"/>
-      <c r="I6" s="38"/>
-      <c r="J6" s="39" t="n">
+      <c r="H6" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="28" t="n">
+        <f aca="false">ROUNDUP(G6/(H6*I6),0)</f>
         <v>7</v>
       </c>
-      <c r="P6" s="37"/>
-      <c r="U6" s="37"/>
-      <c r="AK6" s="37"/>
-      <c r="BT6" s="37"/>
+      <c r="P6" s="41"/>
+      <c r="U6" s="41"/>
+      <c r="AK6" s="41"/>
+      <c r="BT6" s="41"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="30" t="s">
+      <c r="C7" s="32"/>
+      <c r="D7" s="32"/>
+      <c r="E7" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="30" t="s">
+      <c r="F7" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="31" t="n">
+      <c r="G7" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="H7" s="31"/>
-      <c r="I7" s="30"/>
-      <c r="J7" s="31" t="n">
+      <c r="H7" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="P7" s="37"/>
-      <c r="U7" s="37"/>
-      <c r="AK7" s="37"/>
-      <c r="BT7" s="37"/>
+      <c r="I7" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="28" t="n">
+        <f aca="false">ROUNDUP(G7/(H7*I7),0)</f>
+        <v>1</v>
+      </c>
+      <c r="P7" s="41"/>
+      <c r="U7" s="41"/>
+      <c r="AK7" s="41"/>
+      <c r="BT7" s="41"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="38" t="s">
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="F8" s="38" t="s">
+      <c r="F8" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="G8" s="39" t="n">
+      <c r="G8" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="H8" s="39"/>
-      <c r="I8" s="38"/>
-      <c r="J8" s="39" t="n">
+      <c r="H8" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="28" t="n">
+        <f aca="false">ROUNDUP(G8/(H8*I8),0)</f>
         <v>3</v>
       </c>
-      <c r="P8" s="37"/>
-      <c r="U8" s="37"/>
-      <c r="V8" s="27" t="n">
+      <c r="P8" s="41"/>
+      <c r="U8" s="41"/>
+      <c r="V8" s="30" t="n">
         <f aca="false">S2</f>
+        <v>3</v>
+      </c>
+      <c r="W8" s="31"/>
+      <c r="X8" s="30" t="n">
+        <f aca="false">V8+V10</f>
         <v>6</v>
       </c>
-      <c r="W8" s="28"/>
-      <c r="X8" s="27" t="n">
-        <f aca="false">V8+V10</f>
-        <v>9</v>
-      </c>
-      <c r="AA8" s="27" t="n">
+      <c r="AA8" s="30" t="n">
         <f aca="false">X8</f>
-        <v>9</v>
-      </c>
-      <c r="AB8" s="28"/>
-      <c r="AC8" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB8" s="31"/>
+      <c r="AC8" s="30" t="n">
         <f aca="false">AA8+AA10</f>
-        <v>16</v>
-      </c>
-      <c r="AK8" s="37"/>
-      <c r="BT8" s="37"/>
+        <v>13</v>
+      </c>
+      <c r="AK8" s="41"/>
+      <c r="BT8" s="41"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="38" t="s">
+      <c r="C9" s="32"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="42" t="s">
         <v>55</v>
       </c>
-      <c r="F9" s="38" t="s">
+      <c r="F9" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="G9" s="39" t="n">
+      <c r="G9" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="H9" s="39"/>
-      <c r="I9" s="38"/>
-      <c r="J9" s="39" t="n">
+      <c r="H9" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" s="44" t="n">
+        <f aca="false">((2*100%)+(100%-$I$12))/3</f>
+        <v>0.883333333333333</v>
+      </c>
+      <c r="J9" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="P9" s="37"/>
-      <c r="U9" s="37"/>
-      <c r="V9" s="32" t="s">
+      <c r="P9" s="41"/>
+      <c r="U9" s="41"/>
+      <c r="V9" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="W9" s="32"/>
-      <c r="X9" s="32"/>
-      <c r="AA9" s="32" t="s">
+      <c r="W9" s="36"/>
+      <c r="X9" s="36"/>
+      <c r="AA9" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="AB9" s="32"/>
-      <c r="AC9" s="32"/>
-      <c r="AK9" s="37"/>
-      <c r="BT9" s="37"/>
+      <c r="AB9" s="36"/>
+      <c r="AC9" s="36"/>
+      <c r="AK9" s="41"/>
+      <c r="BT9" s="41"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="38" t="s">
+      <c r="C10" s="32"/>
+      <c r="D10" s="32"/>
+      <c r="E10" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="38" t="s">
+      <c r="F10" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="G10" s="39" t="n">
+      <c r="G10" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="39"/>
-      <c r="I10" s="38"/>
-      <c r="J10" s="39" t="n">
+      <c r="H10" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" s="44" t="n">
+        <f aca="false">((2*100%)+(100%-$I$12))/3</f>
+        <v>0.883333333333333</v>
+      </c>
+      <c r="J10" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="P10" s="37"/>
-      <c r="U10" s="35"/>
-      <c r="V10" s="33" t="n">
+      <c r="P10" s="41"/>
+      <c r="U10" s="39"/>
+      <c r="V10" s="37" t="n">
         <f aca="false">J5</f>
         <v>3</v>
       </c>
-      <c r="W10" s="34" t="n">
+      <c r="W10" s="38" t="n">
         <f aca="false">X11-X8</f>
-        <v>0</v>
-      </c>
-      <c r="X10" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="X10" s="37" t="n">
         <f aca="false">AA8-X8</f>
         <v>0</v>
       </c>
-      <c r="Y10" s="35"/>
-      <c r="Z10" s="35"/>
-      <c r="AA10" s="33" t="n">
+      <c r="Y10" s="39"/>
+      <c r="Z10" s="39"/>
+      <c r="AA10" s="37" t="n">
         <f aca="false">J6</f>
         <v>7</v>
       </c>
-      <c r="AB10" s="34" t="n">
+      <c r="AB10" s="38" t="n">
         <f aca="false">AC11-AC8</f>
-        <v>0</v>
-      </c>
-      <c r="AC10" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC10" s="37" t="n">
         <f aca="false">AL2-AC8</f>
         <v>0</v>
       </c>
-      <c r="AD10" s="35"/>
-      <c r="AE10" s="35"/>
-      <c r="AF10" s="35"/>
-      <c r="AG10" s="35"/>
-      <c r="AH10" s="35"/>
-      <c r="AI10" s="35"/>
-      <c r="AJ10" s="35"/>
-      <c r="AK10" s="37"/>
-      <c r="BT10" s="37"/>
+      <c r="AD10" s="39"/>
+      <c r="AE10" s="39"/>
+      <c r="AF10" s="39"/>
+      <c r="AG10" s="39"/>
+      <c r="AH10" s="39"/>
+      <c r="AI10" s="39"/>
+      <c r="AJ10" s="39"/>
+      <c r="AK10" s="41"/>
+      <c r="BT10" s="41"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="29" t="s">
+      <c r="B11" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="38" t="s">
+      <c r="C11" s="32"/>
+      <c r="D11" s="32"/>
+      <c r="E11" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="F11" s="38" t="s">
+      <c r="F11" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="39" t="n">
+      <c r="G11" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="H11" s="39"/>
-      <c r="I11" s="38"/>
-      <c r="J11" s="39" t="n">
+      <c r="H11" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" s="44" t="n">
+        <f aca="false">((2*100%)+(100%-$I$12))/3</f>
+        <v>0.883333333333333</v>
+      </c>
+      <c r="J11" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="P11" s="37"/>
-      <c r="V11" s="27" t="n">
+      <c r="P11" s="41"/>
+      <c r="V11" s="30" t="n">
         <f aca="false">X11-V10</f>
-        <v>6</v>
-      </c>
-      <c r="W11" s="28"/>
-      <c r="X11" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="W11" s="31"/>
+      <c r="X11" s="30" t="n">
         <f aca="false">AA11</f>
-        <v>9</v>
-      </c>
-      <c r="AA11" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA11" s="30" t="n">
         <f aca="false">AC11-AA10</f>
-        <v>9</v>
-      </c>
-      <c r="AB11" s="28"/>
-      <c r="AC11" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB11" s="31"/>
+      <c r="AC11" s="30" t="n">
         <f aca="false">AL5</f>
-        <v>16</v>
-      </c>
-      <c r="AK11" s="37"/>
-      <c r="BT11" s="37"/>
+        <v>17</v>
+      </c>
+      <c r="AK11" s="41"/>
+      <c r="BT11" s="41"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="29" t="s">
+      <c r="B12" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="29"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="38" t="s">
+      <c r="C12" s="32"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="F12" s="38" t="s">
+      <c r="F12" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="G12" s="39" t="n">
+      <c r="G12" s="43" t="n">
         <v>10</v>
       </c>
-      <c r="H12" s="39"/>
-      <c r="I12" s="38"/>
-      <c r="J12" s="39" t="n">
-        <v>10</v>
-      </c>
-      <c r="P12" s="37"/>
-      <c r="AA12" s="40"/>
-      <c r="AK12" s="37"/>
-      <c r="BT12" s="37"/>
+      <c r="H12" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="44" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J12" s="28" t="n">
+        <f aca="false">ROUNDUP(G12/(H12*I12),0)</f>
+        <v>29</v>
+      </c>
+      <c r="P12" s="41"/>
+      <c r="AA12" s="45"/>
+      <c r="AK12" s="41"/>
+      <c r="BT12" s="41"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="38" t="s">
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="F13" s="38" t="s">
+      <c r="F13" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="G13" s="39" t="n">
+      <c r="G13" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="H13" s="39"/>
-      <c r="I13" s="38"/>
-      <c r="J13" s="39" t="n">
+      <c r="H13" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="P13" s="37"/>
-      <c r="AA13" s="40"/>
-      <c r="AK13" s="37"/>
-      <c r="BT13" s="37"/>
+      <c r="I13" s="44" t="n">
+        <f aca="false">((2*100%)+(100%-$I$12))/3</f>
+        <v>0.883333333333333</v>
+      </c>
+      <c r="J13" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="P13" s="41"/>
+      <c r="AA13" s="45"/>
+      <c r="AK13" s="41"/>
+      <c r="BT13" s="41"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="29" t="s">
+      <c r="B14" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="38" t="s">
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="F14" s="38" t="s">
+      <c r="F14" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="G14" s="39" t="n">
+      <c r="G14" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="H14" s="39"/>
-      <c r="I14" s="38"/>
-      <c r="J14" s="39" t="n">
+      <c r="H14" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="P14" s="37"/>
-      <c r="Q14" s="27" t="n">
+      <c r="I14" s="44" t="n">
+        <f aca="false">((2*100%)+(100%-$I$12))/3</f>
+        <v>0.883333333333333</v>
+      </c>
+      <c r="J14" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="P14" s="41"/>
+      <c r="Q14" s="30" t="n">
         <f aca="false">N2</f>
-        <v>5</v>
-      </c>
-      <c r="R14" s="28"/>
-      <c r="S14" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" s="31"/>
+      <c r="S14" s="30" t="n">
         <f aca="false">Q14+Q16</f>
+        <v>3</v>
+      </c>
+      <c r="V14" s="30" t="n">
+        <f aca="false">S14</f>
+        <v>3</v>
+      </c>
+      <c r="W14" s="31"/>
+      <c r="X14" s="30" t="n">
+        <f aca="false">V14+V16</f>
         <v>6</v>
       </c>
-      <c r="V14" s="27" t="n">
-        <f aca="false">S14</f>
+      <c r="AK14" s="41"/>
+      <c r="AL14" s="30" t="n">
+        <f aca="false">X14</f>
         <v>6</v>
       </c>
-      <c r="W14" s="28"/>
-      <c r="X14" s="27" t="n">
-        <f aca="false">V14+V16</f>
-        <v>9</v>
-      </c>
-      <c r="AK14" s="37"/>
-      <c r="AL14" s="27" t="n">
-        <f aca="false">X14</f>
-        <v>9</v>
-      </c>
-      <c r="AM14" s="28"/>
-      <c r="AN14" s="27" t="n">
+      <c r="AM14" s="31"/>
+      <c r="AN14" s="30" t="n">
         <f aca="false">AL14+AL16</f>
-        <v>19</v>
-      </c>
-      <c r="BT14" s="37"/>
+        <v>35</v>
+      </c>
+      <c r="BT14" s="41"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="29" t="s">
+      <c r="B15" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="38" t="s">
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="F15" s="38" t="s">
+      <c r="F15" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="G15" s="39" t="n">
+      <c r="G15" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="39"/>
-      <c r="I15" s="38"/>
-      <c r="J15" s="39" t="n">
+      <c r="H15" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" s="44" t="n">
+        <f aca="false">((2*100%)+(100%-$I$12))/3</f>
+        <v>0.883333333333333</v>
+      </c>
+      <c r="J15" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="P15" s="37"/>
-      <c r="Q15" s="32" t="s">
+      <c r="P15" s="41"/>
+      <c r="Q15" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="R15" s="32"/>
-      <c r="S15" s="32"/>
-      <c r="V15" s="32" t="s">
+      <c r="R15" s="36"/>
+      <c r="S15" s="36"/>
+      <c r="V15" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="W15" s="32"/>
-      <c r="X15" s="32"/>
-      <c r="Y15" s="35"/>
-      <c r="Z15" s="35"/>
-      <c r="AA15" s="35"/>
-      <c r="AB15" s="35"/>
-      <c r="AC15" s="35"/>
-      <c r="AD15" s="35"/>
-      <c r="AE15" s="35"/>
-      <c r="AF15" s="35"/>
-      <c r="AG15" s="35"/>
-      <c r="AH15" s="35"/>
-      <c r="AI15" s="35"/>
-      <c r="AJ15" s="35"/>
-      <c r="AK15" s="40"/>
-      <c r="AL15" s="32" t="s">
+      <c r="W15" s="36"/>
+      <c r="X15" s="36"/>
+      <c r="Y15" s="39"/>
+      <c r="Z15" s="39"/>
+      <c r="AA15" s="39"/>
+      <c r="AB15" s="39"/>
+      <c r="AC15" s="39"/>
+      <c r="AD15" s="39"/>
+      <c r="AE15" s="39"/>
+      <c r="AF15" s="39"/>
+      <c r="AG15" s="39"/>
+      <c r="AH15" s="39"/>
+      <c r="AI15" s="39"/>
+      <c r="AJ15" s="39"/>
+      <c r="AK15" s="45"/>
+      <c r="AL15" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="AM15" s="32"/>
-      <c r="AN15" s="32"/>
-      <c r="BT15" s="37"/>
+      <c r="AM15" s="36"/>
+      <c r="AN15" s="36"/>
+      <c r="BT15" s="41"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="29" t="s">
+      <c r="B16" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="38" t="s">
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="F16" s="38" t="s">
+      <c r="F16" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="G16" s="39" t="n">
+      <c r="G16" s="43" t="n">
         <v>5</v>
       </c>
-      <c r="H16" s="39"/>
-      <c r="I16" s="38"/>
-      <c r="J16" s="39" t="n">
+      <c r="H16" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" s="44" t="n">
+        <f aca="false">((2*100%)+(100%-$I$12))/3</f>
+        <v>0.883333333333333</v>
+      </c>
+      <c r="J16" s="43" t="n">
         <v>5</v>
       </c>
-      <c r="P16" s="35"/>
-      <c r="Q16" s="33" t="n">
+      <c r="P16" s="39"/>
+      <c r="Q16" s="37" t="n">
         <f aca="false">J7</f>
         <v>1</v>
       </c>
-      <c r="R16" s="34" t="n">
+      <c r="R16" s="38" t="n">
         <f aca="false">S17-S14</f>
-        <v>7</v>
-      </c>
-      <c r="S16" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="37" t="n">
         <f aca="false">V14-S14</f>
         <v>0</v>
       </c>
-      <c r="T16" s="35"/>
-      <c r="U16" s="35"/>
-      <c r="V16" s="33" t="n">
+      <c r="T16" s="39"/>
+      <c r="U16" s="39"/>
+      <c r="V16" s="37" t="n">
         <f aca="false">J8</f>
         <v>3</v>
       </c>
-      <c r="W16" s="34" t="n">
+      <c r="W16" s="38" t="n">
         <f aca="false">X17-X14</f>
-        <v>7</v>
-      </c>
-      <c r="X16" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" s="37" t="n">
         <f aca="false">MIN(AL14,AL2)-X14</f>
         <v>0</v>
       </c>
-      <c r="Y16" s="35"/>
-      <c r="Z16" s="35"/>
-      <c r="AA16" s="35"/>
-      <c r="AB16" s="35"/>
-      <c r="AC16" s="35"/>
-      <c r="AD16" s="35"/>
-      <c r="AE16" s="35"/>
-      <c r="AF16" s="35"/>
-      <c r="AG16" s="35"/>
-      <c r="AH16" s="35"/>
-      <c r="AI16" s="35"/>
-      <c r="AJ16" s="35"/>
-      <c r="AK16" s="35"/>
-      <c r="AL16" s="33" t="n">
+      <c r="Y16" s="39"/>
+      <c r="Z16" s="39"/>
+      <c r="AA16" s="39"/>
+      <c r="AB16" s="39"/>
+      <c r="AC16" s="39"/>
+      <c r="AD16" s="39"/>
+      <c r="AE16" s="39"/>
+      <c r="AF16" s="39"/>
+      <c r="AG16" s="39"/>
+      <c r="AH16" s="39"/>
+      <c r="AI16" s="39"/>
+      <c r="AJ16" s="39"/>
+      <c r="AK16" s="39"/>
+      <c r="AL16" s="37" t="n">
         <f aca="false">J12</f>
-        <v>10</v>
-      </c>
-      <c r="AM16" s="34" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM16" s="38" t="n">
         <f aca="false">AN17-AN14</f>
-        <v>15</v>
-      </c>
-      <c r="AN16" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" s="37" t="n">
         <f aca="false">BU2-AN14</f>
-        <v>15</v>
-      </c>
-      <c r="AO16" s="35"/>
-      <c r="AP16" s="35"/>
-      <c r="AQ16" s="35"/>
-      <c r="AR16" s="35"/>
-      <c r="AS16" s="35"/>
-      <c r="AT16" s="35"/>
-      <c r="AU16" s="35"/>
-      <c r="AV16" s="35"/>
-      <c r="AW16" s="35"/>
-      <c r="AX16" s="35"/>
-      <c r="AY16" s="35"/>
-      <c r="AZ16" s="35"/>
-      <c r="BA16" s="35"/>
-      <c r="BB16" s="35"/>
-      <c r="BC16" s="35"/>
-      <c r="BD16" s="35"/>
-      <c r="BE16" s="35"/>
-      <c r="BF16" s="35"/>
-      <c r="BG16" s="35"/>
-      <c r="BH16" s="35"/>
-      <c r="BI16" s="35"/>
-      <c r="BJ16" s="35"/>
-      <c r="BK16" s="35"/>
-      <c r="BL16" s="35"/>
-      <c r="BM16" s="35"/>
-      <c r="BN16" s="35"/>
-      <c r="BO16" s="35"/>
-      <c r="BP16" s="35"/>
-      <c r="BQ16" s="35"/>
-      <c r="BR16" s="35"/>
-      <c r="BS16" s="35"/>
+        <v>0</v>
+      </c>
+      <c r="AO16" s="39"/>
+      <c r="AP16" s="39"/>
+      <c r="AQ16" s="39"/>
+      <c r="AR16" s="39"/>
+      <c r="AS16" s="39"/>
+      <c r="AT16" s="39"/>
+      <c r="AU16" s="39"/>
+      <c r="AV16" s="39"/>
+      <c r="AW16" s="39"/>
+      <c r="AX16" s="39"/>
+      <c r="AY16" s="39"/>
+      <c r="AZ16" s="39"/>
+      <c r="BA16" s="39"/>
+      <c r="BB16" s="39"/>
+      <c r="BC16" s="39"/>
+      <c r="BD16" s="39"/>
+      <c r="BE16" s="39"/>
+      <c r="BF16" s="39"/>
+      <c r="BG16" s="39"/>
+      <c r="BH16" s="39"/>
+      <c r="BI16" s="39"/>
+      <c r="BJ16" s="39"/>
+      <c r="BK16" s="39"/>
+      <c r="BL16" s="39"/>
+      <c r="BM16" s="39"/>
+      <c r="BN16" s="39"/>
+      <c r="BO16" s="39"/>
+      <c r="BP16" s="39"/>
+      <c r="BQ16" s="39"/>
+      <c r="BR16" s="39"/>
+      <c r="BS16" s="39"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="41" t="s">
+      <c r="B17" s="46" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="41"/>
-      <c r="D17" s="41"/>
-      <c r="E17" s="42" t="s">
+      <c r="C17" s="46"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="47" t="s">
         <v>57</v>
       </c>
-      <c r="F17" s="43"/>
-      <c r="G17" s="44" t="n">
+      <c r="F17" s="48"/>
+      <c r="G17" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="44"/>
-      <c r="I17" s="43"/>
-      <c r="J17" s="44" t="n">
+      <c r="H17" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="Q17" s="27" t="n">
+      <c r="I17" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="30" t="n">
         <f aca="false">S17-Q16</f>
-        <v>12</v>
-      </c>
-      <c r="R17" s="28"/>
-      <c r="S17" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" s="31"/>
+      <c r="S17" s="30" t="n">
         <f aca="false">V17</f>
-        <v>13</v>
-      </c>
-      <c r="V17" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="V17" s="30" t="n">
         <f aca="false">X17-V16</f>
-        <v>13</v>
-      </c>
-      <c r="W17" s="28"/>
-      <c r="X17" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="W17" s="31"/>
+      <c r="X17" s="30" t="n">
         <f aca="false">MIN(AL5,AL17)</f>
-        <v>16</v>
-      </c>
-      <c r="AL17" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL17" s="30" t="n">
         <f aca="false">AN17-AL16</f>
-        <v>24</v>
-      </c>
-      <c r="AM17" s="28"/>
-      <c r="AN17" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM17" s="31"/>
+      <c r="AN17" s="30" t="n">
         <f aca="false">BU5</f>
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="45" t="s">
+      <c r="A19" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="B19" s="46" t="s">
+      <c r="B19" s="52" t="s">
         <v>59</v>
       </c>
-      <c r="C19" s="47"/>
-      <c r="D19" s="48" t="s">
+      <c r="C19" s="53"/>
+      <c r="D19" s="54" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="32" t="s">
+      <c r="B20" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="C20" s="32"/>
-      <c r="D20" s="32"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="32" t="s">
+      <c r="B21" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="C21" s="34" t="s">
+      <c r="C21" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="D21" s="33" t="s">
+      <c r="D21" s="37" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="49" t="s">
+      <c r="A22" s="55" t="s">
         <v>63</v>
       </c>
-      <c r="B22" s="50" t="s">
+      <c r="B22" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="C22" s="51"/>
-      <c r="D22" s="52" t="s">
+      <c r="C22" s="57"/>
+      <c r="D22" s="58" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="53" t="s">
+      <c r="B24" s="59" t="s">
         <v>64</v>
       </c>
-      <c r="C24" s="28"/>
-      <c r="D24" s="27" t="s">
+      <c r="C24" s="31"/>
+      <c r="D24" s="30" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="32" t="s">
+      <c r="B25" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="C25" s="32"/>
-      <c r="D25" s="32"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="36"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="32" t="s">
+      <c r="B26" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="C26" s="34" t="s">
+      <c r="C26" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="D26" s="33" t="s">
+      <c r="D26" s="37" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="53" t="s">
+      <c r="B27" s="59" t="s">
         <v>70</v>
       </c>
-      <c r="C27" s="28"/>
-      <c r="D27" s="27" t="s">
+      <c r="C27" s="31"/>
+      <c r="D27" s="30" t="s">
         <v>71</v>
       </c>
     </row>
@@ -3463,58 +3573,58 @@
       <c r="A29" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="B29" s="54" t="s">
+      <c r="B29" s="60" t="s">
         <v>72</v>
       </c>
-      <c r="C29" s="55" t="s">
+      <c r="C29" s="61" t="s">
         <v>73</v>
       </c>
-      <c r="D29" s="55"/>
+      <c r="D29" s="61"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="B30" s="54" t="s">
+      <c r="B30" s="60" t="s">
         <v>72</v>
       </c>
-      <c r="C30" s="55" t="s">
+      <c r="C30" s="61" t="s">
         <v>74</v>
       </c>
-      <c r="D30" s="55"/>
+      <c r="D30" s="61"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="54"/>
+      <c r="B31" s="60"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="B32" s="54" t="s">
+      <c r="B32" s="60" t="s">
         <v>72</v>
       </c>
-      <c r="C32" s="55" t="s">
+      <c r="C32" s="61" t="s">
         <v>74</v>
       </c>
-      <c r="D32" s="55"/>
+      <c r="D32" s="61"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="B33" s="54" t="s">
+      <c r="B33" s="60" t="s">
         <v>72</v>
       </c>
-      <c r="C33" s="55" t="s">
+      <c r="C33" s="61" t="s">
         <v>73</v>
       </c>
-      <c r="D33" s="55"/>
+      <c r="D33" s="61"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="54"/>
+      <c r="B34" s="60"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="54"/>
+      <c r="B35" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="39">
@@ -3570,5 +3680,6 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Übungen/Online_Shop.xlsx
+++ b/Übungen/Online_Shop.xlsx
@@ -360,7 +360,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -438,6 +438,13 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="23">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -473,7 +480,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="59">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -610,7 +617,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -634,11 +641,19 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -793,13 +808,13 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>907200</xdr:colOff>
+      <xdr:colOff>907560</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>154440</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>11520</xdr:colOff>
+      <xdr:colOff>11880</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>154440</xdr:rowOff>
     </xdr:to>
@@ -810,8 +825,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="5483520" y="479520"/>
-          <a:ext cx="5536080" cy="0"/>
+          <a:off x="5488560" y="479520"/>
+          <a:ext cx="5545080" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -852,7 +867,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5483160" y="488160"/>
+          <a:off x="5488200" y="488160"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -893,7 +908,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5482440" y="488160"/>
+          <a:off x="5487480" y="488160"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -935,7 +950,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5495040" y="1125360"/>
+          <a:off x="5501520" y="1125360"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -977,7 +992,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5495040" y="1612800"/>
+          <a:off x="5501520" y="1612800"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1019,7 +1034,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5495040" y="2099880"/>
+          <a:off x="5501520" y="2099880"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1061,7 +1076,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5495040" y="2587320"/>
+          <a:off x="5501520" y="2587320"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1103,7 +1118,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8251560" y="324720"/>
+          <a:off x="8261640" y="324720"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1145,7 +1160,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8251560" y="487440"/>
+          <a:off x="8261640" y="487440"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1187,7 +1202,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8251560" y="1125360"/>
+          <a:off x="8261640" y="1125360"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1229,7 +1244,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8251560" y="1612800"/>
+          <a:off x="8261640" y="1612800"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1271,7 +1286,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8251560" y="2587320"/>
+          <a:off x="8261640" y="2587320"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1313,7 +1328,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8251560" y="3074400"/>
+          <a:off x="8261640" y="3074400"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1355,7 +1370,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8251560" y="4048920"/>
+          <a:off x="8261640" y="4048920"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1397,7 +1412,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8251560" y="5023440"/>
+          <a:off x="8261640" y="5023440"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1439,7 +1454,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11008440" y="487440"/>
+          <a:off x="11022480" y="487440"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1481,7 +1496,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11008440" y="1125360"/>
+          <a:off x="11022480" y="1125360"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1523,7 +1538,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11008440" y="1612800"/>
+          <a:off x="11022480" y="1612800"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1565,7 +1580,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11008440" y="2099880"/>
+          <a:off x="11022480" y="2099880"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1607,7 +1622,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8244000" y="3557520"/>
+          <a:off x="8253000" y="3557520"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1649,7 +1664,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8244000" y="4533480"/>
+          <a:off x="8253000" y="4533480"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1691,7 +1706,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8244000" y="2093760"/>
+          <a:off x="8253000" y="2093760"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1722,7 +1737,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M41"/>
-  <sheetFormatPr defaultColWidth="13.0390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="13.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.77"/>
   </cols>
@@ -2264,7 +2279,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:BT35"/>
-  <sheetFormatPr defaultColWidth="11.78515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.8046875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="20" width="11.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.52"/>
@@ -2313,57 +2328,100 @@
         <v>0</v>
       </c>
       <c r="J2" s="28"/>
-      <c r="K2" s="27"/>
+      <c r="K2" s="27" t="n">
+        <f aca="false">I2+I4</f>
+        <v>5</v>
+      </c>
       <c r="N2" s="27" t="n">
-        <v>0</v>
+        <f aca="false">K2</f>
+        <v>5</v>
       </c>
       <c r="O2" s="28"/>
-      <c r="P2" s="27"/>
+      <c r="P2" s="27" t="n">
+        <f aca="false">N2+N4</f>
+        <v>6</v>
+      </c>
       <c r="S2" s="27" t="n">
-        <v>0</v>
+        <f aca="false">P2</f>
+        <v>6</v>
       </c>
       <c r="T2" s="28"/>
-      <c r="U2" s="27"/>
+      <c r="U2" s="27" t="n">
+        <f aca="false">S2+S4</f>
+        <v>10</v>
+      </c>
       <c r="AI2" s="27" t="n">
-        <v>0</v>
+        <f aca="false">MAX(U2,Z8)</f>
+        <v>16</v>
       </c>
       <c r="AJ2" s="28"/>
-      <c r="AK2" s="27"/>
+      <c r="AK2" s="27" t="n">
+        <f aca="false">AI2+AI4</f>
+        <v>18</v>
+      </c>
       <c r="AN2" s="27" t="n">
-        <v>0</v>
+        <f aca="false">AK2</f>
+        <v>18</v>
       </c>
       <c r="AO2" s="28"/>
-      <c r="AP2" s="27"/>
+      <c r="AP2" s="27" t="n">
+        <f aca="false">AN2+AN4</f>
+        <v>20</v>
+      </c>
       <c r="AS2" s="27" t="n">
-        <v>0</v>
+        <f aca="false">AP2</f>
+        <v>20</v>
       </c>
       <c r="AT2" s="28"/>
-      <c r="AU2" s="27"/>
+      <c r="AU2" s="27" t="n">
+        <f aca="false">AS2+AS4</f>
+        <v>22</v>
+      </c>
       <c r="AX2" s="27" t="n">
-        <v>0</v>
+        <f aca="false">AU2</f>
+        <v>22</v>
       </c>
       <c r="AY2" s="28"/>
-      <c r="AZ2" s="27"/>
+      <c r="AZ2" s="27" t="n">
+        <f aca="false">AX2+AX4</f>
+        <v>25</v>
+      </c>
       <c r="BC2" s="27" t="n">
-        <v>0</v>
+        <f aca="false">AZ2</f>
+        <v>25</v>
       </c>
       <c r="BD2" s="28"/>
-      <c r="BE2" s="27"/>
+      <c r="BE2" s="27" t="n">
+        <f aca="false">BC2+BC4</f>
+        <v>28</v>
+      </c>
       <c r="BH2" s="27" t="n">
-        <v>0</v>
+        <f aca="false">BE2</f>
+        <v>28</v>
       </c>
       <c r="BI2" s="28"/>
-      <c r="BJ2" s="27"/>
+      <c r="BJ2" s="27" t="n">
+        <f aca="false">BH2+BH4</f>
+        <v>29</v>
+      </c>
       <c r="BM2" s="27" t="n">
-        <v>0</v>
+        <f aca="false">BJ2</f>
+        <v>29</v>
       </c>
       <c r="BN2" s="28"/>
-      <c r="BO2" s="27"/>
+      <c r="BO2" s="27" t="n">
+        <f aca="false">BM2+BM4</f>
+        <v>34</v>
+      </c>
       <c r="BR2" s="27" t="n">
-        <v>0</v>
+        <f aca="false">MAX(BO2,AK14)</f>
+        <v>34</v>
       </c>
       <c r="BS2" s="28"/>
-      <c r="BT2" s="27"/>
+      <c r="BT2" s="27" t="n">
+        <f aca="false">BR2+BR4</f>
+        <v>35</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
@@ -2439,7 +2497,7 @@
       <c r="BS3" s="32"/>
       <c r="BT3" s="32"/>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="12.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
         <v>21</v>
       </c>
@@ -2461,24 +2519,42 @@
         <f aca="false">G2</f>
         <v>5</v>
       </c>
-      <c r="J4" s="34"/>
-      <c r="K4" s="33"/>
+      <c r="J4" s="34" t="n">
+        <f aca="false">K5-K2</f>
+        <v>0</v>
+      </c>
+      <c r="K4" s="33" t="n">
+        <f aca="false">MIN(N2,N14)-K2</f>
+        <v>0</v>
+      </c>
       <c r="L4" s="35"/>
       <c r="M4" s="36"/>
       <c r="N4" s="33" t="n">
         <f aca="false">G3</f>
         <v>1</v>
       </c>
-      <c r="O4" s="34"/>
-      <c r="P4" s="33"/>
+      <c r="O4" s="34" t="n">
+        <f aca="false">P5-P2</f>
+        <v>0</v>
+      </c>
+      <c r="P4" s="33" t="n">
+        <f aca="false">MIN(S2,S8)-P2</f>
+        <v>0</v>
+      </c>
       <c r="Q4" s="35"/>
       <c r="R4" s="36"/>
       <c r="S4" s="33" t="n">
         <f aca="false">G4</f>
         <v>4</v>
       </c>
-      <c r="T4" s="34"/>
-      <c r="U4" s="33"/>
+      <c r="T4" s="34" t="n">
+        <f aca="false">U5-U2</f>
+        <v>6</v>
+      </c>
+      <c r="U4" s="33" t="n">
+        <f aca="false">AI2-U2</f>
+        <v>6</v>
+      </c>
       <c r="V4" s="35"/>
       <c r="W4" s="35"/>
       <c r="X4" s="35"/>
@@ -2496,63 +2572,108 @@
         <f aca="false">G9</f>
         <v>2</v>
       </c>
-      <c r="AJ4" s="34"/>
-      <c r="AK4" s="33"/>
+      <c r="AJ4" s="34" t="n">
+        <f aca="false">AK5-AK2</f>
+        <v>0</v>
+      </c>
+      <c r="AK4" s="33" t="n">
+        <f aca="false">AN2-AK2</f>
+        <v>0</v>
+      </c>
       <c r="AL4" s="35"/>
       <c r="AM4" s="35"/>
       <c r="AN4" s="33" t="n">
         <f aca="false">G10</f>
         <v>2</v>
       </c>
-      <c r="AO4" s="34"/>
-      <c r="AP4" s="33"/>
+      <c r="AO4" s="34" t="n">
+        <f aca="false">AP5-AP2</f>
+        <v>0</v>
+      </c>
+      <c r="AP4" s="33" t="n">
+        <f aca="false">AS2-AP2</f>
+        <v>0</v>
+      </c>
       <c r="AQ4" s="35"/>
       <c r="AR4" s="35"/>
       <c r="AS4" s="33" t="n">
         <f aca="false">G11</f>
         <v>2</v>
       </c>
-      <c r="AT4" s="34"/>
-      <c r="AU4" s="33"/>
+      <c r="AT4" s="34" t="n">
+        <f aca="false">AU5-AU2</f>
+        <v>0</v>
+      </c>
+      <c r="AU4" s="33" t="n">
+        <f aca="false">AX2-AU2</f>
+        <v>0</v>
+      </c>
       <c r="AV4" s="35"/>
       <c r="AW4" s="35"/>
       <c r="AX4" s="33" t="n">
         <f aca="false">G13</f>
         <v>3</v>
       </c>
-      <c r="AY4" s="34"/>
-      <c r="AZ4" s="33"/>
+      <c r="AY4" s="34" t="n">
+        <f aca="false">AZ5-AZ2</f>
+        <v>0</v>
+      </c>
+      <c r="AZ4" s="33" t="n">
+        <f aca="false">BC2-AZ2</f>
+        <v>0</v>
+      </c>
       <c r="BA4" s="35"/>
       <c r="BB4" s="35"/>
       <c r="BC4" s="33" t="n">
         <f aca="false">G14</f>
         <v>3</v>
       </c>
-      <c r="BD4" s="34"/>
-      <c r="BE4" s="33"/>
+      <c r="BD4" s="34" t="n">
+        <f aca="false">BE5-BE2</f>
+        <v>0</v>
+      </c>
+      <c r="BE4" s="33" t="n">
+        <f aca="false">BH2-BE2</f>
+        <v>0</v>
+      </c>
       <c r="BF4" s="35"/>
       <c r="BG4" s="35"/>
       <c r="BH4" s="33" t="n">
         <f aca="false">G15</f>
         <v>1</v>
       </c>
-      <c r="BI4" s="34"/>
-      <c r="BJ4" s="33"/>
+      <c r="BI4" s="34" t="n">
+        <f aca="false">BJ5-BJ2</f>
+        <v>0</v>
+      </c>
+      <c r="BJ4" s="33" t="n">
+        <f aca="false">BM2-BJ2</f>
+        <v>0</v>
+      </c>
       <c r="BK4" s="35"/>
       <c r="BL4" s="35"/>
       <c r="BM4" s="33" t="n">
         <f aca="false">G16</f>
         <v>5</v>
       </c>
-      <c r="BN4" s="34"/>
-      <c r="BO4" s="33"/>
+      <c r="BN4" s="34" t="n">
+        <f aca="false">BO5-BO2</f>
+        <v>0</v>
+      </c>
+      <c r="BO4" s="33" t="n">
+        <f aca="false">BR2-BO2</f>
+        <v>0</v>
+      </c>
       <c r="BP4" s="35"/>
       <c r="BQ4" s="36"/>
       <c r="BR4" s="33" t="n">
         <f aca="false">G17</f>
         <v>1</v>
       </c>
-      <c r="BS4" s="34"/>
+      <c r="BS4" s="34" t="n">
+        <f aca="false">BT5-BT2</f>
+        <v>0</v>
+      </c>
       <c r="BT4" s="33"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2577,61 +2698,104 @@
         <v>0</v>
       </c>
       <c r="J5" s="28"/>
-      <c r="K5" s="27"/>
+      <c r="K5" s="27" t="n">
+        <f aca="false">MIN(N5,N17)</f>
+        <v>5</v>
+      </c>
       <c r="M5" s="37"/>
       <c r="N5" s="27" t="n">
-        <v>0</v>
+        <f aca="false">P5-N4</f>
+        <v>5</v>
       </c>
       <c r="O5" s="28"/>
-      <c r="P5" s="27"/>
+      <c r="P5" s="27" t="n">
+        <f aca="false">MIN(S5,S11)</f>
+        <v>6</v>
+      </c>
       <c r="R5" s="37"/>
       <c r="S5" s="27" t="n">
-        <v>0</v>
+        <f aca="false">U5-S4</f>
+        <v>12</v>
       </c>
       <c r="T5" s="28"/>
-      <c r="U5" s="27"/>
+      <c r="U5" s="27" t="n">
+        <f aca="false">AI5</f>
+        <v>16</v>
+      </c>
       <c r="AH5" s="37"/>
       <c r="AI5" s="27" t="n">
-        <v>0</v>
+        <f aca="false">AK5-AI4</f>
+        <v>16</v>
       </c>
       <c r="AJ5" s="28"/>
-      <c r="AK5" s="27"/>
+      <c r="AK5" s="27" t="n">
+        <f aca="false">AN5</f>
+        <v>18</v>
+      </c>
       <c r="AN5" s="27" t="n">
-        <v>0</v>
+        <f aca="false">AP5-AN4</f>
+        <v>18</v>
       </c>
       <c r="AO5" s="28"/>
-      <c r="AP5" s="27"/>
+      <c r="AP5" s="27" t="n">
+        <f aca="false">AS5</f>
+        <v>20</v>
+      </c>
       <c r="AS5" s="27" t="n">
-        <v>0</v>
+        <f aca="false">AU5-AS4</f>
+        <v>20</v>
       </c>
       <c r="AT5" s="28"/>
-      <c r="AU5" s="27"/>
+      <c r="AU5" s="27" t="n">
+        <f aca="false">AX5</f>
+        <v>22</v>
+      </c>
       <c r="AX5" s="27" t="n">
-        <v>0</v>
+        <f aca="false">AZ5-AX4</f>
+        <v>22</v>
       </c>
       <c r="AY5" s="28"/>
-      <c r="AZ5" s="27"/>
+      <c r="AZ5" s="27" t="n">
+        <f aca="false">BC5</f>
+        <v>25</v>
+      </c>
       <c r="BC5" s="27" t="n">
-        <v>0</v>
+        <f aca="false">BE5-BC4</f>
+        <v>25</v>
       </c>
       <c r="BD5" s="28"/>
-      <c r="BE5" s="27"/>
+      <c r="BE5" s="27" t="n">
+        <f aca="false">BH5</f>
+        <v>28</v>
+      </c>
       <c r="BH5" s="27" t="n">
-        <v>0</v>
+        <f aca="false">BJ5-BH4</f>
+        <v>28</v>
       </c>
       <c r="BI5" s="28"/>
-      <c r="BJ5" s="27"/>
+      <c r="BJ5" s="27" t="n">
+        <f aca="false">BM5</f>
+        <v>29</v>
+      </c>
       <c r="BM5" s="27" t="n">
-        <v>0</v>
+        <f aca="false">BO5-BM4</f>
+        <v>29</v>
       </c>
       <c r="BN5" s="28"/>
-      <c r="BO5" s="27"/>
+      <c r="BO5" s="27" t="n">
+        <f aca="false">BR5</f>
+        <v>34</v>
+      </c>
       <c r="BQ5" s="37"/>
       <c r="BR5" s="27" t="n">
-        <v>0</v>
+        <f aca="false">BT5-BR4</f>
+        <v>34</v>
       </c>
       <c r="BS5" s="28"/>
-      <c r="BT5" s="27"/>
+      <c r="BT5" s="27" t="n">
+        <f aca="false">BT2</f>
+        <v>35</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
@@ -2700,15 +2864,23 @@
       <c r="M8" s="37"/>
       <c r="R8" s="37"/>
       <c r="S8" s="27" t="n">
-        <v>0</v>
+        <f aca="false">P2</f>
+        <v>6</v>
       </c>
       <c r="T8" s="28"/>
-      <c r="U8" s="27"/>
+      <c r="U8" s="27" t="n">
+        <f aca="false">S8+S10</f>
+        <v>9</v>
+      </c>
       <c r="X8" s="27" t="n">
-        <v>0</v>
+        <f aca="false">U8</f>
+        <v>9</v>
       </c>
       <c r="Y8" s="28"/>
-      <c r="Z8" s="27"/>
+      <c r="Z8" s="27" t="n">
+        <f aca="false">X8+X10</f>
+        <v>16</v>
+      </c>
       <c r="AH8" s="37"/>
       <c r="BQ8" s="37"/>
     </row>
@@ -2745,7 +2917,7 @@
       <c r="AH9" s="37"/>
       <c r="BQ9" s="37"/>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="12.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
         <v>35</v>
       </c>
@@ -2769,16 +2941,28 @@
         <f aca="false">G5</f>
         <v>3</v>
       </c>
-      <c r="T10" s="34"/>
-      <c r="U10" s="33"/>
+      <c r="T10" s="34" t="n">
+        <f aca="false">U11-U8</f>
+        <v>0</v>
+      </c>
+      <c r="U10" s="33" t="n">
+        <f aca="false">X8-U8</f>
+        <v>0</v>
+      </c>
       <c r="V10" s="35"/>
       <c r="W10" s="35"/>
       <c r="X10" s="33" t="n">
         <f aca="false">G6</f>
         <v>7</v>
       </c>
-      <c r="Y10" s="34"/>
-      <c r="Z10" s="40"/>
+      <c r="Y10" s="34" t="n">
+        <f aca="false">Z11-Z8</f>
+        <v>0</v>
+      </c>
+      <c r="Z10" s="40" t="n">
+        <f aca="false">AI2-Z8</f>
+        <v>0</v>
+      </c>
       <c r="AA10" s="35"/>
       <c r="AB10" s="35"/>
       <c r="AC10" s="35"/>
@@ -2809,15 +2993,23 @@
       </c>
       <c r="M11" s="37"/>
       <c r="S11" s="27" t="n">
-        <v>0</v>
+        <f aca="false">U11-S10</f>
+        <v>6</v>
       </c>
       <c r="T11" s="28"/>
-      <c r="U11" s="27"/>
+      <c r="U11" s="27" t="n">
+        <f aca="false">X11</f>
+        <v>9</v>
+      </c>
       <c r="X11" s="27" t="n">
-        <v>0</v>
+        <f aca="false">Z11-X10</f>
+        <v>9</v>
       </c>
       <c r="Y11" s="28"/>
-      <c r="Z11" s="27"/>
+      <c r="Z11" s="27" t="n">
+        <f aca="false">AI5</f>
+        <v>16</v>
+      </c>
       <c r="AH11" s="37"/>
       <c r="BQ11" s="37"/>
     </row>
@@ -2887,22 +3079,45 @@
       </c>
       <c r="M14" s="37"/>
       <c r="N14" s="27" t="n">
-        <v>0</v>
+        <f aca="false">K2</f>
+        <v>5</v>
       </c>
       <c r="O14" s="28"/>
-      <c r="P14" s="27"/>
+      <c r="P14" s="27" t="n">
+        <f aca="false">N14+N16</f>
+        <v>6</v>
+      </c>
       <c r="S14" s="27" t="n">
-        <v>0</v>
+        <f aca="false">P14</f>
+        <v>6</v>
       </c>
       <c r="T14" s="28"/>
-      <c r="U14" s="27"/>
-      <c r="X14" s="41"/>
+      <c r="U14" s="27" t="n">
+        <f aca="false">S14+S16</f>
+        <v>9</v>
+      </c>
+      <c r="V14" s="42"/>
+      <c r="W14" s="42"/>
+      <c r="X14" s="42"/>
+      <c r="Y14" s="42"/>
+      <c r="Z14" s="42"/>
+      <c r="AA14" s="42"/>
+      <c r="AB14" s="42"/>
+      <c r="AC14" s="42"/>
+      <c r="AD14" s="42"/>
+      <c r="AE14" s="42"/>
+      <c r="AF14" s="42"/>
+      <c r="AG14" s="42"/>
       <c r="AH14" s="37"/>
       <c r="AI14" s="27" t="n">
-        <v>0</v>
+        <f aca="false">U14</f>
+        <v>9</v>
       </c>
       <c r="AJ14" s="28"/>
-      <c r="AK14" s="27"/>
+      <c r="AK14" s="27" t="n">
+        <f aca="false">AI14+AI16</f>
+        <v>19</v>
+      </c>
       <c r="BQ14" s="37"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2935,7 +3150,7 @@
       <c r="T15" s="32"/>
       <c r="U15" s="32"/>
       <c r="X15" s="41"/>
-      <c r="AH15" s="37"/>
+      <c r="AH15" s="43"/>
       <c r="AI15" s="32" t="s">
         <v>17</v>
       </c>
@@ -2966,16 +3181,28 @@
         <f aca="false">G7</f>
         <v>1</v>
       </c>
-      <c r="O16" s="34"/>
-      <c r="P16" s="33"/>
+      <c r="O16" s="34" t="n">
+        <f aca="false">P17-P14</f>
+        <v>7</v>
+      </c>
+      <c r="P16" s="33" t="n">
+        <f aca="false">S14-P14</f>
+        <v>0</v>
+      </c>
       <c r="Q16" s="35"/>
       <c r="R16" s="35"/>
       <c r="S16" s="33" t="n">
         <f aca="false">G8</f>
         <v>3</v>
       </c>
-      <c r="T16" s="34"/>
-      <c r="U16" s="33"/>
+      <c r="T16" s="34" t="n">
+        <f aca="false">U17-U14</f>
+        <v>7</v>
+      </c>
+      <c r="U16" s="33" t="n">
+        <f aca="false">MIN(AI2,AI14)-U14</f>
+        <v>0</v>
+      </c>
       <c r="V16" s="35"/>
       <c r="W16" s="35"/>
       <c r="X16" s="35"/>
@@ -2993,8 +3220,14 @@
         <f aca="false">G12</f>
         <v>10</v>
       </c>
-      <c r="AJ16" s="34"/>
-      <c r="AK16" s="40"/>
+      <c r="AJ16" s="34" t="n">
+        <f aca="false">AK17-AK14</f>
+        <v>15</v>
+      </c>
+      <c r="AK16" s="40" t="n">
+        <f aca="false">BR2-AK14</f>
+        <v>15</v>
+      </c>
       <c r="AL16" s="35"/>
       <c r="AM16" s="35"/>
       <c r="AN16" s="35"/>
@@ -3031,43 +3264,55 @@
       <c r="A17" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="42" t="s">
+      <c r="B17" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="42"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="43" t="s">
+      <c r="C17" s="44"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="F17" s="44"/>
-      <c r="G17" s="45" t="n">
+      <c r="F17" s="46"/>
+      <c r="G17" s="47" t="n">
         <v>1</v>
       </c>
       <c r="N17" s="27" t="n">
-        <v>0</v>
+        <f aca="false">P17-N16</f>
+        <v>12</v>
       </c>
       <c r="O17" s="28"/>
-      <c r="P17" s="27"/>
+      <c r="P17" s="27" t="n">
+        <f aca="false">S17</f>
+        <v>13</v>
+      </c>
       <c r="S17" s="27" t="n">
-        <v>0</v>
+        <f aca="false">U17-S16</f>
+        <v>13</v>
       </c>
       <c r="T17" s="28"/>
-      <c r="U17" s="27"/>
+      <c r="U17" s="27" t="n">
+        <f aca="false">MIN(AI5,AI17)</f>
+        <v>16</v>
+      </c>
       <c r="AI17" s="27" t="n">
-        <v>0</v>
+        <f aca="false">AK17-AI16</f>
+        <v>24</v>
       </c>
       <c r="AJ17" s="28"/>
-      <c r="AK17" s="27"/>
+      <c r="AK17" s="27" t="n">
+        <f aca="false">BR5</f>
+        <v>34</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="46" t="s">
+      <c r="A19" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="47" t="s">
+      <c r="B19" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="C19" s="48"/>
-      <c r="D19" s="49" t="s">
+      <c r="C19" s="50"/>
+      <c r="D19" s="51" t="s">
         <v>57</v>
       </c>
     </row>
@@ -3090,19 +3335,19 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="50" t="s">
+      <c r="A22" s="52" t="s">
         <v>60</v>
       </c>
-      <c r="B22" s="51" t="s">
+      <c r="B22" s="53" t="s">
         <v>56</v>
       </c>
-      <c r="C22" s="52"/>
-      <c r="D22" s="53" t="s">
+      <c r="C22" s="54"/>
+      <c r="D22" s="55" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="54" t="s">
+      <c r="B24" s="56" t="s">
         <v>61</v>
       </c>
       <c r="C24" s="28"/>
@@ -3129,7 +3374,7 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="54" t="s">
+      <c r="B27" s="56" t="s">
         <v>67</v>
       </c>
       <c r="C27" s="28"/>
@@ -3141,58 +3386,58 @@
       <c r="A29" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="B29" s="55" t="s">
+      <c r="B29" s="57" t="s">
         <v>69</v>
       </c>
-      <c r="C29" s="56" t="s">
+      <c r="C29" s="58" t="s">
         <v>70</v>
       </c>
-      <c r="D29" s="56"/>
+      <c r="D29" s="58"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
         <v>62</v>
       </c>
-      <c r="B30" s="55" t="s">
+      <c r="B30" s="57" t="s">
         <v>69</v>
       </c>
-      <c r="C30" s="56" t="s">
+      <c r="C30" s="58" t="s">
         <v>71</v>
       </c>
-      <c r="D30" s="56"/>
+      <c r="D30" s="58"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="55"/>
+      <c r="B31" s="57"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
         <v>62</v>
       </c>
-      <c r="B32" s="55" t="s">
+      <c r="B32" s="57" t="s">
         <v>69</v>
       </c>
-      <c r="C32" s="56" t="s">
+      <c r="C32" s="58" t="s">
         <v>71</v>
       </c>
-      <c r="D32" s="56"/>
+      <c r="D32" s="58"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="B33" s="55" t="s">
+      <c r="B33" s="57" t="s">
         <v>69</v>
       </c>
-      <c r="C33" s="56" t="s">
+      <c r="C33" s="58" t="s">
         <v>70</v>
       </c>
-      <c r="D33" s="56"/>
+      <c r="D33" s="58"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="55"/>
+      <c r="B34" s="57"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="55"/>
+      <c r="B35" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="39">
@@ -3236,7 +3481,7 @@
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="C33:D33"/>
   </mergeCells>
-  <conditionalFormatting sqref="J4 C21 C26 O4 T4 O16 U16 AJ4 AO4 AT4 AY4 S10:T10 AK16 BD4 BI4 BN4 BS4">
+  <conditionalFormatting sqref="C21 C26 T16:U16 S10:T10 AJ16:AK16 BS4 BN4 BI4 BD4 AY4 AT4 AO4 AJ4 Y10 T4 O16 O4 J4">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>

--- a/Übungen/Online_Shop.xlsx
+++ b/Übungen/Online_Shop.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="78">
   <si>
     <t xml:space="preserve">Beispiel: Funktionsorientierter Projektstrukturplan</t>
   </si>
@@ -168,13 +168,31 @@
     <t xml:space="preserve">Nachfolger</t>
   </si>
   <si>
+    <t xml:space="preserve">Aufwand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kapazität</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dauer</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.1, 1.2.2</t>
   </si>
   <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.1.2, 1.1.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
   </si>
   <si>
     <t xml:space="preserve">1.2.4, 1.3.1</t>
@@ -244,11 +262,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
     <numFmt numFmtId="166" formatCode="@"/>
-    <numFmt numFmtId="167" formatCode="General"/>
+    <numFmt numFmtId="167" formatCode="0.00\ %"/>
+    <numFmt numFmtId="168" formatCode="General"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -480,7 +499,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="64">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -565,6 +584,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -573,6 +596,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="167" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -589,6 +616,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -609,15 +640,19 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -641,7 +676,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1731,6 +1770,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
@@ -2278,1200 +2321,1379 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BT35"/>
+  <dimension ref="A1:BW35"/>
   <sheetFormatPr defaultColWidth="11.8046875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="20" width="11.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="16.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="3" width="11.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="104" min="8" style="0" width="3.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1022" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="3" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="21" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="3" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="107" min="11" style="0" width="3.83"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="22" t="s">
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="G1" s="22" t="s">
+      <c r="G1" s="23" t="s">
         <v>48</v>
+      </c>
+      <c r="H1" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="I1" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" s="23" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="25" t="s">
-        <v>49</v>
-      </c>
-      <c r="G2" s="26" t="n">
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="G2" s="28" t="n">
         <v>5</v>
       </c>
-      <c r="I2" s="27" t="n">
+      <c r="H2" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="I2" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" s="28" t="n">
+        <f aca="false">ROUNDUP(G2/(H2*I2),0)</f>
+        <v>2</v>
+      </c>
+      <c r="L2" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="28"/>
-      <c r="K2" s="27" t="n">
-        <f aca="false">I2+I4</f>
-        <v>5</v>
-      </c>
-      <c r="N2" s="27" t="n">
-        <f aca="false">K2</f>
-        <v>5</v>
-      </c>
-      <c r="O2" s="28"/>
-      <c r="P2" s="27" t="n">
-        <f aca="false">N2+N4</f>
-        <v>6</v>
-      </c>
-      <c r="S2" s="27" t="n">
-        <f aca="false">P2</f>
-        <v>6</v>
-      </c>
-      <c r="T2" s="28"/>
-      <c r="U2" s="27" t="n">
-        <f aca="false">S2+S4</f>
-        <v>10</v>
-      </c>
-      <c r="AI2" s="27" t="n">
-        <f aca="false">MAX(U2,Z8)</f>
+      <c r="M2" s="31"/>
+      <c r="N2" s="30" t="n">
+        <f aca="false">L2+L4</f>
+        <v>2</v>
+      </c>
+      <c r="Q2" s="30" t="n">
+        <f aca="false">N2</f>
+        <v>2</v>
+      </c>
+      <c r="R2" s="31"/>
+      <c r="S2" s="30" t="n">
+        <f aca="false">Q2+Q4</f>
+        <v>3</v>
+      </c>
+      <c r="V2" s="30" t="n">
+        <f aca="false">S2</f>
+        <v>3</v>
+      </c>
+      <c r="W2" s="31"/>
+      <c r="X2" s="30" t="n">
+        <f aca="false">V2+V4</f>
+        <v>11</v>
+      </c>
+      <c r="AL2" s="30" t="n">
+        <f aca="false">MAX(X2,AC8)</f>
+        <v>11</v>
+      </c>
+      <c r="AM2" s="31"/>
+      <c r="AN2" s="30" t="n">
+        <f aca="false">AL2+AL4</f>
+        <v>12</v>
+      </c>
+      <c r="AQ2" s="30" t="n">
+        <f aca="false">AN2</f>
+        <v>12</v>
+      </c>
+      <c r="AR2" s="31"/>
+      <c r="AS2" s="30" t="n">
+        <f aca="false">AQ2+AQ4</f>
+        <v>13</v>
+      </c>
+      <c r="AV2" s="30" t="n">
+        <f aca="false">AS2</f>
+        <v>13</v>
+      </c>
+      <c r="AW2" s="31"/>
+      <c r="AX2" s="30" t="n">
+        <f aca="false">AV2+AV4</f>
+        <v>14</v>
+      </c>
+      <c r="BA2" s="30" t="n">
+        <f aca="false">AX2</f>
+        <v>14</v>
+      </c>
+      <c r="BB2" s="31"/>
+      <c r="BC2" s="30" t="n">
+        <f aca="false">BA2+BA4</f>
         <v>16</v>
       </c>
-      <c r="AJ2" s="28"/>
-      <c r="AK2" s="27" t="n">
-        <f aca="false">AI2+AI4</f>
+      <c r="BF2" s="30" t="n">
+        <f aca="false">BC2</f>
+        <v>16</v>
+      </c>
+      <c r="BG2" s="31"/>
+      <c r="BH2" s="30" t="n">
+        <f aca="false">BF2+BF4</f>
         <v>18</v>
       </c>
-      <c r="AN2" s="27" t="n">
-        <f aca="false">AK2</f>
+      <c r="BK2" s="30" t="n">
+        <f aca="false">BH2</f>
         <v>18</v>
       </c>
-      <c r="AO2" s="28"/>
-      <c r="AP2" s="27" t="n">
-        <f aca="false">AN2+AN4</f>
-        <v>20</v>
-      </c>
-      <c r="AS2" s="27" t="n">
-        <f aca="false">AP2</f>
-        <v>20</v>
-      </c>
-      <c r="AT2" s="28"/>
-      <c r="AU2" s="27" t="n">
-        <f aca="false">AS2+AS4</f>
+      <c r="BL2" s="31"/>
+      <c r="BM2" s="30" t="n">
+        <f aca="false">BK2+BK4</f>
+        <v>19</v>
+      </c>
+      <c r="BP2" s="30" t="n">
+        <f aca="false">BM2</f>
+        <v>19</v>
+      </c>
+      <c r="BQ2" s="31"/>
+      <c r="BR2" s="30" t="n">
+        <f aca="false">BP2+BP4</f>
         <v>22</v>
       </c>
-      <c r="AX2" s="27" t="n">
-        <f aca="false">AU2</f>
-        <v>22</v>
-      </c>
-      <c r="AY2" s="28"/>
-      <c r="AZ2" s="27" t="n">
-        <f aca="false">AX2+AX4</f>
+      <c r="BU2" s="30" t="n">
+        <f aca="false">MAX(BR2,AN14)</f>
         <v>25</v>
       </c>
-      <c r="BC2" s="27" t="n">
-        <f aca="false">AZ2</f>
-        <v>25</v>
-      </c>
-      <c r="BD2" s="28"/>
-      <c r="BE2" s="27" t="n">
-        <f aca="false">BC2+BC4</f>
-        <v>28</v>
-      </c>
-      <c r="BH2" s="27" t="n">
-        <f aca="false">BE2</f>
-        <v>28</v>
-      </c>
-      <c r="BI2" s="28"/>
-      <c r="BJ2" s="27" t="n">
-        <f aca="false">BH2+BH4</f>
-        <v>29</v>
-      </c>
-      <c r="BM2" s="27" t="n">
-        <f aca="false">BJ2</f>
-        <v>29</v>
-      </c>
-      <c r="BN2" s="28"/>
-      <c r="BO2" s="27" t="n">
-        <f aca="false">BM2+BM4</f>
-        <v>34</v>
-      </c>
-      <c r="BR2" s="27" t="n">
-        <f aca="false">MAX(BO2,AK14)</f>
-        <v>34</v>
-      </c>
-      <c r="BS2" s="28"/>
-      <c r="BT2" s="27" t="n">
-        <f aca="false">BR2+BR4</f>
-        <v>35</v>
+      <c r="BV2" s="31"/>
+      <c r="BW2" s="30" t="n">
+        <f aca="false">BU2+BU4</f>
+        <v>26</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="30" t="s">
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="30" t="s">
-        <v>50</v>
-      </c>
-      <c r="G3" s="31" t="n">
+      <c r="F3" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="G3" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="I3" s="32" t="s">
+      <c r="H3" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="I3" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="28" t="n">
+        <f aca="false">ROUNDUP(G3/(H3*I3),0)</f>
+        <v>1</v>
+      </c>
+      <c r="L3" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="32"/>
-      <c r="K3" s="32"/>
-      <c r="N3" s="32" t="s">
+      <c r="M3" s="36"/>
+      <c r="N3" s="36"/>
+      <c r="Q3" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="O3" s="32"/>
-      <c r="P3" s="32"/>
-      <c r="S3" s="32" t="s">
+      <c r="R3" s="36"/>
+      <c r="S3" s="36"/>
+      <c r="V3" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="T3" s="32"/>
-      <c r="U3" s="32"/>
-      <c r="AI3" s="32" t="s">
+      <c r="W3" s="36"/>
+      <c r="X3" s="36"/>
+      <c r="AL3" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="AJ3" s="32"/>
-      <c r="AK3" s="32"/>
-      <c r="AN3" s="32" t="s">
+      <c r="AM3" s="36"/>
+      <c r="AN3" s="36"/>
+      <c r="AQ3" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="AO3" s="32"/>
-      <c r="AP3" s="32"/>
-      <c r="AS3" s="32" t="s">
+      <c r="AR3" s="36"/>
+      <c r="AS3" s="36"/>
+      <c r="AV3" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="AT3" s="32"/>
-      <c r="AU3" s="32"/>
-      <c r="AX3" s="32" t="s">
+      <c r="AW3" s="36"/>
+      <c r="AX3" s="36"/>
+      <c r="BA3" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="AY3" s="32"/>
-      <c r="AZ3" s="32"/>
-      <c r="BC3" s="32" t="s">
+      <c r="BB3" s="36"/>
+      <c r="BC3" s="36"/>
+      <c r="BF3" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="BD3" s="32"/>
-      <c r="BE3" s="32"/>
-      <c r="BH3" s="32" t="s">
+      <c r="BG3" s="36"/>
+      <c r="BH3" s="36"/>
+      <c r="BK3" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="BI3" s="32"/>
-      <c r="BJ3" s="32"/>
-      <c r="BM3" s="32" t="s">
+      <c r="BL3" s="36"/>
+      <c r="BM3" s="36"/>
+      <c r="BP3" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="BN3" s="32"/>
-      <c r="BO3" s="32"/>
-      <c r="BR3" s="32" t="s">
+      <c r="BQ3" s="36"/>
+      <c r="BR3" s="36"/>
+      <c r="BU3" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="BS3" s="32"/>
-      <c r="BT3" s="32"/>
-    </row>
-    <row r="4" customFormat="false" ht="12.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="BV3" s="36"/>
+      <c r="BW3" s="36"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="30" t="s">
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="30" t="s">
+      <c r="F4" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="31" t="n">
+      <c r="G4" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="I4" s="33" t="n">
-        <f aca="false">G2</f>
-        <v>5</v>
-      </c>
-      <c r="J4" s="34" t="n">
-        <f aca="false">K5-K2</f>
+      <c r="H4" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="I4" s="35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J4" s="28" t="n">
+        <f aca="false">ROUNDUP(G4/(H4*I4),0)</f>
+        <v>8</v>
+      </c>
+      <c r="L4" s="37" t="n">
+        <f aca="false">J2</f>
+        <v>2</v>
+      </c>
+      <c r="M4" s="38" t="n">
+        <f aca="false">N5-N2</f>
         <v>0</v>
       </c>
-      <c r="K4" s="33" t="n">
-        <f aca="false">MIN(N2,N14)-K2</f>
+      <c r="N4" s="37" t="n">
+        <f aca="false">MIN(Q2,Q14)-N2</f>
         <v>0</v>
       </c>
-      <c r="L4" s="35"/>
-      <c r="M4" s="36"/>
-      <c r="N4" s="33" t="n">
-        <f aca="false">G3</f>
+      <c r="O4" s="39"/>
+      <c r="P4" s="40"/>
+      <c r="Q4" s="37" t="n">
+        <f aca="false">J3</f>
         <v>1</v>
       </c>
-      <c r="O4" s="34" t="n">
-        <f aca="false">P5-P2</f>
+      <c r="R4" s="38" t="n">
+        <f aca="false">S5-S2</f>
+        <v>3</v>
+      </c>
+      <c r="S4" s="37" t="n">
+        <f aca="false">MIN(V2,V8)-S2</f>
         <v>0</v>
       </c>
-      <c r="P4" s="33" t="n">
-        <f aca="false">MIN(S2,S8)-P2</f>
+      <c r="T4" s="39"/>
+      <c r="U4" s="40"/>
+      <c r="V4" s="37" t="n">
+        <f aca="false">J4</f>
+        <v>8</v>
+      </c>
+      <c r="W4" s="38" t="n">
+        <f aca="false">X5-X2</f>
+        <v>3</v>
+      </c>
+      <c r="X4" s="37" t="n">
+        <f aca="false">AL2-X2</f>
         <v>0</v>
       </c>
-      <c r="Q4" s="35"/>
-      <c r="R4" s="36"/>
-      <c r="S4" s="33" t="n">
-        <f aca="false">G4</f>
-        <v>4</v>
-      </c>
-      <c r="T4" s="34" t="n">
-        <f aca="false">U5-U2</f>
-        <v>6</v>
-      </c>
-      <c r="U4" s="33" t="n">
-        <f aca="false">AI2-U2</f>
-        <v>6</v>
-      </c>
-      <c r="V4" s="35"/>
-      <c r="W4" s="35"/>
-      <c r="X4" s="35"/>
-      <c r="Y4" s="35"/>
-      <c r="Z4" s="35"/>
-      <c r="AA4" s="35"/>
-      <c r="AB4" s="35"/>
-      <c r="AC4" s="35"/>
-      <c r="AD4" s="35"/>
-      <c r="AE4" s="35"/>
-      <c r="AF4" s="35"/>
-      <c r="AG4" s="35"/>
-      <c r="AH4" s="36"/>
-      <c r="AI4" s="33" t="n">
-        <f aca="false">G9</f>
+      <c r="Y4" s="39"/>
+      <c r="Z4" s="39"/>
+      <c r="AA4" s="39"/>
+      <c r="AB4" s="39"/>
+      <c r="AC4" s="39"/>
+      <c r="AD4" s="39"/>
+      <c r="AE4" s="39"/>
+      <c r="AF4" s="39"/>
+      <c r="AG4" s="39"/>
+      <c r="AH4" s="39"/>
+      <c r="AI4" s="39"/>
+      <c r="AJ4" s="39"/>
+      <c r="AK4" s="40"/>
+      <c r="AL4" s="37" t="n">
+        <f aca="false">J9</f>
+        <v>1</v>
+      </c>
+      <c r="AM4" s="38" t="n">
+        <f aca="false">AN5-AN2</f>
+        <v>3</v>
+      </c>
+      <c r="AN4" s="37" t="n">
+        <f aca="false">AQ2-AN2</f>
+        <v>0</v>
+      </c>
+      <c r="AO4" s="39"/>
+      <c r="AP4" s="39"/>
+      <c r="AQ4" s="37" t="n">
+        <f aca="false">J10</f>
+        <v>1</v>
+      </c>
+      <c r="AR4" s="38" t="n">
+        <f aca="false">AS5-AS2</f>
+        <v>3</v>
+      </c>
+      <c r="AS4" s="37" t="n">
+        <f aca="false">AV2-AS2</f>
+        <v>0</v>
+      </c>
+      <c r="AT4" s="39"/>
+      <c r="AU4" s="39"/>
+      <c r="AV4" s="37" t="n">
+        <f aca="false">J11</f>
+        <v>1</v>
+      </c>
+      <c r="AW4" s="38" t="n">
+        <f aca="false">AX5-AX2</f>
+        <v>3</v>
+      </c>
+      <c r="AX4" s="37" t="n">
+        <f aca="false">BA2-AX2</f>
+        <v>0</v>
+      </c>
+      <c r="AY4" s="39"/>
+      <c r="AZ4" s="39"/>
+      <c r="BA4" s="37" t="n">
+        <f aca="false">J13</f>
         <v>2</v>
       </c>
-      <c r="AJ4" s="34" t="n">
-        <f aca="false">AK5-AK2</f>
+      <c r="BB4" s="38" t="n">
+        <f aca="false">BC5-BC2</f>
+        <v>3</v>
+      </c>
+      <c r="BC4" s="37" t="n">
+        <f aca="false">BF2-BC2</f>
         <v>0</v>
       </c>
-      <c r="AK4" s="33" t="n">
-        <f aca="false">AN2-AK2</f>
+      <c r="BD4" s="39"/>
+      <c r="BE4" s="39"/>
+      <c r="BF4" s="37" t="n">
+        <f aca="false">J14</f>
+        <v>2</v>
+      </c>
+      <c r="BG4" s="38" t="n">
+        <f aca="false">BH5-BH2</f>
+        <v>3</v>
+      </c>
+      <c r="BH4" s="37" t="n">
+        <f aca="false">BK2-BH2</f>
         <v>0</v>
       </c>
-      <c r="AL4" s="35"/>
-      <c r="AM4" s="35"/>
-      <c r="AN4" s="33" t="n">
-        <f aca="false">G10</f>
-        <v>2</v>
-      </c>
-      <c r="AO4" s="34" t="n">
-        <f aca="false">AP5-AP2</f>
+      <c r="BI4" s="39"/>
+      <c r="BJ4" s="39"/>
+      <c r="BK4" s="37" t="n">
+        <f aca="false">J15</f>
+        <v>1</v>
+      </c>
+      <c r="BL4" s="38" t="n">
+        <f aca="false">BM5-BM2</f>
+        <v>3</v>
+      </c>
+      <c r="BM4" s="37" t="n">
+        <f aca="false">BP2-BM2</f>
         <v>0</v>
       </c>
-      <c r="AP4" s="33" t="n">
-        <f aca="false">AS2-AP2</f>
+      <c r="BN4" s="39"/>
+      <c r="BO4" s="39"/>
+      <c r="BP4" s="37" t="n">
+        <f aca="false">J16</f>
+        <v>3</v>
+      </c>
+      <c r="BQ4" s="38" t="n">
+        <f aca="false">BR5-BR2</f>
+        <v>3</v>
+      </c>
+      <c r="BR4" s="37" t="n">
+        <f aca="false">BU2-BR2</f>
+        <v>3</v>
+      </c>
+      <c r="BS4" s="39"/>
+      <c r="BT4" s="40"/>
+      <c r="BU4" s="37" t="n">
+        <f aca="false">J17</f>
+        <v>1</v>
+      </c>
+      <c r="BV4" s="38" t="n">
+        <f aca="false">BW5-BW2</f>
         <v>0</v>
       </c>
-      <c r="AQ4" s="35"/>
-      <c r="AR4" s="35"/>
-      <c r="AS4" s="33" t="n">
-        <f aca="false">G11</f>
-        <v>2</v>
-      </c>
-      <c r="AT4" s="34" t="n">
-        <f aca="false">AU5-AU2</f>
-        <v>0</v>
-      </c>
-      <c r="AU4" s="33" t="n">
-        <f aca="false">AX2-AU2</f>
-        <v>0</v>
-      </c>
-      <c r="AV4" s="35"/>
-      <c r="AW4" s="35"/>
-      <c r="AX4" s="33" t="n">
-        <f aca="false">G13</f>
-        <v>3</v>
-      </c>
-      <c r="AY4" s="34" t="n">
-        <f aca="false">AZ5-AZ2</f>
-        <v>0</v>
-      </c>
-      <c r="AZ4" s="33" t="n">
-        <f aca="false">BC2-AZ2</f>
-        <v>0</v>
-      </c>
-      <c r="BA4" s="35"/>
-      <c r="BB4" s="35"/>
-      <c r="BC4" s="33" t="n">
-        <f aca="false">G14</f>
-        <v>3</v>
-      </c>
-      <c r="BD4" s="34" t="n">
-        <f aca="false">BE5-BE2</f>
-        <v>0</v>
-      </c>
-      <c r="BE4" s="33" t="n">
-        <f aca="false">BH2-BE2</f>
-        <v>0</v>
-      </c>
-      <c r="BF4" s="35"/>
-      <c r="BG4" s="35"/>
-      <c r="BH4" s="33" t="n">
-        <f aca="false">G15</f>
-        <v>1</v>
-      </c>
-      <c r="BI4" s="34" t="n">
-        <f aca="false">BJ5-BJ2</f>
-        <v>0</v>
-      </c>
-      <c r="BJ4" s="33" t="n">
-        <f aca="false">BM2-BJ2</f>
-        <v>0</v>
-      </c>
-      <c r="BK4" s="35"/>
-      <c r="BL4" s="35"/>
-      <c r="BM4" s="33" t="n">
-        <f aca="false">G16</f>
-        <v>5</v>
-      </c>
-      <c r="BN4" s="34" t="n">
-        <f aca="false">BO5-BO2</f>
-        <v>0</v>
-      </c>
-      <c r="BO4" s="33" t="n">
-        <f aca="false">BR2-BO2</f>
-        <v>0</v>
-      </c>
-      <c r="BP4" s="35"/>
-      <c r="BQ4" s="36"/>
-      <c r="BR4" s="33" t="n">
-        <f aca="false">G17</f>
-        <v>1</v>
-      </c>
-      <c r="BS4" s="34" t="n">
-        <f aca="false">BT5-BT2</f>
-        <v>0</v>
-      </c>
-      <c r="BT4" s="33"/>
+      <c r="BW4" s="37"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="30" t="s">
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="30" t="s">
+      <c r="F5" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="31" t="n">
+      <c r="G5" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="I5" s="27" t="n">
+      <c r="H5" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="I5" s="35" t="n">
+        <f aca="false">150%/2</f>
+        <v>0.75</v>
+      </c>
+      <c r="J5" s="28" t="n">
+        <f aca="false">ROUNDUP(G5/(H5*I5),0)</f>
+        <v>2</v>
+      </c>
+      <c r="L5" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="28"/>
-      <c r="K5" s="27" t="n">
-        <f aca="false">MIN(N5,N17)</f>
+      <c r="M5" s="31"/>
+      <c r="N5" s="30" t="n">
+        <f aca="false">MIN(Q5,Q17)</f>
+        <v>2</v>
+      </c>
+      <c r="P5" s="41"/>
+      <c r="Q5" s="30" t="n">
+        <f aca="false">S5-Q4</f>
         <v>5</v>
       </c>
-      <c r="M5" s="37"/>
-      <c r="N5" s="27" t="n">
-        <f aca="false">P5-N4</f>
-        <v>5</v>
-      </c>
-      <c r="O5" s="28"/>
-      <c r="P5" s="27" t="n">
-        <f aca="false">MIN(S5,S11)</f>
+      <c r="R5" s="31"/>
+      <c r="S5" s="30" t="n">
+        <f aca="false">MIN(V5,V11)</f>
         <v>6</v>
       </c>
-      <c r="R5" s="37"/>
-      <c r="S5" s="27" t="n">
-        <f aca="false">U5-S4</f>
-        <v>12</v>
-      </c>
-      <c r="T5" s="28"/>
-      <c r="U5" s="27" t="n">
-        <f aca="false">AI5</f>
+      <c r="U5" s="41"/>
+      <c r="V5" s="30" t="n">
+        <f aca="false">X5-V4</f>
+        <v>6</v>
+      </c>
+      <c r="W5" s="31"/>
+      <c r="X5" s="30" t="n">
+        <f aca="false">AL5</f>
+        <v>14</v>
+      </c>
+      <c r="AK5" s="41"/>
+      <c r="AL5" s="30" t="n">
+        <f aca="false">AN5-AL4</f>
+        <v>14</v>
+      </c>
+      <c r="AM5" s="31"/>
+      <c r="AN5" s="30" t="n">
+        <f aca="false">AQ5</f>
+        <v>15</v>
+      </c>
+      <c r="AQ5" s="30" t="n">
+        <f aca="false">AS5-AQ4</f>
+        <v>15</v>
+      </c>
+      <c r="AR5" s="31"/>
+      <c r="AS5" s="30" t="n">
+        <f aca="false">AV5</f>
         <v>16</v>
       </c>
-      <c r="AH5" s="37"/>
-      <c r="AI5" s="27" t="n">
-        <f aca="false">AK5-AI4</f>
+      <c r="AV5" s="30" t="n">
+        <f aca="false">AX5-AV4</f>
         <v>16</v>
       </c>
-      <c r="AJ5" s="28"/>
-      <c r="AK5" s="27" t="n">
-        <f aca="false">AN5</f>
-        <v>18</v>
-      </c>
-      <c r="AN5" s="27" t="n">
-        <f aca="false">AP5-AN4</f>
-        <v>18</v>
-      </c>
-      <c r="AO5" s="28"/>
-      <c r="AP5" s="27" t="n">
-        <f aca="false">AS5</f>
-        <v>20</v>
-      </c>
-      <c r="AS5" s="27" t="n">
-        <f aca="false">AU5-AS4</f>
-        <v>20</v>
-      </c>
-      <c r="AT5" s="28"/>
-      <c r="AU5" s="27" t="n">
-        <f aca="false">AX5</f>
+      <c r="AW5" s="31"/>
+      <c r="AX5" s="30" t="n">
+        <f aca="false">BA5</f>
+        <v>17</v>
+      </c>
+      <c r="BA5" s="30" t="n">
+        <f aca="false">BC5-BA4</f>
+        <v>17</v>
+      </c>
+      <c r="BB5" s="31"/>
+      <c r="BC5" s="30" t="n">
+        <f aca="false">BF5</f>
+        <v>19</v>
+      </c>
+      <c r="BF5" s="30" t="n">
+        <f aca="false">BH5-BF4</f>
+        <v>19</v>
+      </c>
+      <c r="BG5" s="31"/>
+      <c r="BH5" s="30" t="n">
+        <f aca="false">BK5</f>
+        <v>21</v>
+      </c>
+      <c r="BK5" s="30" t="n">
+        <f aca="false">BM5-BK4</f>
+        <v>21</v>
+      </c>
+      <c r="BL5" s="31"/>
+      <c r="BM5" s="30" t="n">
+        <f aca="false">BP5</f>
         <v>22</v>
       </c>
-      <c r="AX5" s="27" t="n">
-        <f aca="false">AZ5-AX4</f>
+      <c r="BP5" s="30" t="n">
+        <f aca="false">BR5-BP4</f>
         <v>22</v>
       </c>
-      <c r="AY5" s="28"/>
-      <c r="AZ5" s="27" t="n">
-        <f aca="false">BC5</f>
+      <c r="BQ5" s="31"/>
+      <c r="BR5" s="30" t="n">
+        <f aca="false">BU5</f>
         <v>25</v>
       </c>
-      <c r="BC5" s="27" t="n">
-        <f aca="false">BE5-BC4</f>
+      <c r="BT5" s="41"/>
+      <c r="BU5" s="30" t="n">
+        <f aca="false">BW5-BU4</f>
         <v>25</v>
       </c>
-      <c r="BD5" s="28"/>
-      <c r="BE5" s="27" t="n">
-        <f aca="false">BH5</f>
-        <v>28</v>
-      </c>
-      <c r="BH5" s="27" t="n">
-        <f aca="false">BJ5-BH4</f>
-        <v>28</v>
-      </c>
-      <c r="BI5" s="28"/>
-      <c r="BJ5" s="27" t="n">
-        <f aca="false">BM5</f>
-        <v>29</v>
-      </c>
-      <c r="BM5" s="27" t="n">
-        <f aca="false">BO5-BM4</f>
-        <v>29</v>
-      </c>
-      <c r="BN5" s="28"/>
-      <c r="BO5" s="27" t="n">
-        <f aca="false">BR5</f>
-        <v>34</v>
-      </c>
-      <c r="BQ5" s="37"/>
-      <c r="BR5" s="27" t="n">
-        <f aca="false">BT5-BR4</f>
-        <v>34</v>
-      </c>
-      <c r="BS5" s="28"/>
-      <c r="BT5" s="27" t="n">
-        <f aca="false">BT2</f>
-        <v>35</v>
+      <c r="BV5" s="31"/>
+      <c r="BW5" s="30" t="n">
+        <f aca="false">BW2</f>
+        <v>26</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="29" t="s">
+      <c r="B6" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="38" t="s">
+      <c r="C6" s="32"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="38" t="s">
+      <c r="F6" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="39" t="n">
+      <c r="G6" s="43" t="n">
         <v>7</v>
       </c>
-      <c r="M6" s="37"/>
-      <c r="R6" s="37"/>
-      <c r="AH6" s="37"/>
-      <c r="BQ6" s="37"/>
+      <c r="H6" s="42" t="s">
+        <v>55</v>
+      </c>
+      <c r="I6" s="35" t="n">
+        <f aca="false">150%/2</f>
+        <v>0.75</v>
+      </c>
+      <c r="J6" s="28" t="n">
+        <f aca="false">ROUNDUP(G6/(H6*I6),0)</f>
+        <v>5</v>
+      </c>
+      <c r="P6" s="41"/>
+      <c r="U6" s="41"/>
+      <c r="AK6" s="41"/>
+      <c r="BT6" s="41"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="30" t="s">
+      <c r="C7" s="32"/>
+      <c r="D7" s="32"/>
+      <c r="E7" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="30" t="s">
+      <c r="F7" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="31" t="n">
+      <c r="G7" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="M7" s="37"/>
-      <c r="R7" s="37"/>
-      <c r="AH7" s="37"/>
-      <c r="BQ7" s="37"/>
+      <c r="H7" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="I7" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="28" t="n">
+        <f aca="false">ROUNDUP(G7/(H7*I7),0)</f>
+        <v>1</v>
+      </c>
+      <c r="P7" s="41"/>
+      <c r="U7" s="41"/>
+      <c r="AK7" s="41"/>
+      <c r="BT7" s="41"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="38" t="s">
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="F8" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="G8" s="39" t="n">
+      <c r="F8" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="M8" s="37"/>
-      <c r="R8" s="37"/>
-      <c r="S8" s="27" t="n">
-        <f aca="false">P2</f>
-        <v>6</v>
-      </c>
-      <c r="T8" s="28"/>
-      <c r="U8" s="27" t="n">
-        <f aca="false">S8+S10</f>
-        <v>9</v>
-      </c>
-      <c r="X8" s="27" t="n">
-        <f aca="false">U8</f>
-        <v>9</v>
-      </c>
-      <c r="Y8" s="28"/>
-      <c r="Z8" s="27" t="n">
-        <f aca="false">X8+X10</f>
-        <v>16</v>
-      </c>
-      <c r="AH8" s="37"/>
-      <c r="BQ8" s="37"/>
+      <c r="H8" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="I8" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="28" t="n">
+        <f aca="false">ROUNDUP(G8/(H8*I8),0)</f>
+        <v>3</v>
+      </c>
+      <c r="P8" s="41"/>
+      <c r="U8" s="41"/>
+      <c r="V8" s="30" t="n">
+        <f aca="false">S2</f>
+        <v>3</v>
+      </c>
+      <c r="W8" s="31"/>
+      <c r="X8" s="30" t="n">
+        <f aca="false">V8+V10</f>
+        <v>5</v>
+      </c>
+      <c r="AA8" s="30" t="n">
+        <f aca="false">X8</f>
+        <v>5</v>
+      </c>
+      <c r="AB8" s="31"/>
+      <c r="AC8" s="30" t="n">
+        <f aca="false">AA8+AA10</f>
+        <v>10</v>
+      </c>
+      <c r="AK8" s="41"/>
+      <c r="BT8" s="41"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="F9" s="38" t="s">
+      <c r="C9" s="32"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="42" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="G9" s="39" t="n">
+      <c r="G9" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="M9" s="37"/>
-      <c r="R9" s="37"/>
-      <c r="S9" s="32" t="s">
+      <c r="H9" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="I9" s="44" t="n">
+        <f aca="false">(200%+(100%-$I$12))/3</f>
+        <v>0.816666666666667</v>
+      </c>
+      <c r="J9" s="28" t="n">
+        <f aca="false">ROUNDUP(G9/(H9*I9),0)</f>
+        <v>1</v>
+      </c>
+      <c r="P9" s="41"/>
+      <c r="U9" s="41"/>
+      <c r="V9" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="T9" s="32"/>
-      <c r="U9" s="32"/>
-      <c r="X9" s="32" t="s">
+      <c r="W9" s="36"/>
+      <c r="X9" s="36"/>
+      <c r="AA9" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="Y9" s="32"/>
-      <c r="Z9" s="32"/>
-      <c r="AH9" s="37"/>
-      <c r="BQ9" s="37"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AB9" s="36"/>
+      <c r="AC9" s="36"/>
+      <c r="AK9" s="41"/>
+      <c r="BT9" s="41"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="38" t="s">
+      <c r="C10" s="32"/>
+      <c r="D10" s="32"/>
+      <c r="E10" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="38" t="s">
+      <c r="F10" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="G10" s="39" t="n">
+      <c r="G10" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="M10" s="37"/>
-      <c r="R10" s="35"/>
-      <c r="S10" s="33" t="n">
-        <f aca="false">G5</f>
-        <v>3</v>
-      </c>
-      <c r="T10" s="34" t="n">
-        <f aca="false">U11-U8</f>
+      <c r="H10" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="I10" s="44" t="n">
+        <f aca="false">(200%+(100%-$I$12))/3</f>
+        <v>0.816666666666667</v>
+      </c>
+      <c r="J10" s="28" t="n">
+        <f aca="false">ROUNDUP(G10/(H10*I10),0)</f>
+        <v>1</v>
+      </c>
+      <c r="P10" s="41"/>
+      <c r="U10" s="39"/>
+      <c r="V10" s="37" t="n">
+        <f aca="false">J5</f>
+        <v>2</v>
+      </c>
+      <c r="W10" s="38" t="n">
+        <f aca="false">X11-X8</f>
+        <v>4</v>
+      </c>
+      <c r="X10" s="37" t="n">
+        <f aca="false">AA8-X8</f>
         <v>0</v>
       </c>
-      <c r="U10" s="33" t="n">
-        <f aca="false">X8-U8</f>
-        <v>0</v>
-      </c>
-      <c r="V10" s="35"/>
-      <c r="W10" s="35"/>
-      <c r="X10" s="33" t="n">
-        <f aca="false">G6</f>
-        <v>7</v>
-      </c>
-      <c r="Y10" s="34" t="n">
-        <f aca="false">Z11-Z8</f>
-        <v>0</v>
-      </c>
-      <c r="Z10" s="40" t="n">
-        <f aca="false">AI2-Z8</f>
-        <v>0</v>
-      </c>
-      <c r="AA10" s="35"/>
-      <c r="AB10" s="35"/>
-      <c r="AC10" s="35"/>
-      <c r="AD10" s="35"/>
-      <c r="AE10" s="35"/>
-      <c r="AF10" s="35"/>
-      <c r="AG10" s="35"/>
-      <c r="AH10" s="37"/>
-      <c r="BQ10" s="37"/>
+      <c r="Y10" s="39"/>
+      <c r="Z10" s="39"/>
+      <c r="AA10" s="37" t="n">
+        <f aca="false">J6</f>
+        <v>5</v>
+      </c>
+      <c r="AB10" s="38" t="n">
+        <f aca="false">AC11-AC8</f>
+        <v>4</v>
+      </c>
+      <c r="AC10" s="45" t="n">
+        <f aca="false">AL2-AC8</f>
+        <v>1</v>
+      </c>
+      <c r="AD10" s="39"/>
+      <c r="AE10" s="39"/>
+      <c r="AF10" s="39"/>
+      <c r="AG10" s="39"/>
+      <c r="AH10" s="39"/>
+      <c r="AI10" s="39"/>
+      <c r="AJ10" s="39"/>
+      <c r="AK10" s="41"/>
+      <c r="BT10" s="41"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="29" t="s">
+      <c r="B11" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="38" t="s">
+      <c r="C11" s="32"/>
+      <c r="D11" s="32"/>
+      <c r="E11" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="F11" s="38" t="s">
+      <c r="F11" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="39" t="n">
+      <c r="G11" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="M11" s="37"/>
-      <c r="S11" s="27" t="n">
-        <f aca="false">U11-S10</f>
-        <v>6</v>
-      </c>
-      <c r="T11" s="28"/>
-      <c r="U11" s="27" t="n">
-        <f aca="false">X11</f>
+      <c r="H11" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="I11" s="44" t="n">
+        <f aca="false">(200%+(100%-$I$12))/3</f>
+        <v>0.816666666666667</v>
+      </c>
+      <c r="J11" s="28" t="n">
+        <f aca="false">ROUNDUP(G11/(H11*I11),0)</f>
+        <v>1</v>
+      </c>
+      <c r="P11" s="41"/>
+      <c r="V11" s="30" t="n">
+        <f aca="false">X11-V10</f>
+        <v>7</v>
+      </c>
+      <c r="W11" s="31"/>
+      <c r="X11" s="30" t="n">
+        <f aca="false">AA11</f>
         <v>9</v>
       </c>
-      <c r="X11" s="27" t="n">
-        <f aca="false">Z11-X10</f>
+      <c r="AA11" s="30" t="n">
+        <f aca="false">AC11-AA10</f>
         <v>9</v>
       </c>
-      <c r="Y11" s="28"/>
-      <c r="Z11" s="27" t="n">
-        <f aca="false">AI5</f>
-        <v>16</v>
-      </c>
-      <c r="AH11" s="37"/>
-      <c r="BQ11" s="37"/>
+      <c r="AB11" s="31"/>
+      <c r="AC11" s="30" t="n">
+        <f aca="false">AL5</f>
+        <v>14</v>
+      </c>
+      <c r="AK11" s="41"/>
+      <c r="BT11" s="41"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="29"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="38" t="s">
+      <c r="B12" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="32"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="F12" s="38" t="s">
+      <c r="F12" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="G12" s="39" t="n">
+      <c r="G12" s="43" t="n">
         <v>10</v>
       </c>
-      <c r="M12" s="37"/>
-      <c r="X12" s="41"/>
-      <c r="AH12" s="37"/>
-      <c r="BQ12" s="37"/>
+      <c r="H12" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="I12" s="44" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J12" s="28" t="n">
+        <f aca="false">ROUNDUP(G12/(H12*I12),0)</f>
+        <v>19</v>
+      </c>
+      <c r="P12" s="41"/>
+      <c r="AA12" s="46"/>
+      <c r="AK12" s="41"/>
+      <c r="BT12" s="41"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="38" t="s">
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="F13" s="38" t="s">
+      <c r="F13" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="G13" s="39" t="n">
+      <c r="G13" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="M13" s="37"/>
-      <c r="X13" s="41"/>
-      <c r="AH13" s="37"/>
-      <c r="BQ13" s="37"/>
+      <c r="H13" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="I13" s="44" t="n">
+        <f aca="false">(200%+(100%-$I$12))/3</f>
+        <v>0.816666666666667</v>
+      </c>
+      <c r="J13" s="28" t="n">
+        <f aca="false">ROUNDUP(G13/(H13*I13),0)</f>
+        <v>2</v>
+      </c>
+      <c r="P13" s="41"/>
+      <c r="AA13" s="46"/>
+      <c r="AK13" s="41"/>
+      <c r="BT13" s="41"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="29" t="s">
+      <c r="B14" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="38" t="s">
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="F14" s="38" t="s">
+      <c r="F14" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="G14" s="39" t="n">
+      <c r="G14" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="M14" s="37"/>
-      <c r="N14" s="27" t="n">
-        <f aca="false">K2</f>
-        <v>5</v>
-      </c>
-      <c r="O14" s="28"/>
-      <c r="P14" s="27" t="n">
-        <f aca="false">N14+N16</f>
+      <c r="H14" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="I14" s="44" t="n">
+        <f aca="false">(200%+(100%-$I$12))/3</f>
+        <v>0.816666666666667</v>
+      </c>
+      <c r="J14" s="28" t="n">
+        <f aca="false">ROUNDUP(G14/(H14*I14),0)</f>
+        <v>2</v>
+      </c>
+      <c r="P14" s="41"/>
+      <c r="Q14" s="30" t="n">
+        <f aca="false">N2</f>
+        <v>2</v>
+      </c>
+      <c r="R14" s="31"/>
+      <c r="S14" s="30" t="n">
+        <f aca="false">Q14+Q16</f>
+        <v>3</v>
+      </c>
+      <c r="V14" s="30" t="n">
+        <f aca="false">S14</f>
+        <v>3</v>
+      </c>
+      <c r="W14" s="31"/>
+      <c r="X14" s="30" t="n">
+        <f aca="false">V14+V16</f>
         <v>6</v>
       </c>
-      <c r="S14" s="27" t="n">
-        <f aca="false">P14</f>
+      <c r="Y14" s="47"/>
+      <c r="Z14" s="47"/>
+      <c r="AA14" s="47"/>
+      <c r="AB14" s="47"/>
+      <c r="AC14" s="47"/>
+      <c r="AD14" s="47"/>
+      <c r="AE14" s="47"/>
+      <c r="AF14" s="47"/>
+      <c r="AG14" s="47"/>
+      <c r="AH14" s="47"/>
+      <c r="AI14" s="47"/>
+      <c r="AJ14" s="47"/>
+      <c r="AK14" s="41"/>
+      <c r="AL14" s="30" t="n">
+        <f aca="false">X14</f>
         <v>6</v>
       </c>
-      <c r="T14" s="28"/>
-      <c r="U14" s="27" t="n">
-        <f aca="false">S14+S16</f>
-        <v>9</v>
-      </c>
-      <c r="V14" s="42"/>
-      <c r="W14" s="42"/>
-      <c r="X14" s="42"/>
-      <c r="Y14" s="42"/>
-      <c r="Z14" s="42"/>
-      <c r="AA14" s="42"/>
-      <c r="AB14" s="42"/>
-      <c r="AC14" s="42"/>
-      <c r="AD14" s="42"/>
-      <c r="AE14" s="42"/>
-      <c r="AF14" s="42"/>
-      <c r="AG14" s="42"/>
-      <c r="AH14" s="37"/>
-      <c r="AI14" s="27" t="n">
-        <f aca="false">U14</f>
-        <v>9</v>
-      </c>
-      <c r="AJ14" s="28"/>
-      <c r="AK14" s="27" t="n">
-        <f aca="false">AI14+AI16</f>
-        <v>19</v>
-      </c>
-      <c r="BQ14" s="37"/>
+      <c r="AM14" s="31"/>
+      <c r="AN14" s="30" t="n">
+        <f aca="false">AL14+AL16</f>
+        <v>25</v>
+      </c>
+      <c r="BT14" s="41"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="29" t="s">
+      <c r="B15" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="38" t="s">
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="F15" s="38" t="s">
+      <c r="F15" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="G15" s="39" t="n">
+      <c r="G15" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="M15" s="37"/>
-      <c r="N15" s="32" t="s">
+      <c r="H15" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="I15" s="44" t="n">
+        <f aca="false">(200%+(100%-$I$12))/3</f>
+        <v>0.816666666666667</v>
+      </c>
+      <c r="J15" s="28" t="n">
+        <f aca="false">ROUNDUP(G15/(H15*I15),0)</f>
+        <v>1</v>
+      </c>
+      <c r="P15" s="41"/>
+      <c r="Q15" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="O15" s="32"/>
-      <c r="P15" s="32"/>
-      <c r="S15" s="32" t="s">
+      <c r="R15" s="36"/>
+      <c r="S15" s="36"/>
+      <c r="V15" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="T15" s="32"/>
-      <c r="U15" s="32"/>
-      <c r="X15" s="41"/>
-      <c r="AH15" s="43"/>
-      <c r="AI15" s="32" t="s">
+      <c r="W15" s="36"/>
+      <c r="X15" s="36"/>
+      <c r="AA15" s="46"/>
+      <c r="AK15" s="48"/>
+      <c r="AL15" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="AJ15" s="32"/>
-      <c r="AK15" s="32"/>
-      <c r="BQ15" s="37"/>
+      <c r="AM15" s="36"/>
+      <c r="AN15" s="36"/>
+      <c r="BT15" s="41"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="29" t="s">
+      <c r="B16" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="38" t="s">
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="F16" s="38" t="s">
+      <c r="F16" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="G16" s="39" t="n">
+      <c r="G16" s="43" t="n">
         <v>5</v>
       </c>
-      <c r="M16" s="35"/>
-      <c r="N16" s="33" t="n">
-        <f aca="false">G7</f>
+      <c r="H16" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="I16" s="44" t="n">
+        <f aca="false">(200%+(100%-$I$12))/3</f>
+        <v>0.816666666666667</v>
+      </c>
+      <c r="J16" s="28" t="n">
+        <f aca="false">ROUNDUP(G16/(H16*I16),0)</f>
+        <v>3</v>
+      </c>
+      <c r="P16" s="39"/>
+      <c r="Q16" s="37" t="n">
+        <f aca="false">J7</f>
         <v>1</v>
       </c>
-      <c r="O16" s="34" t="n">
-        <f aca="false">P17-P14</f>
-        <v>7</v>
-      </c>
-      <c r="P16" s="33" t="n">
-        <f aca="false">S14-P14</f>
+      <c r="R16" s="38" t="n">
+        <f aca="false">S17-S14</f>
         <v>0</v>
       </c>
-      <c r="Q16" s="35"/>
-      <c r="R16" s="35"/>
-      <c r="S16" s="33" t="n">
-        <f aca="false">G8</f>
+      <c r="S16" s="37" t="n">
+        <f aca="false">V14-S14</f>
+        <v>0</v>
+      </c>
+      <c r="T16" s="39"/>
+      <c r="U16" s="39"/>
+      <c r="V16" s="37" t="n">
+        <f aca="false">J8</f>
         <v>3</v>
       </c>
-      <c r="T16" s="34" t="n">
-        <f aca="false">U17-U14</f>
-        <v>7</v>
-      </c>
-      <c r="U16" s="33" t="n">
-        <f aca="false">MIN(AI2,AI14)-U14</f>
+      <c r="W16" s="38" t="n">
+        <f aca="false">X17-X14</f>
         <v>0</v>
       </c>
-      <c r="V16" s="35"/>
-      <c r="W16" s="35"/>
-      <c r="X16" s="35"/>
-      <c r="Y16" s="35"/>
-      <c r="Z16" s="35"/>
-      <c r="AA16" s="35"/>
-      <c r="AB16" s="35"/>
-      <c r="AC16" s="35"/>
-      <c r="AD16" s="35"/>
-      <c r="AE16" s="35"/>
-      <c r="AF16" s="35"/>
-      <c r="AG16" s="35"/>
-      <c r="AH16" s="35"/>
-      <c r="AI16" s="33" t="n">
-        <f aca="false">G12</f>
-        <v>10</v>
-      </c>
-      <c r="AJ16" s="34" t="n">
-        <f aca="false">AK17-AK14</f>
-        <v>15</v>
-      </c>
-      <c r="AK16" s="40" t="n">
-        <f aca="false">BR2-AK14</f>
-        <v>15</v>
-      </c>
-      <c r="AL16" s="35"/>
-      <c r="AM16" s="35"/>
-      <c r="AN16" s="35"/>
-      <c r="AO16" s="35"/>
-      <c r="AP16" s="35"/>
-      <c r="AQ16" s="35"/>
-      <c r="AR16" s="35"/>
-      <c r="AS16" s="35"/>
-      <c r="AT16" s="35"/>
-      <c r="AU16" s="35"/>
-      <c r="AV16" s="35"/>
-      <c r="AW16" s="35"/>
-      <c r="AX16" s="35"/>
-      <c r="AY16" s="35"/>
-      <c r="AZ16" s="35"/>
-      <c r="BA16" s="35"/>
-      <c r="BB16" s="35"/>
-      <c r="BC16" s="35"/>
-      <c r="BD16" s="35"/>
-      <c r="BE16" s="35"/>
-      <c r="BF16" s="35"/>
-      <c r="BG16" s="35"/>
-      <c r="BH16" s="35"/>
-      <c r="BI16" s="35"/>
-      <c r="BJ16" s="35"/>
-      <c r="BK16" s="35"/>
-      <c r="BL16" s="35"/>
-      <c r="BM16" s="35"/>
-      <c r="BN16" s="35"/>
-      <c r="BO16" s="35"/>
-      <c r="BP16" s="35"/>
+      <c r="X16" s="37" t="n">
+        <f aca="false">MIN(AL2,AL14)-X14</f>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="39"/>
+      <c r="Z16" s="39"/>
+      <c r="AA16" s="39"/>
+      <c r="AB16" s="39"/>
+      <c r="AC16" s="39"/>
+      <c r="AD16" s="39"/>
+      <c r="AE16" s="39"/>
+      <c r="AF16" s="39"/>
+      <c r="AG16" s="39"/>
+      <c r="AH16" s="39"/>
+      <c r="AI16" s="39"/>
+      <c r="AJ16" s="39"/>
+      <c r="AK16" s="39"/>
+      <c r="AL16" s="37" t="n">
+        <f aca="false">J12</f>
+        <v>19</v>
+      </c>
+      <c r="AM16" s="38" t="n">
+        <f aca="false">AN17-AN14</f>
+        <v>0</v>
+      </c>
+      <c r="AN16" s="45" t="n">
+        <f aca="false">BU2-AN14</f>
+        <v>0</v>
+      </c>
+      <c r="AO16" s="39"/>
+      <c r="AP16" s="39"/>
+      <c r="AQ16" s="39"/>
+      <c r="AR16" s="39"/>
+      <c r="AS16" s="39"/>
+      <c r="AT16" s="39"/>
+      <c r="AU16" s="39"/>
+      <c r="AV16" s="39"/>
+      <c r="AW16" s="39"/>
+      <c r="AX16" s="39"/>
+      <c r="AY16" s="39"/>
+      <c r="AZ16" s="39"/>
+      <c r="BA16" s="39"/>
+      <c r="BB16" s="39"/>
+      <c r="BC16" s="39"/>
+      <c r="BD16" s="39"/>
+      <c r="BE16" s="39"/>
+      <c r="BF16" s="39"/>
+      <c r="BG16" s="39"/>
+      <c r="BH16" s="39"/>
+      <c r="BI16" s="39"/>
+      <c r="BJ16" s="39"/>
+      <c r="BK16" s="39"/>
+      <c r="BL16" s="39"/>
+      <c r="BM16" s="39"/>
+      <c r="BN16" s="39"/>
+      <c r="BO16" s="39"/>
+      <c r="BP16" s="39"/>
+      <c r="BQ16" s="39"/>
+      <c r="BR16" s="39"/>
+      <c r="BS16" s="39"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="44" t="s">
+      <c r="B17" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="44"/>
-      <c r="D17" s="44"/>
-      <c r="E17" s="45" t="s">
-        <v>54</v>
-      </c>
-      <c r="F17" s="46"/>
-      <c r="G17" s="47" t="n">
+      <c r="C17" s="49"/>
+      <c r="D17" s="49"/>
+      <c r="E17" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" s="51"/>
+      <c r="G17" s="52" t="n">
         <v>1</v>
       </c>
-      <c r="N17" s="27" t="n">
-        <f aca="false">P17-N16</f>
-        <v>12</v>
-      </c>
-      <c r="O17" s="28"/>
-      <c r="P17" s="27" t="n">
-        <f aca="false">S17</f>
-        <v>13</v>
-      </c>
-      <c r="S17" s="27" t="n">
-        <f aca="false">U17-S16</f>
-        <v>13</v>
-      </c>
-      <c r="T17" s="28"/>
-      <c r="U17" s="27" t="n">
-        <f aca="false">MIN(AI5,AI17)</f>
-        <v>16</v>
-      </c>
-      <c r="AI17" s="27" t="n">
-        <f aca="false">AK17-AI16</f>
-        <v>24</v>
-      </c>
-      <c r="AJ17" s="28"/>
-      <c r="AK17" s="27" t="n">
-        <f aca="false">BR5</f>
-        <v>34</v>
+      <c r="H17" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="I17" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="28" t="n">
+        <f aca="false">ROUNDUP(G17/(H17*I17),0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q17" s="30" t="n">
+        <f aca="false">S17-Q16</f>
+        <v>2</v>
+      </c>
+      <c r="R17" s="31"/>
+      <c r="S17" s="30" t="n">
+        <f aca="false">V17</f>
+        <v>3</v>
+      </c>
+      <c r="V17" s="30" t="n">
+        <f aca="false">X17-V16</f>
+        <v>3</v>
+      </c>
+      <c r="W17" s="31"/>
+      <c r="X17" s="30" t="n">
+        <f aca="false">MIN(AL5,AL17)</f>
+        <v>6</v>
+      </c>
+      <c r="AL17" s="30" t="n">
+        <f aca="false">AN17-AL16</f>
+        <v>6</v>
+      </c>
+      <c r="AM17" s="31"/>
+      <c r="AN17" s="30" t="n">
+        <f aca="false">BU5</f>
+        <v>25</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="48" t="s">
-        <v>55</v>
-      </c>
-      <c r="B19" s="49" t="s">
-        <v>56</v>
-      </c>
-      <c r="C19" s="50"/>
-      <c r="D19" s="51" t="s">
-        <v>57</v>
+      <c r="A19" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" s="54" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" s="55"/>
+      <c r="D19" s="56" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="32" t="s">
+      <c r="B20" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="C20" s="32"/>
-      <c r="D20" s="32"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="C21" s="34" t="s">
-        <v>58</v>
-      </c>
-      <c r="D21" s="33" t="s">
-        <v>59</v>
+      <c r="B21" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="38" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" s="37" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="52" t="s">
-        <v>60</v>
-      </c>
-      <c r="B22" s="53" t="s">
-        <v>56</v>
-      </c>
-      <c r="C22" s="54"/>
-      <c r="D22" s="55" t="s">
-        <v>57</v>
+      <c r="A22" s="57" t="s">
+        <v>66</v>
+      </c>
+      <c r="B22" s="58" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" s="59"/>
+      <c r="D22" s="60" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="56" t="s">
-        <v>61</v>
-      </c>
-      <c r="C24" s="28"/>
-      <c r="D24" s="27" t="s">
-        <v>62</v>
+      <c r="B24" s="61" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" s="31"/>
+      <c r="D24" s="30" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="32" t="s">
-        <v>63</v>
-      </c>
-      <c r="C25" s="32"/>
-      <c r="D25" s="32"/>
+      <c r="B25" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="36"/>
+      <c r="D25" s="36"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="32" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" s="34" t="s">
-        <v>65</v>
-      </c>
-      <c r="D26" s="33" t="s">
-        <v>66</v>
+      <c r="B26" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="C26" s="38" t="s">
+        <v>71</v>
+      </c>
+      <c r="D26" s="37" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="56" t="s">
-        <v>67</v>
-      </c>
-      <c r="C27" s="28"/>
-      <c r="D27" s="27" t="s">
-        <v>68</v>
+      <c r="B27" s="61" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" s="31"/>
+      <c r="D27" s="30" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>61</v>
-      </c>
-      <c r="B29" s="57" t="s">
-        <v>69</v>
-      </c>
-      <c r="C29" s="58" t="s">
-        <v>70</v>
-      </c>
-      <c r="D29" s="58"/>
+        <v>67</v>
+      </c>
+      <c r="B29" s="62" t="s">
+        <v>75</v>
+      </c>
+      <c r="C29" s="63" t="s">
+        <v>76</v>
+      </c>
+      <c r="D29" s="63"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>62</v>
-      </c>
-      <c r="B30" s="57" t="s">
-        <v>69</v>
-      </c>
-      <c r="C30" s="58" t="s">
-        <v>71</v>
-      </c>
-      <c r="D30" s="58"/>
+        <v>68</v>
+      </c>
+      <c r="B30" s="62" t="s">
+        <v>75</v>
+      </c>
+      <c r="C30" s="63" t="s">
+        <v>77</v>
+      </c>
+      <c r="D30" s="63"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="57"/>
+      <c r="B31" s="62"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>62</v>
-      </c>
-      <c r="B32" s="57" t="s">
-        <v>69</v>
-      </c>
-      <c r="C32" s="58" t="s">
-        <v>71</v>
-      </c>
-      <c r="D32" s="58"/>
+        <v>68</v>
+      </c>
+      <c r="B32" s="62" t="s">
+        <v>75</v>
+      </c>
+      <c r="C32" s="63" t="s">
+        <v>77</v>
+      </c>
+      <c r="D32" s="63"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>61</v>
-      </c>
-      <c r="B33" s="57" t="s">
-        <v>69</v>
-      </c>
-      <c r="C33" s="58" t="s">
-        <v>70</v>
-      </c>
-      <c r="D33" s="58"/>
+        <v>67</v>
+      </c>
+      <c r="B33" s="62" t="s">
+        <v>75</v>
+      </c>
+      <c r="C33" s="63" t="s">
+        <v>76</v>
+      </c>
+      <c r="D33" s="63"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="57"/>
+      <c r="B34" s="62"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="57"/>
+      <c r="B35" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="39">
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B3:D3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="S3:U3"/>
-    <mergeCell ref="AI3:AK3"/>
-    <mergeCell ref="AN3:AP3"/>
-    <mergeCell ref="AS3:AU3"/>
-    <mergeCell ref="AX3:AZ3"/>
-    <mergeCell ref="BC3:BE3"/>
-    <mergeCell ref="BH3:BJ3"/>
-    <mergeCell ref="BM3:BO3"/>
-    <mergeCell ref="BR3:BT3"/>
+    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="Q3:S3"/>
+    <mergeCell ref="V3:X3"/>
+    <mergeCell ref="AL3:AN3"/>
+    <mergeCell ref="AQ3:AS3"/>
+    <mergeCell ref="AV3:AX3"/>
+    <mergeCell ref="BA3:BC3"/>
+    <mergeCell ref="BF3:BH3"/>
+    <mergeCell ref="BK3:BM3"/>
+    <mergeCell ref="BP3:BR3"/>
+    <mergeCell ref="BU3:BW3"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B9:D9"/>
-    <mergeCell ref="S9:U9"/>
-    <mergeCell ref="X9:Z9"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="AA9:AC9"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B15:D15"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="S15:U15"/>
-    <mergeCell ref="AI15:AK15"/>
+    <mergeCell ref="Q15:S15"/>
+    <mergeCell ref="V15:X15"/>
+    <mergeCell ref="AL15:AN15"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="B20:D20"/>
@@ -3481,7 +3703,7 @@
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="C33:D33"/>
   </mergeCells>
-  <conditionalFormatting sqref="C21 C26 T16:U16 S10:T10 AJ16:AK16 BS4 BN4 BI4 BD4 AY4 AT4 AO4 AJ4 Y10 T4 O16 O4 J4">
+  <conditionalFormatting sqref="C21 C26 W16:X16 V10:W10 AM16:AN16 BV4 BQ4 BL4 BG4 BB4 AW4 AR4 AM4 AB10 W4 R16 R4 M4">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -3493,5 +3715,6 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Übungen/Online_Shop.xlsx
+++ b/Übungen/Online_Shop.xlsx
@@ -823,13 +823,13 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>907560</xdr:colOff>
+      <xdr:colOff>907920</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>154440</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>11880</xdr:colOff>
+      <xdr:colOff>12240</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>154440</xdr:rowOff>
     </xdr:to>
@@ -840,8 +840,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="5493960" y="479520"/>
-          <a:ext cx="5554080" cy="0"/>
+          <a:off x="5499000" y="479520"/>
+          <a:ext cx="5563080" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -882,7 +882,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5493240" y="488160"/>
+          <a:off x="5498280" y="488160"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -923,7 +923,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5492520" y="488160"/>
+          <a:off x="5497560" y="488160"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -965,7 +965,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5507640" y="1125360"/>
+          <a:off x="5514120" y="1125360"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1007,7 +1007,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5507640" y="1612800"/>
+          <a:off x="5514120" y="1612800"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1049,7 +1049,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5507640" y="2099880"/>
+          <a:off x="5514120" y="2099880"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1091,7 +1091,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5507640" y="2587320"/>
+          <a:off x="5514120" y="2587320"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1133,7 +1133,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8272080" y="324720"/>
+          <a:off x="8282160" y="324720"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1175,7 +1175,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8272080" y="487440"/>
+          <a:off x="8282160" y="487440"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1217,7 +1217,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8272080" y="1125360"/>
+          <a:off x="8282160" y="1125360"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1259,7 +1259,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8272080" y="1612800"/>
+          <a:off x="8282160" y="1612800"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1301,7 +1301,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8272080" y="2587320"/>
+          <a:off x="8282160" y="2587320"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1343,7 +1343,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8272080" y="3074400"/>
+          <a:off x="8282160" y="3074400"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1385,7 +1385,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8272080" y="4048920"/>
+          <a:off x="8282160" y="4048920"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1427,7 +1427,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8272080" y="5023440"/>
+          <a:off x="8282160" y="5023440"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1469,7 +1469,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11036520" y="487440"/>
+          <a:off x="11050560" y="487440"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1511,7 +1511,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11036520" y="1125360"/>
+          <a:off x="11050560" y="1125360"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1553,7 +1553,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11036520" y="1612800"/>
+          <a:off x="11050560" y="1612800"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1595,7 +1595,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11036520" y="2099880"/>
+          <a:off x="11050560" y="2099880"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1637,7 +1637,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8261640" y="3557520"/>
+          <a:off x="8270640" y="3557520"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1679,7 +1679,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8261640" y="4533480"/>
+          <a:off x="8270640" y="4533480"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1721,7 +1721,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8261640" y="2093760"/>
+          <a:off x="8270640" y="2093760"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1756,7 +1756,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M41"/>
-  <sheetFormatPr defaultColWidth="13.07421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="13.09375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.77"/>
   </cols>
@@ -2298,7 +2298,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:BW35"/>
-  <sheetFormatPr defaultColWidth="11.82421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.83984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="20" width="11.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.52"/>
@@ -2387,79 +2387,79 @@
       <c r="W2" s="31"/>
       <c r="X2" s="30" t="n">
         <f aca="false">V2+V4</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AL2" s="30" t="n">
         <f aca="false">MAX(X2,AC8,X14)</f>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AM2" s="31"/>
       <c r="AN2" s="30" t="n">
         <f aca="false">AL2+AL4</f>
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AQ2" s="30" t="n">
         <f aca="false">AN2</f>
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AR2" s="31"/>
       <c r="AS2" s="30" t="n">
         <f aca="false">AQ2+AQ4</f>
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AV2" s="30" t="n">
         <f aca="false">AS2</f>
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AW2" s="31"/>
       <c r="AX2" s="30" t="n">
         <f aca="false">AV2+AV4</f>
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="BA2" s="30" t="n">
         <f aca="false">AX2</f>
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="BB2" s="31"/>
       <c r="BC2" s="30" t="n">
         <f aca="false">BA2+BA4</f>
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="BF2" s="30" t="n">
         <f aca="false">BC2</f>
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="BG2" s="31"/>
       <c r="BH2" s="30" t="n">
         <f aca="false">BF2+BF4</f>
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="BK2" s="30" t="n">
         <f aca="false">BH2</f>
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="BL2" s="31"/>
       <c r="BM2" s="30" t="n">
         <f aca="false">BK2+BK4</f>
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="BP2" s="30" t="n">
         <f aca="false">BM2</f>
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="BQ2" s="31"/>
       <c r="BR2" s="30" t="n">
         <f aca="false">BP2+BP4</f>
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="BU2" s="30" t="n">
         <f aca="false">MAX(BR2,AN14)</f>
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="BV2" s="31"/>
       <c r="BW2" s="30" t="n">
         <f aca="false">BU2+BU4</f>
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2481,7 +2481,7 @@
         <v>1</v>
       </c>
       <c r="H3" s="34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" s="35" t="n">
         <v>1</v>
@@ -2568,11 +2568,11 @@
         <v>1</v>
       </c>
       <c r="I4" s="35" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J4" s="28" t="n">
         <f aca="false">ROUNDUP(G4/(H4*I4),0)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L4" s="37" t="n">
         <f aca="false">J2</f>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="R4" s="38" t="n">
         <f aca="false">S5-S2</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S4" s="37" t="n">
         <f aca="false">V2-S2</f>
@@ -2604,15 +2604,15 @@
       <c r="U4" s="40"/>
       <c r="V4" s="37" t="n">
         <f aca="false">J4</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="W4" s="38" t="n">
         <f aca="false">X5-X2</f>
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X4" s="37" t="n">
         <f aca="false">AL2-X2</f>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y4" s="39"/>
       <c r="Z4" s="39"/>
@@ -2629,11 +2629,11 @@
       <c r="AK4" s="40"/>
       <c r="AL4" s="37" t="n">
         <f aca="false">J9</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM4" s="38" t="n">
         <f aca="false">AN5-AN2</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN4" s="38" t="n">
         <f aca="false">AO5-AO2</f>
@@ -2643,11 +2643,11 @@
       <c r="AP4" s="39"/>
       <c r="AQ4" s="37" t="n">
         <f aca="false">J10</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR4" s="38" t="n">
         <f aca="false">AS5-AS2</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AS4" s="38" t="n">
         <f aca="false">AT5-AT2</f>
@@ -2657,11 +2657,11 @@
       <c r="AU4" s="39"/>
       <c r="AV4" s="37" t="n">
         <f aca="false">J11</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW4" s="38" t="n">
         <f aca="false">AX5-AX2</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX4" s="38" t="n">
         <f aca="false">AY5-AY2</f>
@@ -2671,11 +2671,11 @@
       <c r="AZ4" s="39"/>
       <c r="BA4" s="37" t="n">
         <f aca="false">J13</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB4" s="38" t="n">
         <f aca="false">BC5-BC2</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC4" s="38" t="n">
         <f aca="false">BD5-BD2</f>
@@ -2685,11 +2685,11 @@
       <c r="BE4" s="39"/>
       <c r="BF4" s="37" t="n">
         <f aca="false">J14</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BG4" s="38" t="n">
         <f aca="false">BH5-BH2</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BH4" s="38" t="n">
         <f aca="false">BI5-BI2</f>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="BL4" s="38" t="n">
         <f aca="false">BM5-BM2</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BM4" s="38" t="n">
         <f aca="false">BN5-BN2</f>
@@ -2713,15 +2713,15 @@
       <c r="BO4" s="39"/>
       <c r="BP4" s="37" t="n">
         <f aca="false">J16</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BQ4" s="38" t="n">
         <f aca="false">BR5-BR2</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BR4" s="37" t="n">
         <f aca="false">BU2-BR2</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BS4" s="39"/>
       <c r="BT4" s="40"/>
@@ -2754,10 +2754,11 @@
         <v>3</v>
       </c>
       <c r="H5" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" s="35" t="n">
-        <v>1</v>
+        <f aca="false">(100%+(100%-$I$4))/2</f>
+        <v>0.7</v>
       </c>
       <c r="J5" s="28" t="n">
         <f aca="false">ROUNDUP(G5/(H5*I5),0)</f>
@@ -2774,96 +2775,96 @@
       <c r="P5" s="41"/>
       <c r="Q5" s="30" t="n">
         <f aca="false">S5-Q4</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R5" s="31"/>
       <c r="S5" s="30" t="n">
         <f aca="false">MIN(V11,V5)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U5" s="41"/>
       <c r="V5" s="30" t="n">
         <f aca="false">X5-V4</f>
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="W5" s="31"/>
       <c r="X5" s="30" t="n">
         <f aca="false">AL5</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK5" s="41"/>
       <c r="AL5" s="30" t="n">
         <f aca="false">AN5-AL4</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AM5" s="31"/>
       <c r="AN5" s="30" t="n">
         <f aca="false">AQ5</f>
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AQ5" s="30" t="n">
         <f aca="false">AS5-AQ4</f>
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AR5" s="31"/>
       <c r="AS5" s="30" t="n">
         <f aca="false">AV5</f>
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AV5" s="30" t="n">
         <f aca="false">AX5-AV4</f>
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AW5" s="31"/>
       <c r="AX5" s="30" t="n">
         <f aca="false">BA5</f>
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="BA5" s="30" t="n">
         <f aca="false">BC5-BA4</f>
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="BB5" s="31"/>
       <c r="BC5" s="30" t="n">
         <f aca="false">BF5</f>
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="BF5" s="30" t="n">
         <f aca="false">BH5-BF4</f>
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="BG5" s="31"/>
       <c r="BH5" s="30" t="n">
         <f aca="false">BK5</f>
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="BK5" s="30" t="n">
         <f aca="false">BM5-BK4</f>
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="BL5" s="31"/>
       <c r="BM5" s="30" t="n">
         <f aca="false">BP5</f>
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="BP5" s="30" t="n">
         <f aca="false">BR5-BP4</f>
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="BQ5" s="31"/>
       <c r="BR5" s="30" t="n">
         <f aca="false">BU5</f>
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="BT5" s="41"/>
       <c r="BU5" s="30" t="n">
         <f aca="false">BW5-BU4</f>
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="BV5" s="31"/>
       <c r="BW5" s="30" t="n">
         <f aca="false">BW2</f>
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2885,14 +2886,15 @@
         <v>7</v>
       </c>
       <c r="H6" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" s="35" t="n">
-        <v>1</v>
+        <f aca="false">(100%+(100%-$I$4))/2</f>
+        <v>0.7</v>
       </c>
       <c r="J6" s="28" t="n">
         <f aca="false">ROUNDUP(G6/(H6*I6),0)</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P6" s="41"/>
       <c r="U6" s="41"/>
@@ -2918,7 +2920,7 @@
         <v>1</v>
       </c>
       <c r="H7" s="43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" s="44" t="n">
         <v>1</v>
@@ -2978,7 +2980,7 @@
       <c r="AB8" s="31"/>
       <c r="AC8" s="30" t="n">
         <f aca="false">AA8+AA10</f>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AK8" s="41"/>
       <c r="BT8" s="41"/>
@@ -3006,10 +3008,11 @@
       </c>
       <c r="I9" s="44" t="n">
         <f aca="false">((2*100%)+(100%-$I$12))/3</f>
-        <v>0.883333333333333</v>
-      </c>
-      <c r="J9" s="43" t="n">
-        <v>2</v>
+        <v>0.833333333333333</v>
+      </c>
+      <c r="J9" s="28" t="n">
+        <f aca="false">ROUNDUP(G9/(H9*I9),0)</f>
+        <v>1</v>
       </c>
       <c r="P9" s="41"/>
       <c r="U9" s="41"/>
@@ -3049,10 +3052,11 @@
       </c>
       <c r="I10" s="44" t="n">
         <f aca="false">((2*100%)+(100%-$I$12))/3</f>
-        <v>0.883333333333333</v>
-      </c>
-      <c r="J10" s="43" t="n">
-        <v>2</v>
+        <v>0.833333333333333</v>
+      </c>
+      <c r="J10" s="28" t="n">
+        <f aca="false">ROUNDUP(G10/(H10*I10),0)</f>
+        <v>1</v>
       </c>
       <c r="P10" s="41"/>
       <c r="U10" s="39"/>
@@ -3062,7 +3066,7 @@
       </c>
       <c r="W10" s="38" t="n">
         <f aca="false">X11-X8</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X10" s="37" t="n">
         <f aca="false">AA8-X8</f>
@@ -3072,11 +3076,11 @@
       <c r="Z10" s="39"/>
       <c r="AA10" s="37" t="n">
         <f aca="false">J6</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AB10" s="38" t="n">
         <f aca="false">AC11-AC8</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC10" s="37" t="n">
         <f aca="false">AL2-AC8</f>
@@ -3115,29 +3119,30 @@
       </c>
       <c r="I11" s="44" t="n">
         <f aca="false">((2*100%)+(100%-$I$12))/3</f>
-        <v>0.883333333333333</v>
-      </c>
-      <c r="J11" s="43" t="n">
-        <v>2</v>
+        <v>0.833333333333333</v>
+      </c>
+      <c r="J11" s="28" t="n">
+        <f aca="false">ROUNDUP(G11/(H11*I11),0)</f>
+        <v>1</v>
       </c>
       <c r="P11" s="41"/>
       <c r="V11" s="30" t="n">
         <f aca="false">X11-V10</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W11" s="31"/>
       <c r="X11" s="30" t="n">
         <f aca="false">AA11</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA11" s="30" t="n">
         <f aca="false">AC11-AA10</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB11" s="31"/>
       <c r="AC11" s="30" t="n">
         <f aca="false">AL5</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK11" s="41"/>
       <c r="BT11" s="41"/>
@@ -3164,11 +3169,11 @@
         <v>1</v>
       </c>
       <c r="I12" s="44" t="n">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="J12" s="28" t="n">
         <f aca="false">ROUNDUP(G12/(H12*I12),0)</f>
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="P12" s="41"/>
       <c r="AA12" s="45"/>
@@ -3198,10 +3203,11 @@
       </c>
       <c r="I13" s="44" t="n">
         <f aca="false">((2*100%)+(100%-$I$12))/3</f>
-        <v>0.883333333333333</v>
-      </c>
-      <c r="J13" s="43" t="n">
-        <v>3</v>
+        <v>0.833333333333333</v>
+      </c>
+      <c r="J13" s="28" t="n">
+        <f aca="false">ROUNDUP(G13/(H13*I13),0)</f>
+        <v>2</v>
       </c>
       <c r="P13" s="41"/>
       <c r="AA13" s="45"/>
@@ -3231,10 +3237,11 @@
       </c>
       <c r="I14" s="44" t="n">
         <f aca="false">((2*100%)+(100%-$I$12))/3</f>
-        <v>0.883333333333333</v>
-      </c>
-      <c r="J14" s="43" t="n">
-        <v>3</v>
+        <v>0.833333333333333</v>
+      </c>
+      <c r="J14" s="28" t="n">
+        <f aca="false">ROUNDUP(G14/(H14*I14),0)</f>
+        <v>2</v>
       </c>
       <c r="P14" s="41"/>
       <c r="Q14" s="30" t="n">
@@ -3263,7 +3270,7 @@
       <c r="AM14" s="31"/>
       <c r="AN14" s="30" t="n">
         <f aca="false">AL14+AL16</f>
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="BT14" s="41"/>
     </row>
@@ -3290,9 +3297,10 @@
       </c>
       <c r="I15" s="44" t="n">
         <f aca="false">((2*100%)+(100%-$I$12))/3</f>
-        <v>0.883333333333333</v>
-      </c>
-      <c r="J15" s="43" t="n">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="J15" s="28" t="n">
+        <f aca="false">ROUNDUP(G15/(H15*I15),0)</f>
         <v>1</v>
       </c>
       <c r="P15" s="41"/>
@@ -3349,10 +3357,11 @@
       </c>
       <c r="I16" s="44" t="n">
         <f aca="false">((2*100%)+(100%-$I$12))/3</f>
-        <v>0.883333333333333</v>
-      </c>
-      <c r="J16" s="43" t="n">
-        <v>5</v>
+        <v>0.833333333333333</v>
+      </c>
+      <c r="J16" s="28" t="n">
+        <f aca="false">ROUNDUP(G16/(H16*I16),0)</f>
+        <v>2</v>
       </c>
       <c r="P16" s="39"/>
       <c r="Q16" s="37" t="n">
@@ -3396,7 +3405,7 @@
       <c r="AK16" s="39"/>
       <c r="AL16" s="37" t="n">
         <f aca="false">J12</f>
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="AM16" s="38" t="n">
         <f aca="false">AN17-AN14</f>
@@ -3460,7 +3469,8 @@
       <c r="I17" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="J17" s="49" t="n">
+      <c r="J17" s="28" t="n">
+        <f aca="false">ROUNDUP(G17/(H17*I17),0)</f>
         <v>1</v>
       </c>
       <c r="Q17" s="30" t="n">
@@ -3488,7 +3498,7 @@
       <c r="AM17" s="31"/>
       <c r="AN17" s="30" t="n">
         <f aca="false">BU5</f>
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Übungen/Online_Shop.xlsx
+++ b/Übungen/Online_Shop.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="75">
   <si>
     <t xml:space="preserve">Beispiel: Funktionsorientierter Projektstrukturplan</t>
   </si>
@@ -166,6 +166,15 @@
   </si>
   <si>
     <t xml:space="preserve">Nachfolger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aufwand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kapazität</t>
   </si>
   <si>
     <t xml:space="preserve">Dauer</t>
@@ -634,10 +643,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -655,6 +660,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -810,8 +819,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="5488560" y="479520"/>
-          <a:ext cx="5545080" cy="0"/>
+          <a:off x="5493960" y="479520"/>
+          <a:ext cx="5554080" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -852,7 +861,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5488200" y="488160"/>
+          <a:off x="5493240" y="488160"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -893,7 +902,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5487480" y="488160"/>
+          <a:off x="5492520" y="488160"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -935,7 +944,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5501520" y="1125360"/>
+          <a:off x="5507640" y="1125360"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -977,7 +986,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5501520" y="1612800"/>
+          <a:off x="5507640" y="1612800"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1019,7 +1028,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5501520" y="2099880"/>
+          <a:off x="5507640" y="2099880"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1061,7 +1070,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5501520" y="2587320"/>
+          <a:off x="5507640" y="2587320"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1103,7 +1112,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8261640" y="324720"/>
+          <a:off x="8272080" y="324720"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1145,7 +1154,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8261640" y="487440"/>
+          <a:off x="8272080" y="487440"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1187,7 +1196,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8261640" y="1125360"/>
+          <a:off x="8272080" y="1125360"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1229,7 +1238,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8261640" y="1612800"/>
+          <a:off x="8272080" y="1612800"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1271,7 +1280,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8261640" y="2587320"/>
+          <a:off x="8272080" y="2587320"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1313,7 +1322,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8261640" y="3074400"/>
+          <a:off x="8272080" y="3074400"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1355,7 +1364,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8261640" y="4048920"/>
+          <a:off x="8272080" y="4048920"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1397,7 +1406,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8261640" y="5023440"/>
+          <a:off x="8272080" y="5023440"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1439,7 +1448,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11022480" y="487440"/>
+          <a:off x="11036520" y="487440"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1481,7 +1490,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11022480" y="1125360"/>
+          <a:off x="11036520" y="1125360"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1523,7 +1532,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11022480" y="1612800"/>
+          <a:off x="11036520" y="1612800"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1565,7 +1574,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11022480" y="2099880"/>
+          <a:off x="11036520" y="2099880"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1607,7 +1616,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8253000" y="3557520"/>
+          <a:off x="8261640" y="3557520"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1649,7 +1658,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8253000" y="4533480"/>
+          <a:off x="8261640" y="4533480"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1691,7 +1700,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8253000" y="2093760"/>
+          <a:off x="8261640" y="2093760"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1716,13 +1725,17 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M41"/>
-  <sheetFormatPr defaultColWidth="13.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="13.07421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.77"/>
   </cols>
@@ -2263,15 +2276,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BT35"/>
-  <sheetFormatPr defaultColWidth="11.8046875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:BW35"/>
+  <sheetFormatPr defaultColWidth="11.82421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="20" width="11.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="16.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="3" width="11.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="104" min="8" style="0" width="3.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1022" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="6" style="3" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="107" min="11" style="0" width="3.83"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2292,6 +2304,15 @@
       <c r="G1" s="22" t="s">
         <v>48</v>
       </c>
+      <c r="H1" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="I1" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" s="22" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
@@ -2304,107 +2325,112 @@
       <c r="D2" s="23"/>
       <c r="E2" s="24"/>
       <c r="F2" s="25" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G2" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="I2" s="27" t="n">
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="L2" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="28"/>
-      <c r="K2" s="27" t="n">
-        <f aca="false">I2+I4</f>
+      <c r="M2" s="28"/>
+      <c r="N2" s="27" t="n">
+        <f aca="false">L2+L4</f>
         <v>5</v>
       </c>
-      <c r="N2" s="27" t="n">
-        <f aca="false">K2</f>
+      <c r="Q2" s="27" t="n">
+        <f aca="false">N2</f>
         <v>5</v>
       </c>
-      <c r="O2" s="28"/>
-      <c r="P2" s="27" t="n">
-        <f aca="false">N2+N4</f>
+      <c r="R2" s="28"/>
+      <c r="S2" s="27" t="n">
+        <f aca="false">Q2+Q4</f>
         <v>6</v>
       </c>
-      <c r="S2" s="27" t="n">
-        <f aca="false">P2</f>
+      <c r="V2" s="27" t="n">
+        <f aca="false">S2</f>
         <v>6</v>
       </c>
-      <c r="T2" s="28"/>
-      <c r="U2" s="27" t="n">
-        <f aca="false">S2+S4</f>
+      <c r="W2" s="28"/>
+      <c r="X2" s="27" t="n">
+        <f aca="false">V2+V4</f>
         <v>10</v>
       </c>
-      <c r="AI2" s="27" t="n">
-        <f aca="false">MAX(U2,Z8,U14)</f>
+      <c r="AL2" s="27" t="n">
+        <f aca="false">MAX(X2,AC8,X14)</f>
         <v>16</v>
       </c>
-      <c r="AJ2" s="28"/>
-      <c r="AK2" s="27" t="n">
-        <f aca="false">AI2+AI4</f>
+      <c r="AM2" s="28"/>
+      <c r="AN2" s="27" t="n">
+        <f aca="false">AL2+AL4</f>
         <v>18</v>
       </c>
-      <c r="AN2" s="27" t="n">
-        <f aca="false">AK2</f>
+      <c r="AQ2" s="27" t="n">
+        <f aca="false">AN2</f>
         <v>18</v>
       </c>
-      <c r="AO2" s="28"/>
-      <c r="AP2" s="27" t="n">
-        <f aca="false">AN2+AN4</f>
+      <c r="AR2" s="28"/>
+      <c r="AS2" s="27" t="n">
+        <f aca="false">AQ2+AQ4</f>
         <v>20</v>
       </c>
-      <c r="AS2" s="27" t="n">
-        <f aca="false">AP2</f>
+      <c r="AV2" s="27" t="n">
+        <f aca="false">AS2</f>
         <v>20</v>
       </c>
-      <c r="AT2" s="28"/>
-      <c r="AU2" s="27" t="n">
-        <f aca="false">AS2+AS4</f>
+      <c r="AW2" s="28"/>
+      <c r="AX2" s="27" t="n">
+        <f aca="false">AV2+AV4</f>
         <v>22</v>
       </c>
-      <c r="AX2" s="27" t="n">
-        <f aca="false">AU2</f>
+      <c r="BA2" s="27" t="n">
+        <f aca="false">AX2</f>
         <v>22</v>
       </c>
-      <c r="AY2" s="28"/>
-      <c r="AZ2" s="27" t="n">
-        <f aca="false">AX2+AX4</f>
+      <c r="BB2" s="28"/>
+      <c r="BC2" s="27" t="n">
+        <f aca="false">BA2+BA4</f>
         <v>25</v>
       </c>
-      <c r="BC2" s="27" t="n">
-        <f aca="false">AZ2</f>
+      <c r="BF2" s="27" t="n">
+        <f aca="false">BC2</f>
         <v>25</v>
       </c>
-      <c r="BD2" s="28"/>
-      <c r="BE2" s="27" t="n">
-        <f aca="false">BC2+BC4</f>
+      <c r="BG2" s="28"/>
+      <c r="BH2" s="27" t="n">
+        <f aca="false">BF2+BF4</f>
         <v>28</v>
       </c>
-      <c r="BH2" s="27" t="n">
-        <f aca="false">BE2</f>
+      <c r="BK2" s="27" t="n">
+        <f aca="false">BH2</f>
         <v>28</v>
       </c>
-      <c r="BI2" s="28"/>
-      <c r="BJ2" s="27" t="n">
-        <f aca="false">BH2+BH4</f>
+      <c r="BL2" s="28"/>
+      <c r="BM2" s="27" t="n">
+        <f aca="false">BK2+BK4</f>
         <v>29</v>
       </c>
-      <c r="BM2" s="27" t="n">
-        <f aca="false">BJ2</f>
+      <c r="BP2" s="27" t="n">
+        <f aca="false">BM2</f>
         <v>29</v>
       </c>
-      <c r="BN2" s="28"/>
-      <c r="BO2" s="27" t="n">
-        <f aca="false">BM2+BM4</f>
+      <c r="BQ2" s="28"/>
+      <c r="BR2" s="27" t="n">
+        <f aca="false">BP2+BP4</f>
         <v>34</v>
       </c>
-      <c r="BR2" s="27" t="n">
-        <f aca="false">MAX(BO2,AK14)</f>
+      <c r="BU2" s="27" t="n">
+        <f aca="false">MAX(BR2,AN14)</f>
         <v>34</v>
       </c>
-      <c r="BS2" s="28"/>
-      <c r="BT2" s="27" t="n">
-        <f aca="false">BR2+BR4</f>
+      <c r="BV2" s="28"/>
+      <c r="BW2" s="27" t="n">
+        <f aca="false">BU2+BU4</f>
         <v>35</v>
       </c>
     </row>
@@ -2421,66 +2447,71 @@
         <v>16</v>
       </c>
       <c r="F3" s="30" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G3" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="I3" s="32" t="s">
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="32"/>
-      <c r="K3" s="32"/>
-      <c r="N3" s="32" t="s">
+      <c r="M3" s="32"/>
+      <c r="N3" s="32"/>
+      <c r="Q3" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="O3" s="32"/>
-      <c r="P3" s="32"/>
-      <c r="S3" s="32" t="s">
+      <c r="R3" s="32"/>
+      <c r="S3" s="32"/>
+      <c r="V3" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="T3" s="32"/>
-      <c r="U3" s="32"/>
-      <c r="AI3" s="32" t="s">
+      <c r="W3" s="32"/>
+      <c r="X3" s="32"/>
+      <c r="AL3" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="AJ3" s="32"/>
-      <c r="AK3" s="32"/>
-      <c r="AN3" s="32" t="s">
+      <c r="AM3" s="32"/>
+      <c r="AN3" s="32"/>
+      <c r="AQ3" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="AO3" s="32"/>
-      <c r="AP3" s="32"/>
-      <c r="AS3" s="32" t="s">
+      <c r="AR3" s="32"/>
+      <c r="AS3" s="32"/>
+      <c r="AV3" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="AT3" s="32"/>
-      <c r="AU3" s="32"/>
-      <c r="AX3" s="32" t="s">
+      <c r="AW3" s="32"/>
+      <c r="AX3" s="32"/>
+      <c r="BA3" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="AY3" s="32"/>
-      <c r="AZ3" s="32"/>
-      <c r="BC3" s="32" t="s">
+      <c r="BB3" s="32"/>
+      <c r="BC3" s="32"/>
+      <c r="BF3" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="BD3" s="32"/>
-      <c r="BE3" s="32"/>
-      <c r="BH3" s="32" t="s">
+      <c r="BG3" s="32"/>
+      <c r="BH3" s="32"/>
+      <c r="BK3" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="BI3" s="32"/>
-      <c r="BJ3" s="32"/>
-      <c r="BM3" s="32" t="s">
+      <c r="BL3" s="32"/>
+      <c r="BM3" s="32"/>
+      <c r="BP3" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="BN3" s="32"/>
-      <c r="BO3" s="32"/>
-      <c r="BR3" s="32" t="s">
+      <c r="BQ3" s="32"/>
+      <c r="BR3" s="32"/>
+      <c r="BU3" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="BS3" s="32"/>
-      <c r="BT3" s="32"/>
+      <c r="BV3" s="32"/>
+      <c r="BW3" s="32"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
@@ -2500,49 +2531,51 @@
       <c r="G4" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="I4" s="33" t="n">
-        <f aca="false">G2</f>
+      <c r="H4" s="30"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="L4" s="33" t="n">
+        <f aca="false">J2</f>
         <v>5</v>
       </c>
-      <c r="J4" s="34" t="n">
-        <f aca="false">K5-K2</f>
+      <c r="M4" s="34" t="n">
+        <f aca="false">N5-N2</f>
         <v>0</v>
       </c>
-      <c r="K4" s="33" t="n">
-        <f aca="false">MIN(N2,N14)-K2</f>
+      <c r="N4" s="33" t="n">
+        <f aca="false">MIN(Q2,Q14)-N2</f>
         <v>0</v>
       </c>
-      <c r="L4" s="35"/>
-      <c r="M4" s="36"/>
-      <c r="N4" s="33" t="n">
-        <f aca="false">G3</f>
+      <c r="O4" s="35"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="33" t="n">
+        <f aca="false">J3</f>
         <v>1</v>
       </c>
-      <c r="O4" s="34" t="n">
-        <f aca="false">P5-P2</f>
+      <c r="R4" s="34" t="n">
+        <f aca="false">S5-S2</f>
         <v>0</v>
       </c>
-      <c r="P4" s="33" t="n">
-        <f aca="false">MIN(S2,S8)-P2</f>
+      <c r="S4" s="33" t="n">
+        <f aca="false">MIN(V2,V8)-S2</f>
         <v>0</v>
       </c>
-      <c r="Q4" s="35"/>
-      <c r="R4" s="36"/>
-      <c r="S4" s="33" t="n">
-        <f aca="false">G4</f>
+      <c r="T4" s="35"/>
+      <c r="U4" s="36"/>
+      <c r="V4" s="33" t="n">
+        <f aca="false">J4</f>
         <v>4</v>
       </c>
-      <c r="T4" s="34" t="n">
-        <f aca="false">U5-U2</f>
+      <c r="W4" s="34" t="n">
+        <f aca="false">X5-X2</f>
         <v>6</v>
       </c>
-      <c r="U4" s="33" t="n">
-        <f aca="false">AI2-U2</f>
+      <c r="X4" s="33" t="n">
+        <f aca="false">AL2-X2</f>
         <v>6</v>
       </c>
-      <c r="V4" s="35"/>
-      <c r="W4" s="35"/>
-      <c r="X4" s="35"/>
       <c r="Y4" s="35"/>
       <c r="Z4" s="35"/>
       <c r="AA4" s="35"/>
@@ -2552,114 +2585,117 @@
       <c r="AE4" s="35"/>
       <c r="AF4" s="35"/>
       <c r="AG4" s="35"/>
-      <c r="AH4" s="36"/>
-      <c r="AI4" s="33" t="n">
-        <f aca="false">G9</f>
+      <c r="AH4" s="35"/>
+      <c r="AI4" s="35"/>
+      <c r="AJ4" s="35"/>
+      <c r="AK4" s="36"/>
+      <c r="AL4" s="33" t="n">
+        <f aca="false">J9</f>
         <v>2</v>
       </c>
-      <c r="AJ4" s="34" t="n">
-        <f aca="false">AK5-AK2</f>
+      <c r="AM4" s="34" t="n">
+        <f aca="false">AN5-AN2</f>
         <v>0</v>
       </c>
-      <c r="AK4" s="33" t="n">
-        <f aca="false">AN2-AK2</f>
+      <c r="AN4" s="33" t="n">
+        <f aca="false">AQ2-AN2</f>
         <v>0</v>
       </c>
-      <c r="AL4" s="35"/>
-      <c r="AM4" s="35"/>
-      <c r="AN4" s="33" t="n">
-        <f aca="false">G10</f>
+      <c r="AO4" s="35"/>
+      <c r="AP4" s="35"/>
+      <c r="AQ4" s="33" t="n">
+        <f aca="false">J10</f>
         <v>2</v>
       </c>
-      <c r="AO4" s="34" t="n">
-        <f aca="false">AP5-AP2</f>
+      <c r="AR4" s="34" t="n">
+        <f aca="false">AS5-AS2</f>
         <v>0</v>
       </c>
-      <c r="AP4" s="33" t="n">
-        <f aca="false">AS2-AP2</f>
+      <c r="AS4" s="33" t="n">
+        <f aca="false">AV2-AS2</f>
         <v>0</v>
       </c>
-      <c r="AQ4" s="35"/>
-      <c r="AR4" s="35"/>
-      <c r="AS4" s="33" t="n">
-        <f aca="false">G11</f>
+      <c r="AT4" s="35"/>
+      <c r="AU4" s="35"/>
+      <c r="AV4" s="33" t="n">
+        <f aca="false">J11</f>
         <v>2</v>
       </c>
-      <c r="AT4" s="34" t="n">
-        <f aca="false">AU5-AU2</f>
+      <c r="AW4" s="34" t="n">
+        <f aca="false">AX5-AX2</f>
         <v>0</v>
       </c>
-      <c r="AU4" s="33" t="n">
-        <f aca="false">AX2-AU2</f>
+      <c r="AX4" s="33" t="n">
+        <f aca="false">BA2-AX2</f>
         <v>0</v>
       </c>
-      <c r="AV4" s="35"/>
-      <c r="AW4" s="35"/>
-      <c r="AX4" s="33" t="n">
-        <f aca="false">G13</f>
+      <c r="AY4" s="35"/>
+      <c r="AZ4" s="35"/>
+      <c r="BA4" s="33" t="n">
+        <f aca="false">J13</f>
         <v>3</v>
       </c>
-      <c r="AY4" s="34" t="n">
-        <f aca="false">AZ5-AZ2</f>
+      <c r="BB4" s="34" t="n">
+        <f aca="false">BC5-BC2</f>
         <v>0</v>
       </c>
-      <c r="AZ4" s="33" t="n">
-        <f aca="false">BC2-AZ2</f>
+      <c r="BC4" s="33" t="n">
+        <f aca="false">BF2-BC2</f>
         <v>0</v>
       </c>
-      <c r="BA4" s="35"/>
-      <c r="BB4" s="35"/>
-      <c r="BC4" s="33" t="n">
-        <f aca="false">G14</f>
+      <c r="BD4" s="35"/>
+      <c r="BE4" s="35"/>
+      <c r="BF4" s="33" t="n">
+        <f aca="false">J14</f>
         <v>3</v>
       </c>
-      <c r="BD4" s="34" t="n">
-        <f aca="false">BE5-BE2</f>
+      <c r="BG4" s="34" t="n">
+        <f aca="false">BH5-BH2</f>
         <v>0</v>
       </c>
-      <c r="BE4" s="33" t="n">
-        <f aca="false">BH2-BE2</f>
+      <c r="BH4" s="33" t="n">
+        <f aca="false">BK2-BH2</f>
         <v>0</v>
       </c>
-      <c r="BF4" s="35"/>
-      <c r="BG4" s="35"/>
-      <c r="BH4" s="33" t="n">
-        <f aca="false">G15</f>
+      <c r="BI4" s="35"/>
+      <c r="BJ4" s="35"/>
+      <c r="BK4" s="33" t="n">
+        <f aca="false">J15</f>
         <v>1</v>
       </c>
-      <c r="BI4" s="34" t="n">
-        <f aca="false">BJ5-BJ2</f>
+      <c r="BL4" s="34" t="n">
+        <f aca="false">BM5-BM2</f>
         <v>0</v>
       </c>
-      <c r="BJ4" s="33" t="n">
-        <f aca="false">BM2-BJ2</f>
+      <c r="BM4" s="33" t="n">
+        <f aca="false">BP2-BM2</f>
         <v>0</v>
       </c>
-      <c r="BK4" s="35"/>
-      <c r="BL4" s="35"/>
-      <c r="BM4" s="33" t="n">
-        <f aca="false">G16</f>
+      <c r="BN4" s="35"/>
+      <c r="BO4" s="35"/>
+      <c r="BP4" s="33" t="n">
+        <f aca="false">J16</f>
         <v>5</v>
       </c>
-      <c r="BN4" s="34" t="n">
-        <f aca="false">BO5-BO2</f>
+      <c r="BQ4" s="34" t="n">
+        <f aca="false">BR5-BR2</f>
         <v>0</v>
       </c>
-      <c r="BO4" s="33" t="n">
-        <f aca="false">BR2-BO2</f>
+      <c r="BR4" s="33" t="n">
+        <f aca="false">BU2-BR2</f>
         <v>0</v>
       </c>
-      <c r="BP4" s="35"/>
-      <c r="BQ4" s="36"/>
-      <c r="BR4" s="33" t="n">
-        <f aca="false">G17</f>
+      <c r="BS4" s="35"/>
+      <c r="BT4" s="36"/>
+      <c r="BU4" s="33" t="n">
+        <f aca="false">J17</f>
         <v>1</v>
       </c>
-      <c r="BS4" s="34" t="n">
-        <f aca="false">BT5-BT2</f>
+      <c r="BV4" s="34" t="n">
+        <f aca="false">BW5-BW2</f>
         <v>0</v>
       </c>
-      <c r="BT4" s="33"/>
+      <c r="BW4" s="33"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
@@ -2679,106 +2715,111 @@
       <c r="G5" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="I5" s="27" t="n">
+      <c r="H5" s="30"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="28"/>
-      <c r="K5" s="27" t="n">
-        <f aca="false">MIN(N5,N17)</f>
+      <c r="M5" s="28"/>
+      <c r="N5" s="27" t="n">
+        <f aca="false">MIN(Q5,Q17)</f>
         <v>5</v>
       </c>
-      <c r="M5" s="37"/>
-      <c r="N5" s="27" t="n">
-        <f aca="false">P5-N4</f>
+      <c r="P5" s="37"/>
+      <c r="Q5" s="27" t="n">
+        <f aca="false">S5-Q4</f>
         <v>5</v>
       </c>
-      <c r="O5" s="28"/>
-      <c r="P5" s="27" t="n">
-        <f aca="false">MIN(S5,S11)</f>
+      <c r="R5" s="28"/>
+      <c r="S5" s="27" t="n">
+        <f aca="false">MIN(V5,V11)</f>
         <v>6</v>
       </c>
-      <c r="R5" s="37"/>
-      <c r="S5" s="27" t="n">
-        <f aca="false">U5-S4</f>
+      <c r="U5" s="37"/>
+      <c r="V5" s="27" t="n">
+        <f aca="false">X5-V4</f>
         <v>12</v>
       </c>
-      <c r="T5" s="28"/>
-      <c r="U5" s="27" t="n">
-        <f aca="false">AI5</f>
+      <c r="W5" s="28"/>
+      <c r="X5" s="27" t="n">
+        <f aca="false">AL5</f>
         <v>16</v>
       </c>
-      <c r="AH5" s="37"/>
-      <c r="AI5" s="27" t="n">
-        <f aca="false">AK5-AI4</f>
+      <c r="AK5" s="37"/>
+      <c r="AL5" s="27" t="n">
+        <f aca="false">AN5-AL4</f>
         <v>16</v>
       </c>
-      <c r="AJ5" s="28"/>
-      <c r="AK5" s="27" t="n">
-        <f aca="false">AN5</f>
+      <c r="AM5" s="28"/>
+      <c r="AN5" s="27" t="n">
+        <f aca="false">AQ5</f>
         <v>18</v>
       </c>
-      <c r="AN5" s="27" t="n">
-        <f aca="false">AP5-AN4</f>
+      <c r="AQ5" s="27" t="n">
+        <f aca="false">AS5-AQ4</f>
         <v>18</v>
       </c>
-      <c r="AO5" s="28"/>
-      <c r="AP5" s="27" t="n">
-        <f aca="false">AS5</f>
+      <c r="AR5" s="28"/>
+      <c r="AS5" s="27" t="n">
+        <f aca="false">AV5</f>
         <v>20</v>
       </c>
-      <c r="AS5" s="27" t="n">
-        <f aca="false">AU5-AS4</f>
+      <c r="AV5" s="27" t="n">
+        <f aca="false">AX5-AV4</f>
         <v>20</v>
       </c>
-      <c r="AT5" s="28"/>
-      <c r="AU5" s="27" t="n">
-        <f aca="false">AX5</f>
+      <c r="AW5" s="28"/>
+      <c r="AX5" s="27" t="n">
+        <f aca="false">BA5</f>
         <v>22</v>
       </c>
-      <c r="AX5" s="27" t="n">
-        <f aca="false">AZ5-AX4</f>
+      <c r="BA5" s="27" t="n">
+        <f aca="false">BC5-BA4</f>
         <v>22</v>
       </c>
-      <c r="AY5" s="28"/>
-      <c r="AZ5" s="27" t="n">
-        <f aca="false">BC5</f>
+      <c r="BB5" s="28"/>
+      <c r="BC5" s="27" t="n">
+        <f aca="false">BF5</f>
         <v>25</v>
       </c>
-      <c r="BC5" s="27" t="n">
-        <f aca="false">BE5-BC4</f>
+      <c r="BF5" s="27" t="n">
+        <f aca="false">BH5-BF4</f>
         <v>25</v>
       </c>
-      <c r="BD5" s="28"/>
-      <c r="BE5" s="27" t="n">
-        <f aca="false">BH5</f>
+      <c r="BG5" s="28"/>
+      <c r="BH5" s="27" t="n">
+        <f aca="false">BK5</f>
         <v>28</v>
       </c>
-      <c r="BH5" s="27" t="n">
-        <f aca="false">BJ5-BH4</f>
+      <c r="BK5" s="27" t="n">
+        <f aca="false">BM5-BK4</f>
         <v>28</v>
       </c>
-      <c r="BI5" s="28"/>
-      <c r="BJ5" s="27" t="n">
-        <f aca="false">BM5</f>
+      <c r="BL5" s="28"/>
+      <c r="BM5" s="27" t="n">
+        <f aca="false">BP5</f>
         <v>29</v>
       </c>
-      <c r="BM5" s="27" t="n">
-        <f aca="false">BO5-BM4</f>
+      <c r="BP5" s="27" t="n">
+        <f aca="false">BR5-BP4</f>
         <v>29</v>
       </c>
-      <c r="BN5" s="28"/>
-      <c r="BO5" s="27" t="n">
-        <f aca="false">BR5</f>
+      <c r="BQ5" s="28"/>
+      <c r="BR5" s="27" t="n">
+        <f aca="false">BU5</f>
         <v>34</v>
       </c>
-      <c r="BQ5" s="37"/>
-      <c r="BR5" s="27" t="n">
-        <f aca="false">BT5-BR4</f>
+      <c r="BT5" s="37"/>
+      <c r="BU5" s="27" t="n">
+        <f aca="false">BW5-BU4</f>
         <v>34</v>
       </c>
-      <c r="BS5" s="28"/>
-      <c r="BT5" s="27" t="n">
-        <f aca="false">BT2</f>
+      <c r="BV5" s="28"/>
+      <c r="BW5" s="27" t="n">
+        <f aca="false">BW2</f>
         <v>35</v>
       </c>
     </row>
@@ -2800,10 +2841,15 @@
       <c r="G6" s="39" t="n">
         <v>7</v>
       </c>
-      <c r="M6" s="37"/>
-      <c r="R6" s="37"/>
-      <c r="AH6" s="37"/>
-      <c r="BQ6" s="37"/>
+      <c r="H6" s="38"/>
+      <c r="I6" s="38"/>
+      <c r="J6" s="39" t="n">
+        <v>7</v>
+      </c>
+      <c r="P6" s="37"/>
+      <c r="U6" s="37"/>
+      <c r="AK6" s="37"/>
+      <c r="BT6" s="37"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
@@ -2823,10 +2869,15 @@
       <c r="G7" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="M7" s="37"/>
-      <c r="R7" s="37"/>
-      <c r="AH7" s="37"/>
-      <c r="BQ7" s="37"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" s="37"/>
+      <c r="U7" s="37"/>
+      <c r="AK7" s="37"/>
+      <c r="BT7" s="37"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
@@ -2841,33 +2892,38 @@
         <v>22</v>
       </c>
       <c r="F8" s="38" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G8" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="M8" s="37"/>
-      <c r="R8" s="37"/>
-      <c r="S8" s="27" t="n">
-        <f aca="false">P2</f>
+      <c r="H8" s="38"/>
+      <c r="I8" s="38"/>
+      <c r="J8" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="P8" s="37"/>
+      <c r="U8" s="37"/>
+      <c r="V8" s="27" t="n">
+        <f aca="false">S2</f>
         <v>6</v>
       </c>
-      <c r="T8" s="28"/>
-      <c r="U8" s="27" t="n">
-        <f aca="false">S8+S10</f>
+      <c r="W8" s="28"/>
+      <c r="X8" s="27" t="n">
+        <f aca="false">V8+V10</f>
         <v>9</v>
       </c>
-      <c r="X8" s="27" t="n">
-        <f aca="false">U8</f>
+      <c r="AA8" s="27" t="n">
+        <f aca="false">X8</f>
         <v>9</v>
       </c>
-      <c r="Y8" s="28"/>
-      <c r="Z8" s="27" t="n">
-        <f aca="false">X8+X10</f>
+      <c r="AB8" s="28"/>
+      <c r="AC8" s="27" t="n">
+        <f aca="false">AA8+AA10</f>
         <v>16</v>
       </c>
-      <c r="AH8" s="37"/>
-      <c r="BQ8" s="37"/>
+      <c r="AK8" s="37"/>
+      <c r="BT8" s="37"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
@@ -2879,7 +2935,7 @@
       <c r="C9" s="29"/>
       <c r="D9" s="29"/>
       <c r="E9" s="38" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F9" s="38" t="s">
         <v>35</v>
@@ -2887,20 +2943,25 @@
       <c r="G9" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="M9" s="37"/>
-      <c r="R9" s="37"/>
-      <c r="S9" s="32" t="s">
+      <c r="H9" s="38"/>
+      <c r="I9" s="38"/>
+      <c r="J9" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="P9" s="37"/>
+      <c r="U9" s="37"/>
+      <c r="V9" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="T9" s="32"/>
-      <c r="U9" s="32"/>
-      <c r="X9" s="32" t="s">
+      <c r="W9" s="32"/>
+      <c r="X9" s="32"/>
+      <c r="AA9" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="Y9" s="32"/>
-      <c r="Z9" s="32"/>
-      <c r="AH9" s="37"/>
-      <c r="BQ9" s="37"/>
+      <c r="AB9" s="32"/>
+      <c r="AC9" s="32"/>
+      <c r="AK9" s="37"/>
+      <c r="BT9" s="37"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
@@ -2920,43 +2981,48 @@
       <c r="G10" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="M10" s="37"/>
-      <c r="R10" s="35"/>
-      <c r="S10" s="33" t="n">
-        <f aca="false">G5</f>
+      <c r="H10" s="38"/>
+      <c r="I10" s="38"/>
+      <c r="J10" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="P10" s="37"/>
+      <c r="U10" s="35"/>
+      <c r="V10" s="33" t="n">
+        <f aca="false">J5</f>
         <v>3</v>
       </c>
-      <c r="T10" s="34" t="n">
-        <f aca="false">U11-U8</f>
+      <c r="W10" s="34" t="n">
+        <f aca="false">X11-X8</f>
         <v>0</v>
       </c>
-      <c r="U10" s="33" t="n">
-        <f aca="false">X8-U8</f>
+      <c r="X10" s="33" t="n">
+        <f aca="false">AA8-X8</f>
         <v>0</v>
       </c>
-      <c r="V10" s="35"/>
-      <c r="W10" s="35"/>
-      <c r="X10" s="33" t="n">
-        <f aca="false">G6</f>
+      <c r="Y10" s="35"/>
+      <c r="Z10" s="35"/>
+      <c r="AA10" s="33" t="n">
+        <f aca="false">J6</f>
         <v>7</v>
       </c>
-      <c r="Y10" s="34" t="n">
-        <f aca="false">Z11-Z8</f>
+      <c r="AB10" s="34" t="n">
+        <f aca="false">AC11-AC8</f>
         <v>0</v>
       </c>
-      <c r="Z10" s="40" t="n">
-        <f aca="false">AI2-Z8</f>
+      <c r="AC10" s="33" t="n">
+        <f aca="false">AL2-AC8</f>
         <v>0</v>
       </c>
-      <c r="AA10" s="35"/>
-      <c r="AB10" s="35"/>
-      <c r="AC10" s="35"/>
       <c r="AD10" s="35"/>
       <c r="AE10" s="35"/>
       <c r="AF10" s="35"/>
       <c r="AG10" s="35"/>
-      <c r="AH10" s="37"/>
-      <c r="BQ10" s="37"/>
+      <c r="AH10" s="35"/>
+      <c r="AI10" s="35"/>
+      <c r="AJ10" s="35"/>
+      <c r="AK10" s="37"/>
+      <c r="BT10" s="37"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
@@ -2976,34 +3042,39 @@
       <c r="G11" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="M11" s="37"/>
-      <c r="S11" s="27" t="n">
-        <f aca="false">U11-S10</f>
+      <c r="H11" s="38"/>
+      <c r="I11" s="38"/>
+      <c r="J11" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="P11" s="37"/>
+      <c r="V11" s="27" t="n">
+        <f aca="false">X11-V10</f>
         <v>6</v>
       </c>
-      <c r="T11" s="28"/>
-      <c r="U11" s="27" t="n">
-        <f aca="false">X11</f>
+      <c r="W11" s="28"/>
+      <c r="X11" s="27" t="n">
+        <f aca="false">AA11</f>
         <v>9</v>
       </c>
-      <c r="X11" s="27" t="n">
-        <f aca="false">Z11-X10</f>
+      <c r="AA11" s="27" t="n">
+        <f aca="false">AC11-AA10</f>
         <v>9</v>
       </c>
-      <c r="Y11" s="28"/>
-      <c r="Z11" s="27" t="n">
-        <f aca="false">AI5</f>
+      <c r="AB11" s="28"/>
+      <c r="AC11" s="27" t="n">
+        <f aca="false">AL5</f>
         <v>16</v>
       </c>
-      <c r="AH11" s="37"/>
-      <c r="BQ11" s="37"/>
+      <c r="AK11" s="37"/>
+      <c r="BT11" s="37"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
         <v>17</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C12" s="29"/>
       <c r="D12" s="29"/>
@@ -3016,10 +3087,15 @@
       <c r="G12" s="39" t="n">
         <v>10</v>
       </c>
-      <c r="M12" s="37"/>
-      <c r="X12" s="41"/>
-      <c r="AH12" s="37"/>
-      <c r="BQ12" s="37"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="38"/>
+      <c r="J12" s="39" t="n">
+        <v>10</v>
+      </c>
+      <c r="P12" s="37"/>
+      <c r="AA12" s="40"/>
+      <c r="AK12" s="37"/>
+      <c r="BT12" s="37"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
@@ -3039,10 +3115,15 @@
       <c r="G13" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="M13" s="37"/>
-      <c r="X13" s="41"/>
-      <c r="AH13" s="37"/>
-      <c r="BQ13" s="37"/>
+      <c r="H13" s="38"/>
+      <c r="I13" s="38"/>
+      <c r="J13" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="P13" s="37"/>
+      <c r="AA13" s="40"/>
+      <c r="AK13" s="37"/>
+      <c r="BT13" s="37"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
@@ -3062,36 +3143,41 @@
       <c r="G14" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="M14" s="37"/>
-      <c r="N14" s="27" t="n">
-        <f aca="false">K2</f>
+      <c r="H14" s="38"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="P14" s="37"/>
+      <c r="Q14" s="27" t="n">
+        <f aca="false">N2</f>
         <v>5</v>
       </c>
-      <c r="O14" s="28"/>
-      <c r="P14" s="27" t="n">
-        <f aca="false">N14+N16</f>
+      <c r="R14" s="28"/>
+      <c r="S14" s="27" t="n">
+        <f aca="false">Q14+Q16</f>
         <v>6</v>
       </c>
-      <c r="S14" s="27" t="n">
-        <f aca="false">P14</f>
+      <c r="V14" s="27" t="n">
+        <f aca="false">S14</f>
         <v>6</v>
       </c>
-      <c r="T14" s="28"/>
-      <c r="U14" s="27" t="n">
-        <f aca="false">S14+S16</f>
+      <c r="W14" s="28"/>
+      <c r="X14" s="27" t="n">
+        <f aca="false">V14+V16</f>
         <v>9</v>
       </c>
-      <c r="AH14" s="37"/>
-      <c r="AI14" s="27" t="n">
-        <f aca="false">U14</f>
+      <c r="AK14" s="37"/>
+      <c r="AL14" s="27" t="n">
+        <f aca="false">X14</f>
         <v>9</v>
       </c>
-      <c r="AJ14" s="28"/>
-      <c r="AK14" s="27" t="n">
-        <f aca="false">AI14+AI16</f>
+      <c r="AM14" s="28"/>
+      <c r="AN14" s="27" t="n">
+        <f aca="false">AL14+AL16</f>
         <v>19</v>
       </c>
-      <c r="BQ14" s="37"/>
+      <c r="BT14" s="37"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
@@ -3111,20 +3197,22 @@
       <c r="G15" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="M15" s="37"/>
-      <c r="N15" s="32" t="s">
+      <c r="H15" s="38"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" s="37"/>
+      <c r="Q15" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="O15" s="32"/>
-      <c r="P15" s="32"/>
-      <c r="S15" s="32" t="s">
+      <c r="R15" s="32"/>
+      <c r="S15" s="32"/>
+      <c r="V15" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="T15" s="32"/>
-      <c r="U15" s="32"/>
-      <c r="V15" s="35"/>
-      <c r="W15" s="35"/>
-      <c r="X15" s="35"/>
+      <c r="W15" s="32"/>
+      <c r="X15" s="32"/>
       <c r="Y15" s="35"/>
       <c r="Z15" s="35"/>
       <c r="AA15" s="35"/>
@@ -3134,13 +3222,16 @@
       <c r="AE15" s="35"/>
       <c r="AF15" s="35"/>
       <c r="AG15" s="35"/>
-      <c r="AH15" s="41"/>
-      <c r="AI15" s="32" t="s">
+      <c r="AH15" s="35"/>
+      <c r="AI15" s="35"/>
+      <c r="AJ15" s="35"/>
+      <c r="AK15" s="40"/>
+      <c r="AL15" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="AJ15" s="32"/>
-      <c r="AK15" s="32"/>
-      <c r="BQ15" s="37"/>
+      <c r="AM15" s="32"/>
+      <c r="AN15" s="32"/>
+      <c r="BT15" s="37"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
@@ -3160,36 +3251,38 @@
       <c r="G16" s="39" t="n">
         <v>5</v>
       </c>
-      <c r="M16" s="35"/>
-      <c r="N16" s="33" t="n">
-        <f aca="false">G7</f>
+      <c r="H16" s="38"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="P16" s="35"/>
+      <c r="Q16" s="33" t="n">
+        <f aca="false">J7</f>
         <v>1</v>
       </c>
-      <c r="O16" s="34" t="n">
-        <f aca="false">P17-P14</f>
+      <c r="R16" s="34" t="n">
+        <f aca="false">S17-S14</f>
         <v>7</v>
       </c>
-      <c r="P16" s="33" t="n">
-        <f aca="false">S14-P14</f>
+      <c r="S16" s="33" t="n">
+        <f aca="false">V14-S14</f>
         <v>0</v>
       </c>
-      <c r="Q16" s="35"/>
-      <c r="R16" s="35"/>
-      <c r="S16" s="33" t="n">
-        <f aca="false">G8</f>
+      <c r="T16" s="35"/>
+      <c r="U16" s="35"/>
+      <c r="V16" s="33" t="n">
+        <f aca="false">J8</f>
         <v>3</v>
       </c>
-      <c r="T16" s="34" t="n">
-        <f aca="false">U17-U14</f>
+      <c r="W16" s="34" t="n">
+        <f aca="false">X17-X14</f>
         <v>7</v>
       </c>
-      <c r="U16" s="33" t="n">
-        <f aca="false">MIN(AI2,AI14)-U14</f>
+      <c r="X16" s="33" t="n">
+        <f aca="false">MIN(AL2,AL14)-X14</f>
         <v>0</v>
       </c>
-      <c r="V16" s="35"/>
-      <c r="W16" s="35"/>
-      <c r="X16" s="35"/>
       <c r="Y16" s="35"/>
       <c r="Z16" s="35"/>
       <c r="AA16" s="35"/>
@@ -3200,21 +3293,21 @@
       <c r="AF16" s="35"/>
       <c r="AG16" s="35"/>
       <c r="AH16" s="35"/>
-      <c r="AI16" s="33" t="n">
-        <f aca="false">G12</f>
+      <c r="AI16" s="35"/>
+      <c r="AJ16" s="35"/>
+      <c r="AK16" s="35"/>
+      <c r="AL16" s="33" t="n">
+        <f aca="false">J12</f>
         <v>10</v>
       </c>
-      <c r="AJ16" s="34" t="n">
-        <f aca="false">AK17-AK14</f>
+      <c r="AM16" s="34" t="n">
+        <f aca="false">AN17-AN14</f>
         <v>15</v>
       </c>
-      <c r="AK16" s="40" t="n">
-        <f aca="false">BR2-AK14</f>
+      <c r="AN16" s="33" t="n">
+        <f aca="false">BU2-AN14</f>
         <v>15</v>
       </c>
-      <c r="AL16" s="35"/>
-      <c r="AM16" s="35"/>
-      <c r="AN16" s="35"/>
       <c r="AO16" s="35"/>
       <c r="AP16" s="35"/>
       <c r="AQ16" s="35"/>
@@ -3243,61 +3336,69 @@
       <c r="BN16" s="35"/>
       <c r="BO16" s="35"/>
       <c r="BP16" s="35"/>
+      <c r="BQ16" s="35"/>
+      <c r="BR16" s="35"/>
+      <c r="BS16" s="35"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="42" t="s">
+      <c r="B17" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="42"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="43" t="s">
-        <v>54</v>
-      </c>
-      <c r="F17" s="44"/>
-      <c r="G17" s="45" t="n">
+      <c r="C17" s="41"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="F17" s="43"/>
+      <c r="G17" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="N17" s="27" t="n">
-        <f aca="false">P17-N16</f>
+      <c r="H17" s="45"/>
+      <c r="I17" s="45"/>
+      <c r="J17" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="27" t="n">
+        <f aca="false">S17-Q16</f>
         <v>12</v>
       </c>
-      <c r="O17" s="28"/>
-      <c r="P17" s="27" t="n">
-        <f aca="false">S17</f>
+      <c r="R17" s="28"/>
+      <c r="S17" s="27" t="n">
+        <f aca="false">V17</f>
         <v>13</v>
       </c>
-      <c r="S17" s="27" t="n">
-        <f aca="false">U17-S16</f>
+      <c r="V17" s="27" t="n">
+        <f aca="false">X17-V16</f>
         <v>13</v>
       </c>
-      <c r="T17" s="28"/>
-      <c r="U17" s="27" t="n">
-        <f aca="false">MIN(AI5,AI17)</f>
+      <c r="W17" s="28"/>
+      <c r="X17" s="27" t="n">
+        <f aca="false">MIN(AL5,AL17)</f>
         <v>16</v>
       </c>
-      <c r="AI17" s="27" t="n">
-        <f aca="false">AK17-AI16</f>
+      <c r="AL17" s="27" t="n">
+        <f aca="false">AN17-AL16</f>
         <v>24</v>
       </c>
-      <c r="AJ17" s="28"/>
-      <c r="AK17" s="27" t="n">
-        <f aca="false">BR5</f>
+      <c r="AM17" s="28"/>
+      <c r="AN17" s="27" t="n">
+        <f aca="false">BU5</f>
         <v>34</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="46" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B19" s="47" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C19" s="48"/>
       <c r="D19" s="49" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3309,84 +3410,84 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="32" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C21" s="34" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D21" s="33" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="50" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B22" s="51" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C22" s="52"/>
       <c r="D22" s="53" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="54" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C24" s="28"/>
       <c r="D24" s="27" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="32" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="32" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C26" s="34" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D26" s="33" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="54" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C27" s="28"/>
       <c r="D27" s="27" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B29" s="55" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C29" s="56" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D29" s="56"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B30" s="55" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C30" s="56" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D30" s="56"/>
     </row>
@@ -3395,25 +3496,25 @@
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B32" s="55" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C32" s="56" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D32" s="56"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B33" s="55" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C33" s="56" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D33" s="56"/>
     </row>
@@ -3428,34 +3529,34 @@
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B3:D3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="S3:U3"/>
-    <mergeCell ref="AI3:AK3"/>
-    <mergeCell ref="AN3:AP3"/>
-    <mergeCell ref="AS3:AU3"/>
-    <mergeCell ref="AX3:AZ3"/>
-    <mergeCell ref="BC3:BE3"/>
-    <mergeCell ref="BH3:BJ3"/>
-    <mergeCell ref="BM3:BO3"/>
-    <mergeCell ref="BR3:BT3"/>
+    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="Q3:S3"/>
+    <mergeCell ref="V3:X3"/>
+    <mergeCell ref="AL3:AN3"/>
+    <mergeCell ref="AQ3:AS3"/>
+    <mergeCell ref="AV3:AX3"/>
+    <mergeCell ref="BA3:BC3"/>
+    <mergeCell ref="BF3:BH3"/>
+    <mergeCell ref="BK3:BM3"/>
+    <mergeCell ref="BP3:BR3"/>
+    <mergeCell ref="BU3:BW3"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B9:D9"/>
-    <mergeCell ref="S9:U9"/>
-    <mergeCell ref="X9:Z9"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="AA9:AC9"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B15:D15"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="S15:U15"/>
-    <mergeCell ref="AI15:AK15"/>
+    <mergeCell ref="Q15:S15"/>
+    <mergeCell ref="V15:X15"/>
+    <mergeCell ref="AL15:AN15"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="B20:D20"/>
@@ -3465,7 +3566,7 @@
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="C33:D33"/>
   </mergeCells>
-  <conditionalFormatting sqref="C21 C26 T16:U16 S10:T10 AJ16:AK16 BS4 BN4 BI4 BD4 AY4 AT4 AO4 AJ4 Y10 T4 O4 O16 J4">
+  <conditionalFormatting sqref="C21 C26 W16:X16 V10:W10 AM16:AN16 BV4 BQ4 BL4 BG4 BB4 AW4 AR4 AM4 AB10 W4 R4 R16 M4">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -3477,5 +3578,6 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Übungen/Online_Shop.xlsx
+++ b/Übungen/Online_Shop.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="78">
   <si>
     <t xml:space="preserve">Beispiel: Funktionsorientierter Projektstrukturplan</t>
   </si>
@@ -183,7 +183,16 @@
     <t xml:space="preserve">1.1.1, 1.2.2</t>
   </si>
   <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.1.2, 1.1.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
   </si>
   <si>
     <t xml:space="preserve">1.2.4, 1.3.1</t>
@@ -253,11 +262,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
     <numFmt numFmtId="166" formatCode="@"/>
-    <numFmt numFmtId="167" formatCode="General"/>
+    <numFmt numFmtId="167" formatCode="0.00\ %"/>
+    <numFmt numFmtId="168" formatCode="General"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -482,7 +492,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="59">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -567,6 +577,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -575,6 +589,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="167" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -591,6 +609,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -615,11 +637,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -660,10 +682,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2277,12 +2295,16 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:BW35"/>
-  <sheetFormatPr defaultColWidth="11.82421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.82421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="1"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="20" width="11.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="16.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="6" style="3" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="2" min="2" style="20" width="11.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="3" min="3" style="0" width="13.52"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="1" max="4" min="4" style="0" width="11.81"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="5" min="5" style="3" width="16.12"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="6" min="6" style="3" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="3" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="21" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="3" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="107" min="11" style="0" width="3.83"/>
   </cols>
   <sheetData>
@@ -2290,27 +2312,27 @@
       <c r="A1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="22" t="s">
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="G1" s="22" t="s">
+      <c r="G1" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="H1" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="I1" s="22" t="s">
+      <c r="I1" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="J1" s="22" t="s">
+      <c r="J1" s="23" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2318,1211 +2340,1300 @@
       <c r="A2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="25" t="s">
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="G2" s="26" t="n">
+      <c r="G2" s="28" t="n">
         <v>5</v>
       </c>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="L2" s="27" t="n">
+      <c r="H2" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="I2" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" s="28" t="n">
+        <f aca="false">ROUNDUP(G2/(H2*I2),0)</f>
+        <v>2</v>
+      </c>
+      <c r="L2" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="M2" s="28"/>
-      <c r="N2" s="27" t="n">
+      <c r="M2" s="31"/>
+      <c r="N2" s="30" t="n">
         <f aca="false">L2+L4</f>
-        <v>5</v>
-      </c>
-      <c r="Q2" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q2" s="30" t="n">
         <f aca="false">N2</f>
-        <v>5</v>
-      </c>
-      <c r="R2" s="28"/>
-      <c r="S2" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="R2" s="31"/>
+      <c r="S2" s="30" t="n">
         <f aca="false">Q2+Q4</f>
-        <v>6</v>
-      </c>
-      <c r="V2" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="V2" s="30" t="n">
         <f aca="false">S2</f>
-        <v>6</v>
-      </c>
-      <c r="W2" s="28"/>
-      <c r="X2" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="W2" s="31"/>
+      <c r="X2" s="30" t="n">
         <f aca="false">V2+V4</f>
-        <v>10</v>
-      </c>
-      <c r="AL2" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AL2" s="30" t="n">
         <f aca="false">MAX(X2,AC8,X14)</f>
-        <v>16</v>
-      </c>
-      <c r="AM2" s="28"/>
-      <c r="AN2" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AM2" s="31"/>
+      <c r="AN2" s="30" t="n">
         <f aca="false">AL2+AL4</f>
-        <v>18</v>
-      </c>
-      <c r="AQ2" s="27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ2" s="30" t="n">
         <f aca="false">AN2</f>
-        <v>18</v>
-      </c>
-      <c r="AR2" s="28"/>
-      <c r="AS2" s="27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR2" s="31"/>
+      <c r="AS2" s="30" t="n">
         <f aca="false">AQ2+AQ4</f>
+        <v>13</v>
+      </c>
+      <c r="AV2" s="30" t="n">
+        <f aca="false">AS2</f>
+        <v>13</v>
+      </c>
+      <c r="AW2" s="31"/>
+      <c r="AX2" s="30" t="n">
+        <f aca="false">AV2+AV4</f>
+        <v>15</v>
+      </c>
+      <c r="BA2" s="30" t="n">
+        <f aca="false">AX2</f>
+        <v>15</v>
+      </c>
+      <c r="BB2" s="31"/>
+      <c r="BC2" s="30" t="n">
+        <f aca="false">BA2+BA4</f>
+        <v>17</v>
+      </c>
+      <c r="BF2" s="30" t="n">
+        <f aca="false">BC2</f>
+        <v>17</v>
+      </c>
+      <c r="BG2" s="31"/>
+      <c r="BH2" s="30" t="n">
+        <f aca="false">BF2+BF4</f>
+        <v>19</v>
+      </c>
+      <c r="BK2" s="30" t="n">
+        <f aca="false">BH2</f>
+        <v>19</v>
+      </c>
+      <c r="BL2" s="31"/>
+      <c r="BM2" s="30" t="n">
+        <f aca="false">BK2+BK4</f>
         <v>20</v>
       </c>
-      <c r="AV2" s="27" t="n">
-        <f aca="false">AS2</f>
+      <c r="BP2" s="30" t="n">
+        <f aca="false">BM2</f>
         <v>20</v>
       </c>
-      <c r="AW2" s="28"/>
-      <c r="AX2" s="27" t="n">
-        <f aca="false">AV2+AV4</f>
-        <v>22</v>
-      </c>
-      <c r="BA2" s="27" t="n">
-        <f aca="false">AX2</f>
-        <v>22</v>
-      </c>
-      <c r="BB2" s="28"/>
-      <c r="BC2" s="27" t="n">
-        <f aca="false">BA2+BA4</f>
-        <v>25</v>
-      </c>
-      <c r="BF2" s="27" t="n">
-        <f aca="false">BC2</f>
-        <v>25</v>
-      </c>
-      <c r="BG2" s="28"/>
-      <c r="BH2" s="27" t="n">
-        <f aca="false">BF2+BF4</f>
-        <v>28</v>
-      </c>
-      <c r="BK2" s="27" t="n">
-        <f aca="false">BH2</f>
-        <v>28</v>
-      </c>
-      <c r="BL2" s="28"/>
-      <c r="BM2" s="27" t="n">
-        <f aca="false">BK2+BK4</f>
+      <c r="BQ2" s="31"/>
+      <c r="BR2" s="30" t="n">
+        <f aca="false">BP2+BP4</f>
+        <v>24</v>
+      </c>
+      <c r="BU2" s="30" t="n">
+        <f aca="false">MAX(BR2,AN14)</f>
         <v>29</v>
       </c>
-      <c r="BP2" s="27" t="n">
-        <f aca="false">BM2</f>
-        <v>29</v>
-      </c>
-      <c r="BQ2" s="28"/>
-      <c r="BR2" s="27" t="n">
-        <f aca="false">BP2+BP4</f>
-        <v>34</v>
-      </c>
-      <c r="BU2" s="27" t="n">
-        <f aca="false">MAX(BR2,AN14)</f>
-        <v>34</v>
-      </c>
-      <c r="BV2" s="28"/>
-      <c r="BW2" s="27" t="n">
+      <c r="BV2" s="31"/>
+      <c r="BW2" s="30" t="n">
         <f aca="false">BU2+BU4</f>
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="30" t="s">
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="30" t="s">
-        <v>53</v>
-      </c>
-      <c r="G3" s="31" t="n">
+      <c r="F3" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="G3" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="31" t="n">
+      <c r="H3" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="I3" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="L3" s="32" t="s">
+      <c r="J3" s="28" t="n">
+        <f aca="false">ROUNDUP(G3/(H3*I3),0)</f>
+        <v>1</v>
+      </c>
+      <c r="L3" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="M3" s="32"/>
-      <c r="N3" s="32"/>
-      <c r="Q3" s="32" t="s">
+      <c r="M3" s="35"/>
+      <c r="N3" s="35"/>
+      <c r="Q3" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="R3" s="32"/>
-      <c r="S3" s="32"/>
-      <c r="V3" s="32" t="s">
+      <c r="R3" s="35"/>
+      <c r="S3" s="35"/>
+      <c r="V3" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="W3" s="32"/>
-      <c r="X3" s="32"/>
-      <c r="AL3" s="32" t="s">
+      <c r="W3" s="35"/>
+      <c r="X3" s="35"/>
+      <c r="AL3" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="AM3" s="32"/>
-      <c r="AN3" s="32"/>
-      <c r="AQ3" s="32" t="s">
+      <c r="AM3" s="35"/>
+      <c r="AN3" s="35"/>
+      <c r="AQ3" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="AR3" s="32"/>
-      <c r="AS3" s="32"/>
-      <c r="AV3" s="32" t="s">
+      <c r="AR3" s="35"/>
+      <c r="AS3" s="35"/>
+      <c r="AV3" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="AW3" s="32"/>
-      <c r="AX3" s="32"/>
-      <c r="BA3" s="32" t="s">
+      <c r="AW3" s="35"/>
+      <c r="AX3" s="35"/>
+      <c r="BA3" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="BB3" s="32"/>
-      <c r="BC3" s="32"/>
-      <c r="BF3" s="32" t="s">
+      <c r="BB3" s="35"/>
+      <c r="BC3" s="35"/>
+      <c r="BF3" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="BG3" s="32"/>
-      <c r="BH3" s="32"/>
-      <c r="BK3" s="32" t="s">
+      <c r="BG3" s="35"/>
+      <c r="BH3" s="35"/>
+      <c r="BK3" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="BL3" s="32"/>
-      <c r="BM3" s="32"/>
-      <c r="BP3" s="32" t="s">
+      <c r="BL3" s="35"/>
+      <c r="BM3" s="35"/>
+      <c r="BP3" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="BQ3" s="32"/>
-      <c r="BR3" s="32"/>
-      <c r="BU3" s="32" t="s">
+      <c r="BQ3" s="35"/>
+      <c r="BR3" s="35"/>
+      <c r="BU3" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="BV3" s="32"/>
-      <c r="BW3" s="32"/>
+      <c r="BV3" s="35"/>
+      <c r="BW3" s="35"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="30" t="s">
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="30" t="s">
+      <c r="F4" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="31" t="n">
+      <c r="G4" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="L4" s="33" t="n">
+      <c r="H4" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="I4" s="29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J4" s="28" t="n">
+        <f aca="false">ROUNDUP(G4/(H4*I4),0)</f>
+        <v>6</v>
+      </c>
+      <c r="L4" s="36" t="n">
         <f aca="false">J2</f>
-        <v>5</v>
-      </c>
-      <c r="M4" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" s="37" t="n">
         <f aca="false">N5-N2</f>
         <v>0</v>
       </c>
-      <c r="N4" s="33" t="n">
+      <c r="N4" s="36" t="n">
         <f aca="false">MIN(Q2,Q14)-N2</f>
         <v>0</v>
       </c>
-      <c r="O4" s="35"/>
-      <c r="P4" s="36"/>
-      <c r="Q4" s="33" t="n">
+      <c r="O4" s="38"/>
+      <c r="P4" s="39"/>
+      <c r="Q4" s="36" t="n">
         <f aca="false">J3</f>
         <v>1</v>
       </c>
-      <c r="R4" s="34" t="n">
+      <c r="R4" s="37" t="n">
         <f aca="false">S5-S2</f>
-        <v>0</v>
-      </c>
-      <c r="S4" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="S4" s="36" t="n">
         <f aca="false">MIN(V2,V8)-S2</f>
         <v>0</v>
       </c>
-      <c r="T4" s="35"/>
-      <c r="U4" s="36"/>
-      <c r="V4" s="33" t="n">
+      <c r="T4" s="38"/>
+      <c r="U4" s="39"/>
+      <c r="V4" s="36" t="n">
         <f aca="false">J4</f>
-        <v>4</v>
-      </c>
-      <c r="W4" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="W4" s="37" t="n">
         <f aca="false">X5-X2</f>
-        <v>6</v>
-      </c>
-      <c r="X4" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="X4" s="36" t="n">
         <f aca="false">AL2-X2</f>
-        <v>6</v>
-      </c>
-      <c r="Y4" s="35"/>
-      <c r="Z4" s="35"/>
-      <c r="AA4" s="35"/>
-      <c r="AB4" s="35"/>
-      <c r="AC4" s="35"/>
-      <c r="AD4" s="35"/>
-      <c r="AE4" s="35"/>
-      <c r="AF4" s="35"/>
-      <c r="AG4" s="35"/>
-      <c r="AH4" s="35"/>
-      <c r="AI4" s="35"/>
-      <c r="AJ4" s="35"/>
-      <c r="AK4" s="36"/>
-      <c r="AL4" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="38"/>
+      <c r="Z4" s="38"/>
+      <c r="AA4" s="38"/>
+      <c r="AB4" s="38"/>
+      <c r="AC4" s="38"/>
+      <c r="AD4" s="38"/>
+      <c r="AE4" s="38"/>
+      <c r="AF4" s="38"/>
+      <c r="AG4" s="38"/>
+      <c r="AH4" s="38"/>
+      <c r="AI4" s="38"/>
+      <c r="AJ4" s="38"/>
+      <c r="AK4" s="39"/>
+      <c r="AL4" s="36" t="n">
         <f aca="false">J9</f>
         <v>2</v>
       </c>
-      <c r="AM4" s="34" t="n">
+      <c r="AM4" s="37" t="n">
         <f aca="false">AN5-AN2</f>
-        <v>0</v>
-      </c>
-      <c r="AN4" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN4" s="36" t="n">
         <f aca="false">AQ2-AN2</f>
         <v>0</v>
       </c>
-      <c r="AO4" s="35"/>
-      <c r="AP4" s="35"/>
-      <c r="AQ4" s="33" t="n">
+      <c r="AO4" s="38"/>
+      <c r="AP4" s="38"/>
+      <c r="AQ4" s="36" t="n">
         <f aca="false">J10</f>
         <v>2</v>
       </c>
-      <c r="AR4" s="34" t="n">
+      <c r="AR4" s="37" t="n">
         <f aca="false">AS5-AS2</f>
-        <v>0</v>
-      </c>
-      <c r="AS4" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS4" s="36" t="n">
         <f aca="false">AV2-AS2</f>
         <v>0</v>
       </c>
-      <c r="AT4" s="35"/>
-      <c r="AU4" s="35"/>
-      <c r="AV4" s="33" t="n">
+      <c r="AT4" s="38"/>
+      <c r="AU4" s="38"/>
+      <c r="AV4" s="36" t="n">
         <f aca="false">J11</f>
         <v>2</v>
       </c>
-      <c r="AW4" s="34" t="n">
+      <c r="AW4" s="37" t="n">
         <f aca="false">AX5-AX2</f>
-        <v>0</v>
-      </c>
-      <c r="AX4" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX4" s="36" t="n">
         <f aca="false">BA2-AX2</f>
         <v>0</v>
       </c>
-      <c r="AY4" s="35"/>
-      <c r="AZ4" s="35"/>
-      <c r="BA4" s="33" t="n">
+      <c r="AY4" s="38"/>
+      <c r="AZ4" s="38"/>
+      <c r="BA4" s="36" t="n">
         <f aca="false">J13</f>
-        <v>3</v>
-      </c>
-      <c r="BB4" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB4" s="37" t="n">
         <f aca="false">BC5-BC2</f>
-        <v>0</v>
-      </c>
-      <c r="BC4" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC4" s="36" t="n">
         <f aca="false">BF2-BC2</f>
         <v>0</v>
       </c>
-      <c r="BD4" s="35"/>
-      <c r="BE4" s="35"/>
-      <c r="BF4" s="33" t="n">
+      <c r="BD4" s="38"/>
+      <c r="BE4" s="38"/>
+      <c r="BF4" s="36" t="n">
         <f aca="false">J14</f>
-        <v>3</v>
-      </c>
-      <c r="BG4" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG4" s="37" t="n">
         <f aca="false">BH5-BH2</f>
-        <v>0</v>
-      </c>
-      <c r="BH4" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH4" s="36" t="n">
         <f aca="false">BK2-BH2</f>
         <v>0</v>
       </c>
-      <c r="BI4" s="35"/>
-      <c r="BJ4" s="35"/>
-      <c r="BK4" s="33" t="n">
+      <c r="BI4" s="38"/>
+      <c r="BJ4" s="38"/>
+      <c r="BK4" s="36" t="n">
         <f aca="false">J15</f>
         <v>1</v>
       </c>
-      <c r="BL4" s="34" t="n">
+      <c r="BL4" s="37" t="n">
         <f aca="false">BM5-BM2</f>
-        <v>0</v>
-      </c>
-      <c r="BM4" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM4" s="36" t="n">
         <f aca="false">BP2-BM2</f>
         <v>0</v>
       </c>
-      <c r="BN4" s="35"/>
-      <c r="BO4" s="35"/>
-      <c r="BP4" s="33" t="n">
+      <c r="BN4" s="38"/>
+      <c r="BO4" s="38"/>
+      <c r="BP4" s="36" t="n">
         <f aca="false">J16</f>
+        <v>4</v>
+      </c>
+      <c r="BQ4" s="37" t="n">
+        <f aca="false">BR5-BR2</f>
         <v>5</v>
       </c>
-      <c r="BQ4" s="34" t="n">
-        <f aca="false">BR5-BR2</f>
-        <v>0</v>
-      </c>
-      <c r="BR4" s="33" t="n">
+      <c r="BR4" s="36" t="n">
         <f aca="false">BU2-BR2</f>
-        <v>0</v>
-      </c>
-      <c r="BS4" s="35"/>
-      <c r="BT4" s="36"/>
-      <c r="BU4" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="BS4" s="38"/>
+      <c r="BT4" s="39"/>
+      <c r="BU4" s="36" t="n">
         <f aca="false">J17</f>
         <v>1</v>
       </c>
-      <c r="BV4" s="34" t="n">
+      <c r="BV4" s="37" t="n">
         <f aca="false">BW5-BW2</f>
         <v>0</v>
       </c>
-      <c r="BW4" s="33"/>
+      <c r="BW4" s="36"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="30" t="s">
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="30" t="s">
+      <c r="F5" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="31" t="n">
+      <c r="G5" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="H5" s="30"/>
-      <c r="I5" s="30"/>
-      <c r="J5" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="L5" s="27" t="n">
+      <c r="H5" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="I5" s="29" t="n">
+        <f aca="false">(100%+50%+25%)/3</f>
+        <v>0.583333333333333</v>
+      </c>
+      <c r="J5" s="28" t="n">
+        <f aca="false">ROUNDUP(G5/(H5*I5),0)</f>
+        <v>2</v>
+      </c>
+      <c r="L5" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="M5" s="28"/>
-      <c r="N5" s="27" t="n">
+      <c r="M5" s="31"/>
+      <c r="N5" s="30" t="n">
         <f aca="false">MIN(Q5,Q17)</f>
-        <v>5</v>
-      </c>
-      <c r="P5" s="37"/>
-      <c r="Q5" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="P5" s="40"/>
+      <c r="Q5" s="30" t="n">
         <f aca="false">S5-Q4</f>
-        <v>5</v>
-      </c>
-      <c r="R5" s="28"/>
-      <c r="S5" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="R5" s="31"/>
+      <c r="S5" s="30" t="n">
         <f aca="false">MIN(V5,V11)</f>
-        <v>6</v>
-      </c>
-      <c r="U5" s="37"/>
-      <c r="V5" s="27" t="n">
+        <v>8</v>
+      </c>
+      <c r="U5" s="40"/>
+      <c r="V5" s="30" t="n">
         <f aca="false">X5-V4</f>
-        <v>12</v>
-      </c>
-      <c r="W5" s="28"/>
-      <c r="X5" s="27" t="n">
+        <v>8</v>
+      </c>
+      <c r="W5" s="31"/>
+      <c r="X5" s="30" t="n">
         <f aca="false">AL5</f>
+        <v>14</v>
+      </c>
+      <c r="AK5" s="40"/>
+      <c r="AL5" s="30" t="n">
+        <f aca="false">AN5-AL4</f>
+        <v>14</v>
+      </c>
+      <c r="AM5" s="31"/>
+      <c r="AN5" s="30" t="n">
+        <f aca="false">AQ5</f>
         <v>16</v>
       </c>
-      <c r="AK5" s="37"/>
-      <c r="AL5" s="27" t="n">
-        <f aca="false">AN5-AL4</f>
+      <c r="AQ5" s="30" t="n">
+        <f aca="false">AS5-AQ4</f>
         <v>16</v>
       </c>
-      <c r="AM5" s="28"/>
-      <c r="AN5" s="27" t="n">
-        <f aca="false">AQ5</f>
+      <c r="AR5" s="31"/>
+      <c r="AS5" s="30" t="n">
+        <f aca="false">AV5</f>
         <v>18</v>
       </c>
-      <c r="AQ5" s="27" t="n">
-        <f aca="false">AS5-AQ4</f>
+      <c r="AV5" s="30" t="n">
+        <f aca="false">AX5-AV4</f>
         <v>18</v>
       </c>
-      <c r="AR5" s="28"/>
-      <c r="AS5" s="27" t="n">
-        <f aca="false">AV5</f>
+      <c r="AW5" s="31"/>
+      <c r="AX5" s="30" t="n">
+        <f aca="false">BA5</f>
         <v>20</v>
       </c>
-      <c r="AV5" s="27" t="n">
-        <f aca="false">AX5-AV4</f>
+      <c r="BA5" s="30" t="n">
+        <f aca="false">BC5-BA4</f>
         <v>20</v>
       </c>
-      <c r="AW5" s="28"/>
-      <c r="AX5" s="27" t="n">
-        <f aca="false">BA5</f>
+      <c r="BB5" s="31"/>
+      <c r="BC5" s="30" t="n">
+        <f aca="false">BF5</f>
         <v>22</v>
       </c>
-      <c r="BA5" s="27" t="n">
-        <f aca="false">BC5-BA4</f>
+      <c r="BF5" s="30" t="n">
+        <f aca="false">BH5-BF4</f>
         <v>22</v>
       </c>
-      <c r="BB5" s="28"/>
-      <c r="BC5" s="27" t="n">
-        <f aca="false">BF5</f>
+      <c r="BG5" s="31"/>
+      <c r="BH5" s="30" t="n">
+        <f aca="false">BK5</f>
+        <v>24</v>
+      </c>
+      <c r="BK5" s="30" t="n">
+        <f aca="false">BM5-BK4</f>
+        <v>24</v>
+      </c>
+      <c r="BL5" s="31"/>
+      <c r="BM5" s="30" t="n">
+        <f aca="false">BP5</f>
         <v>25</v>
       </c>
-      <c r="BF5" s="27" t="n">
-        <f aca="false">BH5-BF4</f>
+      <c r="BP5" s="30" t="n">
+        <f aca="false">BR5-BP4</f>
         <v>25</v>
       </c>
-      <c r="BG5" s="28"/>
-      <c r="BH5" s="27" t="n">
-        <f aca="false">BK5</f>
-        <v>28</v>
-      </c>
-      <c r="BK5" s="27" t="n">
-        <f aca="false">BM5-BK4</f>
-        <v>28</v>
-      </c>
-      <c r="BL5" s="28"/>
-      <c r="BM5" s="27" t="n">
-        <f aca="false">BP5</f>
+      <c r="BQ5" s="31"/>
+      <c r="BR5" s="30" t="n">
+        <f aca="false">BU5</f>
         <v>29</v>
       </c>
-      <c r="BP5" s="27" t="n">
-        <f aca="false">BR5-BP4</f>
+      <c r="BT5" s="40"/>
+      <c r="BU5" s="30" t="n">
+        <f aca="false">BW5-BU4</f>
         <v>29</v>
       </c>
-      <c r="BQ5" s="28"/>
-      <c r="BR5" s="27" t="n">
-        <f aca="false">BU5</f>
-        <v>34</v>
-      </c>
-      <c r="BT5" s="37"/>
-      <c r="BU5" s="27" t="n">
-        <f aca="false">BW5-BU4</f>
-        <v>34</v>
-      </c>
-      <c r="BV5" s="28"/>
-      <c r="BW5" s="27" t="n">
+      <c r="BV5" s="31"/>
+      <c r="BW5" s="30" t="n">
         <f aca="false">BW2</f>
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="29" t="s">
+      <c r="B6" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="38" t="s">
+      <c r="C6" s="32"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="38" t="s">
+      <c r="F6" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="39" t="n">
+      <c r="G6" s="42" t="n">
         <v>7</v>
       </c>
-      <c r="H6" s="38"/>
-      <c r="I6" s="38"/>
-      <c r="J6" s="39" t="n">
-        <v>7</v>
-      </c>
-      <c r="P6" s="37"/>
-      <c r="U6" s="37"/>
-      <c r="AK6" s="37"/>
-      <c r="BT6" s="37"/>
+      <c r="H6" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="I6" s="29" t="n">
+        <f aca="false">(100%+50%+25%)/3</f>
+        <v>0.583333333333333</v>
+      </c>
+      <c r="J6" s="28" t="n">
+        <f aca="false">ROUNDUP(G6/(H6*I6),0)</f>
+        <v>4</v>
+      </c>
+      <c r="P6" s="40"/>
+      <c r="U6" s="40"/>
+      <c r="AK6" s="40"/>
+      <c r="BT6" s="40"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="30" t="s">
+      <c r="C7" s="32"/>
+      <c r="D7" s="32"/>
+      <c r="E7" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="30" t="s">
+      <c r="F7" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="31" t="n">
+      <c r="G7" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="H7" s="30"/>
-      <c r="I7" s="30"/>
-      <c r="J7" s="31" t="n">
+      <c r="H7" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="I7" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="P7" s="37"/>
-      <c r="U7" s="37"/>
-      <c r="AK7" s="37"/>
-      <c r="BT7" s="37"/>
+      <c r="J7" s="28" t="n">
+        <f aca="false">ROUNDUP(G7/(H7*I7),0)</f>
+        <v>1</v>
+      </c>
+      <c r="P7" s="40"/>
+      <c r="U7" s="40"/>
+      <c r="AK7" s="40"/>
+      <c r="BT7" s="40"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="38" t="s">
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="F8" s="38" t="s">
-        <v>54</v>
-      </c>
-      <c r="G8" s="39" t="n">
+      <c r="F8" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="H8" s="38"/>
-      <c r="I8" s="38"/>
-      <c r="J8" s="39" t="n">
+      <c r="H8" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="I8" s="29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J8" s="28" t="n">
+        <f aca="false">ROUNDUP(G8/(H8*I8),0)</f>
+        <v>6</v>
+      </c>
+      <c r="P8" s="40"/>
+      <c r="U8" s="40"/>
+      <c r="V8" s="30" t="n">
+        <f aca="false">S2</f>
         <v>3</v>
       </c>
-      <c r="P8" s="37"/>
-      <c r="U8" s="37"/>
-      <c r="V8" s="27" t="n">
-        <f aca="false">S2</f>
-        <v>6</v>
-      </c>
-      <c r="W8" s="28"/>
-      <c r="X8" s="27" t="n">
+      <c r="W8" s="31"/>
+      <c r="X8" s="30" t="n">
         <f aca="false">V8+V10</f>
+        <v>5</v>
+      </c>
+      <c r="AA8" s="30" t="n">
+        <f aca="false">X8</f>
+        <v>5</v>
+      </c>
+      <c r="AB8" s="31"/>
+      <c r="AC8" s="30" t="n">
+        <f aca="false">AA8+AA10</f>
         <v>9</v>
       </c>
-      <c r="AA8" s="27" t="n">
-        <f aca="false">X8</f>
-        <v>9</v>
-      </c>
-      <c r="AB8" s="28"/>
-      <c r="AC8" s="27" t="n">
-        <f aca="false">AA8+AA10</f>
-        <v>16</v>
-      </c>
-      <c r="AK8" s="37"/>
-      <c r="BT8" s="37"/>
+      <c r="AK8" s="40"/>
+      <c r="BT8" s="40"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="38" t="s">
+      <c r="C9" s="32"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" s="41" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="F9" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="39" t="n">
+      <c r="I9" s="29" t="n">
+        <f aca="false">(100%+(100%-$I$12))/2</f>
+        <v>0.75</v>
+      </c>
+      <c r="J9" s="28" t="n">
+        <f aca="false">ROUNDUP(G9/(H9*I9),0)</f>
         <v>2</v>
       </c>
-      <c r="H9" s="38"/>
-      <c r="I9" s="38"/>
-      <c r="J9" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="P9" s="37"/>
-      <c r="U9" s="37"/>
-      <c r="V9" s="32" t="s">
+      <c r="P9" s="40"/>
+      <c r="U9" s="40"/>
+      <c r="V9" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="W9" s="32"/>
-      <c r="X9" s="32"/>
-      <c r="AA9" s="32" t="s">
+      <c r="W9" s="35"/>
+      <c r="X9" s="35"/>
+      <c r="AA9" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="AB9" s="32"/>
-      <c r="AC9" s="32"/>
-      <c r="AK9" s="37"/>
-      <c r="BT9" s="37"/>
+      <c r="AB9" s="35"/>
+      <c r="AC9" s="35"/>
+      <c r="AK9" s="40"/>
+      <c r="BT9" s="40"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="38" t="s">
+      <c r="C10" s="32"/>
+      <c r="D10" s="32"/>
+      <c r="E10" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="38" t="s">
+      <c r="F10" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="G10" s="39" t="n">
+      <c r="G10" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="38"/>
-      <c r="I10" s="38"/>
-      <c r="J10" s="39" t="n">
+      <c r="H10" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="I10" s="29" t="n">
+        <f aca="false">(100%+(100%-$I$12))/2</f>
+        <v>0.75</v>
+      </c>
+      <c r="J10" s="28" t="n">
+        <f aca="false">ROUNDUP(G10/(H10*I10),0)</f>
         <v>2</v>
       </c>
-      <c r="P10" s="37"/>
-      <c r="U10" s="35"/>
-      <c r="V10" s="33" t="n">
+      <c r="P10" s="40"/>
+      <c r="U10" s="38"/>
+      <c r="V10" s="36" t="n">
         <f aca="false">J5</f>
-        <v>3</v>
-      </c>
-      <c r="W10" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="W10" s="37" t="n">
         <f aca="false">X11-X8</f>
-        <v>0</v>
-      </c>
-      <c r="X10" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="X10" s="36" t="n">
         <f aca="false">AA8-X8</f>
         <v>0</v>
       </c>
-      <c r="Y10" s="35"/>
-      <c r="Z10" s="35"/>
-      <c r="AA10" s="33" t="n">
+      <c r="Y10" s="38"/>
+      <c r="Z10" s="38"/>
+      <c r="AA10" s="36" t="n">
         <f aca="false">J6</f>
-        <v>7</v>
-      </c>
-      <c r="AB10" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB10" s="37" t="n">
         <f aca="false">AC11-AC8</f>
-        <v>0</v>
-      </c>
-      <c r="AC10" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC10" s="36" t="n">
         <f aca="false">AL2-AC8</f>
         <v>0</v>
       </c>
-      <c r="AD10" s="35"/>
-      <c r="AE10" s="35"/>
-      <c r="AF10" s="35"/>
-      <c r="AG10" s="35"/>
-      <c r="AH10" s="35"/>
-      <c r="AI10" s="35"/>
-      <c r="AJ10" s="35"/>
-      <c r="AK10" s="37"/>
-      <c r="BT10" s="37"/>
+      <c r="AD10" s="38"/>
+      <c r="AE10" s="38"/>
+      <c r="AF10" s="38"/>
+      <c r="AG10" s="38"/>
+      <c r="AH10" s="38"/>
+      <c r="AI10" s="38"/>
+      <c r="AJ10" s="38"/>
+      <c r="AK10" s="40"/>
+      <c r="BT10" s="40"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="29" t="s">
+      <c r="B11" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="38" t="s">
+      <c r="C11" s="32"/>
+      <c r="D11" s="32"/>
+      <c r="E11" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="F11" s="38" t="s">
+      <c r="F11" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="39" t="n">
+      <c r="G11" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="H11" s="38"/>
-      <c r="I11" s="38"/>
-      <c r="J11" s="39" t="n">
+      <c r="H11" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="I11" s="29" t="n">
+        <f aca="false">(100%+(100%-$I$12))/2</f>
+        <v>0.75</v>
+      </c>
+      <c r="J11" s="28" t="n">
+        <f aca="false">ROUNDUP(G11/(H11*I11),0)</f>
         <v>2</v>
       </c>
-      <c r="P11" s="37"/>
-      <c r="V11" s="27" t="n">
+      <c r="P11" s="40"/>
+      <c r="V11" s="30" t="n">
         <f aca="false">X11-V10</f>
-        <v>6</v>
-      </c>
-      <c r="W11" s="28"/>
-      <c r="X11" s="27" t="n">
+        <v>8</v>
+      </c>
+      <c r="W11" s="31"/>
+      <c r="X11" s="30" t="n">
         <f aca="false">AA11</f>
-        <v>9</v>
-      </c>
-      <c r="AA11" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA11" s="30" t="n">
         <f aca="false">AC11-AA10</f>
-        <v>9</v>
-      </c>
-      <c r="AB11" s="28"/>
-      <c r="AC11" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB11" s="31"/>
+      <c r="AC11" s="30" t="n">
         <f aca="false">AL5</f>
-        <v>16</v>
-      </c>
-      <c r="AK11" s="37"/>
-      <c r="BT11" s="37"/>
+        <v>14</v>
+      </c>
+      <c r="AK11" s="40"/>
+      <c r="BT11" s="40"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="29" t="s">
+      <c r="B12" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="32"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="41" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="42" t="n">
+        <v>10</v>
+      </c>
+      <c r="H12" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="29"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="F12" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="G12" s="39" t="n">
-        <v>10</v>
-      </c>
-      <c r="H12" s="38"/>
-      <c r="I12" s="38"/>
-      <c r="J12" s="39" t="n">
-        <v>10</v>
-      </c>
-      <c r="P12" s="37"/>
-      <c r="AA12" s="40"/>
-      <c r="AK12" s="37"/>
-      <c r="BT12" s="37"/>
+      <c r="I12" s="29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J12" s="28" t="n">
+        <f aca="false">ROUNDUP(G12/(H12*I12),0)</f>
+        <v>20</v>
+      </c>
+      <c r="P12" s="40"/>
+      <c r="AA12" s="43"/>
+      <c r="AK12" s="40"/>
+      <c r="BT12" s="40"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="38" t="s">
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="F13" s="38" t="s">
+      <c r="F13" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="G13" s="39" t="n">
+      <c r="G13" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="H13" s="38"/>
-      <c r="I13" s="38"/>
-      <c r="J13" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="P13" s="37"/>
-      <c r="AA13" s="40"/>
-      <c r="AK13" s="37"/>
-      <c r="BT13" s="37"/>
+      <c r="H13" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="I13" s="29" t="n">
+        <f aca="false">(100%+(100%-$I$12))/2</f>
+        <v>0.75</v>
+      </c>
+      <c r="J13" s="28" t="n">
+        <f aca="false">ROUNDUP(G13/(H13*I13),0)</f>
+        <v>2</v>
+      </c>
+      <c r="P13" s="40"/>
+      <c r="AA13" s="43"/>
+      <c r="AK13" s="40"/>
+      <c r="BT13" s="40"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="29" t="s">
+      <c r="B14" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="38" t="s">
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="F14" s="38" t="s">
+      <c r="F14" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="G14" s="39" t="n">
+      <c r="G14" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="H14" s="38"/>
-      <c r="I14" s="38"/>
-      <c r="J14" s="39" t="n">
+      <c r="H14" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="I14" s="29" t="n">
+        <f aca="false">(100%+(100%-$I$12))/2</f>
+        <v>0.75</v>
+      </c>
+      <c r="J14" s="28" t="n">
+        <f aca="false">ROUNDUP(G14/(H14*I14),0)</f>
+        <v>2</v>
+      </c>
+      <c r="P14" s="40"/>
+      <c r="Q14" s="30" t="n">
+        <f aca="false">N2</f>
+        <v>2</v>
+      </c>
+      <c r="R14" s="31"/>
+      <c r="S14" s="30" t="n">
+        <f aca="false">Q14+Q16</f>
         <v>3</v>
       </c>
-      <c r="P14" s="37"/>
-      <c r="Q14" s="27" t="n">
-        <f aca="false">N2</f>
-        <v>5</v>
-      </c>
-      <c r="R14" s="28"/>
-      <c r="S14" s="27" t="n">
-        <f aca="false">Q14+Q16</f>
-        <v>6</v>
-      </c>
-      <c r="V14" s="27" t="n">
+      <c r="V14" s="30" t="n">
         <f aca="false">S14</f>
-        <v>6</v>
-      </c>
-      <c r="W14" s="28"/>
-      <c r="X14" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="W14" s="31"/>
+      <c r="X14" s="30" t="n">
         <f aca="false">V14+V16</f>
         <v>9</v>
       </c>
-      <c r="AK14" s="37"/>
-      <c r="AL14" s="27" t="n">
+      <c r="AK14" s="40"/>
+      <c r="AL14" s="30" t="n">
         <f aca="false">X14</f>
         <v>9</v>
       </c>
-      <c r="AM14" s="28"/>
-      <c r="AN14" s="27" t="n">
+      <c r="AM14" s="31"/>
+      <c r="AN14" s="30" t="n">
         <f aca="false">AL14+AL16</f>
-        <v>19</v>
-      </c>
-      <c r="BT14" s="37"/>
+        <v>29</v>
+      </c>
+      <c r="BT14" s="40"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="29" t="s">
+      <c r="B15" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="38" t="s">
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="F15" s="38" t="s">
+      <c r="F15" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="G15" s="39" t="n">
+      <c r="G15" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="38"/>
-      <c r="I15" s="38"/>
-      <c r="J15" s="39" t="n">
+      <c r="H15" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="I15" s="29" t="n">
+        <f aca="false">(100%+(100%-$I$12))/2</f>
+        <v>0.75</v>
+      </c>
+      <c r="J15" s="28" t="n">
+        <f aca="false">ROUNDUP(G15/(H15*I15),0)</f>
         <v>1</v>
       </c>
-      <c r="P15" s="37"/>
-      <c r="Q15" s="32" t="s">
+      <c r="P15" s="40"/>
+      <c r="Q15" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="R15" s="32"/>
-      <c r="S15" s="32"/>
-      <c r="V15" s="32" t="s">
+      <c r="R15" s="35"/>
+      <c r="S15" s="35"/>
+      <c r="V15" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="W15" s="32"/>
-      <c r="X15" s="32"/>
-      <c r="Y15" s="35"/>
-      <c r="Z15" s="35"/>
-      <c r="AA15" s="35"/>
-      <c r="AB15" s="35"/>
-      <c r="AC15" s="35"/>
-      <c r="AD15" s="35"/>
-      <c r="AE15" s="35"/>
-      <c r="AF15" s="35"/>
-      <c r="AG15" s="35"/>
-      <c r="AH15" s="35"/>
-      <c r="AI15" s="35"/>
-      <c r="AJ15" s="35"/>
-      <c r="AK15" s="40"/>
-      <c r="AL15" s="32" t="s">
+      <c r="W15" s="35"/>
+      <c r="X15" s="35"/>
+      <c r="Y15" s="38"/>
+      <c r="Z15" s="38"/>
+      <c r="AA15" s="38"/>
+      <c r="AB15" s="38"/>
+      <c r="AC15" s="38"/>
+      <c r="AD15" s="38"/>
+      <c r="AE15" s="38"/>
+      <c r="AF15" s="38"/>
+      <c r="AG15" s="38"/>
+      <c r="AH15" s="38"/>
+      <c r="AI15" s="38"/>
+      <c r="AJ15" s="38"/>
+      <c r="AK15" s="43"/>
+      <c r="AL15" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="AM15" s="32"/>
-      <c r="AN15" s="32"/>
-      <c r="BT15" s="37"/>
+      <c r="AM15" s="35"/>
+      <c r="AN15" s="35"/>
+      <c r="BT15" s="40"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="29" t="s">
+      <c r="B16" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="38" t="s">
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="F16" s="38" t="s">
+      <c r="F16" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="G16" s="39" t="n">
+      <c r="G16" s="42" t="n">
         <v>5</v>
       </c>
-      <c r="H16" s="38"/>
-      <c r="I16" s="38"/>
-      <c r="J16" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="P16" s="35"/>
-      <c r="Q16" s="33" t="n">
+      <c r="H16" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="I16" s="29" t="n">
+        <f aca="false">(100%+(100%-$I$12))/2</f>
+        <v>0.75</v>
+      </c>
+      <c r="J16" s="28" t="n">
+        <f aca="false">ROUNDUP(G16/(H16*I16),0)</f>
+        <v>4</v>
+      </c>
+      <c r="P16" s="38"/>
+      <c r="Q16" s="36" t="n">
         <f aca="false">J7</f>
         <v>1</v>
       </c>
-      <c r="R16" s="34" t="n">
+      <c r="R16" s="37" t="n">
         <f aca="false">S17-S14</f>
-        <v>7</v>
-      </c>
-      <c r="S16" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="36" t="n">
         <f aca="false">V14-S14</f>
         <v>0</v>
       </c>
-      <c r="T16" s="35"/>
-      <c r="U16" s="35"/>
-      <c r="V16" s="33" t="n">
+      <c r="T16" s="38"/>
+      <c r="U16" s="38"/>
+      <c r="V16" s="36" t="n">
         <f aca="false">J8</f>
-        <v>3</v>
-      </c>
-      <c r="W16" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="W16" s="37" t="n">
         <f aca="false">X17-X14</f>
-        <v>7</v>
-      </c>
-      <c r="X16" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" s="36" t="n">
         <f aca="false">MIN(AL2,AL14)-X14</f>
         <v>0</v>
       </c>
-      <c r="Y16" s="35"/>
-      <c r="Z16" s="35"/>
-      <c r="AA16" s="35"/>
-      <c r="AB16" s="35"/>
-      <c r="AC16" s="35"/>
-      <c r="AD16" s="35"/>
-      <c r="AE16" s="35"/>
-      <c r="AF16" s="35"/>
-      <c r="AG16" s="35"/>
-      <c r="AH16" s="35"/>
-      <c r="AI16" s="35"/>
-      <c r="AJ16" s="35"/>
-      <c r="AK16" s="35"/>
-      <c r="AL16" s="33" t="n">
+      <c r="Y16" s="38"/>
+      <c r="Z16" s="38"/>
+      <c r="AA16" s="38"/>
+      <c r="AB16" s="38"/>
+      <c r="AC16" s="38"/>
+      <c r="AD16" s="38"/>
+      <c r="AE16" s="38"/>
+      <c r="AF16" s="38"/>
+      <c r="AG16" s="38"/>
+      <c r="AH16" s="38"/>
+      <c r="AI16" s="38"/>
+      <c r="AJ16" s="38"/>
+      <c r="AK16" s="38"/>
+      <c r="AL16" s="36" t="n">
         <f aca="false">J12</f>
-        <v>10</v>
-      </c>
-      <c r="AM16" s="34" t="n">
+        <v>20</v>
+      </c>
+      <c r="AM16" s="37" t="n">
         <f aca="false">AN17-AN14</f>
-        <v>15</v>
-      </c>
-      <c r="AN16" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" s="36" t="n">
         <f aca="false">BU2-AN14</f>
-        <v>15</v>
-      </c>
-      <c r="AO16" s="35"/>
-      <c r="AP16" s="35"/>
-      <c r="AQ16" s="35"/>
-      <c r="AR16" s="35"/>
-      <c r="AS16" s="35"/>
-      <c r="AT16" s="35"/>
-      <c r="AU16" s="35"/>
-      <c r="AV16" s="35"/>
-      <c r="AW16" s="35"/>
-      <c r="AX16" s="35"/>
-      <c r="AY16" s="35"/>
-      <c r="AZ16" s="35"/>
-      <c r="BA16" s="35"/>
-      <c r="BB16" s="35"/>
-      <c r="BC16" s="35"/>
-      <c r="BD16" s="35"/>
-      <c r="BE16" s="35"/>
-      <c r="BF16" s="35"/>
-      <c r="BG16" s="35"/>
-      <c r="BH16" s="35"/>
-      <c r="BI16" s="35"/>
-      <c r="BJ16" s="35"/>
-      <c r="BK16" s="35"/>
-      <c r="BL16" s="35"/>
-      <c r="BM16" s="35"/>
-      <c r="BN16" s="35"/>
-      <c r="BO16" s="35"/>
-      <c r="BP16" s="35"/>
-      <c r="BQ16" s="35"/>
-      <c r="BR16" s="35"/>
-      <c r="BS16" s="35"/>
+        <v>0</v>
+      </c>
+      <c r="AO16" s="38"/>
+      <c r="AP16" s="38"/>
+      <c r="AQ16" s="38"/>
+      <c r="AR16" s="38"/>
+      <c r="AS16" s="38"/>
+      <c r="AT16" s="38"/>
+      <c r="AU16" s="38"/>
+      <c r="AV16" s="38"/>
+      <c r="AW16" s="38"/>
+      <c r="AX16" s="38"/>
+      <c r="AY16" s="38"/>
+      <c r="AZ16" s="38"/>
+      <c r="BA16" s="38"/>
+      <c r="BB16" s="38"/>
+      <c r="BC16" s="38"/>
+      <c r="BD16" s="38"/>
+      <c r="BE16" s="38"/>
+      <c r="BF16" s="38"/>
+      <c r="BG16" s="38"/>
+      <c r="BH16" s="38"/>
+      <c r="BI16" s="38"/>
+      <c r="BJ16" s="38"/>
+      <c r="BK16" s="38"/>
+      <c r="BL16" s="38"/>
+      <c r="BM16" s="38"/>
+      <c r="BN16" s="38"/>
+      <c r="BO16" s="38"/>
+      <c r="BP16" s="38"/>
+      <c r="BQ16" s="38"/>
+      <c r="BR16" s="38"/>
+      <c r="BS16" s="38"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="41" t="s">
+      <c r="B17" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="41"/>
-      <c r="D17" s="41"/>
-      <c r="E17" s="42" t="s">
-        <v>57</v>
-      </c>
-      <c r="F17" s="43"/>
-      <c r="G17" s="44" t="n">
+      <c r="C17" s="44"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="45" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" s="46"/>
+      <c r="G17" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="45"/>
-      <c r="I17" s="45"/>
-      <c r="J17" s="44" t="n">
+      <c r="H17" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="I17" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="Q17" s="27" t="n">
+      <c r="J17" s="28" t="n">
+        <f aca="false">ROUNDUP(G17/(H17*I17),0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q17" s="30" t="n">
         <f aca="false">S17-Q16</f>
-        <v>12</v>
-      </c>
-      <c r="R17" s="28"/>
-      <c r="S17" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" s="31"/>
+      <c r="S17" s="30" t="n">
         <f aca="false">V17</f>
-        <v>13</v>
-      </c>
-      <c r="V17" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="V17" s="30" t="n">
         <f aca="false">X17-V16</f>
-        <v>13</v>
-      </c>
-      <c r="W17" s="28"/>
-      <c r="X17" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="W17" s="31"/>
+      <c r="X17" s="30" t="n">
         <f aca="false">MIN(AL5,AL17)</f>
-        <v>16</v>
-      </c>
-      <c r="AL17" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AL17" s="30" t="n">
         <f aca="false">AN17-AL16</f>
-        <v>24</v>
-      </c>
-      <c r="AM17" s="28"/>
-      <c r="AN17" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AM17" s="31"/>
+      <c r="AN17" s="30" t="n">
         <f aca="false">BU5</f>
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="46" t="s">
-        <v>58</v>
-      </c>
-      <c r="B19" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="C19" s="48"/>
-      <c r="D19" s="49" t="s">
-        <v>60</v>
+      <c r="A19" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" s="50"/>
+      <c r="D19" s="51" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="32" t="s">
+      <c r="B20" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="C20" s="32"/>
-      <c r="D20" s="32"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="35"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="32" t="s">
+      <c r="B21" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="C21" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="D21" s="33" t="s">
+      <c r="C21" s="37" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" s="36" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="52" t="s">
+        <v>66</v>
+      </c>
+      <c r="B22" s="53" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="50" t="s">
+      <c r="C22" s="54"/>
+      <c r="D22" s="55" t="s">
         <v>63</v>
       </c>
-      <c r="B22" s="51" t="s">
-        <v>59</v>
-      </c>
-      <c r="C22" s="52"/>
-      <c r="D22" s="53" t="s">
-        <v>60</v>
-      </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="54" t="s">
-        <v>64</v>
-      </c>
-      <c r="C24" s="28"/>
-      <c r="D24" s="27" t="s">
-        <v>65</v>
+      <c r="B24" s="56" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" s="31"/>
+      <c r="D24" s="30" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="32" t="s">
-        <v>66</v>
-      </c>
-      <c r="C25" s="32"/>
-      <c r="D25" s="32"/>
+      <c r="B25" s="35" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="35"/>
+      <c r="D25" s="35"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="32" t="s">
-        <v>67</v>
-      </c>
-      <c r="C26" s="34" t="s">
-        <v>68</v>
-      </c>
-      <c r="D26" s="33" t="s">
-        <v>69</v>
+      <c r="B26" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="C26" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="D26" s="36" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="54" t="s">
-        <v>70</v>
-      </c>
-      <c r="C27" s="28"/>
-      <c r="D27" s="27" t="s">
-        <v>71</v>
+      <c r="B27" s="56" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" s="31"/>
+      <c r="D27" s="30" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="B29" s="55" t="s">
-        <v>72</v>
-      </c>
-      <c r="C29" s="56" t="s">
-        <v>73</v>
-      </c>
-      <c r="D29" s="56"/>
+        <v>67</v>
+      </c>
+      <c r="B29" s="57" t="s">
+        <v>75</v>
+      </c>
+      <c r="C29" s="58" t="s">
+        <v>76</v>
+      </c>
+      <c r="D29" s="58"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="B30" s="55" t="s">
-        <v>72</v>
-      </c>
-      <c r="C30" s="56" t="s">
-        <v>74</v>
-      </c>
-      <c r="D30" s="56"/>
+        <v>68</v>
+      </c>
+      <c r="B30" s="57" t="s">
+        <v>75</v>
+      </c>
+      <c r="C30" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="D30" s="58"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="55"/>
+      <c r="B31" s="57"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="B32" s="55" t="s">
-        <v>72</v>
-      </c>
-      <c r="C32" s="56" t="s">
-        <v>74</v>
-      </c>
-      <c r="D32" s="56"/>
+        <v>68</v>
+      </c>
+      <c r="B32" s="57" t="s">
+        <v>75</v>
+      </c>
+      <c r="C32" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="D32" s="58"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="B33" s="55" t="s">
-        <v>72</v>
-      </c>
-      <c r="C33" s="56" t="s">
-        <v>73</v>
-      </c>
-      <c r="D33" s="56"/>
+        <v>67</v>
+      </c>
+      <c r="B33" s="57" t="s">
+        <v>75</v>
+      </c>
+      <c r="C33" s="58" t="s">
+        <v>76</v>
+      </c>
+      <c r="D33" s="58"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="55"/>
+      <c r="B34" s="57"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="55"/>
+      <c r="B35" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="39">

--- a/Übungen/Online_Shop.xlsx
+++ b/Übungen/Online_Shop.xlsx
@@ -5,11 +5,12 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="PSP" sheetId="1" state="visible" r:id="rId2"/>
     <sheet name="Netzplan" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="Gantt" sheetId="3" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="78">
   <si>
     <t xml:space="preserve">Beispiel: Funktionsorientierter Projektstrukturplan</t>
   </si>
@@ -262,14 +263,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
     <numFmt numFmtId="166" formatCode="@"/>
     <numFmt numFmtId="167" formatCode="0.00\ %"/>
     <numFmt numFmtId="168" formatCode="General"/>
+    <numFmt numFmtId="169" formatCode="0\ %"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="13">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -328,8 +330,36 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF127622"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF55308D"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF8000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFDDDDDD"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -357,7 +387,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFAADCF7"/>
-        <bgColor rgb="FFCCCCFF"/>
+        <bgColor rgb="FFDDDDDD"/>
       </patternFill>
     </fill>
     <fill>
@@ -369,13 +399,19 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00A933"/>
-        <bgColor rgb="FF008000"/>
+        <bgColor rgb="FF008080"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF8000"/>
         <bgColor rgb="FFFF6600"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFEEEEEE"/>
       </patternFill>
     </fill>
   </fills>
@@ -492,7 +528,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="86">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -727,6 +763,114 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="70" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="70" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="70" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="9" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="9" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -741,7 +885,7 @@
     <cellStyle name="KritischerPfad" xfId="21"/>
     <cellStyle name="Wochenende" xfId="22"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="4">
     <dxf>
       <font>
         <name val="Arial"/>
@@ -750,6 +894,48 @@
         <b val="1"/>
         <color rgb="FFFF0000"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="2"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF666666"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="2"/>
+        <b val="1"/>
+        <i val="0"/>
+        <color rgb="FFFFFFFF"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCC0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="2"/>
+        <color rgb="FFFFBF00"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFBF00"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <colors>
@@ -762,8 +948,8 @@
       <rgbColor rgb="FFFFFF00"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FFCC0000"/>
+      <rgbColor rgb="FF127622"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
@@ -777,7 +963,7 @@
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFDDDDDD"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -808,7 +994,7 @@
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF55308D"/>
       <rgbColor rgb="FF333333"/>
     </indexedColors>
   </colors>
@@ -820,13 +1006,13 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>907560</xdr:colOff>
+      <xdr:colOff>907920</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>154440</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>11880</xdr:colOff>
+      <xdr:colOff>12240</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>154440</xdr:rowOff>
     </xdr:to>
@@ -837,8 +1023,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="5493960" y="479520"/>
-          <a:ext cx="5554080" cy="0"/>
+          <a:off x="5499000" y="479520"/>
+          <a:ext cx="5563080" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -879,7 +1065,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5493240" y="488160"/>
+          <a:off x="5498280" y="488160"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -920,7 +1106,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5492520" y="488160"/>
+          <a:off x="5497560" y="488160"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -962,7 +1148,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5507640" y="1125360"/>
+          <a:off x="5514120" y="1125360"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1004,7 +1190,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5507640" y="1612800"/>
+          <a:off x="5514120" y="1612800"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1046,7 +1232,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5507640" y="2099880"/>
+          <a:off x="5514120" y="2099880"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1088,7 +1274,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5507640" y="2587320"/>
+          <a:off x="5514120" y="2587320"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1130,7 +1316,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8272080" y="324720"/>
+          <a:off x="8282160" y="324720"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1172,7 +1358,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8272080" y="487440"/>
+          <a:off x="8282160" y="487440"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1214,7 +1400,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8272080" y="1125360"/>
+          <a:off x="8282160" y="1125360"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1256,7 +1442,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8272080" y="1612800"/>
+          <a:off x="8282160" y="1612800"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1298,7 +1484,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8272080" y="2587320"/>
+          <a:off x="8282160" y="2587320"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1340,7 +1526,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8272080" y="3074400"/>
+          <a:off x="8282160" y="3074400"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1382,7 +1568,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8272080" y="4048920"/>
+          <a:off x="8282160" y="4048920"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1424,7 +1610,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8272080" y="5023440"/>
+          <a:off x="8282160" y="5023440"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1466,7 +1652,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11036520" y="487440"/>
+          <a:off x="11050560" y="487440"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1508,7 +1694,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11036520" y="1125360"/>
+          <a:off x="11050560" y="1125360"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1550,7 +1736,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11036520" y="1612800"/>
+          <a:off x="11050560" y="1612800"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1592,7 +1778,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11036520" y="2099880"/>
+          <a:off x="11050560" y="2099880"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1634,7 +1820,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8261640" y="3557520"/>
+          <a:off x="8270640" y="3557520"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1676,7 +1862,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8261640" y="4533480"/>
+          <a:off x="8270640" y="4533480"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1718,7 +1904,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8261640" y="2093760"/>
+          <a:off x="8270640" y="2093760"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1743,17 +1929,13 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M41"/>
-  <sheetFormatPr defaultColWidth="13.07421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="13.09375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.77"/>
   </cols>
@@ -2295,7 +2477,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:BW35"/>
-  <sheetFormatPr defaultColWidth="11.82421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="11.83984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="1"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="2" min="2" style="20" width="11.71"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="3" min="3" style="0" width="13.52"/>
@@ -3689,6 +3871,1543 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>
   </headerFooter>
-  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:BM17"/>
+  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="1"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="5" min="5" style="0" width="16.2"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="6" min="6" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="1" max="8" min="8" style="0" width="3.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="9" style="0" width="3.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="59" width="3.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="62" min="20" style="0" width="3.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="63" min="63" style="0" width="7.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="64" style="0" width="8.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="65" min="65" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1022" style="0" width="11.52"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="40.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" s="60" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1" s="60"/>
+      <c r="I1" s="61" t="n">
+        <v>44515</v>
+      </c>
+      <c r="J1" s="61" t="n">
+        <v>44516</v>
+      </c>
+      <c r="K1" s="61" t="n">
+        <v>44517</v>
+      </c>
+      <c r="L1" s="61" t="n">
+        <v>44518</v>
+      </c>
+      <c r="M1" s="61" t="n">
+        <v>44519</v>
+      </c>
+      <c r="N1" s="61" t="n">
+        <v>44520</v>
+      </c>
+      <c r="O1" s="61" t="n">
+        <v>44521</v>
+      </c>
+      <c r="P1" s="61" t="n">
+        <v>44522</v>
+      </c>
+      <c r="Q1" s="61" t="n">
+        <v>44523</v>
+      </c>
+      <c r="R1" s="61" t="n">
+        <v>44524</v>
+      </c>
+      <c r="S1" s="62" t="n">
+        <v>44525</v>
+      </c>
+      <c r="T1" s="61" t="n">
+        <v>44526</v>
+      </c>
+      <c r="U1" s="61" t="n">
+        <v>44527</v>
+      </c>
+      <c r="V1" s="61" t="n">
+        <v>44528</v>
+      </c>
+      <c r="W1" s="61" t="n">
+        <v>44529</v>
+      </c>
+      <c r="X1" s="61" t="n">
+        <v>44530</v>
+      </c>
+      <c r="Y1" s="61" t="n">
+        <v>44531</v>
+      </c>
+      <c r="Z1" s="61" t="n">
+        <v>44532</v>
+      </c>
+      <c r="AA1" s="61" t="n">
+        <v>44533</v>
+      </c>
+      <c r="AB1" s="61" t="n">
+        <v>44534</v>
+      </c>
+      <c r="AC1" s="61" t="n">
+        <v>44535</v>
+      </c>
+      <c r="AD1" s="61" t="n">
+        <v>44536</v>
+      </c>
+      <c r="AE1" s="61" t="n">
+        <v>44537</v>
+      </c>
+      <c r="AF1" s="61" t="n">
+        <v>44538</v>
+      </c>
+      <c r="AG1" s="61" t="n">
+        <v>44539</v>
+      </c>
+      <c r="AH1" s="61" t="n">
+        <v>44540</v>
+      </c>
+      <c r="AI1" s="61" t="n">
+        <v>44541</v>
+      </c>
+      <c r="AJ1" s="61" t="n">
+        <v>44542</v>
+      </c>
+      <c r="AK1" s="61" t="n">
+        <v>44543</v>
+      </c>
+      <c r="AL1" s="61" t="n">
+        <v>44544</v>
+      </c>
+      <c r="AM1" s="61" t="n">
+        <v>44545</v>
+      </c>
+      <c r="AN1" s="61" t="n">
+        <v>44546</v>
+      </c>
+      <c r="AO1" s="61" t="n">
+        <v>44547</v>
+      </c>
+      <c r="AP1" s="61" t="n">
+        <v>44548</v>
+      </c>
+      <c r="AQ1" s="61" t="n">
+        <v>44549</v>
+      </c>
+      <c r="AR1" s="61" t="n">
+        <v>44550</v>
+      </c>
+      <c r="AS1" s="61" t="n">
+        <v>44551</v>
+      </c>
+      <c r="AT1" s="61" t="n">
+        <v>44552</v>
+      </c>
+      <c r="AU1" s="61" t="n">
+        <v>44553</v>
+      </c>
+      <c r="AV1" s="63" t="n">
+        <v>44554</v>
+      </c>
+      <c r="AW1" s="61" t="n">
+        <v>44555</v>
+      </c>
+      <c r="AX1" s="61" t="n">
+        <v>44556</v>
+      </c>
+      <c r="AY1" s="61" t="n">
+        <v>44557</v>
+      </c>
+      <c r="AZ1" s="61" t="n">
+        <v>44558</v>
+      </c>
+      <c r="BA1" s="61" t="n">
+        <v>44559</v>
+      </c>
+      <c r="BB1" s="61" t="n">
+        <v>44560</v>
+      </c>
+      <c r="BC1" s="63" t="n">
+        <v>44561</v>
+      </c>
+      <c r="BD1" s="61" t="n">
+        <v>44562</v>
+      </c>
+      <c r="BE1" s="61" t="n">
+        <v>44563</v>
+      </c>
+      <c r="BF1" s="61" t="n">
+        <v>44564</v>
+      </c>
+      <c r="BG1" s="61" t="n">
+        <v>44565</v>
+      </c>
+      <c r="BH1" s="61" t="n">
+        <v>44566</v>
+      </c>
+      <c r="BI1" s="63" t="n">
+        <v>44567</v>
+      </c>
+      <c r="BJ1" s="61" t="n">
+        <v>44568</v>
+      </c>
+      <c r="BK1" s="64"/>
+      <c r="BL1" s="65"/>
+      <c r="BM1" s="66"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="G2" s="67" t="n">
+        <f aca="false">Netzplan!J2</f>
+        <v>2</v>
+      </c>
+      <c r="H2" s="68" t="n">
+        <f aca="false">SUM(I2:BJ2)</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
+      <c r="N2" s="70"/>
+      <c r="O2" s="70"/>
+      <c r="P2" s="70"/>
+      <c r="Q2" s="70"/>
+      <c r="R2" s="70"/>
+      <c r="S2" s="71"/>
+      <c r="T2" s="70"/>
+      <c r="U2" s="70"/>
+      <c r="V2" s="70"/>
+      <c r="W2" s="70"/>
+      <c r="X2" s="70"/>
+      <c r="Y2" s="70"/>
+      <c r="Z2" s="70"/>
+      <c r="AA2" s="70"/>
+      <c r="AB2" s="70"/>
+      <c r="AC2" s="70"/>
+      <c r="AD2" s="70"/>
+      <c r="AE2" s="70"/>
+      <c r="AF2" s="70"/>
+      <c r="AG2" s="70"/>
+      <c r="AH2" s="70"/>
+      <c r="AI2" s="70"/>
+      <c r="AJ2" s="70"/>
+      <c r="AK2" s="70"/>
+      <c r="AL2" s="70"/>
+      <c r="AM2" s="70"/>
+      <c r="AN2" s="70"/>
+      <c r="AO2" s="70"/>
+      <c r="AP2" s="70"/>
+      <c r="AQ2" s="70"/>
+      <c r="AR2" s="70"/>
+      <c r="AS2" s="70"/>
+      <c r="AT2" s="70"/>
+      <c r="AU2" s="70"/>
+      <c r="AV2" s="72"/>
+      <c r="AW2" s="70"/>
+      <c r="AX2" s="70"/>
+      <c r="AY2" s="70"/>
+      <c r="AZ2" s="70"/>
+      <c r="BA2" s="70"/>
+      <c r="BB2" s="70"/>
+      <c r="BC2" s="72"/>
+      <c r="BD2" s="70"/>
+      <c r="BE2" s="70"/>
+      <c r="BF2" s="70"/>
+      <c r="BG2" s="70"/>
+      <c r="BH2" s="70"/>
+      <c r="BI2" s="72"/>
+      <c r="BJ2" s="73"/>
+      <c r="BK2" s="64"/>
+      <c r="BL2" s="65"/>
+      <c r="BM2" s="66"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="G3" s="67" t="n">
+        <f aca="false">Netzplan!J3</f>
+        <v>1</v>
+      </c>
+      <c r="H3" s="68" t="n">
+        <f aca="false">SUM(I3:BJ3)</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="74"/>
+      <c r="J3" s="74"/>
+      <c r="K3" s="74"/>
+      <c r="L3" s="74"/>
+      <c r="M3" s="74"/>
+      <c r="N3" s="74"/>
+      <c r="O3" s="74"/>
+      <c r="P3" s="75"/>
+      <c r="Q3" s="74"/>
+      <c r="R3" s="74"/>
+      <c r="S3" s="76"/>
+      <c r="T3" s="74"/>
+      <c r="U3" s="74"/>
+      <c r="V3" s="74"/>
+      <c r="W3" s="74"/>
+      <c r="X3" s="74"/>
+      <c r="Y3" s="74"/>
+      <c r="Z3" s="74"/>
+      <c r="AA3" s="74"/>
+      <c r="AB3" s="74"/>
+      <c r="AC3" s="74"/>
+      <c r="AD3" s="74"/>
+      <c r="AE3" s="74"/>
+      <c r="AF3" s="74"/>
+      <c r="AG3" s="74"/>
+      <c r="AH3" s="74"/>
+      <c r="AI3" s="74"/>
+      <c r="AJ3" s="74"/>
+      <c r="AK3" s="74"/>
+      <c r="AL3" s="74"/>
+      <c r="AM3" s="74"/>
+      <c r="AN3" s="74"/>
+      <c r="AO3" s="74"/>
+      <c r="AP3" s="74"/>
+      <c r="AQ3" s="74"/>
+      <c r="AR3" s="74"/>
+      <c r="AS3" s="74"/>
+      <c r="AT3" s="74"/>
+      <c r="AU3" s="74"/>
+      <c r="AV3" s="77"/>
+      <c r="AW3" s="74"/>
+      <c r="AX3" s="74"/>
+      <c r="AY3" s="74"/>
+      <c r="AZ3" s="74"/>
+      <c r="BA3" s="74"/>
+      <c r="BB3" s="74"/>
+      <c r="BC3" s="77"/>
+      <c r="BD3" s="74"/>
+      <c r="BE3" s="74"/>
+      <c r="BF3" s="74"/>
+      <c r="BG3" s="74"/>
+      <c r="BH3" s="74"/>
+      <c r="BI3" s="77"/>
+      <c r="BJ3" s="78"/>
+      <c r="BK3" s="64"/>
+      <c r="BL3" s="65"/>
+      <c r="BM3" s="66"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="67" t="n">
+        <f aca="false">Netzplan!J4</f>
+        <v>6</v>
+      </c>
+      <c r="H4" s="68" t="n">
+        <f aca="false">SUM(I4:BJ4)</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="74"/>
+      <c r="J4" s="74"/>
+      <c r="K4" s="74"/>
+      <c r="L4" s="74"/>
+      <c r="M4" s="74"/>
+      <c r="N4" s="74"/>
+      <c r="O4" s="74"/>
+      <c r="P4" s="74"/>
+      <c r="Q4" s="75"/>
+      <c r="R4" s="75"/>
+      <c r="S4" s="79"/>
+      <c r="T4" s="75"/>
+      <c r="U4" s="74"/>
+      <c r="V4" s="74"/>
+      <c r="W4" s="74"/>
+      <c r="X4" s="74"/>
+      <c r="Y4" s="74"/>
+      <c r="Z4" s="74"/>
+      <c r="AA4" s="74"/>
+      <c r="AB4" s="74"/>
+      <c r="AC4" s="74"/>
+      <c r="AD4" s="74"/>
+      <c r="AE4" s="74"/>
+      <c r="AF4" s="74"/>
+      <c r="AG4" s="74"/>
+      <c r="AH4" s="74"/>
+      <c r="AI4" s="74"/>
+      <c r="AJ4" s="74"/>
+      <c r="AK4" s="74"/>
+      <c r="AL4" s="74"/>
+      <c r="AM4" s="74"/>
+      <c r="AN4" s="74"/>
+      <c r="AO4" s="74"/>
+      <c r="AP4" s="74"/>
+      <c r="AQ4" s="74"/>
+      <c r="AR4" s="74"/>
+      <c r="AS4" s="74"/>
+      <c r="AT4" s="74"/>
+      <c r="AU4" s="74"/>
+      <c r="AV4" s="77"/>
+      <c r="AW4" s="74"/>
+      <c r="AX4" s="74"/>
+      <c r="AY4" s="74"/>
+      <c r="AZ4" s="74"/>
+      <c r="BA4" s="74"/>
+      <c r="BB4" s="74"/>
+      <c r="BC4" s="77"/>
+      <c r="BD4" s="74"/>
+      <c r="BE4" s="74"/>
+      <c r="BF4" s="74"/>
+      <c r="BG4" s="74"/>
+      <c r="BH4" s="74"/>
+      <c r="BI4" s="77"/>
+      <c r="BJ4" s="78"/>
+      <c r="BK4" s="64"/>
+      <c r="BL4" s="65"/>
+      <c r="BM4" s="66"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="67" t="n">
+        <f aca="false">Netzplan!J5</f>
+        <v>2</v>
+      </c>
+      <c r="H5" s="68" t="n">
+        <f aca="false">SUM(I5:BJ5)</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
+      <c r="K5" s="74"/>
+      <c r="L5" s="74"/>
+      <c r="M5" s="74"/>
+      <c r="N5" s="74"/>
+      <c r="O5" s="74"/>
+      <c r="P5" s="74"/>
+      <c r="Q5" s="75"/>
+      <c r="R5" s="75"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="74"/>
+      <c r="U5" s="74"/>
+      <c r="V5" s="74"/>
+      <c r="W5" s="74"/>
+      <c r="X5" s="74"/>
+      <c r="Y5" s="74"/>
+      <c r="Z5" s="74"/>
+      <c r="AA5" s="74"/>
+      <c r="AB5" s="74"/>
+      <c r="AC5" s="74"/>
+      <c r="AD5" s="74"/>
+      <c r="AE5" s="74"/>
+      <c r="AF5" s="74"/>
+      <c r="AG5" s="74"/>
+      <c r="AH5" s="74"/>
+      <c r="AI5" s="74"/>
+      <c r="AJ5" s="74"/>
+      <c r="AK5" s="74"/>
+      <c r="AL5" s="74"/>
+      <c r="AM5" s="74"/>
+      <c r="AN5" s="74"/>
+      <c r="AO5" s="74"/>
+      <c r="AP5" s="74"/>
+      <c r="AQ5" s="74"/>
+      <c r="AR5" s="74"/>
+      <c r="AS5" s="74"/>
+      <c r="AT5" s="74"/>
+      <c r="AU5" s="74"/>
+      <c r="AV5" s="77"/>
+      <c r="AW5" s="74"/>
+      <c r="AX5" s="74"/>
+      <c r="AY5" s="74"/>
+      <c r="AZ5" s="74"/>
+      <c r="BA5" s="74"/>
+      <c r="BB5" s="74"/>
+      <c r="BC5" s="77"/>
+      <c r="BD5" s="74"/>
+      <c r="BE5" s="74"/>
+      <c r="BF5" s="74"/>
+      <c r="BG5" s="74"/>
+      <c r="BH5" s="74"/>
+      <c r="BI5" s="77"/>
+      <c r="BJ5" s="78"/>
+      <c r="BK5" s="64"/>
+      <c r="BL5" s="65"/>
+      <c r="BM5" s="66"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="41" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="67" t="n">
+        <f aca="false">Netzplan!J6</f>
+        <v>4</v>
+      </c>
+      <c r="H6" s="68" t="n">
+        <f aca="false">SUM(I6:BJ6)</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="74"/>
+      <c r="J6" s="74"/>
+      <c r="K6" s="74"/>
+      <c r="L6" s="74"/>
+      <c r="M6" s="74"/>
+      <c r="N6" s="74"/>
+      <c r="O6" s="74"/>
+      <c r="P6" s="74"/>
+      <c r="Q6" s="74"/>
+      <c r="R6" s="74"/>
+      <c r="S6" s="76"/>
+      <c r="T6" s="75"/>
+      <c r="U6" s="74"/>
+      <c r="V6" s="74"/>
+      <c r="W6" s="75"/>
+      <c r="X6" s="75"/>
+      <c r="Y6" s="75"/>
+      <c r="Z6" s="75"/>
+      <c r="AA6" s="80"/>
+      <c r="AB6" s="74"/>
+      <c r="AC6" s="74"/>
+      <c r="AD6" s="74"/>
+      <c r="AE6" s="74"/>
+      <c r="AF6" s="74"/>
+      <c r="AG6" s="74"/>
+      <c r="AH6" s="74"/>
+      <c r="AI6" s="74"/>
+      <c r="AJ6" s="74"/>
+      <c r="AK6" s="74"/>
+      <c r="AL6" s="74"/>
+      <c r="AM6" s="74"/>
+      <c r="AN6" s="74"/>
+      <c r="AO6" s="74"/>
+      <c r="AP6" s="74"/>
+      <c r="AQ6" s="74"/>
+      <c r="AR6" s="74"/>
+      <c r="AS6" s="74"/>
+      <c r="AT6" s="74"/>
+      <c r="AU6" s="74"/>
+      <c r="AV6" s="77"/>
+      <c r="AW6" s="74"/>
+      <c r="AX6" s="74"/>
+      <c r="AY6" s="74"/>
+      <c r="AZ6" s="74"/>
+      <c r="BA6" s="74"/>
+      <c r="BB6" s="74"/>
+      <c r="BC6" s="77"/>
+      <c r="BD6" s="74"/>
+      <c r="BE6" s="74"/>
+      <c r="BF6" s="74"/>
+      <c r="BG6" s="74"/>
+      <c r="BH6" s="74"/>
+      <c r="BI6" s="77"/>
+      <c r="BJ6" s="78"/>
+      <c r="BK6" s="64"/>
+      <c r="BL6" s="65"/>
+      <c r="BM6" s="66"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="67" t="n">
+        <f aca="false">Netzplan!J7</f>
+        <v>1</v>
+      </c>
+      <c r="H7" s="68" t="n">
+        <f aca="false">SUM(I7:BJ7)</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="74"/>
+      <c r="J7" s="74"/>
+      <c r="K7" s="74"/>
+      <c r="L7" s="74"/>
+      <c r="M7" s="74"/>
+      <c r="N7" s="74"/>
+      <c r="O7" s="74"/>
+      <c r="P7" s="75"/>
+      <c r="Q7" s="74"/>
+      <c r="R7" s="74"/>
+      <c r="S7" s="76"/>
+      <c r="T7" s="74"/>
+      <c r="U7" s="74"/>
+      <c r="V7" s="74"/>
+      <c r="W7" s="74"/>
+      <c r="X7" s="74"/>
+      <c r="Y7" s="74"/>
+      <c r="Z7" s="74"/>
+      <c r="AA7" s="74"/>
+      <c r="AB7" s="74"/>
+      <c r="AC7" s="74"/>
+      <c r="AD7" s="74"/>
+      <c r="AE7" s="74"/>
+      <c r="AF7" s="74"/>
+      <c r="AG7" s="74"/>
+      <c r="AH7" s="74"/>
+      <c r="AI7" s="74"/>
+      <c r="AJ7" s="74"/>
+      <c r="AK7" s="74"/>
+      <c r="AL7" s="74"/>
+      <c r="AM7" s="74"/>
+      <c r="AN7" s="74"/>
+      <c r="AO7" s="74"/>
+      <c r="AP7" s="74"/>
+      <c r="AQ7" s="74"/>
+      <c r="AR7" s="74"/>
+      <c r="AS7" s="74"/>
+      <c r="AT7" s="74"/>
+      <c r="AU7" s="74"/>
+      <c r="AV7" s="77"/>
+      <c r="AW7" s="74"/>
+      <c r="AX7" s="74"/>
+      <c r="AY7" s="74"/>
+      <c r="AZ7" s="74"/>
+      <c r="BA7" s="74"/>
+      <c r="BB7" s="74"/>
+      <c r="BC7" s="77"/>
+      <c r="BD7" s="74"/>
+      <c r="BE7" s="74"/>
+      <c r="BF7" s="74"/>
+      <c r="BG7" s="74"/>
+      <c r="BH7" s="74"/>
+      <c r="BI7" s="77"/>
+      <c r="BJ7" s="78"/>
+      <c r="BK7" s="64"/>
+      <c r="BL7" s="65"/>
+      <c r="BM7" s="66"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8" s="67" t="n">
+        <f aca="false">Netzplan!J8</f>
+        <v>6</v>
+      </c>
+      <c r="H8" s="68" t="n">
+        <f aca="false">SUM(I8:BJ8)</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="74"/>
+      <c r="J8" s="74"/>
+      <c r="K8" s="74"/>
+      <c r="L8" s="74"/>
+      <c r="M8" s="74"/>
+      <c r="N8" s="74"/>
+      <c r="O8" s="74"/>
+      <c r="P8" s="74"/>
+      <c r="Q8" s="75"/>
+      <c r="R8" s="75"/>
+      <c r="S8" s="79"/>
+      <c r="T8" s="74"/>
+      <c r="U8" s="74"/>
+      <c r="V8" s="74"/>
+      <c r="W8" s="74"/>
+      <c r="X8" s="74"/>
+      <c r="Y8" s="74"/>
+      <c r="Z8" s="74"/>
+      <c r="AA8" s="74"/>
+      <c r="AB8" s="74"/>
+      <c r="AC8" s="74"/>
+      <c r="AD8" s="74"/>
+      <c r="AE8" s="74"/>
+      <c r="AF8" s="74"/>
+      <c r="AG8" s="74"/>
+      <c r="AH8" s="74"/>
+      <c r="AI8" s="74"/>
+      <c r="AJ8" s="74"/>
+      <c r="AK8" s="74"/>
+      <c r="AL8" s="74"/>
+      <c r="AM8" s="74"/>
+      <c r="AN8" s="74"/>
+      <c r="AO8" s="74"/>
+      <c r="AP8" s="74"/>
+      <c r="AQ8" s="74"/>
+      <c r="AR8" s="74"/>
+      <c r="AS8" s="74"/>
+      <c r="AT8" s="74"/>
+      <c r="AU8" s="74"/>
+      <c r="AV8" s="77"/>
+      <c r="AW8" s="74"/>
+      <c r="AX8" s="74"/>
+      <c r="AY8" s="74"/>
+      <c r="AZ8" s="74"/>
+      <c r="BA8" s="74"/>
+      <c r="BB8" s="74"/>
+      <c r="BC8" s="77"/>
+      <c r="BD8" s="74"/>
+      <c r="BE8" s="74"/>
+      <c r="BF8" s="74"/>
+      <c r="BG8" s="74"/>
+      <c r="BH8" s="74"/>
+      <c r="BI8" s="77"/>
+      <c r="BJ8" s="78"/>
+      <c r="BK8" s="64"/>
+      <c r="BL8" s="65"/>
+      <c r="BM8" s="66"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" s="41" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="67" t="n">
+        <f aca="false">Netzplan!J9</f>
+        <v>2</v>
+      </c>
+      <c r="H9" s="68" t="n">
+        <f aca="false">SUM(I9:BJ9)</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="74"/>
+      <c r="J9" s="74"/>
+      <c r="K9" s="74"/>
+      <c r="L9" s="74"/>
+      <c r="M9" s="74"/>
+      <c r="N9" s="74"/>
+      <c r="O9" s="74"/>
+      <c r="P9" s="74"/>
+      <c r="Q9" s="74"/>
+      <c r="R9" s="74"/>
+      <c r="S9" s="76"/>
+      <c r="T9" s="74"/>
+      <c r="U9" s="74"/>
+      <c r="V9" s="74"/>
+      <c r="W9" s="75"/>
+      <c r="X9" s="75"/>
+      <c r="Y9" s="75"/>
+      <c r="Z9" s="75"/>
+      <c r="AA9" s="78"/>
+      <c r="AB9" s="74"/>
+      <c r="AC9" s="74"/>
+      <c r="AD9" s="75"/>
+      <c r="AE9" s="74"/>
+      <c r="AF9" s="74"/>
+      <c r="AG9" s="74"/>
+      <c r="AH9" s="74"/>
+      <c r="AI9" s="74"/>
+      <c r="AJ9" s="74"/>
+      <c r="AK9" s="74"/>
+      <c r="AL9" s="74"/>
+      <c r="AM9" s="74"/>
+      <c r="AN9" s="74"/>
+      <c r="AO9" s="74"/>
+      <c r="AP9" s="74"/>
+      <c r="AQ9" s="74"/>
+      <c r="AR9" s="74"/>
+      <c r="AS9" s="74"/>
+      <c r="AT9" s="74"/>
+      <c r="AU9" s="74"/>
+      <c r="AV9" s="77"/>
+      <c r="AW9" s="74"/>
+      <c r="AX9" s="74"/>
+      <c r="AY9" s="74"/>
+      <c r="AZ9" s="74"/>
+      <c r="BA9" s="74"/>
+      <c r="BB9" s="74"/>
+      <c r="BC9" s="77"/>
+      <c r="BD9" s="74"/>
+      <c r="BE9" s="74"/>
+      <c r="BF9" s="74"/>
+      <c r="BG9" s="74"/>
+      <c r="BH9" s="74"/>
+      <c r="BI9" s="77"/>
+      <c r="BJ9" s="78"/>
+      <c r="BK9" s="64"/>
+      <c r="BL9" s="65"/>
+      <c r="BM9" s="66"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="41" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="67" t="n">
+        <f aca="false">Netzplan!J10</f>
+        <v>2</v>
+      </c>
+      <c r="H10" s="68" t="n">
+        <f aca="false">SUM(I10:BJ10)</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="74"/>
+      <c r="J10" s="74"/>
+      <c r="K10" s="74"/>
+      <c r="L10" s="74"/>
+      <c r="M10" s="74"/>
+      <c r="N10" s="74"/>
+      <c r="O10" s="74"/>
+      <c r="P10" s="74"/>
+      <c r="Q10" s="74"/>
+      <c r="R10" s="74"/>
+      <c r="S10" s="76"/>
+      <c r="T10" s="74"/>
+      <c r="U10" s="74"/>
+      <c r="V10" s="74"/>
+      <c r="W10" s="74"/>
+      <c r="X10" s="74"/>
+      <c r="Y10" s="74"/>
+      <c r="Z10" s="74"/>
+      <c r="AA10" s="74"/>
+      <c r="AB10" s="74"/>
+      <c r="AC10" s="74"/>
+      <c r="AE10" s="78"/>
+      <c r="AF10" s="74"/>
+      <c r="AG10" s="74"/>
+      <c r="AH10" s="74"/>
+      <c r="AI10" s="74"/>
+      <c r="AJ10" s="74"/>
+      <c r="AK10" s="74"/>
+      <c r="AL10" s="74"/>
+      <c r="AM10" s="74"/>
+      <c r="AN10" s="74"/>
+      <c r="AO10" s="74"/>
+      <c r="AP10" s="74"/>
+      <c r="AQ10" s="74"/>
+      <c r="AR10" s="74"/>
+      <c r="AS10" s="74"/>
+      <c r="AT10" s="74"/>
+      <c r="AU10" s="74"/>
+      <c r="AV10" s="77"/>
+      <c r="AW10" s="74"/>
+      <c r="AX10" s="74"/>
+      <c r="AY10" s="74"/>
+      <c r="AZ10" s="74"/>
+      <c r="BA10" s="74"/>
+      <c r="BB10" s="74"/>
+      <c r="BC10" s="77"/>
+      <c r="BD10" s="74"/>
+      <c r="BE10" s="74"/>
+      <c r="BF10" s="74"/>
+      <c r="BG10" s="74"/>
+      <c r="BH10" s="74"/>
+      <c r="BI10" s="77"/>
+      <c r="BJ10" s="78"/>
+      <c r="BK10" s="64"/>
+      <c r="BL10" s="65"/>
+      <c r="BM10" s="66"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="41" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="67" t="n">
+        <f aca="false">Netzplan!J11</f>
+        <v>2</v>
+      </c>
+      <c r="H11" s="68" t="n">
+        <f aca="false">SUM(I11:BJ11)</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="74"/>
+      <c r="J11" s="74"/>
+      <c r="K11" s="74"/>
+      <c r="L11" s="74"/>
+      <c r="M11" s="74"/>
+      <c r="N11" s="74"/>
+      <c r="O11" s="74"/>
+      <c r="P11" s="74"/>
+      <c r="Q11" s="74"/>
+      <c r="R11" s="74"/>
+      <c r="S11" s="76"/>
+      <c r="T11" s="74"/>
+      <c r="U11" s="74"/>
+      <c r="V11" s="74"/>
+      <c r="W11" s="74"/>
+      <c r="X11" s="74"/>
+      <c r="Y11" s="74"/>
+      <c r="Z11" s="74"/>
+      <c r="AA11" s="74"/>
+      <c r="AB11" s="74"/>
+      <c r="AC11" s="74"/>
+      <c r="AE11" s="78"/>
+      <c r="AF11" s="74"/>
+      <c r="AG11" s="75"/>
+      <c r="AH11" s="75"/>
+      <c r="AI11" s="74"/>
+      <c r="AJ11" s="74"/>
+      <c r="AK11" s="74"/>
+      <c r="AL11" s="74"/>
+      <c r="AM11" s="74"/>
+      <c r="AN11" s="74"/>
+      <c r="AO11" s="74"/>
+      <c r="AP11" s="74"/>
+      <c r="AQ11" s="74"/>
+      <c r="AR11" s="74"/>
+      <c r="AS11" s="74"/>
+      <c r="AT11" s="74"/>
+      <c r="AU11" s="74"/>
+      <c r="AV11" s="77"/>
+      <c r="AW11" s="74"/>
+      <c r="AX11" s="74"/>
+      <c r="AY11" s="74"/>
+      <c r="AZ11" s="74"/>
+      <c r="BA11" s="74"/>
+      <c r="BB11" s="74"/>
+      <c r="BC11" s="77"/>
+      <c r="BD11" s="74"/>
+      <c r="BE11" s="74"/>
+      <c r="BF11" s="74"/>
+      <c r="BG11" s="74"/>
+      <c r="BH11" s="74"/>
+      <c r="BI11" s="77"/>
+      <c r="BJ11" s="78"/>
+      <c r="BK11" s="64"/>
+      <c r="BL11" s="65"/>
+      <c r="BM11" s="66"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="41" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="67" t="n">
+        <f aca="false">Netzplan!J12</f>
+        <v>20</v>
+      </c>
+      <c r="H12" s="68" t="n">
+        <f aca="false">SUM(I12:BJ12)</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="74"/>
+      <c r="J12" s="74"/>
+      <c r="K12" s="74"/>
+      <c r="L12" s="74"/>
+      <c r="M12" s="74"/>
+      <c r="N12" s="74"/>
+      <c r="O12" s="74"/>
+      <c r="P12" s="74"/>
+      <c r="Q12" s="74"/>
+      <c r="R12" s="74"/>
+      <c r="S12" s="76"/>
+      <c r="T12" s="75"/>
+      <c r="U12" s="74"/>
+      <c r="V12" s="74"/>
+      <c r="W12" s="75"/>
+      <c r="X12" s="75"/>
+      <c r="Y12" s="75"/>
+      <c r="Z12" s="75"/>
+      <c r="AA12" s="80"/>
+      <c r="AB12" s="74"/>
+      <c r="AC12" s="74"/>
+      <c r="AD12" s="75"/>
+      <c r="AE12" s="75"/>
+      <c r="AF12" s="75"/>
+      <c r="AG12" s="75"/>
+      <c r="AH12" s="75"/>
+      <c r="AI12" s="74"/>
+      <c r="AJ12" s="74"/>
+      <c r="AK12" s="75"/>
+      <c r="AL12" s="75"/>
+      <c r="AM12" s="75"/>
+      <c r="AN12" s="75"/>
+      <c r="AO12" s="75"/>
+      <c r="AP12" s="74"/>
+      <c r="AQ12" s="74"/>
+      <c r="AR12" s="75"/>
+      <c r="AS12" s="75"/>
+      <c r="AT12" s="75"/>
+      <c r="AU12" s="75"/>
+      <c r="AV12" s="77"/>
+      <c r="AW12" s="74"/>
+      <c r="AX12" s="74"/>
+      <c r="AY12" s="75"/>
+      <c r="AZ12" s="75"/>
+      <c r="BA12" s="75"/>
+      <c r="BB12" s="75"/>
+      <c r="BC12" s="77"/>
+      <c r="BD12" s="74"/>
+      <c r="BE12" s="74"/>
+      <c r="BF12" s="74"/>
+      <c r="BG12" s="74"/>
+      <c r="BH12" s="74"/>
+      <c r="BI12" s="77"/>
+      <c r="BJ12" s="78"/>
+      <c r="BK12" s="64"/>
+      <c r="BL12" s="65"/>
+      <c r="BM12" s="66"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="41" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" s="67" t="n">
+        <f aca="false">Netzplan!J13</f>
+        <v>2</v>
+      </c>
+      <c r="H13" s="68" t="n">
+        <f aca="false">SUM(I13:BJ13)</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="74"/>
+      <c r="J13" s="74"/>
+      <c r="K13" s="74"/>
+      <c r="L13" s="74"/>
+      <c r="M13" s="74"/>
+      <c r="N13" s="74"/>
+      <c r="O13" s="74"/>
+      <c r="P13" s="74"/>
+      <c r="Q13" s="74"/>
+      <c r="R13" s="74"/>
+      <c r="S13" s="76"/>
+      <c r="T13" s="74"/>
+      <c r="U13" s="74"/>
+      <c r="V13" s="74"/>
+      <c r="W13" s="74"/>
+      <c r="X13" s="74"/>
+      <c r="Y13" s="74"/>
+      <c r="Z13" s="74"/>
+      <c r="AA13" s="74"/>
+      <c r="AB13" s="74"/>
+      <c r="AC13" s="74"/>
+      <c r="AD13" s="74"/>
+      <c r="AE13" s="74"/>
+      <c r="AF13" s="78"/>
+      <c r="AG13" s="74"/>
+      <c r="AH13" s="74"/>
+      <c r="AI13" s="74"/>
+      <c r="AJ13" s="74"/>
+      <c r="AK13" s="75"/>
+      <c r="AL13" s="75"/>
+      <c r="AM13" s="75"/>
+      <c r="AN13" s="75"/>
+      <c r="AO13" s="75"/>
+      <c r="AP13" s="74"/>
+      <c r="AQ13" s="74"/>
+      <c r="AR13" s="74"/>
+      <c r="AS13" s="74"/>
+      <c r="AT13" s="74"/>
+      <c r="AU13" s="74"/>
+      <c r="AV13" s="77"/>
+      <c r="AW13" s="74"/>
+      <c r="AX13" s="74"/>
+      <c r="AY13" s="74"/>
+      <c r="AZ13" s="74"/>
+      <c r="BA13" s="74"/>
+      <c r="BB13" s="74"/>
+      <c r="BC13" s="77"/>
+      <c r="BD13" s="74"/>
+      <c r="BE13" s="74"/>
+      <c r="BF13" s="74"/>
+      <c r="BG13" s="74"/>
+      <c r="BH13" s="74"/>
+      <c r="BI13" s="77"/>
+      <c r="BJ13" s="78"/>
+      <c r="BK13" s="64"/>
+      <c r="BL13" s="65"/>
+      <c r="BM13" s="66"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="G14" s="67" t="n">
+        <f aca="false">Netzplan!J14</f>
+        <v>2</v>
+      </c>
+      <c r="H14" s="68" t="n">
+        <f aca="false">SUM(I14:BJ14)</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="74"/>
+      <c r="J14" s="74"/>
+      <c r="K14" s="74"/>
+      <c r="L14" s="74"/>
+      <c r="M14" s="74"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="74"/>
+      <c r="P14" s="74"/>
+      <c r="Q14" s="74"/>
+      <c r="R14" s="74"/>
+      <c r="S14" s="76"/>
+      <c r="T14" s="74"/>
+      <c r="U14" s="74"/>
+      <c r="V14" s="74"/>
+      <c r="W14" s="74"/>
+      <c r="X14" s="74"/>
+      <c r="Y14" s="74"/>
+      <c r="Z14" s="74"/>
+      <c r="AA14" s="74"/>
+      <c r="AB14" s="74"/>
+      <c r="AC14" s="74"/>
+      <c r="AD14" s="74"/>
+      <c r="AE14" s="74"/>
+      <c r="AF14" s="74"/>
+      <c r="AG14" s="74"/>
+      <c r="AH14" s="78"/>
+      <c r="AI14" s="74"/>
+      <c r="AJ14" s="74"/>
+      <c r="AL14" s="74"/>
+      <c r="AM14" s="74"/>
+      <c r="AN14" s="74"/>
+      <c r="AO14" s="75"/>
+      <c r="AP14" s="74"/>
+      <c r="AQ14" s="74"/>
+      <c r="AR14" s="75"/>
+      <c r="AS14" s="75"/>
+      <c r="AT14" s="75"/>
+      <c r="AU14" s="74"/>
+      <c r="AV14" s="77"/>
+      <c r="AW14" s="74"/>
+      <c r="AX14" s="74"/>
+      <c r="AY14" s="74"/>
+      <c r="AZ14" s="74"/>
+      <c r="BA14" s="74"/>
+      <c r="BB14" s="74"/>
+      <c r="BC14" s="77"/>
+      <c r="BD14" s="74"/>
+      <c r="BE14" s="74"/>
+      <c r="BF14" s="74"/>
+      <c r="BG14" s="74"/>
+      <c r="BH14" s="74"/>
+      <c r="BI14" s="77"/>
+      <c r="BJ14" s="78"/>
+      <c r="BK14" s="64"/>
+      <c r="BL14" s="65"/>
+      <c r="BM14" s="66"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="41" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="G15" s="67" t="n">
+        <f aca="false">Netzplan!J15</f>
+        <v>1</v>
+      </c>
+      <c r="H15" s="68" t="n">
+        <f aca="false">SUM(I15:BJ15)</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="74"/>
+      <c r="J15" s="74"/>
+      <c r="K15" s="74"/>
+      <c r="L15" s="74"/>
+      <c r="M15" s="74"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="74"/>
+      <c r="P15" s="74"/>
+      <c r="Q15" s="74"/>
+      <c r="R15" s="74"/>
+      <c r="S15" s="76"/>
+      <c r="T15" s="74"/>
+      <c r="U15" s="74"/>
+      <c r="V15" s="74"/>
+      <c r="W15" s="74"/>
+      <c r="X15" s="74"/>
+      <c r="Y15" s="74"/>
+      <c r="Z15" s="74"/>
+      <c r="AA15" s="74"/>
+      <c r="AB15" s="74"/>
+      <c r="AC15" s="74"/>
+      <c r="AD15" s="74"/>
+      <c r="AE15" s="74"/>
+      <c r="AF15" s="74"/>
+      <c r="AG15" s="74"/>
+      <c r="AH15" s="74"/>
+      <c r="AI15" s="74"/>
+      <c r="AJ15" s="74"/>
+      <c r="AL15" s="74"/>
+      <c r="AM15" s="78"/>
+      <c r="AO15" s="74"/>
+      <c r="AP15" s="74"/>
+      <c r="AQ15" s="74"/>
+      <c r="AR15" s="78"/>
+      <c r="AS15" s="75"/>
+      <c r="AT15" s="74"/>
+      <c r="AU15" s="74"/>
+      <c r="AV15" s="77"/>
+      <c r="AW15" s="74"/>
+      <c r="AX15" s="74"/>
+      <c r="AY15" s="74"/>
+      <c r="AZ15" s="74"/>
+      <c r="BA15" s="74"/>
+      <c r="BB15" s="74"/>
+      <c r="BC15" s="77"/>
+      <c r="BD15" s="74"/>
+      <c r="BE15" s="74"/>
+      <c r="BF15" s="74"/>
+      <c r="BG15" s="74"/>
+      <c r="BH15" s="74"/>
+      <c r="BI15" s="77"/>
+      <c r="BJ15" s="78"/>
+      <c r="BK15" s="64"/>
+      <c r="BL15" s="65"/>
+      <c r="BM15" s="66"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G16" s="67" t="n">
+        <f aca="false">Netzplan!J16</f>
+        <v>4</v>
+      </c>
+      <c r="H16" s="68" t="n">
+        <f aca="false">SUM(I16:BJ16)</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="74"/>
+      <c r="J16" s="74"/>
+      <c r="K16" s="74"/>
+      <c r="L16" s="74"/>
+      <c r="M16" s="74"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="74"/>
+      <c r="P16" s="74"/>
+      <c r="Q16" s="74"/>
+      <c r="R16" s="74"/>
+      <c r="S16" s="76"/>
+      <c r="T16" s="74"/>
+      <c r="U16" s="74"/>
+      <c r="V16" s="74"/>
+      <c r="W16" s="74"/>
+      <c r="X16" s="74"/>
+      <c r="Y16" s="74"/>
+      <c r="Z16" s="74"/>
+      <c r="AA16" s="74"/>
+      <c r="AB16" s="74"/>
+      <c r="AC16" s="74"/>
+      <c r="AD16" s="74"/>
+      <c r="AE16" s="74"/>
+      <c r="AF16" s="74"/>
+      <c r="AG16" s="74"/>
+      <c r="AH16" s="74"/>
+      <c r="AI16" s="74"/>
+      <c r="AJ16" s="74"/>
+      <c r="AK16" s="74"/>
+      <c r="AL16" s="74"/>
+      <c r="AM16" s="78"/>
+      <c r="AN16" s="78"/>
+      <c r="AO16" s="78"/>
+      <c r="AP16" s="74"/>
+      <c r="AQ16" s="74"/>
+      <c r="AR16" s="74"/>
+      <c r="AS16" s="78"/>
+      <c r="AT16" s="74"/>
+      <c r="AU16" s="75"/>
+      <c r="AV16" s="77"/>
+      <c r="AW16" s="74"/>
+      <c r="AX16" s="74"/>
+      <c r="AY16" s="75"/>
+      <c r="AZ16" s="75"/>
+      <c r="BA16" s="75"/>
+      <c r="BB16" s="74"/>
+      <c r="BC16" s="77"/>
+      <c r="BD16" s="74"/>
+      <c r="BE16" s="74"/>
+      <c r="BF16" s="74"/>
+      <c r="BG16" s="74"/>
+      <c r="BH16" s="74"/>
+      <c r="BI16" s="77"/>
+      <c r="BJ16" s="78"/>
+      <c r="BK16" s="64"/>
+      <c r="BL16" s="65"/>
+      <c r="BM16" s="66"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="45" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" s="46"/>
+      <c r="G17" s="67" t="n">
+        <f aca="false">Netzplan!J17</f>
+        <v>1</v>
+      </c>
+      <c r="H17" s="68" t="n">
+        <f aca="false">SUM(I17:BJ17)</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="81"/>
+      <c r="J17" s="81"/>
+      <c r="K17" s="81"/>
+      <c r="L17" s="81"/>
+      <c r="M17" s="81"/>
+      <c r="N17" s="81"/>
+      <c r="O17" s="81"/>
+      <c r="P17" s="81"/>
+      <c r="Q17" s="81"/>
+      <c r="R17" s="81"/>
+      <c r="S17" s="82"/>
+      <c r="T17" s="81"/>
+      <c r="U17" s="81"/>
+      <c r="V17" s="81"/>
+      <c r="W17" s="81"/>
+      <c r="X17" s="81"/>
+      <c r="Y17" s="81"/>
+      <c r="Z17" s="81"/>
+      <c r="AA17" s="81"/>
+      <c r="AB17" s="81"/>
+      <c r="AC17" s="81"/>
+      <c r="AD17" s="81"/>
+      <c r="AE17" s="81"/>
+      <c r="AF17" s="81"/>
+      <c r="AG17" s="81"/>
+      <c r="AH17" s="81"/>
+      <c r="AI17" s="81"/>
+      <c r="AJ17" s="81"/>
+      <c r="AK17" s="81"/>
+      <c r="AL17" s="81"/>
+      <c r="AM17" s="81"/>
+      <c r="AN17" s="81"/>
+      <c r="AO17" s="81"/>
+      <c r="AP17" s="81"/>
+      <c r="AQ17" s="81"/>
+      <c r="AR17" s="81"/>
+      <c r="AS17" s="81"/>
+      <c r="AT17" s="81"/>
+      <c r="AU17" s="81"/>
+      <c r="AV17" s="83"/>
+      <c r="AW17" s="81"/>
+      <c r="AX17" s="81"/>
+      <c r="AY17" s="84"/>
+      <c r="AZ17" s="84"/>
+      <c r="BA17" s="81"/>
+      <c r="BB17" s="81"/>
+      <c r="BC17" s="83"/>
+      <c r="BD17" s="81"/>
+      <c r="BE17" s="81"/>
+      <c r="BF17" s="81"/>
+      <c r="BG17" s="81"/>
+      <c r="BH17" s="81"/>
+      <c r="BI17" s="83"/>
+      <c r="BJ17" s="85"/>
+      <c r="BK17" s="64"/>
+      <c r="BL17" s="65"/>
+      <c r="BM17" s="66"/>
+    </row>
+  </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+  </mergeCells>
+  <conditionalFormatting sqref="I1:BF9 I12:BF13 I10:AC11 AE10:BF11 I16:BF17 I14:AJ15 AL14:BF14 AL15:AM15 AO15:BF15">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>IF(OR(WEEKDAY(I$1)=7,WEEKDAY(I$1)=1),1,0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H2:H17">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>IF(H2&lt;&gt;G2,TRUE())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:BF9 I12:BF13 I10:AC11 AE10:BF11 I16:BF17 I14:AJ15 AL14:BF14 AL15:AM15 AO15:BF15">
+    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
--- a/Übungen/Online_Shop.xlsx
+++ b/Übungen/Online_Shop.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="PSP" sheetId="1" state="visible" r:id="rId2"/>
@@ -528,7 +528,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="80">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -765,10 +765,6 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -777,10 +773,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="70" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="70" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="70" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -813,10 +805,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -833,10 +821,6 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -847,14 +831,6 @@
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
@@ -1023,8 +999,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="5499000" y="479520"/>
-          <a:ext cx="5563080" cy="0"/>
+          <a:off x="5504400" y="479520"/>
+          <a:ext cx="5572080" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -1065,7 +1041,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5498280" y="488160"/>
+          <a:off x="5503320" y="488160"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1106,7 +1082,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5497560" y="488160"/>
+          <a:off x="5502600" y="488160"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1148,7 +1124,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5514120" y="1125360"/>
+          <a:off x="5520600" y="1125360"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1190,7 +1166,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5514120" y="1612800"/>
+          <a:off x="5520600" y="1612800"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1232,7 +1208,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5514120" y="2099880"/>
+          <a:off x="5520600" y="2099880"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1274,7 +1250,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5514120" y="2587320"/>
+          <a:off x="5520600" y="2587320"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1316,7 +1292,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8282160" y="324720"/>
+          <a:off x="8292240" y="324720"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1358,7 +1334,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8282160" y="487440"/>
+          <a:off x="8292240" y="487440"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1400,7 +1376,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8282160" y="1125360"/>
+          <a:off x="8292240" y="1125360"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1442,7 +1418,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8282160" y="1612800"/>
+          <a:off x="8292240" y="1612800"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1484,7 +1460,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8282160" y="2587320"/>
+          <a:off x="8292240" y="2587320"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1526,7 +1502,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8282160" y="3074400"/>
+          <a:off x="8292240" y="3074400"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1568,7 +1544,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8282160" y="4048920"/>
+          <a:off x="8292240" y="4048920"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1610,7 +1586,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8282160" y="5023440"/>
+          <a:off x="8292240" y="5023440"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1652,7 +1628,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11050560" y="487440"/>
+          <a:off x="11064600" y="487440"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1694,7 +1670,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11050560" y="1125360"/>
+          <a:off x="11064600" y="1125360"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1736,7 +1712,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11050560" y="1612800"/>
+          <a:off x="11064600" y="1612800"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1778,7 +1754,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11050560" y="2099880"/>
+          <a:off x="11064600" y="2099880"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1820,7 +1796,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8270640" y="3557520"/>
+          <a:off x="8279640" y="3557520"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1862,7 +1838,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8270640" y="4533480"/>
+          <a:off x="8279640" y="4533480"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1904,7 +1880,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8270640" y="2093760"/>
+          <a:off x="8279640" y="2093760"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1929,13 +1905,17 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M41"/>
-  <sheetFormatPr defaultColWidth="13.09375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="13.109375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.77"/>
   </cols>
@@ -2477,13 +2457,13 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:BW35"/>
-  <sheetFormatPr defaultColWidth="11.83984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="11.859375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="1"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="2" min="2" style="20" width="11.71"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="3" min="3" style="0" width="13.52"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="1" max="4" min="4" style="0" width="11.81"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="5" min="5" style="3" width="16.12"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="6" min="6" style="3" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="1" max="2" min="2" style="20" width="11.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="1" max="3" min="3" style="0" width="13.52"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="1" max="4" min="4" style="0" width="11.81"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="1" max="5" min="5" style="3" width="16.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="1" max="6" min="6" style="3" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="3" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="21" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="3" width="11.52"/>
@@ -3722,6 +3702,34 @@
       <c r="C22" s="54"/>
       <c r="D22" s="55" t="s">
         <v>63</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I22" s="21" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <f aca="false">G22/(H22*I22)</f>
+        <v>6.66666666666667</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G23" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I23" s="21" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <f aca="false">G23/(H23*I23)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3871,6 +3879,7 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3880,15 +3889,13 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:BM17"/>
-  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="1"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="5" min="5" style="0" width="16.2"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="6" min="6" style="0" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11.59"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="1" max="8" min="8" style="0" width="3.59"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="9" style="0" width="3.59"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="59" width="3.59"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="62" min="20" style="0" width="3.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="62" min="9" style="0" width="3.59"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="63" min="63" style="0" width="7.65"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="64" style="0" width="8.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="65" min="65" style="0" width="11.52"/>
@@ -3910,175 +3917,175 @@
       <c r="F1" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="G1" s="60" t="s">
+      <c r="G1" s="59" t="s">
         <v>51</v>
       </c>
-      <c r="H1" s="60"/>
-      <c r="I1" s="61" t="n">
+      <c r="H1" s="59"/>
+      <c r="I1" s="60" t="n">
         <v>44515</v>
       </c>
-      <c r="J1" s="61" t="n">
+      <c r="J1" s="60" t="n">
         <v>44516</v>
       </c>
-      <c r="K1" s="61" t="n">
+      <c r="K1" s="60" t="n">
         <v>44517</v>
       </c>
-      <c r="L1" s="61" t="n">
+      <c r="L1" s="60" t="n">
         <v>44518</v>
       </c>
-      <c r="M1" s="61" t="n">
+      <c r="M1" s="60" t="n">
         <v>44519</v>
       </c>
-      <c r="N1" s="61" t="n">
+      <c r="N1" s="60" t="n">
         <v>44520</v>
       </c>
-      <c r="O1" s="61" t="n">
+      <c r="O1" s="60" t="n">
         <v>44521</v>
       </c>
-      <c r="P1" s="61" t="n">
+      <c r="P1" s="60" t="n">
         <v>44522</v>
       </c>
-      <c r="Q1" s="61" t="n">
+      <c r="Q1" s="60" t="n">
         <v>44523</v>
       </c>
-      <c r="R1" s="61" t="n">
+      <c r="R1" s="60" t="n">
         <v>44524</v>
       </c>
-      <c r="S1" s="62" t="n">
+      <c r="S1" s="60" t="n">
         <v>44525</v>
       </c>
-      <c r="T1" s="61" t="n">
+      <c r="T1" s="60" t="n">
         <v>44526</v>
       </c>
-      <c r="U1" s="61" t="n">
+      <c r="U1" s="60" t="n">
         <v>44527</v>
       </c>
-      <c r="V1" s="61" t="n">
+      <c r="V1" s="60" t="n">
         <v>44528</v>
       </c>
-      <c r="W1" s="61" t="n">
+      <c r="W1" s="60" t="n">
         <v>44529</v>
       </c>
-      <c r="X1" s="61" t="n">
+      <c r="X1" s="60" t="n">
         <v>44530</v>
       </c>
-      <c r="Y1" s="61" t="n">
+      <c r="Y1" s="60" t="n">
         <v>44531</v>
       </c>
-      <c r="Z1" s="61" t="n">
+      <c r="Z1" s="60" t="n">
         <v>44532</v>
       </c>
-      <c r="AA1" s="61" t="n">
+      <c r="AA1" s="60" t="n">
         <v>44533</v>
       </c>
-      <c r="AB1" s="61" t="n">
+      <c r="AB1" s="60" t="n">
         <v>44534</v>
       </c>
-      <c r="AC1" s="61" t="n">
+      <c r="AC1" s="60" t="n">
         <v>44535</v>
       </c>
-      <c r="AD1" s="61" t="n">
+      <c r="AD1" s="60" t="n">
         <v>44536</v>
       </c>
-      <c r="AE1" s="61" t="n">
+      <c r="AE1" s="60" t="n">
         <v>44537</v>
       </c>
-      <c r="AF1" s="61" t="n">
+      <c r="AF1" s="60" t="n">
         <v>44538</v>
       </c>
-      <c r="AG1" s="61" t="n">
+      <c r="AG1" s="60" t="n">
         <v>44539</v>
       </c>
-      <c r="AH1" s="61" t="n">
+      <c r="AH1" s="60" t="n">
         <v>44540</v>
       </c>
-      <c r="AI1" s="61" t="n">
+      <c r="AI1" s="60" t="n">
         <v>44541</v>
       </c>
-      <c r="AJ1" s="61" t="n">
+      <c r="AJ1" s="60" t="n">
         <v>44542</v>
       </c>
-      <c r="AK1" s="61" t="n">
+      <c r="AK1" s="60" t="n">
         <v>44543</v>
       </c>
-      <c r="AL1" s="61" t="n">
+      <c r="AL1" s="60" t="n">
         <v>44544</v>
       </c>
-      <c r="AM1" s="61" t="n">
+      <c r="AM1" s="60" t="n">
         <v>44545</v>
       </c>
-      <c r="AN1" s="61" t="n">
+      <c r="AN1" s="60" t="n">
         <v>44546</v>
       </c>
-      <c r="AO1" s="61" t="n">
+      <c r="AO1" s="60" t="n">
         <v>44547</v>
       </c>
-      <c r="AP1" s="61" t="n">
+      <c r="AP1" s="60" t="n">
         <v>44548</v>
       </c>
-      <c r="AQ1" s="61" t="n">
+      <c r="AQ1" s="60" t="n">
         <v>44549</v>
       </c>
-      <c r="AR1" s="61" t="n">
+      <c r="AR1" s="60" t="n">
         <v>44550</v>
       </c>
-      <c r="AS1" s="61" t="n">
+      <c r="AS1" s="60" t="n">
         <v>44551</v>
       </c>
-      <c r="AT1" s="61" t="n">
+      <c r="AT1" s="60" t="n">
         <v>44552</v>
       </c>
-      <c r="AU1" s="61" t="n">
+      <c r="AU1" s="60" t="n">
         <v>44553</v>
       </c>
-      <c r="AV1" s="63" t="n">
+      <c r="AV1" s="61" t="n">
         <v>44554</v>
       </c>
-      <c r="AW1" s="61" t="n">
+      <c r="AW1" s="60" t="n">
         <v>44555</v>
       </c>
-      <c r="AX1" s="61" t="n">
+      <c r="AX1" s="60" t="n">
         <v>44556</v>
       </c>
-      <c r="AY1" s="61" t="n">
+      <c r="AY1" s="60" t="n">
         <v>44557</v>
       </c>
-      <c r="AZ1" s="61" t="n">
+      <c r="AZ1" s="60" t="n">
         <v>44558</v>
       </c>
-      <c r="BA1" s="61" t="n">
+      <c r="BA1" s="60" t="n">
         <v>44559</v>
       </c>
-      <c r="BB1" s="61" t="n">
+      <c r="BB1" s="60" t="n">
         <v>44560</v>
       </c>
-      <c r="BC1" s="63" t="n">
+      <c r="BC1" s="61" t="n">
         <v>44561</v>
       </c>
-      <c r="BD1" s="61" t="n">
+      <c r="BD1" s="60" t="n">
         <v>44562</v>
       </c>
-      <c r="BE1" s="61" t="n">
+      <c r="BE1" s="60" t="n">
         <v>44563</v>
       </c>
-      <c r="BF1" s="61" t="n">
+      <c r="BF1" s="60" t="n">
         <v>44564</v>
       </c>
-      <c r="BG1" s="61" t="n">
+      <c r="BG1" s="60" t="n">
         <v>44565</v>
       </c>
-      <c r="BH1" s="61" t="n">
+      <c r="BH1" s="60" t="n">
         <v>44566</v>
       </c>
-      <c r="BI1" s="63" t="n">
+      <c r="BI1" s="61" t="n">
         <v>44567</v>
       </c>
-      <c r="BJ1" s="61" t="n">
+      <c r="BJ1" s="60" t="n">
         <v>44568</v>
       </c>
-      <c r="BK1" s="64"/>
-      <c r="BL1" s="65"/>
-      <c r="BM1" s="66"/>
+      <c r="BK1" s="62"/>
+      <c r="BL1" s="63"/>
+      <c r="BM1" s="64"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
@@ -4093,71 +4100,71 @@
       <c r="F2" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="G2" s="67" t="n">
+      <c r="G2" s="65" t="n">
         <f aca="false">Netzplan!J2</f>
         <v>2</v>
       </c>
-      <c r="H2" s="68" t="n">
+      <c r="H2" s="66" t="n">
         <f aca="false">SUM(I2:BJ2)</f>
         <v>0</v>
       </c>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
-      <c r="N2" s="70"/>
-      <c r="O2" s="70"/>
-      <c r="P2" s="70"/>
-      <c r="Q2" s="70"/>
-      <c r="R2" s="70"/>
-      <c r="S2" s="71"/>
-      <c r="T2" s="70"/>
-      <c r="U2" s="70"/>
-      <c r="V2" s="70"/>
-      <c r="W2" s="70"/>
-      <c r="X2" s="70"/>
-      <c r="Y2" s="70"/>
-      <c r="Z2" s="70"/>
-      <c r="AA2" s="70"/>
-      <c r="AB2" s="70"/>
-      <c r="AC2" s="70"/>
-      <c r="AD2" s="70"/>
-      <c r="AE2" s="70"/>
-      <c r="AF2" s="70"/>
-      <c r="AG2" s="70"/>
-      <c r="AH2" s="70"/>
-      <c r="AI2" s="70"/>
-      <c r="AJ2" s="70"/>
-      <c r="AK2" s="70"/>
-      <c r="AL2" s="70"/>
-      <c r="AM2" s="70"/>
-      <c r="AN2" s="70"/>
-      <c r="AO2" s="70"/>
-      <c r="AP2" s="70"/>
-      <c r="AQ2" s="70"/>
-      <c r="AR2" s="70"/>
-      <c r="AS2" s="70"/>
-      <c r="AT2" s="70"/>
-      <c r="AU2" s="70"/>
-      <c r="AV2" s="72"/>
-      <c r="AW2" s="70"/>
-      <c r="AX2" s="70"/>
-      <c r="AY2" s="70"/>
-      <c r="AZ2" s="70"/>
-      <c r="BA2" s="70"/>
-      <c r="BB2" s="70"/>
-      <c r="BC2" s="72"/>
-      <c r="BD2" s="70"/>
-      <c r="BE2" s="70"/>
-      <c r="BF2" s="70"/>
-      <c r="BG2" s="70"/>
-      <c r="BH2" s="70"/>
-      <c r="BI2" s="72"/>
-      <c r="BJ2" s="73"/>
-      <c r="BK2" s="64"/>
-      <c r="BL2" s="65"/>
-      <c r="BM2" s="66"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
+      <c r="N2" s="68"/>
+      <c r="O2" s="68"/>
+      <c r="P2" s="68"/>
+      <c r="Q2" s="68"/>
+      <c r="R2" s="68"/>
+      <c r="S2" s="68"/>
+      <c r="T2" s="68"/>
+      <c r="U2" s="68"/>
+      <c r="V2" s="68"/>
+      <c r="W2" s="68"/>
+      <c r="X2" s="68"/>
+      <c r="Y2" s="68"/>
+      <c r="Z2" s="68"/>
+      <c r="AA2" s="68"/>
+      <c r="AB2" s="68"/>
+      <c r="AC2" s="68"/>
+      <c r="AD2" s="68"/>
+      <c r="AE2" s="68"/>
+      <c r="AF2" s="68"/>
+      <c r="AG2" s="68"/>
+      <c r="AH2" s="68"/>
+      <c r="AI2" s="68"/>
+      <c r="AJ2" s="68"/>
+      <c r="AK2" s="68"/>
+      <c r="AL2" s="68"/>
+      <c r="AM2" s="68"/>
+      <c r="AN2" s="68"/>
+      <c r="AO2" s="68"/>
+      <c r="AP2" s="68"/>
+      <c r="AQ2" s="68"/>
+      <c r="AR2" s="68"/>
+      <c r="AS2" s="68"/>
+      <c r="AT2" s="68"/>
+      <c r="AU2" s="68"/>
+      <c r="AV2" s="69"/>
+      <c r="AW2" s="68"/>
+      <c r="AX2" s="68"/>
+      <c r="AY2" s="68"/>
+      <c r="AZ2" s="68"/>
+      <c r="BA2" s="68"/>
+      <c r="BB2" s="68"/>
+      <c r="BC2" s="69"/>
+      <c r="BD2" s="68"/>
+      <c r="BE2" s="68"/>
+      <c r="BF2" s="68"/>
+      <c r="BG2" s="68"/>
+      <c r="BH2" s="68"/>
+      <c r="BI2" s="69"/>
+      <c r="BJ2" s="70"/>
+      <c r="BK2" s="62"/>
+      <c r="BL2" s="63"/>
+      <c r="BM2" s="64"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
@@ -4174,71 +4181,71 @@
       <c r="F3" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="G3" s="67" t="n">
+      <c r="G3" s="65" t="n">
         <f aca="false">Netzplan!J3</f>
         <v>1</v>
       </c>
-      <c r="H3" s="68" t="n">
+      <c r="H3" s="66" t="n">
         <f aca="false">SUM(I3:BJ3)</f>
         <v>0</v>
       </c>
-      <c r="I3" s="74"/>
-      <c r="J3" s="74"/>
-      <c r="K3" s="74"/>
-      <c r="L3" s="74"/>
-      <c r="M3" s="74"/>
-      <c r="N3" s="74"/>
-      <c r="O3" s="74"/>
-      <c r="P3" s="75"/>
-      <c r="Q3" s="74"/>
-      <c r="R3" s="74"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="74"/>
-      <c r="U3" s="74"/>
-      <c r="V3" s="74"/>
-      <c r="W3" s="74"/>
-      <c r="X3" s="74"/>
-      <c r="Y3" s="74"/>
-      <c r="Z3" s="74"/>
-      <c r="AA3" s="74"/>
-      <c r="AB3" s="74"/>
-      <c r="AC3" s="74"/>
-      <c r="AD3" s="74"/>
-      <c r="AE3" s="74"/>
-      <c r="AF3" s="74"/>
-      <c r="AG3" s="74"/>
-      <c r="AH3" s="74"/>
-      <c r="AI3" s="74"/>
-      <c r="AJ3" s="74"/>
-      <c r="AK3" s="74"/>
-      <c r="AL3" s="74"/>
-      <c r="AM3" s="74"/>
-      <c r="AN3" s="74"/>
-      <c r="AO3" s="74"/>
-      <c r="AP3" s="74"/>
-      <c r="AQ3" s="74"/>
-      <c r="AR3" s="74"/>
-      <c r="AS3" s="74"/>
-      <c r="AT3" s="74"/>
-      <c r="AU3" s="74"/>
-      <c r="AV3" s="77"/>
-      <c r="AW3" s="74"/>
-      <c r="AX3" s="74"/>
-      <c r="AY3" s="74"/>
-      <c r="AZ3" s="74"/>
-      <c r="BA3" s="74"/>
-      <c r="BB3" s="74"/>
-      <c r="BC3" s="77"/>
-      <c r="BD3" s="74"/>
-      <c r="BE3" s="74"/>
-      <c r="BF3" s="74"/>
-      <c r="BG3" s="74"/>
-      <c r="BH3" s="74"/>
-      <c r="BI3" s="77"/>
-      <c r="BJ3" s="78"/>
-      <c r="BK3" s="64"/>
-      <c r="BL3" s="65"/>
-      <c r="BM3" s="66"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71"/>
+      <c r="K3" s="71"/>
+      <c r="L3" s="71"/>
+      <c r="M3" s="71"/>
+      <c r="N3" s="71"/>
+      <c r="O3" s="71"/>
+      <c r="P3" s="72"/>
+      <c r="Q3" s="71"/>
+      <c r="R3" s="71"/>
+      <c r="S3" s="71"/>
+      <c r="T3" s="71"/>
+      <c r="U3" s="71"/>
+      <c r="V3" s="71"/>
+      <c r="W3" s="71"/>
+      <c r="X3" s="71"/>
+      <c r="Y3" s="71"/>
+      <c r="Z3" s="71"/>
+      <c r="AA3" s="71"/>
+      <c r="AB3" s="71"/>
+      <c r="AC3" s="71"/>
+      <c r="AD3" s="71"/>
+      <c r="AE3" s="71"/>
+      <c r="AF3" s="71"/>
+      <c r="AG3" s="71"/>
+      <c r="AH3" s="71"/>
+      <c r="AI3" s="71"/>
+      <c r="AJ3" s="71"/>
+      <c r="AK3" s="71"/>
+      <c r="AL3" s="71"/>
+      <c r="AM3" s="71"/>
+      <c r="AN3" s="71"/>
+      <c r="AO3" s="71"/>
+      <c r="AP3" s="71"/>
+      <c r="AQ3" s="71"/>
+      <c r="AR3" s="71"/>
+      <c r="AS3" s="71"/>
+      <c r="AT3" s="71"/>
+      <c r="AU3" s="71"/>
+      <c r="AV3" s="73"/>
+      <c r="AW3" s="71"/>
+      <c r="AX3" s="71"/>
+      <c r="AY3" s="71"/>
+      <c r="AZ3" s="71"/>
+      <c r="BA3" s="71"/>
+      <c r="BB3" s="71"/>
+      <c r="BC3" s="73"/>
+      <c r="BD3" s="71"/>
+      <c r="BE3" s="71"/>
+      <c r="BF3" s="71"/>
+      <c r="BG3" s="71"/>
+      <c r="BH3" s="71"/>
+      <c r="BI3" s="73"/>
+      <c r="BJ3" s="74"/>
+      <c r="BK3" s="62"/>
+      <c r="BL3" s="63"/>
+      <c r="BM3" s="64"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
@@ -4255,71 +4262,71 @@
       <c r="F4" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="67" t="n">
+      <c r="G4" s="65" t="n">
         <f aca="false">Netzplan!J4</f>
         <v>6</v>
       </c>
-      <c r="H4" s="68" t="n">
+      <c r="H4" s="66" t="n">
         <f aca="false">SUM(I4:BJ4)</f>
         <v>0</v>
       </c>
-      <c r="I4" s="74"/>
-      <c r="J4" s="74"/>
-      <c r="K4" s="74"/>
-      <c r="L4" s="74"/>
-      <c r="M4" s="74"/>
-      <c r="N4" s="74"/>
-      <c r="O4" s="74"/>
-      <c r="P4" s="74"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="75"/>
-      <c r="S4" s="79"/>
-      <c r="T4" s="75"/>
-      <c r="U4" s="74"/>
-      <c r="V4" s="74"/>
-      <c r="W4" s="74"/>
-      <c r="X4" s="74"/>
-      <c r="Y4" s="74"/>
-      <c r="Z4" s="74"/>
-      <c r="AA4" s="74"/>
-      <c r="AB4" s="74"/>
-      <c r="AC4" s="74"/>
-      <c r="AD4" s="74"/>
-      <c r="AE4" s="74"/>
-      <c r="AF4" s="74"/>
-      <c r="AG4" s="74"/>
-      <c r="AH4" s="74"/>
-      <c r="AI4" s="74"/>
-      <c r="AJ4" s="74"/>
-      <c r="AK4" s="74"/>
-      <c r="AL4" s="74"/>
-      <c r="AM4" s="74"/>
-      <c r="AN4" s="74"/>
-      <c r="AO4" s="74"/>
-      <c r="AP4" s="74"/>
-      <c r="AQ4" s="74"/>
-      <c r="AR4" s="74"/>
-      <c r="AS4" s="74"/>
-      <c r="AT4" s="74"/>
-      <c r="AU4" s="74"/>
-      <c r="AV4" s="77"/>
-      <c r="AW4" s="74"/>
-      <c r="AX4" s="74"/>
-      <c r="AY4" s="74"/>
-      <c r="AZ4" s="74"/>
-      <c r="BA4" s="74"/>
-      <c r="BB4" s="74"/>
-      <c r="BC4" s="77"/>
-      <c r="BD4" s="74"/>
-      <c r="BE4" s="74"/>
-      <c r="BF4" s="74"/>
-      <c r="BG4" s="74"/>
-      <c r="BH4" s="74"/>
-      <c r="BI4" s="77"/>
-      <c r="BJ4" s="78"/>
-      <c r="BK4" s="64"/>
-      <c r="BL4" s="65"/>
-      <c r="BM4" s="66"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="71"/>
+      <c r="K4" s="71"/>
+      <c r="L4" s="71"/>
+      <c r="M4" s="71"/>
+      <c r="N4" s="71"/>
+      <c r="O4" s="71"/>
+      <c r="P4" s="71"/>
+      <c r="Q4" s="72"/>
+      <c r="R4" s="72"/>
+      <c r="S4" s="75"/>
+      <c r="T4" s="72"/>
+      <c r="U4" s="71"/>
+      <c r="V4" s="71"/>
+      <c r="W4" s="71"/>
+      <c r="X4" s="71"/>
+      <c r="Y4" s="71"/>
+      <c r="Z4" s="71"/>
+      <c r="AA4" s="71"/>
+      <c r="AB4" s="71"/>
+      <c r="AC4" s="71"/>
+      <c r="AD4" s="71"/>
+      <c r="AE4" s="71"/>
+      <c r="AF4" s="71"/>
+      <c r="AG4" s="71"/>
+      <c r="AH4" s="71"/>
+      <c r="AI4" s="71"/>
+      <c r="AJ4" s="71"/>
+      <c r="AK4" s="71"/>
+      <c r="AL4" s="71"/>
+      <c r="AM4" s="71"/>
+      <c r="AN4" s="71"/>
+      <c r="AO4" s="71"/>
+      <c r="AP4" s="71"/>
+      <c r="AQ4" s="71"/>
+      <c r="AR4" s="71"/>
+      <c r="AS4" s="71"/>
+      <c r="AT4" s="71"/>
+      <c r="AU4" s="71"/>
+      <c r="AV4" s="73"/>
+      <c r="AW4" s="71"/>
+      <c r="AX4" s="71"/>
+      <c r="AY4" s="71"/>
+      <c r="AZ4" s="71"/>
+      <c r="BA4" s="71"/>
+      <c r="BB4" s="71"/>
+      <c r="BC4" s="73"/>
+      <c r="BD4" s="71"/>
+      <c r="BE4" s="71"/>
+      <c r="BF4" s="71"/>
+      <c r="BG4" s="71"/>
+      <c r="BH4" s="71"/>
+      <c r="BI4" s="73"/>
+      <c r="BJ4" s="74"/>
+      <c r="BK4" s="62"/>
+      <c r="BL4" s="63"/>
+      <c r="BM4" s="64"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
@@ -4336,71 +4343,71 @@
       <c r="F5" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="67" t="n">
+      <c r="G5" s="65" t="n">
         <f aca="false">Netzplan!J5</f>
         <v>2</v>
       </c>
-      <c r="H5" s="68" t="n">
+      <c r="H5" s="66" t="n">
         <f aca="false">SUM(I5:BJ5)</f>
         <v>0</v>
       </c>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
-      <c r="K5" s="74"/>
-      <c r="L5" s="74"/>
-      <c r="M5" s="74"/>
-      <c r="N5" s="74"/>
-      <c r="O5" s="74"/>
-      <c r="P5" s="74"/>
-      <c r="Q5" s="75"/>
-      <c r="R5" s="75"/>
-      <c r="S5" s="79"/>
-      <c r="T5" s="74"/>
-      <c r="U5" s="74"/>
-      <c r="V5" s="74"/>
-      <c r="W5" s="74"/>
-      <c r="X5" s="74"/>
-      <c r="Y5" s="74"/>
-      <c r="Z5" s="74"/>
-      <c r="AA5" s="74"/>
-      <c r="AB5" s="74"/>
-      <c r="AC5" s="74"/>
-      <c r="AD5" s="74"/>
-      <c r="AE5" s="74"/>
-      <c r="AF5" s="74"/>
-      <c r="AG5" s="74"/>
-      <c r="AH5" s="74"/>
-      <c r="AI5" s="74"/>
-      <c r="AJ5" s="74"/>
-      <c r="AK5" s="74"/>
-      <c r="AL5" s="74"/>
-      <c r="AM5" s="74"/>
-      <c r="AN5" s="74"/>
-      <c r="AO5" s="74"/>
-      <c r="AP5" s="74"/>
-      <c r="AQ5" s="74"/>
-      <c r="AR5" s="74"/>
-      <c r="AS5" s="74"/>
-      <c r="AT5" s="74"/>
-      <c r="AU5" s="74"/>
-      <c r="AV5" s="77"/>
-      <c r="AW5" s="74"/>
-      <c r="AX5" s="74"/>
-      <c r="AY5" s="74"/>
-      <c r="AZ5" s="74"/>
-      <c r="BA5" s="74"/>
-      <c r="BB5" s="74"/>
-      <c r="BC5" s="77"/>
-      <c r="BD5" s="74"/>
-      <c r="BE5" s="74"/>
-      <c r="BF5" s="74"/>
-      <c r="BG5" s="74"/>
-      <c r="BH5" s="74"/>
-      <c r="BI5" s="77"/>
-      <c r="BJ5" s="78"/>
-      <c r="BK5" s="64"/>
-      <c r="BL5" s="65"/>
-      <c r="BM5" s="66"/>
+      <c r="I5" s="71"/>
+      <c r="J5" s="71"/>
+      <c r="K5" s="71"/>
+      <c r="L5" s="71"/>
+      <c r="M5" s="71"/>
+      <c r="N5" s="71"/>
+      <c r="O5" s="71"/>
+      <c r="P5" s="71"/>
+      <c r="Q5" s="72"/>
+      <c r="R5" s="72"/>
+      <c r="S5" s="75"/>
+      <c r="T5" s="71"/>
+      <c r="U5" s="71"/>
+      <c r="V5" s="71"/>
+      <c r="W5" s="71"/>
+      <c r="X5" s="71"/>
+      <c r="Y5" s="71"/>
+      <c r="Z5" s="71"/>
+      <c r="AA5" s="71"/>
+      <c r="AB5" s="71"/>
+      <c r="AC5" s="71"/>
+      <c r="AD5" s="71"/>
+      <c r="AE5" s="71"/>
+      <c r="AF5" s="71"/>
+      <c r="AG5" s="71"/>
+      <c r="AH5" s="71"/>
+      <c r="AI5" s="71"/>
+      <c r="AJ5" s="71"/>
+      <c r="AK5" s="71"/>
+      <c r="AL5" s="71"/>
+      <c r="AM5" s="71"/>
+      <c r="AN5" s="71"/>
+      <c r="AO5" s="71"/>
+      <c r="AP5" s="71"/>
+      <c r="AQ5" s="71"/>
+      <c r="AR5" s="71"/>
+      <c r="AS5" s="71"/>
+      <c r="AT5" s="71"/>
+      <c r="AU5" s="71"/>
+      <c r="AV5" s="73"/>
+      <c r="AW5" s="71"/>
+      <c r="AX5" s="71"/>
+      <c r="AY5" s="71"/>
+      <c r="AZ5" s="71"/>
+      <c r="BA5" s="71"/>
+      <c r="BB5" s="71"/>
+      <c r="BC5" s="73"/>
+      <c r="BD5" s="71"/>
+      <c r="BE5" s="71"/>
+      <c r="BF5" s="71"/>
+      <c r="BG5" s="71"/>
+      <c r="BH5" s="71"/>
+      <c r="BI5" s="73"/>
+      <c r="BJ5" s="74"/>
+      <c r="BK5" s="62"/>
+      <c r="BL5" s="63"/>
+      <c r="BM5" s="64"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
@@ -4417,71 +4424,71 @@
       <c r="F6" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="67" t="n">
+      <c r="G6" s="65" t="n">
         <f aca="false">Netzplan!J6</f>
         <v>4</v>
       </c>
-      <c r="H6" s="68" t="n">
+      <c r="H6" s="66" t="n">
         <f aca="false">SUM(I6:BJ6)</f>
         <v>0</v>
       </c>
-      <c r="I6" s="74"/>
-      <c r="J6" s="74"/>
-      <c r="K6" s="74"/>
-      <c r="L6" s="74"/>
-      <c r="M6" s="74"/>
-      <c r="N6" s="74"/>
-      <c r="O6" s="74"/>
-      <c r="P6" s="74"/>
-      <c r="Q6" s="74"/>
-      <c r="R6" s="74"/>
-      <c r="S6" s="76"/>
-      <c r="T6" s="75"/>
-      <c r="U6" s="74"/>
-      <c r="V6" s="74"/>
-      <c r="W6" s="75"/>
-      <c r="X6" s="75"/>
-      <c r="Y6" s="75"/>
-      <c r="Z6" s="75"/>
-      <c r="AA6" s="80"/>
-      <c r="AB6" s="74"/>
-      <c r="AC6" s="74"/>
-      <c r="AD6" s="74"/>
-      <c r="AE6" s="74"/>
-      <c r="AF6" s="74"/>
-      <c r="AG6" s="74"/>
-      <c r="AH6" s="74"/>
-      <c r="AI6" s="74"/>
-      <c r="AJ6" s="74"/>
-      <c r="AK6" s="74"/>
-      <c r="AL6" s="74"/>
-      <c r="AM6" s="74"/>
-      <c r="AN6" s="74"/>
-      <c r="AO6" s="74"/>
-      <c r="AP6" s="74"/>
-      <c r="AQ6" s="74"/>
-      <c r="AR6" s="74"/>
-      <c r="AS6" s="74"/>
-      <c r="AT6" s="74"/>
-      <c r="AU6" s="74"/>
-      <c r="AV6" s="77"/>
-      <c r="AW6" s="74"/>
-      <c r="AX6" s="74"/>
-      <c r="AY6" s="74"/>
-      <c r="AZ6" s="74"/>
-      <c r="BA6" s="74"/>
-      <c r="BB6" s="74"/>
-      <c r="BC6" s="77"/>
-      <c r="BD6" s="74"/>
-      <c r="BE6" s="74"/>
-      <c r="BF6" s="74"/>
-      <c r="BG6" s="74"/>
-      <c r="BH6" s="74"/>
-      <c r="BI6" s="77"/>
-      <c r="BJ6" s="78"/>
-      <c r="BK6" s="64"/>
-      <c r="BL6" s="65"/>
-      <c r="BM6" s="66"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="71"/>
+      <c r="K6" s="71"/>
+      <c r="L6" s="71"/>
+      <c r="M6" s="71"/>
+      <c r="N6" s="71"/>
+      <c r="O6" s="71"/>
+      <c r="P6" s="71"/>
+      <c r="Q6" s="71"/>
+      <c r="R6" s="71"/>
+      <c r="S6" s="71"/>
+      <c r="T6" s="72"/>
+      <c r="U6" s="71"/>
+      <c r="V6" s="71"/>
+      <c r="W6" s="72"/>
+      <c r="X6" s="72"/>
+      <c r="Y6" s="72"/>
+      <c r="Z6" s="72"/>
+      <c r="AA6" s="75"/>
+      <c r="AB6" s="71"/>
+      <c r="AC6" s="71"/>
+      <c r="AD6" s="71"/>
+      <c r="AE6" s="71"/>
+      <c r="AF6" s="71"/>
+      <c r="AG6" s="71"/>
+      <c r="AH6" s="71"/>
+      <c r="AI6" s="71"/>
+      <c r="AJ6" s="71"/>
+      <c r="AK6" s="71"/>
+      <c r="AL6" s="71"/>
+      <c r="AM6" s="71"/>
+      <c r="AN6" s="71"/>
+      <c r="AO6" s="71"/>
+      <c r="AP6" s="71"/>
+      <c r="AQ6" s="71"/>
+      <c r="AR6" s="71"/>
+      <c r="AS6" s="71"/>
+      <c r="AT6" s="71"/>
+      <c r="AU6" s="71"/>
+      <c r="AV6" s="73"/>
+      <c r="AW6" s="71"/>
+      <c r="AX6" s="71"/>
+      <c r="AY6" s="71"/>
+      <c r="AZ6" s="71"/>
+      <c r="BA6" s="71"/>
+      <c r="BB6" s="71"/>
+      <c r="BC6" s="73"/>
+      <c r="BD6" s="71"/>
+      <c r="BE6" s="71"/>
+      <c r="BF6" s="71"/>
+      <c r="BG6" s="71"/>
+      <c r="BH6" s="71"/>
+      <c r="BI6" s="73"/>
+      <c r="BJ6" s="74"/>
+      <c r="BK6" s="62"/>
+      <c r="BL6" s="63"/>
+      <c r="BM6" s="64"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
@@ -4498,71 +4505,71 @@
       <c r="F7" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="67" t="n">
+      <c r="G7" s="65" t="n">
         <f aca="false">Netzplan!J7</f>
         <v>1</v>
       </c>
-      <c r="H7" s="68" t="n">
+      <c r="H7" s="66" t="n">
         <f aca="false">SUM(I7:BJ7)</f>
         <v>0</v>
       </c>
-      <c r="I7" s="74"/>
-      <c r="J7" s="74"/>
-      <c r="K7" s="74"/>
-      <c r="L7" s="74"/>
-      <c r="M7" s="74"/>
-      <c r="N7" s="74"/>
-      <c r="O7" s="74"/>
-      <c r="P7" s="75"/>
-      <c r="Q7" s="74"/>
-      <c r="R7" s="74"/>
-      <c r="S7" s="76"/>
-      <c r="T7" s="74"/>
-      <c r="U7" s="74"/>
-      <c r="V7" s="74"/>
-      <c r="W7" s="74"/>
-      <c r="X7" s="74"/>
-      <c r="Y7" s="74"/>
-      <c r="Z7" s="74"/>
-      <c r="AA7" s="74"/>
-      <c r="AB7" s="74"/>
-      <c r="AC7" s="74"/>
-      <c r="AD7" s="74"/>
-      <c r="AE7" s="74"/>
-      <c r="AF7" s="74"/>
-      <c r="AG7" s="74"/>
-      <c r="AH7" s="74"/>
-      <c r="AI7" s="74"/>
-      <c r="AJ7" s="74"/>
-      <c r="AK7" s="74"/>
-      <c r="AL7" s="74"/>
-      <c r="AM7" s="74"/>
-      <c r="AN7" s="74"/>
-      <c r="AO7" s="74"/>
-      <c r="AP7" s="74"/>
-      <c r="AQ7" s="74"/>
-      <c r="AR7" s="74"/>
-      <c r="AS7" s="74"/>
-      <c r="AT7" s="74"/>
-      <c r="AU7" s="74"/>
-      <c r="AV7" s="77"/>
-      <c r="AW7" s="74"/>
-      <c r="AX7" s="74"/>
-      <c r="AY7" s="74"/>
-      <c r="AZ7" s="74"/>
-      <c r="BA7" s="74"/>
-      <c r="BB7" s="74"/>
-      <c r="BC7" s="77"/>
-      <c r="BD7" s="74"/>
-      <c r="BE7" s="74"/>
-      <c r="BF7" s="74"/>
-      <c r="BG7" s="74"/>
-      <c r="BH7" s="74"/>
-      <c r="BI7" s="77"/>
-      <c r="BJ7" s="78"/>
-      <c r="BK7" s="64"/>
-      <c r="BL7" s="65"/>
-      <c r="BM7" s="66"/>
+      <c r="I7" s="71"/>
+      <c r="J7" s="71"/>
+      <c r="K7" s="71"/>
+      <c r="L7" s="71"/>
+      <c r="M7" s="71"/>
+      <c r="N7" s="71"/>
+      <c r="O7" s="71"/>
+      <c r="P7" s="72"/>
+      <c r="Q7" s="71"/>
+      <c r="R7" s="71"/>
+      <c r="S7" s="71"/>
+      <c r="T7" s="71"/>
+      <c r="U7" s="71"/>
+      <c r="V7" s="71"/>
+      <c r="W7" s="71"/>
+      <c r="X7" s="71"/>
+      <c r="Y7" s="71"/>
+      <c r="Z7" s="71"/>
+      <c r="AA7" s="71"/>
+      <c r="AB7" s="71"/>
+      <c r="AC7" s="71"/>
+      <c r="AD7" s="71"/>
+      <c r="AE7" s="71"/>
+      <c r="AF7" s="71"/>
+      <c r="AG7" s="71"/>
+      <c r="AH7" s="71"/>
+      <c r="AI7" s="71"/>
+      <c r="AJ7" s="71"/>
+      <c r="AK7" s="71"/>
+      <c r="AL7" s="71"/>
+      <c r="AM7" s="71"/>
+      <c r="AN7" s="71"/>
+      <c r="AO7" s="71"/>
+      <c r="AP7" s="71"/>
+      <c r="AQ7" s="71"/>
+      <c r="AR7" s="71"/>
+      <c r="AS7" s="71"/>
+      <c r="AT7" s="71"/>
+      <c r="AU7" s="71"/>
+      <c r="AV7" s="73"/>
+      <c r="AW7" s="71"/>
+      <c r="AX7" s="71"/>
+      <c r="AY7" s="71"/>
+      <c r="AZ7" s="71"/>
+      <c r="BA7" s="71"/>
+      <c r="BB7" s="71"/>
+      <c r="BC7" s="73"/>
+      <c r="BD7" s="71"/>
+      <c r="BE7" s="71"/>
+      <c r="BF7" s="71"/>
+      <c r="BG7" s="71"/>
+      <c r="BH7" s="71"/>
+      <c r="BI7" s="73"/>
+      <c r="BJ7" s="74"/>
+      <c r="BK7" s="62"/>
+      <c r="BL7" s="63"/>
+      <c r="BM7" s="64"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
@@ -4579,71 +4586,71 @@
       <c r="F8" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="67" t="n">
+      <c r="G8" s="65" t="n">
         <f aca="false">Netzplan!J8</f>
         <v>6</v>
       </c>
-      <c r="H8" s="68" t="n">
+      <c r="H8" s="66" t="n">
         <f aca="false">SUM(I8:BJ8)</f>
         <v>0</v>
       </c>
-      <c r="I8" s="74"/>
-      <c r="J8" s="74"/>
-      <c r="K8" s="74"/>
-      <c r="L8" s="74"/>
-      <c r="M8" s="74"/>
-      <c r="N8" s="74"/>
-      <c r="O8" s="74"/>
-      <c r="P8" s="74"/>
-      <c r="Q8" s="75"/>
-      <c r="R8" s="75"/>
-      <c r="S8" s="79"/>
-      <c r="T8" s="74"/>
-      <c r="U8" s="74"/>
-      <c r="V8" s="74"/>
-      <c r="W8" s="74"/>
-      <c r="X8" s="74"/>
-      <c r="Y8" s="74"/>
-      <c r="Z8" s="74"/>
-      <c r="AA8" s="74"/>
-      <c r="AB8" s="74"/>
-      <c r="AC8" s="74"/>
-      <c r="AD8" s="74"/>
-      <c r="AE8" s="74"/>
-      <c r="AF8" s="74"/>
-      <c r="AG8" s="74"/>
-      <c r="AH8" s="74"/>
-      <c r="AI8" s="74"/>
-      <c r="AJ8" s="74"/>
-      <c r="AK8" s="74"/>
-      <c r="AL8" s="74"/>
-      <c r="AM8" s="74"/>
-      <c r="AN8" s="74"/>
-      <c r="AO8" s="74"/>
-      <c r="AP8" s="74"/>
-      <c r="AQ8" s="74"/>
-      <c r="AR8" s="74"/>
-      <c r="AS8" s="74"/>
-      <c r="AT8" s="74"/>
-      <c r="AU8" s="74"/>
-      <c r="AV8" s="77"/>
-      <c r="AW8" s="74"/>
-      <c r="AX8" s="74"/>
-      <c r="AY8" s="74"/>
-      <c r="AZ8" s="74"/>
-      <c r="BA8" s="74"/>
-      <c r="BB8" s="74"/>
-      <c r="BC8" s="77"/>
-      <c r="BD8" s="74"/>
-      <c r="BE8" s="74"/>
-      <c r="BF8" s="74"/>
-      <c r="BG8" s="74"/>
-      <c r="BH8" s="74"/>
-      <c r="BI8" s="77"/>
-      <c r="BJ8" s="78"/>
-      <c r="BK8" s="64"/>
-      <c r="BL8" s="65"/>
-      <c r="BM8" s="66"/>
+      <c r="I8" s="71"/>
+      <c r="J8" s="71"/>
+      <c r="K8" s="71"/>
+      <c r="L8" s="71"/>
+      <c r="M8" s="71"/>
+      <c r="N8" s="71"/>
+      <c r="O8" s="71"/>
+      <c r="P8" s="71"/>
+      <c r="Q8" s="72"/>
+      <c r="R8" s="72"/>
+      <c r="S8" s="75"/>
+      <c r="T8" s="71"/>
+      <c r="U8" s="71"/>
+      <c r="V8" s="71"/>
+      <c r="W8" s="71"/>
+      <c r="X8" s="71"/>
+      <c r="Y8" s="71"/>
+      <c r="Z8" s="71"/>
+      <c r="AA8" s="71"/>
+      <c r="AB8" s="71"/>
+      <c r="AC8" s="71"/>
+      <c r="AD8" s="71"/>
+      <c r="AE8" s="71"/>
+      <c r="AF8" s="71"/>
+      <c r="AG8" s="71"/>
+      <c r="AH8" s="71"/>
+      <c r="AI8" s="71"/>
+      <c r="AJ8" s="71"/>
+      <c r="AK8" s="71"/>
+      <c r="AL8" s="71"/>
+      <c r="AM8" s="71"/>
+      <c r="AN8" s="71"/>
+      <c r="AO8" s="71"/>
+      <c r="AP8" s="71"/>
+      <c r="AQ8" s="71"/>
+      <c r="AR8" s="71"/>
+      <c r="AS8" s="71"/>
+      <c r="AT8" s="71"/>
+      <c r="AU8" s="71"/>
+      <c r="AV8" s="73"/>
+      <c r="AW8" s="71"/>
+      <c r="AX8" s="71"/>
+      <c r="AY8" s="71"/>
+      <c r="AZ8" s="71"/>
+      <c r="BA8" s="71"/>
+      <c r="BB8" s="71"/>
+      <c r="BC8" s="73"/>
+      <c r="BD8" s="71"/>
+      <c r="BE8" s="71"/>
+      <c r="BF8" s="71"/>
+      <c r="BG8" s="71"/>
+      <c r="BH8" s="71"/>
+      <c r="BI8" s="73"/>
+      <c r="BJ8" s="74"/>
+      <c r="BK8" s="62"/>
+      <c r="BL8" s="63"/>
+      <c r="BM8" s="64"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
@@ -4660,71 +4667,71 @@
       <c r="F9" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="G9" s="67" t="n">
+      <c r="G9" s="65" t="n">
         <f aca="false">Netzplan!J9</f>
         <v>2</v>
       </c>
-      <c r="H9" s="68" t="n">
+      <c r="H9" s="66" t="n">
         <f aca="false">SUM(I9:BJ9)</f>
         <v>0</v>
       </c>
-      <c r="I9" s="74"/>
-      <c r="J9" s="74"/>
-      <c r="K9" s="74"/>
-      <c r="L9" s="74"/>
-      <c r="M9" s="74"/>
-      <c r="N9" s="74"/>
-      <c r="O9" s="74"/>
-      <c r="P9" s="74"/>
-      <c r="Q9" s="74"/>
-      <c r="R9" s="74"/>
-      <c r="S9" s="76"/>
-      <c r="T9" s="74"/>
-      <c r="U9" s="74"/>
-      <c r="V9" s="74"/>
-      <c r="W9" s="75"/>
-      <c r="X9" s="75"/>
-      <c r="Y9" s="75"/>
-      <c r="Z9" s="75"/>
-      <c r="AA9" s="78"/>
-      <c r="AB9" s="74"/>
-      <c r="AC9" s="74"/>
-      <c r="AD9" s="75"/>
-      <c r="AE9" s="74"/>
-      <c r="AF9" s="74"/>
-      <c r="AG9" s="74"/>
-      <c r="AH9" s="74"/>
-      <c r="AI9" s="74"/>
-      <c r="AJ9" s="74"/>
-      <c r="AK9" s="74"/>
-      <c r="AL9" s="74"/>
-      <c r="AM9" s="74"/>
-      <c r="AN9" s="74"/>
-      <c r="AO9" s="74"/>
-      <c r="AP9" s="74"/>
-      <c r="AQ9" s="74"/>
-      <c r="AR9" s="74"/>
-      <c r="AS9" s="74"/>
-      <c r="AT9" s="74"/>
-      <c r="AU9" s="74"/>
-      <c r="AV9" s="77"/>
-      <c r="AW9" s="74"/>
-      <c r="AX9" s="74"/>
-      <c r="AY9" s="74"/>
-      <c r="AZ9" s="74"/>
-      <c r="BA9" s="74"/>
-      <c r="BB9" s="74"/>
-      <c r="BC9" s="77"/>
-      <c r="BD9" s="74"/>
-      <c r="BE9" s="74"/>
-      <c r="BF9" s="74"/>
-      <c r="BG9" s="74"/>
-      <c r="BH9" s="74"/>
-      <c r="BI9" s="77"/>
-      <c r="BJ9" s="78"/>
-      <c r="BK9" s="64"/>
-      <c r="BL9" s="65"/>
-      <c r="BM9" s="66"/>
+      <c r="I9" s="71"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="71"/>
+      <c r="L9" s="71"/>
+      <c r="M9" s="71"/>
+      <c r="N9" s="71"/>
+      <c r="O9" s="71"/>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71"/>
+      <c r="R9" s="71"/>
+      <c r="S9" s="71"/>
+      <c r="T9" s="71"/>
+      <c r="U9" s="71"/>
+      <c r="V9" s="71"/>
+      <c r="W9" s="72"/>
+      <c r="X9" s="72"/>
+      <c r="Y9" s="72"/>
+      <c r="Z9" s="72"/>
+      <c r="AA9" s="74"/>
+      <c r="AB9" s="71"/>
+      <c r="AC9" s="71"/>
+      <c r="AD9" s="72"/>
+      <c r="AE9" s="71"/>
+      <c r="AF9" s="71"/>
+      <c r="AG9" s="71"/>
+      <c r="AH9" s="71"/>
+      <c r="AI9" s="71"/>
+      <c r="AJ9" s="71"/>
+      <c r="AK9" s="71"/>
+      <c r="AL9" s="71"/>
+      <c r="AM9" s="71"/>
+      <c r="AN9" s="71"/>
+      <c r="AO9" s="71"/>
+      <c r="AP9" s="71"/>
+      <c r="AQ9" s="71"/>
+      <c r="AR9" s="71"/>
+      <c r="AS9" s="71"/>
+      <c r="AT9" s="71"/>
+      <c r="AU9" s="71"/>
+      <c r="AV9" s="73"/>
+      <c r="AW9" s="71"/>
+      <c r="AX9" s="71"/>
+      <c r="AY9" s="71"/>
+      <c r="AZ9" s="71"/>
+      <c r="BA9" s="71"/>
+      <c r="BB9" s="71"/>
+      <c r="BC9" s="73"/>
+      <c r="BD9" s="71"/>
+      <c r="BE9" s="71"/>
+      <c r="BF9" s="71"/>
+      <c r="BG9" s="71"/>
+      <c r="BH9" s="71"/>
+      <c r="BI9" s="73"/>
+      <c r="BJ9" s="74"/>
+      <c r="BK9" s="62"/>
+      <c r="BL9" s="63"/>
+      <c r="BM9" s="64"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
@@ -4741,70 +4748,70 @@
       <c r="F10" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="G10" s="67" t="n">
+      <c r="G10" s="65" t="n">
         <f aca="false">Netzplan!J10</f>
         <v>2</v>
       </c>
-      <c r="H10" s="68" t="n">
+      <c r="H10" s="66" t="n">
         <f aca="false">SUM(I10:BJ10)</f>
         <v>0</v>
       </c>
-      <c r="I10" s="74"/>
-      <c r="J10" s="74"/>
-      <c r="K10" s="74"/>
-      <c r="L10" s="74"/>
-      <c r="M10" s="74"/>
-      <c r="N10" s="74"/>
-      <c r="O10" s="74"/>
-      <c r="P10" s="74"/>
-      <c r="Q10" s="74"/>
-      <c r="R10" s="74"/>
-      <c r="S10" s="76"/>
-      <c r="T10" s="74"/>
-      <c r="U10" s="74"/>
-      <c r="V10" s="74"/>
-      <c r="W10" s="74"/>
-      <c r="X10" s="74"/>
-      <c r="Y10" s="74"/>
-      <c r="Z10" s="74"/>
-      <c r="AA10" s="74"/>
-      <c r="AB10" s="74"/>
-      <c r="AC10" s="74"/>
-      <c r="AE10" s="78"/>
-      <c r="AF10" s="74"/>
-      <c r="AG10" s="74"/>
-      <c r="AH10" s="74"/>
-      <c r="AI10" s="74"/>
-      <c r="AJ10" s="74"/>
-      <c r="AK10" s="74"/>
-      <c r="AL10" s="74"/>
-      <c r="AM10" s="74"/>
-      <c r="AN10" s="74"/>
-      <c r="AO10" s="74"/>
-      <c r="AP10" s="74"/>
-      <c r="AQ10" s="74"/>
-      <c r="AR10" s="74"/>
-      <c r="AS10" s="74"/>
-      <c r="AT10" s="74"/>
-      <c r="AU10" s="74"/>
-      <c r="AV10" s="77"/>
-      <c r="AW10" s="74"/>
-      <c r="AX10" s="74"/>
-      <c r="AY10" s="74"/>
-      <c r="AZ10" s="74"/>
-      <c r="BA10" s="74"/>
-      <c r="BB10" s="74"/>
-      <c r="BC10" s="77"/>
-      <c r="BD10" s="74"/>
-      <c r="BE10" s="74"/>
-      <c r="BF10" s="74"/>
-      <c r="BG10" s="74"/>
-      <c r="BH10" s="74"/>
-      <c r="BI10" s="77"/>
-      <c r="BJ10" s="78"/>
-      <c r="BK10" s="64"/>
-      <c r="BL10" s="65"/>
-      <c r="BM10" s="66"/>
+      <c r="I10" s="71"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="71"/>
+      <c r="L10" s="71"/>
+      <c r="M10" s="71"/>
+      <c r="N10" s="71"/>
+      <c r="O10" s="71"/>
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71"/>
+      <c r="R10" s="71"/>
+      <c r="S10" s="71"/>
+      <c r="T10" s="71"/>
+      <c r="U10" s="71"/>
+      <c r="V10" s="71"/>
+      <c r="W10" s="71"/>
+      <c r="X10" s="71"/>
+      <c r="Y10" s="71"/>
+      <c r="Z10" s="71"/>
+      <c r="AA10" s="71"/>
+      <c r="AB10" s="71"/>
+      <c r="AC10" s="71"/>
+      <c r="AE10" s="74"/>
+      <c r="AF10" s="71"/>
+      <c r="AG10" s="71"/>
+      <c r="AH10" s="71"/>
+      <c r="AI10" s="71"/>
+      <c r="AJ10" s="71"/>
+      <c r="AK10" s="71"/>
+      <c r="AL10" s="71"/>
+      <c r="AM10" s="71"/>
+      <c r="AN10" s="71"/>
+      <c r="AO10" s="71"/>
+      <c r="AP10" s="71"/>
+      <c r="AQ10" s="71"/>
+      <c r="AR10" s="71"/>
+      <c r="AS10" s="71"/>
+      <c r="AT10" s="71"/>
+      <c r="AU10" s="71"/>
+      <c r="AV10" s="73"/>
+      <c r="AW10" s="71"/>
+      <c r="AX10" s="71"/>
+      <c r="AY10" s="71"/>
+      <c r="AZ10" s="71"/>
+      <c r="BA10" s="71"/>
+      <c r="BB10" s="71"/>
+      <c r="BC10" s="73"/>
+      <c r="BD10" s="71"/>
+      <c r="BE10" s="71"/>
+      <c r="BF10" s="71"/>
+      <c r="BG10" s="71"/>
+      <c r="BH10" s="71"/>
+      <c r="BI10" s="73"/>
+      <c r="BJ10" s="74"/>
+      <c r="BK10" s="62"/>
+      <c r="BL10" s="63"/>
+      <c r="BM10" s="64"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
@@ -4821,70 +4828,70 @@
       <c r="F11" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="67" t="n">
+      <c r="G11" s="65" t="n">
         <f aca="false">Netzplan!J11</f>
         <v>2</v>
       </c>
-      <c r="H11" s="68" t="n">
+      <c r="H11" s="66" t="n">
         <f aca="false">SUM(I11:BJ11)</f>
         <v>0</v>
       </c>
-      <c r="I11" s="74"/>
-      <c r="J11" s="74"/>
-      <c r="K11" s="74"/>
-      <c r="L11" s="74"/>
-      <c r="M11" s="74"/>
-      <c r="N11" s="74"/>
-      <c r="O11" s="74"/>
-      <c r="P11" s="74"/>
-      <c r="Q11" s="74"/>
-      <c r="R11" s="74"/>
-      <c r="S11" s="76"/>
-      <c r="T11" s="74"/>
-      <c r="U11" s="74"/>
-      <c r="V11" s="74"/>
-      <c r="W11" s="74"/>
-      <c r="X11" s="74"/>
-      <c r="Y11" s="74"/>
-      <c r="Z11" s="74"/>
-      <c r="AA11" s="74"/>
-      <c r="AB11" s="74"/>
-      <c r="AC11" s="74"/>
-      <c r="AE11" s="78"/>
-      <c r="AF11" s="74"/>
-      <c r="AG11" s="75"/>
-      <c r="AH11" s="75"/>
-      <c r="AI11" s="74"/>
-      <c r="AJ11" s="74"/>
-      <c r="AK11" s="74"/>
-      <c r="AL11" s="74"/>
-      <c r="AM11" s="74"/>
-      <c r="AN11" s="74"/>
-      <c r="AO11" s="74"/>
-      <c r="AP11" s="74"/>
-      <c r="AQ11" s="74"/>
-      <c r="AR11" s="74"/>
-      <c r="AS11" s="74"/>
-      <c r="AT11" s="74"/>
-      <c r="AU11" s="74"/>
-      <c r="AV11" s="77"/>
-      <c r="AW11" s="74"/>
-      <c r="AX11" s="74"/>
-      <c r="AY11" s="74"/>
-      <c r="AZ11" s="74"/>
-      <c r="BA11" s="74"/>
-      <c r="BB11" s="74"/>
-      <c r="BC11" s="77"/>
-      <c r="BD11" s="74"/>
-      <c r="BE11" s="74"/>
-      <c r="BF11" s="74"/>
-      <c r="BG11" s="74"/>
-      <c r="BH11" s="74"/>
-      <c r="BI11" s="77"/>
-      <c r="BJ11" s="78"/>
-      <c r="BK11" s="64"/>
-      <c r="BL11" s="65"/>
-      <c r="BM11" s="66"/>
+      <c r="I11" s="71"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="71"/>
+      <c r="L11" s="71"/>
+      <c r="M11" s="71"/>
+      <c r="N11" s="71"/>
+      <c r="O11" s="71"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="71"/>
+      <c r="S11" s="71"/>
+      <c r="T11" s="71"/>
+      <c r="U11" s="71"/>
+      <c r="V11" s="71"/>
+      <c r="W11" s="71"/>
+      <c r="X11" s="71"/>
+      <c r="Y11" s="71"/>
+      <c r="Z11" s="71"/>
+      <c r="AA11" s="71"/>
+      <c r="AB11" s="71"/>
+      <c r="AC11" s="71"/>
+      <c r="AE11" s="74"/>
+      <c r="AF11" s="71"/>
+      <c r="AG11" s="72"/>
+      <c r="AH11" s="72"/>
+      <c r="AI11" s="71"/>
+      <c r="AJ11" s="71"/>
+      <c r="AK11" s="71"/>
+      <c r="AL11" s="71"/>
+      <c r="AM11" s="71"/>
+      <c r="AN11" s="71"/>
+      <c r="AO11" s="71"/>
+      <c r="AP11" s="71"/>
+      <c r="AQ11" s="71"/>
+      <c r="AR11" s="71"/>
+      <c r="AS11" s="71"/>
+      <c r="AT11" s="71"/>
+      <c r="AU11" s="71"/>
+      <c r="AV11" s="73"/>
+      <c r="AW11" s="71"/>
+      <c r="AX11" s="71"/>
+      <c r="AY11" s="71"/>
+      <c r="AZ11" s="71"/>
+      <c r="BA11" s="71"/>
+      <c r="BB11" s="71"/>
+      <c r="BC11" s="73"/>
+      <c r="BD11" s="71"/>
+      <c r="BE11" s="71"/>
+      <c r="BF11" s="71"/>
+      <c r="BG11" s="71"/>
+      <c r="BH11" s="71"/>
+      <c r="BI11" s="73"/>
+      <c r="BJ11" s="74"/>
+      <c r="BK11" s="62"/>
+      <c r="BL11" s="63"/>
+      <c r="BM11" s="64"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
@@ -4901,71 +4908,71 @@
       <c r="F12" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="G12" s="67" t="n">
+      <c r="G12" s="65" t="n">
         <f aca="false">Netzplan!J12</f>
         <v>20</v>
       </c>
-      <c r="H12" s="68" t="n">
+      <c r="H12" s="66" t="n">
         <f aca="false">SUM(I12:BJ12)</f>
         <v>0</v>
       </c>
-      <c r="I12" s="74"/>
-      <c r="J12" s="74"/>
-      <c r="K12" s="74"/>
-      <c r="L12" s="74"/>
-      <c r="M12" s="74"/>
-      <c r="N12" s="74"/>
-      <c r="O12" s="74"/>
-      <c r="P12" s="74"/>
-      <c r="Q12" s="74"/>
-      <c r="R12" s="74"/>
-      <c r="S12" s="76"/>
-      <c r="T12" s="75"/>
-      <c r="U12" s="74"/>
-      <c r="V12" s="74"/>
-      <c r="W12" s="75"/>
-      <c r="X12" s="75"/>
-      <c r="Y12" s="75"/>
-      <c r="Z12" s="75"/>
-      <c r="AA12" s="80"/>
-      <c r="AB12" s="74"/>
-      <c r="AC12" s="74"/>
-      <c r="AD12" s="75"/>
-      <c r="AE12" s="75"/>
-      <c r="AF12" s="75"/>
-      <c r="AG12" s="75"/>
-      <c r="AH12" s="75"/>
-      <c r="AI12" s="74"/>
-      <c r="AJ12" s="74"/>
-      <c r="AK12" s="75"/>
-      <c r="AL12" s="75"/>
-      <c r="AM12" s="75"/>
-      <c r="AN12" s="75"/>
-      <c r="AO12" s="75"/>
-      <c r="AP12" s="74"/>
-      <c r="AQ12" s="74"/>
-      <c r="AR12" s="75"/>
-      <c r="AS12" s="75"/>
-      <c r="AT12" s="75"/>
-      <c r="AU12" s="75"/>
-      <c r="AV12" s="77"/>
-      <c r="AW12" s="74"/>
-      <c r="AX12" s="74"/>
-      <c r="AY12" s="75"/>
-      <c r="AZ12" s="75"/>
-      <c r="BA12" s="75"/>
-      <c r="BB12" s="75"/>
-      <c r="BC12" s="77"/>
-      <c r="BD12" s="74"/>
-      <c r="BE12" s="74"/>
-      <c r="BF12" s="74"/>
-      <c r="BG12" s="74"/>
-      <c r="BH12" s="74"/>
-      <c r="BI12" s="77"/>
-      <c r="BJ12" s="78"/>
-      <c r="BK12" s="64"/>
-      <c r="BL12" s="65"/>
-      <c r="BM12" s="66"/>
+      <c r="I12" s="71"/>
+      <c r="J12" s="71"/>
+      <c r="K12" s="71"/>
+      <c r="L12" s="71"/>
+      <c r="M12" s="71"/>
+      <c r="N12" s="71"/>
+      <c r="O12" s="71"/>
+      <c r="P12" s="71"/>
+      <c r="Q12" s="71"/>
+      <c r="R12" s="71"/>
+      <c r="S12" s="71"/>
+      <c r="T12" s="72"/>
+      <c r="U12" s="71"/>
+      <c r="V12" s="71"/>
+      <c r="W12" s="72"/>
+      <c r="X12" s="72"/>
+      <c r="Y12" s="72"/>
+      <c r="Z12" s="72"/>
+      <c r="AA12" s="75"/>
+      <c r="AB12" s="71"/>
+      <c r="AC12" s="71"/>
+      <c r="AD12" s="72"/>
+      <c r="AE12" s="72"/>
+      <c r="AF12" s="72"/>
+      <c r="AG12" s="72"/>
+      <c r="AH12" s="72"/>
+      <c r="AI12" s="71"/>
+      <c r="AJ12" s="71"/>
+      <c r="AK12" s="72"/>
+      <c r="AL12" s="72"/>
+      <c r="AM12" s="72"/>
+      <c r="AN12" s="72"/>
+      <c r="AO12" s="72"/>
+      <c r="AP12" s="71"/>
+      <c r="AQ12" s="71"/>
+      <c r="AR12" s="72"/>
+      <c r="AS12" s="72"/>
+      <c r="AT12" s="72"/>
+      <c r="AU12" s="72"/>
+      <c r="AV12" s="73"/>
+      <c r="AW12" s="71"/>
+      <c r="AX12" s="71"/>
+      <c r="AY12" s="72"/>
+      <c r="AZ12" s="72"/>
+      <c r="BA12" s="72"/>
+      <c r="BB12" s="72"/>
+      <c r="BC12" s="73"/>
+      <c r="BD12" s="71"/>
+      <c r="BE12" s="71"/>
+      <c r="BF12" s="71"/>
+      <c r="BG12" s="71"/>
+      <c r="BH12" s="71"/>
+      <c r="BI12" s="73"/>
+      <c r="BJ12" s="74"/>
+      <c r="BK12" s="62"/>
+      <c r="BL12" s="63"/>
+      <c r="BM12" s="64"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
@@ -4982,71 +4989,71 @@
       <c r="F13" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="G13" s="67" t="n">
+      <c r="G13" s="65" t="n">
         <f aca="false">Netzplan!J13</f>
         <v>2</v>
       </c>
-      <c r="H13" s="68" t="n">
+      <c r="H13" s="66" t="n">
         <f aca="false">SUM(I13:BJ13)</f>
         <v>0</v>
       </c>
-      <c r="I13" s="74"/>
-      <c r="J13" s="74"/>
-      <c r="K13" s="74"/>
-      <c r="L13" s="74"/>
-      <c r="M13" s="74"/>
-      <c r="N13" s="74"/>
-      <c r="O13" s="74"/>
-      <c r="P13" s="74"/>
-      <c r="Q13" s="74"/>
-      <c r="R13" s="74"/>
-      <c r="S13" s="76"/>
-      <c r="T13" s="74"/>
-      <c r="U13" s="74"/>
-      <c r="V13" s="74"/>
-      <c r="W13" s="74"/>
-      <c r="X13" s="74"/>
-      <c r="Y13" s="74"/>
-      <c r="Z13" s="74"/>
-      <c r="AA13" s="74"/>
-      <c r="AB13" s="74"/>
-      <c r="AC13" s="74"/>
-      <c r="AD13" s="74"/>
-      <c r="AE13" s="74"/>
-      <c r="AF13" s="78"/>
-      <c r="AG13" s="74"/>
-      <c r="AH13" s="74"/>
-      <c r="AI13" s="74"/>
-      <c r="AJ13" s="74"/>
-      <c r="AK13" s="75"/>
-      <c r="AL13" s="75"/>
-      <c r="AM13" s="75"/>
-      <c r="AN13" s="75"/>
-      <c r="AO13" s="75"/>
-      <c r="AP13" s="74"/>
-      <c r="AQ13" s="74"/>
-      <c r="AR13" s="74"/>
-      <c r="AS13" s="74"/>
-      <c r="AT13" s="74"/>
-      <c r="AU13" s="74"/>
-      <c r="AV13" s="77"/>
-      <c r="AW13" s="74"/>
-      <c r="AX13" s="74"/>
-      <c r="AY13" s="74"/>
-      <c r="AZ13" s="74"/>
-      <c r="BA13" s="74"/>
-      <c r="BB13" s="74"/>
-      <c r="BC13" s="77"/>
-      <c r="BD13" s="74"/>
-      <c r="BE13" s="74"/>
-      <c r="BF13" s="74"/>
-      <c r="BG13" s="74"/>
-      <c r="BH13" s="74"/>
-      <c r="BI13" s="77"/>
-      <c r="BJ13" s="78"/>
-      <c r="BK13" s="64"/>
-      <c r="BL13" s="65"/>
-      <c r="BM13" s="66"/>
+      <c r="I13" s="71"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="71"/>
+      <c r="L13" s="71"/>
+      <c r="M13" s="71"/>
+      <c r="N13" s="71"/>
+      <c r="O13" s="71"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="71"/>
+      <c r="S13" s="71"/>
+      <c r="T13" s="71"/>
+      <c r="U13" s="71"/>
+      <c r="V13" s="71"/>
+      <c r="W13" s="71"/>
+      <c r="X13" s="71"/>
+      <c r="Y13" s="71"/>
+      <c r="Z13" s="71"/>
+      <c r="AA13" s="71"/>
+      <c r="AB13" s="71"/>
+      <c r="AC13" s="71"/>
+      <c r="AD13" s="71"/>
+      <c r="AE13" s="71"/>
+      <c r="AF13" s="74"/>
+      <c r="AG13" s="71"/>
+      <c r="AH13" s="71"/>
+      <c r="AI13" s="71"/>
+      <c r="AJ13" s="71"/>
+      <c r="AK13" s="72"/>
+      <c r="AL13" s="72"/>
+      <c r="AM13" s="72"/>
+      <c r="AN13" s="72"/>
+      <c r="AO13" s="72"/>
+      <c r="AP13" s="71"/>
+      <c r="AQ13" s="71"/>
+      <c r="AR13" s="71"/>
+      <c r="AS13" s="71"/>
+      <c r="AT13" s="71"/>
+      <c r="AU13" s="71"/>
+      <c r="AV13" s="73"/>
+      <c r="AW13" s="71"/>
+      <c r="AX13" s="71"/>
+      <c r="AY13" s="71"/>
+      <c r="AZ13" s="71"/>
+      <c r="BA13" s="71"/>
+      <c r="BB13" s="71"/>
+      <c r="BC13" s="73"/>
+      <c r="BD13" s="71"/>
+      <c r="BE13" s="71"/>
+      <c r="BF13" s="71"/>
+      <c r="BG13" s="71"/>
+      <c r="BH13" s="71"/>
+      <c r="BI13" s="73"/>
+      <c r="BJ13" s="74"/>
+      <c r="BK13" s="62"/>
+      <c r="BL13" s="63"/>
+      <c r="BM13" s="64"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
@@ -5063,70 +5070,70 @@
       <c r="F14" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="G14" s="67" t="n">
+      <c r="G14" s="65" t="n">
         <f aca="false">Netzplan!J14</f>
         <v>2</v>
       </c>
-      <c r="H14" s="68" t="n">
+      <c r="H14" s="66" t="n">
         <f aca="false">SUM(I14:BJ14)</f>
         <v>0</v>
       </c>
-      <c r="I14" s="74"/>
-      <c r="J14" s="74"/>
-      <c r="K14" s="74"/>
-      <c r="L14" s="74"/>
-      <c r="M14" s="74"/>
-      <c r="N14" s="74"/>
-      <c r="O14" s="74"/>
-      <c r="P14" s="74"/>
-      <c r="Q14" s="74"/>
-      <c r="R14" s="74"/>
-      <c r="S14" s="76"/>
-      <c r="T14" s="74"/>
-      <c r="U14" s="74"/>
-      <c r="V14" s="74"/>
-      <c r="W14" s="74"/>
-      <c r="X14" s="74"/>
-      <c r="Y14" s="74"/>
-      <c r="Z14" s="74"/>
-      <c r="AA14" s="74"/>
-      <c r="AB14" s="74"/>
-      <c r="AC14" s="74"/>
-      <c r="AD14" s="74"/>
-      <c r="AE14" s="74"/>
-      <c r="AF14" s="74"/>
-      <c r="AG14" s="74"/>
-      <c r="AH14" s="78"/>
-      <c r="AI14" s="74"/>
-      <c r="AJ14" s="74"/>
-      <c r="AL14" s="74"/>
-      <c r="AM14" s="74"/>
-      <c r="AN14" s="74"/>
-      <c r="AO14" s="75"/>
-      <c r="AP14" s="74"/>
-      <c r="AQ14" s="74"/>
-      <c r="AR14" s="75"/>
-      <c r="AS14" s="75"/>
-      <c r="AT14" s="75"/>
-      <c r="AU14" s="74"/>
-      <c r="AV14" s="77"/>
-      <c r="AW14" s="74"/>
-      <c r="AX14" s="74"/>
-      <c r="AY14" s="74"/>
-      <c r="AZ14" s="74"/>
-      <c r="BA14" s="74"/>
-      <c r="BB14" s="74"/>
-      <c r="BC14" s="77"/>
-      <c r="BD14" s="74"/>
-      <c r="BE14" s="74"/>
-      <c r="BF14" s="74"/>
-      <c r="BG14" s="74"/>
-      <c r="BH14" s="74"/>
-      <c r="BI14" s="77"/>
-      <c r="BJ14" s="78"/>
-      <c r="BK14" s="64"/>
-      <c r="BL14" s="65"/>
-      <c r="BM14" s="66"/>
+      <c r="I14" s="71"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="71"/>
+      <c r="L14" s="71"/>
+      <c r="M14" s="71"/>
+      <c r="N14" s="71"/>
+      <c r="O14" s="71"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="71"/>
+      <c r="S14" s="71"/>
+      <c r="T14" s="71"/>
+      <c r="U14" s="71"/>
+      <c r="V14" s="71"/>
+      <c r="W14" s="71"/>
+      <c r="X14" s="71"/>
+      <c r="Y14" s="71"/>
+      <c r="Z14" s="71"/>
+      <c r="AA14" s="71"/>
+      <c r="AB14" s="71"/>
+      <c r="AC14" s="71"/>
+      <c r="AD14" s="71"/>
+      <c r="AE14" s="71"/>
+      <c r="AF14" s="71"/>
+      <c r="AG14" s="71"/>
+      <c r="AH14" s="74"/>
+      <c r="AI14" s="71"/>
+      <c r="AJ14" s="71"/>
+      <c r="AL14" s="71"/>
+      <c r="AM14" s="71"/>
+      <c r="AN14" s="71"/>
+      <c r="AO14" s="72"/>
+      <c r="AP14" s="71"/>
+      <c r="AQ14" s="71"/>
+      <c r="AR14" s="72"/>
+      <c r="AS14" s="72"/>
+      <c r="AT14" s="72"/>
+      <c r="AU14" s="71"/>
+      <c r="AV14" s="73"/>
+      <c r="AW14" s="71"/>
+      <c r="AX14" s="71"/>
+      <c r="AY14" s="71"/>
+      <c r="AZ14" s="71"/>
+      <c r="BA14" s="71"/>
+      <c r="BB14" s="71"/>
+      <c r="BC14" s="73"/>
+      <c r="BD14" s="71"/>
+      <c r="BE14" s="71"/>
+      <c r="BF14" s="71"/>
+      <c r="BG14" s="71"/>
+      <c r="BH14" s="71"/>
+      <c r="BI14" s="73"/>
+      <c r="BJ14" s="74"/>
+      <c r="BK14" s="62"/>
+      <c r="BL14" s="63"/>
+      <c r="BM14" s="64"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
@@ -5143,69 +5150,69 @@
       <c r="F15" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="G15" s="67" t="n">
+      <c r="G15" s="65" t="n">
         <f aca="false">Netzplan!J15</f>
         <v>1</v>
       </c>
-      <c r="H15" s="68" t="n">
+      <c r="H15" s="66" t="n">
         <f aca="false">SUM(I15:BJ15)</f>
         <v>0</v>
       </c>
-      <c r="I15" s="74"/>
-      <c r="J15" s="74"/>
-      <c r="K15" s="74"/>
-      <c r="L15" s="74"/>
-      <c r="M15" s="74"/>
-      <c r="N15" s="74"/>
-      <c r="O15" s="74"/>
-      <c r="P15" s="74"/>
-      <c r="Q15" s="74"/>
-      <c r="R15" s="74"/>
-      <c r="S15" s="76"/>
-      <c r="T15" s="74"/>
-      <c r="U15" s="74"/>
-      <c r="V15" s="74"/>
-      <c r="W15" s="74"/>
-      <c r="X15" s="74"/>
-      <c r="Y15" s="74"/>
-      <c r="Z15" s="74"/>
-      <c r="AA15" s="74"/>
-      <c r="AB15" s="74"/>
-      <c r="AC15" s="74"/>
-      <c r="AD15" s="74"/>
-      <c r="AE15" s="74"/>
-      <c r="AF15" s="74"/>
-      <c r="AG15" s="74"/>
-      <c r="AH15" s="74"/>
-      <c r="AI15" s="74"/>
-      <c r="AJ15" s="74"/>
-      <c r="AL15" s="74"/>
-      <c r="AM15" s="78"/>
-      <c r="AO15" s="74"/>
-      <c r="AP15" s="74"/>
-      <c r="AQ15" s="74"/>
-      <c r="AR15" s="78"/>
-      <c r="AS15" s="75"/>
-      <c r="AT15" s="74"/>
-      <c r="AU15" s="74"/>
-      <c r="AV15" s="77"/>
-      <c r="AW15" s="74"/>
-      <c r="AX15" s="74"/>
-      <c r="AY15" s="74"/>
-      <c r="AZ15" s="74"/>
-      <c r="BA15" s="74"/>
-      <c r="BB15" s="74"/>
-      <c r="BC15" s="77"/>
-      <c r="BD15" s="74"/>
-      <c r="BE15" s="74"/>
-      <c r="BF15" s="74"/>
-      <c r="BG15" s="74"/>
-      <c r="BH15" s="74"/>
-      <c r="BI15" s="77"/>
-      <c r="BJ15" s="78"/>
-      <c r="BK15" s="64"/>
-      <c r="BL15" s="65"/>
-      <c r="BM15" s="66"/>
+      <c r="I15" s="71"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="71"/>
+      <c r="L15" s="71"/>
+      <c r="M15" s="71"/>
+      <c r="N15" s="71"/>
+      <c r="O15" s="71"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="71"/>
+      <c r="S15" s="71"/>
+      <c r="T15" s="71"/>
+      <c r="U15" s="71"/>
+      <c r="V15" s="71"/>
+      <c r="W15" s="71"/>
+      <c r="X15" s="71"/>
+      <c r="Y15" s="71"/>
+      <c r="Z15" s="71"/>
+      <c r="AA15" s="71"/>
+      <c r="AB15" s="71"/>
+      <c r="AC15" s="71"/>
+      <c r="AD15" s="71"/>
+      <c r="AE15" s="71"/>
+      <c r="AF15" s="71"/>
+      <c r="AG15" s="71"/>
+      <c r="AH15" s="71"/>
+      <c r="AI15" s="71"/>
+      <c r="AJ15" s="71"/>
+      <c r="AL15" s="71"/>
+      <c r="AM15" s="74"/>
+      <c r="AO15" s="71"/>
+      <c r="AP15" s="71"/>
+      <c r="AQ15" s="71"/>
+      <c r="AR15" s="74"/>
+      <c r="AS15" s="72"/>
+      <c r="AT15" s="71"/>
+      <c r="AU15" s="71"/>
+      <c r="AV15" s="73"/>
+      <c r="AW15" s="71"/>
+      <c r="AX15" s="71"/>
+      <c r="AY15" s="71"/>
+      <c r="AZ15" s="71"/>
+      <c r="BA15" s="71"/>
+      <c r="BB15" s="71"/>
+      <c r="BC15" s="73"/>
+      <c r="BD15" s="71"/>
+      <c r="BE15" s="71"/>
+      <c r="BF15" s="71"/>
+      <c r="BG15" s="71"/>
+      <c r="BH15" s="71"/>
+      <c r="BI15" s="73"/>
+      <c r="BJ15" s="74"/>
+      <c r="BK15" s="62"/>
+      <c r="BL15" s="63"/>
+      <c r="BM15" s="64"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
@@ -5222,71 +5229,71 @@
       <c r="F16" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="G16" s="67" t="n">
+      <c r="G16" s="65" t="n">
         <f aca="false">Netzplan!J16</f>
         <v>4</v>
       </c>
-      <c r="H16" s="68" t="n">
+      <c r="H16" s="66" t="n">
         <f aca="false">SUM(I16:BJ16)</f>
         <v>0</v>
       </c>
-      <c r="I16" s="74"/>
-      <c r="J16" s="74"/>
-      <c r="K16" s="74"/>
-      <c r="L16" s="74"/>
-      <c r="M16" s="74"/>
-      <c r="N16" s="74"/>
-      <c r="O16" s="74"/>
-      <c r="P16" s="74"/>
-      <c r="Q16" s="74"/>
-      <c r="R16" s="74"/>
-      <c r="S16" s="76"/>
-      <c r="T16" s="74"/>
-      <c r="U16" s="74"/>
-      <c r="V16" s="74"/>
-      <c r="W16" s="74"/>
-      <c r="X16" s="74"/>
-      <c r="Y16" s="74"/>
-      <c r="Z16" s="74"/>
-      <c r="AA16" s="74"/>
-      <c r="AB16" s="74"/>
-      <c r="AC16" s="74"/>
-      <c r="AD16" s="74"/>
-      <c r="AE16" s="74"/>
-      <c r="AF16" s="74"/>
-      <c r="AG16" s="74"/>
-      <c r="AH16" s="74"/>
-      <c r="AI16" s="74"/>
-      <c r="AJ16" s="74"/>
-      <c r="AK16" s="74"/>
-      <c r="AL16" s="74"/>
-      <c r="AM16" s="78"/>
-      <c r="AN16" s="78"/>
-      <c r="AO16" s="78"/>
-      <c r="AP16" s="74"/>
-      <c r="AQ16" s="74"/>
-      <c r="AR16" s="74"/>
-      <c r="AS16" s="78"/>
-      <c r="AT16" s="74"/>
-      <c r="AU16" s="75"/>
-      <c r="AV16" s="77"/>
-      <c r="AW16" s="74"/>
-      <c r="AX16" s="74"/>
-      <c r="AY16" s="75"/>
-      <c r="AZ16" s="75"/>
-      <c r="BA16" s="75"/>
-      <c r="BB16" s="74"/>
-      <c r="BC16" s="77"/>
-      <c r="BD16" s="74"/>
-      <c r="BE16" s="74"/>
-      <c r="BF16" s="74"/>
-      <c r="BG16" s="74"/>
-      <c r="BH16" s="74"/>
-      <c r="BI16" s="77"/>
-      <c r="BJ16" s="78"/>
-      <c r="BK16" s="64"/>
-      <c r="BL16" s="65"/>
-      <c r="BM16" s="66"/>
+      <c r="I16" s="71"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="71"/>
+      <c r="L16" s="71"/>
+      <c r="M16" s="71"/>
+      <c r="N16" s="71"/>
+      <c r="O16" s="71"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="71"/>
+      <c r="S16" s="71"/>
+      <c r="T16" s="71"/>
+      <c r="U16" s="71"/>
+      <c r="V16" s="71"/>
+      <c r="W16" s="71"/>
+      <c r="X16" s="71"/>
+      <c r="Y16" s="71"/>
+      <c r="Z16" s="71"/>
+      <c r="AA16" s="71"/>
+      <c r="AB16" s="71"/>
+      <c r="AC16" s="71"/>
+      <c r="AD16" s="71"/>
+      <c r="AE16" s="71"/>
+      <c r="AF16" s="71"/>
+      <c r="AG16" s="71"/>
+      <c r="AH16" s="71"/>
+      <c r="AI16" s="71"/>
+      <c r="AJ16" s="71"/>
+      <c r="AK16" s="71"/>
+      <c r="AL16" s="71"/>
+      <c r="AM16" s="74"/>
+      <c r="AN16" s="74"/>
+      <c r="AO16" s="74"/>
+      <c r="AP16" s="71"/>
+      <c r="AQ16" s="71"/>
+      <c r="AR16" s="71"/>
+      <c r="AS16" s="74"/>
+      <c r="AT16" s="71"/>
+      <c r="AU16" s="72"/>
+      <c r="AV16" s="73"/>
+      <c r="AW16" s="71"/>
+      <c r="AX16" s="71"/>
+      <c r="AY16" s="72"/>
+      <c r="AZ16" s="72"/>
+      <c r="BA16" s="72"/>
+      <c r="BB16" s="71"/>
+      <c r="BC16" s="73"/>
+      <c r="BD16" s="71"/>
+      <c r="BE16" s="71"/>
+      <c r="BF16" s="71"/>
+      <c r="BG16" s="71"/>
+      <c r="BH16" s="71"/>
+      <c r="BI16" s="73"/>
+      <c r="BJ16" s="74"/>
+      <c r="BK16" s="62"/>
+      <c r="BL16" s="63"/>
+      <c r="BM16" s="64"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="17" t="s">
@@ -5301,71 +5308,71 @@
         <v>60</v>
       </c>
       <c r="F17" s="46"/>
-      <c r="G17" s="67" t="n">
+      <c r="G17" s="65" t="n">
         <f aca="false">Netzplan!J17</f>
         <v>1</v>
       </c>
-      <c r="H17" s="68" t="n">
+      <c r="H17" s="66" t="n">
         <f aca="false">SUM(I17:BJ17)</f>
         <v>0</v>
       </c>
-      <c r="I17" s="81"/>
-      <c r="J17" s="81"/>
-      <c r="K17" s="81"/>
-      <c r="L17" s="81"/>
-      <c r="M17" s="81"/>
-      <c r="N17" s="81"/>
-      <c r="O17" s="81"/>
-      <c r="P17" s="81"/>
-      <c r="Q17" s="81"/>
-      <c r="R17" s="81"/>
-      <c r="S17" s="82"/>
-      <c r="T17" s="81"/>
-      <c r="U17" s="81"/>
-      <c r="V17" s="81"/>
-      <c r="W17" s="81"/>
-      <c r="X17" s="81"/>
-      <c r="Y17" s="81"/>
-      <c r="Z17" s="81"/>
-      <c r="AA17" s="81"/>
-      <c r="AB17" s="81"/>
-      <c r="AC17" s="81"/>
-      <c r="AD17" s="81"/>
-      <c r="AE17" s="81"/>
-      <c r="AF17" s="81"/>
-      <c r="AG17" s="81"/>
-      <c r="AH17" s="81"/>
-      <c r="AI17" s="81"/>
-      <c r="AJ17" s="81"/>
-      <c r="AK17" s="81"/>
-      <c r="AL17" s="81"/>
-      <c r="AM17" s="81"/>
-      <c r="AN17" s="81"/>
-      <c r="AO17" s="81"/>
-      <c r="AP17" s="81"/>
-      <c r="AQ17" s="81"/>
-      <c r="AR17" s="81"/>
-      <c r="AS17" s="81"/>
-      <c r="AT17" s="81"/>
-      <c r="AU17" s="81"/>
-      <c r="AV17" s="83"/>
-      <c r="AW17" s="81"/>
-      <c r="AX17" s="81"/>
-      <c r="AY17" s="84"/>
-      <c r="AZ17" s="84"/>
-      <c r="BA17" s="81"/>
-      <c r="BB17" s="81"/>
-      <c r="BC17" s="83"/>
-      <c r="BD17" s="81"/>
-      <c r="BE17" s="81"/>
-      <c r="BF17" s="81"/>
-      <c r="BG17" s="81"/>
-      <c r="BH17" s="81"/>
-      <c r="BI17" s="83"/>
-      <c r="BJ17" s="85"/>
-      <c r="BK17" s="64"/>
-      <c r="BL17" s="65"/>
-      <c r="BM17" s="66"/>
+      <c r="I17" s="76"/>
+      <c r="J17" s="76"/>
+      <c r="K17" s="76"/>
+      <c r="L17" s="76"/>
+      <c r="M17" s="76"/>
+      <c r="N17" s="76"/>
+      <c r="O17" s="76"/>
+      <c r="P17" s="76"/>
+      <c r="Q17" s="76"/>
+      <c r="R17" s="76"/>
+      <c r="S17" s="76"/>
+      <c r="T17" s="76"/>
+      <c r="U17" s="76"/>
+      <c r="V17" s="76"/>
+      <c r="W17" s="76"/>
+      <c r="X17" s="76"/>
+      <c r="Y17" s="76"/>
+      <c r="Z17" s="76"/>
+      <c r="AA17" s="76"/>
+      <c r="AB17" s="76"/>
+      <c r="AC17" s="76"/>
+      <c r="AD17" s="76"/>
+      <c r="AE17" s="76"/>
+      <c r="AF17" s="76"/>
+      <c r="AG17" s="76"/>
+      <c r="AH17" s="76"/>
+      <c r="AI17" s="76"/>
+      <c r="AJ17" s="76"/>
+      <c r="AK17" s="76"/>
+      <c r="AL17" s="76"/>
+      <c r="AM17" s="76"/>
+      <c r="AN17" s="76"/>
+      <c r="AO17" s="76"/>
+      <c r="AP17" s="76"/>
+      <c r="AQ17" s="76"/>
+      <c r="AR17" s="76"/>
+      <c r="AS17" s="76"/>
+      <c r="AT17" s="76"/>
+      <c r="AU17" s="76"/>
+      <c r="AV17" s="77"/>
+      <c r="AW17" s="76"/>
+      <c r="AX17" s="76"/>
+      <c r="AY17" s="78"/>
+      <c r="AZ17" s="78"/>
+      <c r="BA17" s="76"/>
+      <c r="BB17" s="76"/>
+      <c r="BC17" s="77"/>
+      <c r="BD17" s="76"/>
+      <c r="BE17" s="76"/>
+      <c r="BF17" s="76"/>
+      <c r="BG17" s="76"/>
+      <c r="BH17" s="76"/>
+      <c r="BI17" s="77"/>
+      <c r="BJ17" s="79"/>
+      <c r="BK17" s="62"/>
+      <c r="BL17" s="63"/>
+      <c r="BM17" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="17">

--- a/Übungen/Online_Shop.xlsx
+++ b/Übungen/Online_Shop.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="PSP" sheetId="1" state="visible" r:id="rId2"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="79">
   <si>
     <t xml:space="preserve">Beispiel: Funktionsorientierter Projektstrukturplan</t>
   </si>
@@ -257,6 +257,9 @@
   </si>
   <si>
     <t xml:space="preserve">FAZ + D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gantt</t>
   </si>
 </sst>
 </file>
@@ -528,7 +531,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="81">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -830,6 +833,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3888,11 +3895,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM17"/>
+  <dimension ref="A1:BM20"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="1"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="5" min="5" style="0" width="16.2"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="6" min="6" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="1" max="5" min="5" style="0" width="16.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="1" max="6" min="6" style="0" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11.59"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="1" max="8" min="8" style="0" width="3.59"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="62" min="9" style="0" width="3.59"/>
@@ -4106,10 +4113,14 @@
       </c>
       <c r="H2" s="66" t="n">
         <f aca="false">SUM(I2:BJ2)</f>
-        <v>0</v>
-      </c>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
+        <v>2</v>
+      </c>
+      <c r="I2" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" s="67" t="n">
+        <v>1</v>
+      </c>
       <c r="K2" s="67"/>
       <c r="L2" s="67"/>
       <c r="M2" s="67"/>
@@ -4187,11 +4198,13 @@
       </c>
       <c r="H3" s="66" t="n">
         <f aca="false">SUM(I3:BJ3)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="71"/>
       <c r="J3" s="71"/>
-      <c r="K3" s="71"/>
+      <c r="K3" s="71" t="n">
+        <v>1</v>
+      </c>
       <c r="L3" s="71"/>
       <c r="M3" s="71"/>
       <c r="N3" s="71"/>
@@ -4268,19 +4281,31 @@
       </c>
       <c r="H4" s="66" t="n">
         <f aca="false">SUM(I4:BJ4)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I4" s="71"/>
       <c r="J4" s="71"/>
       <c r="K4" s="71"/>
-      <c r="L4" s="71"/>
-      <c r="M4" s="71"/>
+      <c r="L4" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="71" t="n">
+        <v>1</v>
+      </c>
       <c r="N4" s="71"/>
       <c r="O4" s="71"/>
-      <c r="P4" s="71"/>
-      <c r="Q4" s="72"/>
-      <c r="R4" s="72"/>
-      <c r="S4" s="75"/>
+      <c r="P4" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" s="72" t="n">
+        <v>1</v>
+      </c>
       <c r="T4" s="72"/>
       <c r="U4" s="71"/>
       <c r="V4" s="71"/>
@@ -4349,13 +4374,17 @@
       </c>
       <c r="H5" s="66" t="n">
         <f aca="false">SUM(I5:BJ5)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" s="71"/>
       <c r="J5" s="71"/>
       <c r="K5" s="71"/>
-      <c r="L5" s="71"/>
-      <c r="M5" s="71"/>
+      <c r="L5" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="72" t="n">
+        <v>1</v>
+      </c>
       <c r="N5" s="71"/>
       <c r="O5" s="71"/>
       <c r="P5" s="71"/>
@@ -4430,7 +4459,7 @@
       </c>
       <c r="H6" s="66" t="n">
         <f aca="false">SUM(I6:BJ6)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I6" s="71"/>
       <c r="J6" s="71"/>
@@ -4439,10 +4468,18 @@
       <c r="M6" s="71"/>
       <c r="N6" s="71"/>
       <c r="O6" s="71"/>
-      <c r="P6" s="71"/>
-      <c r="Q6" s="71"/>
-      <c r="R6" s="71"/>
-      <c r="S6" s="71"/>
+      <c r="P6" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" s="72" t="n">
+        <v>1</v>
+      </c>
       <c r="T6" s="72"/>
       <c r="U6" s="71"/>
       <c r="V6" s="71"/>
@@ -4511,11 +4548,13 @@
       </c>
       <c r="H7" s="66" t="n">
         <f aca="false">SUM(I7:BJ7)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="71"/>
       <c r="J7" s="71"/>
-      <c r="K7" s="71"/>
+      <c r="K7" s="71" t="n">
+        <v>1</v>
+      </c>
       <c r="L7" s="71"/>
       <c r="M7" s="71"/>
       <c r="N7" s="71"/>
@@ -4592,19 +4631,31 @@
       </c>
       <c r="H8" s="66" t="n">
         <f aca="false">SUM(I8:BJ8)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I8" s="71"/>
       <c r="J8" s="71"/>
       <c r="K8" s="71"/>
-      <c r="L8" s="71"/>
-      <c r="M8" s="71"/>
+      <c r="L8" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" s="72" t="n">
+        <v>1</v>
+      </c>
       <c r="N8" s="71"/>
       <c r="O8" s="71"/>
-      <c r="P8" s="71"/>
-      <c r="Q8" s="72"/>
-      <c r="R8" s="72"/>
-      <c r="S8" s="75"/>
+      <c r="P8" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" s="72" t="n">
+        <v>1</v>
+      </c>
       <c r="T8" s="71"/>
       <c r="U8" s="71"/>
       <c r="V8" s="71"/>
@@ -4673,7 +4724,7 @@
       </c>
       <c r="H9" s="66" t="n">
         <f aca="false">SUM(I9:BJ9)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" s="71"/>
       <c r="J9" s="71"/>
@@ -4686,10 +4737,14 @@
       <c r="Q9" s="71"/>
       <c r="R9" s="71"/>
       <c r="S9" s="71"/>
-      <c r="T9" s="71"/>
+      <c r="T9" s="72" t="n">
+        <v>1</v>
+      </c>
       <c r="U9" s="71"/>
       <c r="V9" s="71"/>
-      <c r="W9" s="72"/>
+      <c r="W9" s="72" t="n">
+        <v>1</v>
+      </c>
       <c r="X9" s="72"/>
       <c r="Y9" s="72"/>
       <c r="Z9" s="72"/>
@@ -4754,7 +4809,7 @@
       </c>
       <c r="H10" s="66" t="n">
         <f aca="false">SUM(I10:BJ10)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10" s="71"/>
       <c r="J10" s="71"/>
@@ -4771,8 +4826,12 @@
       <c r="U10" s="71"/>
       <c r="V10" s="71"/>
       <c r="W10" s="71"/>
-      <c r="X10" s="71"/>
-      <c r="Y10" s="71"/>
+      <c r="X10" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="72" t="n">
+        <v>1</v>
+      </c>
       <c r="Z10" s="71"/>
       <c r="AA10" s="71"/>
       <c r="AB10" s="71"/>
@@ -4834,7 +4893,7 @@
       </c>
       <c r="H11" s="66" t="n">
         <f aca="false">SUM(I11:BJ11)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" s="71"/>
       <c r="J11" s="71"/>
@@ -4853,8 +4912,12 @@
       <c r="W11" s="71"/>
       <c r="X11" s="71"/>
       <c r="Y11" s="71"/>
-      <c r="Z11" s="71"/>
-      <c r="AA11" s="71"/>
+      <c r="Z11" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="72" t="n">
+        <v>1</v>
+      </c>
       <c r="AB11" s="71"/>
       <c r="AC11" s="71"/>
       <c r="AE11" s="74"/>
@@ -4914,7 +4977,7 @@
       </c>
       <c r="H12" s="66" t="n">
         <f aca="false">SUM(I12:BJ12)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I12" s="71"/>
       <c r="J12" s="71"/>
@@ -4927,35 +4990,75 @@
       <c r="Q12" s="71"/>
       <c r="R12" s="71"/>
       <c r="S12" s="71"/>
-      <c r="T12" s="72"/>
+      <c r="T12" s="72" t="n">
+        <v>1</v>
+      </c>
       <c r="U12" s="71"/>
       <c r="V12" s="71"/>
-      <c r="W12" s="72"/>
-      <c r="X12" s="72"/>
-      <c r="Y12" s="72"/>
-      <c r="Z12" s="72"/>
-      <c r="AA12" s="75"/>
+      <c r="W12" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="72" t="n">
+        <v>1</v>
+      </c>
       <c r="AB12" s="71"/>
       <c r="AC12" s="71"/>
-      <c r="AD12" s="72"/>
-      <c r="AE12" s="72"/>
-      <c r="AF12" s="72"/>
-      <c r="AG12" s="72"/>
-      <c r="AH12" s="72"/>
+      <c r="AD12" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE12" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF12" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG12" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH12" s="72" t="n">
+        <v>1</v>
+      </c>
       <c r="AI12" s="71"/>
       <c r="AJ12" s="71"/>
-      <c r="AK12" s="72"/>
-      <c r="AL12" s="72"/>
-      <c r="AM12" s="72"/>
-      <c r="AN12" s="72"/>
-      <c r="AO12" s="72"/>
+      <c r="AK12" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL12" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM12" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN12" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO12" s="72" t="n">
+        <v>1</v>
+      </c>
       <c r="AP12" s="71"/>
       <c r="AQ12" s="71"/>
-      <c r="AR12" s="72"/>
-      <c r="AS12" s="72"/>
-      <c r="AT12" s="72"/>
-      <c r="AU12" s="72"/>
-      <c r="AV12" s="73"/>
+      <c r="AR12" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS12" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT12" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU12" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV12" s="76"/>
       <c r="AW12" s="71"/>
       <c r="AX12" s="71"/>
       <c r="AY12" s="72"/>
@@ -4995,7 +5098,7 @@
       </c>
       <c r="H13" s="66" t="n">
         <f aca="false">SUM(I13:BJ13)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13" s="71"/>
       <c r="J13" s="71"/>
@@ -5018,8 +5121,12 @@
       <c r="AA13" s="71"/>
       <c r="AB13" s="71"/>
       <c r="AC13" s="71"/>
-      <c r="AD13" s="71"/>
-      <c r="AE13" s="71"/>
+      <c r="AD13" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE13" s="72" t="n">
+        <v>1</v>
+      </c>
       <c r="AF13" s="74"/>
       <c r="AG13" s="71"/>
       <c r="AH13" s="71"/>
@@ -5076,7 +5183,7 @@
       </c>
       <c r="H14" s="66" t="n">
         <f aca="false">SUM(I14:BJ14)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" s="71"/>
       <c r="J14" s="71"/>
@@ -5101,8 +5208,12 @@
       <c r="AC14" s="71"/>
       <c r="AD14" s="71"/>
       <c r="AE14" s="71"/>
-      <c r="AF14" s="71"/>
-      <c r="AG14" s="71"/>
+      <c r="AF14" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG14" s="71" t="n">
+        <v>1</v>
+      </c>
       <c r="AH14" s="74"/>
       <c r="AI14" s="71"/>
       <c r="AJ14" s="71"/>
@@ -5156,7 +5267,7 @@
       </c>
       <c r="H15" s="66" t="n">
         <f aca="false">SUM(I15:BJ15)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="71"/>
       <c r="J15" s="71"/>
@@ -5183,7 +5294,9 @@
       <c r="AE15" s="71"/>
       <c r="AF15" s="71"/>
       <c r="AG15" s="71"/>
-      <c r="AH15" s="71"/>
+      <c r="AH15" s="71" t="n">
+        <v>1</v>
+      </c>
       <c r="AI15" s="71"/>
       <c r="AJ15" s="71"/>
       <c r="AL15" s="71"/>
@@ -5235,7 +5348,7 @@
       </c>
       <c r="H16" s="66" t="n">
         <f aca="false">SUM(I16:BJ16)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I16" s="71"/>
       <c r="J16" s="71"/>
@@ -5265,10 +5378,18 @@
       <c r="AH16" s="71"/>
       <c r="AI16" s="71"/>
       <c r="AJ16" s="71"/>
-      <c r="AK16" s="71"/>
-      <c r="AL16" s="71"/>
-      <c r="AM16" s="74"/>
-      <c r="AN16" s="74"/>
+      <c r="AK16" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL16" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM16" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN16" s="74" t="n">
+        <v>1</v>
+      </c>
       <c r="AO16" s="74"/>
       <c r="AP16" s="71"/>
       <c r="AQ16" s="71"/>
@@ -5314,65 +5435,72 @@
       </c>
       <c r="H17" s="66" t="n">
         <f aca="false">SUM(I17:BJ17)</f>
-        <v>0</v>
-      </c>
-      <c r="I17" s="76"/>
-      <c r="J17" s="76"/>
-      <c r="K17" s="76"/>
-      <c r="L17" s="76"/>
-      <c r="M17" s="76"/>
-      <c r="N17" s="76"/>
-      <c r="O17" s="76"/>
-      <c r="P17" s="76"/>
-      <c r="Q17" s="76"/>
-      <c r="R17" s="76"/>
-      <c r="S17" s="76"/>
-      <c r="T17" s="76"/>
-      <c r="U17" s="76"/>
-      <c r="V17" s="76"/>
-      <c r="W17" s="76"/>
-      <c r="X17" s="76"/>
-      <c r="Y17" s="76"/>
-      <c r="Z17" s="76"/>
-      <c r="AA17" s="76"/>
-      <c r="AB17" s="76"/>
-      <c r="AC17" s="76"/>
-      <c r="AD17" s="76"/>
-      <c r="AE17" s="76"/>
-      <c r="AF17" s="76"/>
-      <c r="AG17" s="76"/>
-      <c r="AH17" s="76"/>
-      <c r="AI17" s="76"/>
-      <c r="AJ17" s="76"/>
-      <c r="AK17" s="76"/>
-      <c r="AL17" s="76"/>
-      <c r="AM17" s="76"/>
-      <c r="AN17" s="76"/>
-      <c r="AO17" s="76"/>
-      <c r="AP17" s="76"/>
-      <c r="AQ17" s="76"/>
-      <c r="AR17" s="76"/>
-      <c r="AS17" s="76"/>
-      <c r="AT17" s="76"/>
-      <c r="AU17" s="76"/>
-      <c r="AV17" s="77"/>
-      <c r="AW17" s="76"/>
-      <c r="AX17" s="76"/>
-      <c r="AY17" s="78"/>
-      <c r="AZ17" s="78"/>
-      <c r="BA17" s="76"/>
-      <c r="BB17" s="76"/>
-      <c r="BC17" s="77"/>
-      <c r="BD17" s="76"/>
-      <c r="BE17" s="76"/>
-      <c r="BF17" s="76"/>
-      <c r="BG17" s="76"/>
-      <c r="BH17" s="76"/>
-      <c r="BI17" s="77"/>
-      <c r="BJ17" s="79"/>
+        <v>1</v>
+      </c>
+      <c r="I17" s="77"/>
+      <c r="J17" s="77"/>
+      <c r="K17" s="77"/>
+      <c r="L17" s="77"/>
+      <c r="M17" s="77"/>
+      <c r="N17" s="77"/>
+      <c r="O17" s="77"/>
+      <c r="P17" s="77"/>
+      <c r="Q17" s="77"/>
+      <c r="R17" s="77"/>
+      <c r="S17" s="77"/>
+      <c r="T17" s="77"/>
+      <c r="U17" s="77"/>
+      <c r="V17" s="77"/>
+      <c r="W17" s="77"/>
+      <c r="X17" s="77"/>
+      <c r="Y17" s="77"/>
+      <c r="Z17" s="77"/>
+      <c r="AA17" s="77"/>
+      <c r="AB17" s="77"/>
+      <c r="AC17" s="77"/>
+      <c r="AD17" s="77"/>
+      <c r="AE17" s="77"/>
+      <c r="AF17" s="77"/>
+      <c r="AG17" s="77"/>
+      <c r="AH17" s="77"/>
+      <c r="AI17" s="77"/>
+      <c r="AJ17" s="77"/>
+      <c r="AK17" s="77"/>
+      <c r="AL17" s="77"/>
+      <c r="AM17" s="77"/>
+      <c r="AN17" s="77"/>
+      <c r="AO17" s="77"/>
+      <c r="AP17" s="77"/>
+      <c r="AQ17" s="77"/>
+      <c r="AR17" s="77"/>
+      <c r="AS17" s="77"/>
+      <c r="AT17" s="77"/>
+      <c r="AU17" s="77"/>
+      <c r="AV17" s="78"/>
+      <c r="AW17" s="77"/>
+      <c r="AX17" s="77"/>
+      <c r="AY17" s="79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ17" s="79"/>
+      <c r="BA17" s="77"/>
+      <c r="BB17" s="77"/>
+      <c r="BC17" s="78"/>
+      <c r="BD17" s="77"/>
+      <c r="BE17" s="77"/>
+      <c r="BF17" s="77"/>
+      <c r="BG17" s="77"/>
+      <c r="BH17" s="77"/>
+      <c r="BI17" s="78"/>
+      <c r="BJ17" s="80"/>
       <c r="BK17" s="62"/>
       <c r="BL17" s="63"/>
       <c r="BM17" s="64"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
+        <v>78</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -5394,7 +5522,7 @@
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B17:D17"/>
   </mergeCells>
-  <conditionalFormatting sqref="I1:BF9 I12:BF13 I10:AC11 AE10:BF11 I16:BF17 I14:AJ15 AL14:BF14 AL15:AM15 AO15:BF15">
+  <conditionalFormatting sqref="I13:BF13 I10:AC12 AE10:BF11 I16:BF17 I14:AJ15 AL14:BF14 AL15:AM15 AO15:BF15 I1:BF9 AD12:BF12">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>IF(OR(WEEKDAY(I$1)=7,WEEKDAY(I$1)=1),1,0)</formula>
     </cfRule>
@@ -5404,7 +5532,7 @@
       <formula>IF(H2&lt;&gt;G2,TRUE())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:BF9 I12:BF13 I10:AC11 AE10:BF11 I16:BF17 I14:AJ15 AL14:BF14 AL15:AM15 AO15:BF15">
+  <conditionalFormatting sqref="I13:BF13 I10:AC12 AE10:BF11 I16:BF17 I14:AJ15 AL14:BF14 AL15:AM15 AO15:BF15 I2:BF9 AD12:BF12">
     <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>1</formula>
     </cfRule>

--- a/Übungen/Online_Shop.xlsx
+++ b/Übungen/Online_Shop.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="81">
   <si>
     <t xml:space="preserve">Beispiel: Funktionsorientierter Projektstrukturplan</t>
   </si>
@@ -257,6 +257,12 @@
   </si>
   <si>
     <t xml:space="preserve">FAZ + D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Datenbankvorbereitung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Testphase</t>
   </si>
   <si>
     <t xml:space="preserve">Gantt</t>
@@ -1006,8 +1012,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="5504400" y="479520"/>
-          <a:ext cx="5572080" cy="0"/>
+          <a:off x="5506920" y="479520"/>
+          <a:ext cx="5576400" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -1048,7 +1054,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5503320" y="488160"/>
+          <a:off x="5505840" y="488160"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1089,7 +1095,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5502600" y="488160"/>
+          <a:off x="5505120" y="488160"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1131,7 +1137,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5520600" y="1125360"/>
+          <a:off x="5523840" y="1125360"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1173,7 +1179,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5520600" y="1612800"/>
+          <a:off x="5523840" y="1612800"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1215,7 +1221,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5520600" y="2099880"/>
+          <a:off x="5523840" y="2099880"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1257,7 +1263,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5520600" y="2587320"/>
+          <a:off x="5523840" y="2587320"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1299,7 +1305,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8292240" y="324720"/>
+          <a:off x="8297280" y="324720"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1341,7 +1347,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8292240" y="487440"/>
+          <a:off x="8297280" y="487440"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1383,7 +1389,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8292240" y="1125360"/>
+          <a:off x="8297280" y="1125360"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1425,7 +1431,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8292240" y="1612800"/>
+          <a:off x="8297280" y="1612800"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1467,7 +1473,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8292240" y="2587320"/>
+          <a:off x="8297280" y="2587320"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1509,7 +1515,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8292240" y="3074400"/>
+          <a:off x="8297280" y="3074400"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1551,7 +1557,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8292240" y="4048920"/>
+          <a:off x="8297280" y="4048920"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1593,7 +1599,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8292240" y="5023440"/>
+          <a:off x="8297280" y="5023440"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1635,7 +1641,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11064600" y="487440"/>
+          <a:off x="11071440" y="487440"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1677,7 +1683,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11064600" y="1125360"/>
+          <a:off x="11071440" y="1125360"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1719,7 +1725,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11064600" y="1612800"/>
+          <a:off x="11071440" y="1612800"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1761,7 +1767,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11064600" y="2099880"/>
+          <a:off x="11071440" y="2099880"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1803,7 +1809,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8279640" y="3557520"/>
+          <a:off x="8283960" y="3557520"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1845,7 +1851,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8279640" y="4533480"/>
+          <a:off x="8283960" y="4533480"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1887,7 +1893,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8279640" y="2093760"/>
+          <a:off x="8283960" y="2093760"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1913,7 +1919,276 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>81720</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>143640</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>199080</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>151920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6995880" y="1630080"/>
+          <a:ext cx="117360" cy="170640"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:rect l="l" t="t" r="r" b="b"/>
+          <a:pathLst>
+            <a:path w="21600" h="21600">
+              <a:moveTo>
+                <a:pt x="10800" y="0"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="21600" y="10800"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="10800" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="0" y="10800"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="10800" y="0"/>
+              </a:lnTo>
+              <a:close/>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="729fcf"/>
+        </a:solidFill>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>11880</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>7200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>129240</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>15120</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9713160" y="2468880"/>
+          <a:ext cx="117360" cy="170640"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:rect l="l" t="t" r="r" b="b"/>
+          <a:pathLst>
+            <a:path w="21600" h="21600">
+              <a:moveTo>
+                <a:pt x="10800" y="0"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="21600" y="10800"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="10800" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="0" y="10800"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="10800" y="0"/>
+              </a:lnTo>
+              <a:close/>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="729fcf"/>
+        </a:solidFill>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>44640</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>2880</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>162000</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>10080</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11773080" y="2953440"/>
+          <a:ext cx="117360" cy="170640"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:rect l="l" t="t" r="r" b="b"/>
+          <a:pathLst>
+            <a:path w="21600" h="21600">
+              <a:moveTo>
+                <a:pt x="10800" y="0"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="21600" y="10800"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="10800" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="0" y="10800"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="10800" y="0"/>
+              </a:lnTo>
+              <a:close/>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="729fcf"/>
+        </a:solidFill>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>50</xdr:col>
+      <xdr:colOff>76320</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>-360</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>50</xdr:col>
+      <xdr:colOff>193680</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>7920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14844960" y="3276720"/>
+          <a:ext cx="117360" cy="170640"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:rect l="l" t="t" r="r" b="b"/>
+          <a:pathLst>
+            <a:path w="21600" h="21600">
+              <a:moveTo>
+                <a:pt x="10800" y="0"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="21600" y="10800"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="10800" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="0" y="10800"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="10800" y="0"/>
+              </a:lnTo>
+              <a:close/>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="729fcf"/>
+        </a:solidFill>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1922,7 +2197,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M41"/>
-  <sheetFormatPr defaultColWidth="13.109375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="13.12109375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.77"/>
   </cols>
@@ -2464,13 +2739,13 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:BW35"/>
-  <sheetFormatPr defaultColWidth="11.859375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="11.875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="1"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="1" max="2" min="2" style="20" width="11.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="1" max="3" min="3" style="0" width="13.52"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="1" max="4" min="4" style="0" width="11.81"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="1" max="5" min="5" style="3" width="16.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="1" max="6" min="6" style="3" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="2" min="2" style="20" width="11.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="3" min="3" style="0" width="13.52"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="1" max="4" min="4" style="0" width="11.81"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="5" min="5" style="3" width="16.12"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="6" min="6" style="3" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="3" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="21" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="3" width="11.52"/>
@@ -3886,7 +4161,6 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>
   </headerFooter>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3895,13 +4169,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM20"/>
-  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="1"/>
+  <dimension ref="A1:BM22"/>
+  <sheetFormatPr defaultColWidth="11.7421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="1"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="1" max="5" min="5" style="0" width="16.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="1" max="6" min="6" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="5" min="5" style="0" width="16.2"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="6" min="6" style="0" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11.59"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="1" max="8" min="8" style="0" width="3.59"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="8" min="8" style="0" width="3.59"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="62" min="9" style="0" width="3.59"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="63" min="63" style="0" width="7.65"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="64" style="0" width="8.52"/>
@@ -4704,54 +4978,38 @@
       <c r="BM8" s="64"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="F9" s="41" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="65" t="n">
-        <f aca="false">Netzplan!J9</f>
-        <v>2</v>
-      </c>
-      <c r="H9" s="66" t="n">
-        <f aca="false">SUM(I9:BJ9)</f>
-        <v>2</v>
-      </c>
+      <c r="A9" s="14"/>
+      <c r="B9" s="42" t="s">
+        <v>78</v>
+      </c>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="65"/>
+      <c r="H9" s="66"/>
       <c r="I9" s="71"/>
       <c r="J9" s="71"/>
       <c r="K9" s="71"/>
-      <c r="L9" s="71"/>
-      <c r="M9" s="71"/>
+      <c r="L9" s="72"/>
+      <c r="M9" s="72"/>
       <c r="N9" s="71"/>
       <c r="O9" s="71"/>
-      <c r="P9" s="71"/>
-      <c r="Q9" s="71"/>
-      <c r="R9" s="71"/>
-      <c r="S9" s="71"/>
-      <c r="T9" s="72" t="n">
-        <v>1</v>
-      </c>
+      <c r="P9" s="72"/>
+      <c r="Q9" s="72"/>
+      <c r="R9" s="72"/>
+      <c r="S9" s="72"/>
+      <c r="T9" s="71"/>
       <c r="U9" s="71"/>
       <c r="V9" s="71"/>
-      <c r="W9" s="72" t="n">
-        <v>1</v>
-      </c>
-      <c r="X9" s="72"/>
-      <c r="Y9" s="72"/>
-      <c r="Z9" s="72"/>
-      <c r="AA9" s="74"/>
+      <c r="W9" s="71"/>
+      <c r="X9" s="71"/>
+      <c r="Y9" s="71"/>
+      <c r="Z9" s="71"/>
+      <c r="AA9" s="71"/>
       <c r="AB9" s="71"/>
       <c r="AC9" s="71"/>
-      <c r="AD9" s="72"/>
+      <c r="AD9" s="71"/>
       <c r="AE9" s="71"/>
       <c r="AF9" s="71"/>
       <c r="AG9" s="71"/>
@@ -4790,21 +5048,21 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C10" s="15"/>
       <c r="D10" s="15"/>
       <c r="E10" s="41" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="F10" s="41" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G10" s="65" t="n">
-        <f aca="false">Netzplan!J10</f>
+        <f aca="false">Netzplan!J9</f>
         <v>2</v>
       </c>
       <c r="H10" s="66" t="n">
@@ -4822,21 +5080,22 @@
       <c r="Q10" s="71"/>
       <c r="R10" s="71"/>
       <c r="S10" s="71"/>
-      <c r="T10" s="71"/>
+      <c r="T10" s="72" t="n">
+        <v>1</v>
+      </c>
       <c r="U10" s="71"/>
       <c r="V10" s="71"/>
-      <c r="W10" s="71"/>
-      <c r="X10" s="72" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y10" s="72" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z10" s="71"/>
-      <c r="AA10" s="71"/>
+      <c r="W10" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" s="72"/>
+      <c r="Y10" s="72"/>
+      <c r="Z10" s="72"/>
+      <c r="AA10" s="74"/>
       <c r="AB10" s="71"/>
       <c r="AC10" s="71"/>
-      <c r="AE10" s="74"/>
+      <c r="AD10" s="72"/>
+      <c r="AE10" s="71"/>
       <c r="AF10" s="71"/>
       <c r="AG10" s="71"/>
       <c r="AH10" s="71"/>
@@ -4874,21 +5133,21 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C11" s="15"/>
       <c r="D11" s="15"/>
       <c r="E11" s="41" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F11" s="41" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="G11" s="65" t="n">
-        <f aca="false">Netzplan!J11</f>
+        <f aca="false">Netzplan!J10</f>
         <v>2</v>
       </c>
       <c r="H11" s="66" t="n">
@@ -4910,20 +5169,20 @@
       <c r="U11" s="71"/>
       <c r="V11" s="71"/>
       <c r="W11" s="71"/>
-      <c r="X11" s="71"/>
-      <c r="Y11" s="71"/>
-      <c r="Z11" s="72" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA11" s="72" t="n">
-        <v>1</v>
-      </c>
+      <c r="X11" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="71"/>
+      <c r="AA11" s="71"/>
       <c r="AB11" s="71"/>
       <c r="AC11" s="71"/>
       <c r="AE11" s="74"/>
       <c r="AF11" s="71"/>
-      <c r="AG11" s="72"/>
-      <c r="AH11" s="72"/>
+      <c r="AG11" s="71"/>
+      <c r="AH11" s="71"/>
       <c r="AI11" s="71"/>
       <c r="AJ11" s="71"/>
       <c r="AK11" s="71"/>
@@ -4958,26 +5217,26 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="C12" s="15"/>
       <c r="D12" s="15"/>
       <c r="E12" s="41" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F12" s="41" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="G12" s="65" t="n">
-        <f aca="false">Netzplan!J12</f>
-        <v>20</v>
+        <f aca="false">Netzplan!J11</f>
+        <v>2</v>
       </c>
       <c r="H12" s="66" t="n">
         <f aca="false">SUM(I12:BJ12)</f>
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="I12" s="71"/>
       <c r="J12" s="71"/>
@@ -4990,20 +5249,12 @@
       <c r="Q12" s="71"/>
       <c r="R12" s="71"/>
       <c r="S12" s="71"/>
-      <c r="T12" s="72" t="n">
-        <v>1</v>
-      </c>
+      <c r="T12" s="71"/>
       <c r="U12" s="71"/>
       <c r="V12" s="71"/>
-      <c r="W12" s="72" t="n">
-        <v>1</v>
-      </c>
-      <c r="X12" s="72" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y12" s="72" t="n">
-        <v>1</v>
-      </c>
+      <c r="W12" s="71"/>
+      <c r="X12" s="71"/>
+      <c r="Y12" s="71"/>
       <c r="Z12" s="72" t="n">
         <v>1</v>
       </c>
@@ -5012,59 +5263,30 @@
       </c>
       <c r="AB12" s="71"/>
       <c r="AC12" s="71"/>
-      <c r="AD12" s="72" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE12" s="72" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF12" s="72" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG12" s="72" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH12" s="72" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE12" s="74"/>
+      <c r="AF12" s="71"/>
+      <c r="AG12" s="72"/>
+      <c r="AH12" s="72"/>
       <c r="AI12" s="71"/>
       <c r="AJ12" s="71"/>
-      <c r="AK12" s="72" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL12" s="72" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM12" s="72" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN12" s="72" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO12" s="72" t="n">
-        <v>1</v>
-      </c>
+      <c r="AK12" s="71"/>
+      <c r="AL12" s="71"/>
+      <c r="AM12" s="71"/>
+      <c r="AN12" s="71"/>
+      <c r="AO12" s="71"/>
       <c r="AP12" s="71"/>
       <c r="AQ12" s="71"/>
-      <c r="AR12" s="72" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS12" s="72" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT12" s="72" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU12" s="72" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV12" s="76"/>
+      <c r="AR12" s="71"/>
+      <c r="AS12" s="71"/>
+      <c r="AT12" s="71"/>
+      <c r="AU12" s="71"/>
+      <c r="AV12" s="73"/>
       <c r="AW12" s="71"/>
       <c r="AX12" s="71"/>
-      <c r="AY12" s="72"/>
-      <c r="AZ12" s="72"/>
-      <c r="BA12" s="72"/>
-      <c r="BB12" s="72"/>
+      <c r="AY12" s="71"/>
+      <c r="AZ12" s="71"/>
+      <c r="BA12" s="71"/>
+      <c r="BB12" s="71"/>
       <c r="BC12" s="73"/>
       <c r="BD12" s="71"/>
       <c r="BE12" s="71"/>
@@ -5079,26 +5301,26 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="C13" s="15"/>
       <c r="D13" s="15"/>
       <c r="E13" s="41" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="F13" s="41" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G13" s="65" t="n">
-        <f aca="false">Netzplan!J13</f>
-        <v>2</v>
+        <f aca="false">Netzplan!J12</f>
+        <v>20</v>
       </c>
       <c r="H13" s="66" t="n">
         <f aca="false">SUM(I13:BJ13)</f>
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="I13" s="71"/>
       <c r="J13" s="71"/>
@@ -5111,14 +5333,26 @@
       <c r="Q13" s="71"/>
       <c r="R13" s="71"/>
       <c r="S13" s="71"/>
-      <c r="T13" s="71"/>
+      <c r="T13" s="72" t="n">
+        <v>1</v>
+      </c>
       <c r="U13" s="71"/>
       <c r="V13" s="71"/>
-      <c r="W13" s="71"/>
-      <c r="X13" s="71"/>
-      <c r="Y13" s="71"/>
-      <c r="Z13" s="71"/>
-      <c r="AA13" s="71"/>
+      <c r="W13" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA13" s="72" t="n">
+        <v>1</v>
+      </c>
       <c r="AB13" s="71"/>
       <c r="AC13" s="71"/>
       <c r="AD13" s="72" t="n">
@@ -5127,29 +5361,53 @@
       <c r="AE13" s="72" t="n">
         <v>1</v>
       </c>
-      <c r="AF13" s="74"/>
-      <c r="AG13" s="71"/>
-      <c r="AH13" s="71"/>
+      <c r="AF13" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG13" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH13" s="72" t="n">
+        <v>1</v>
+      </c>
       <c r="AI13" s="71"/>
       <c r="AJ13" s="71"/>
-      <c r="AK13" s="72"/>
-      <c r="AL13" s="72"/>
-      <c r="AM13" s="72"/>
-      <c r="AN13" s="72"/>
-      <c r="AO13" s="72"/>
+      <c r="AK13" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL13" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM13" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN13" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO13" s="72" t="n">
+        <v>1</v>
+      </c>
       <c r="AP13" s="71"/>
       <c r="AQ13" s="71"/>
-      <c r="AR13" s="71"/>
-      <c r="AS13" s="71"/>
-      <c r="AT13" s="71"/>
-      <c r="AU13" s="71"/>
-      <c r="AV13" s="73"/>
+      <c r="AR13" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS13" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT13" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU13" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV13" s="76"/>
       <c r="AW13" s="71"/>
       <c r="AX13" s="71"/>
-      <c r="AY13" s="71"/>
-      <c r="AZ13" s="71"/>
-      <c r="BA13" s="71"/>
-      <c r="BB13" s="71"/>
+      <c r="AY13" s="72"/>
+      <c r="AZ13" s="72"/>
+      <c r="BA13" s="72"/>
+      <c r="BB13" s="72"/>
       <c r="BC13" s="73"/>
       <c r="BD13" s="71"/>
       <c r="BE13" s="71"/>
@@ -5163,28 +5421,16 @@
       <c r="BM13" s="64"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="F14" s="41" t="s">
-        <v>29</v>
-      </c>
-      <c r="G14" s="65" t="n">
-        <f aca="false">Netzplan!J14</f>
-        <v>2</v>
-      </c>
-      <c r="H14" s="66" t="n">
-        <f aca="false">SUM(I14:BJ14)</f>
-        <v>2</v>
-      </c>
+      <c r="A14" s="14"/>
+      <c r="B14" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" s="42"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="65"/>
+      <c r="H14" s="66"/>
       <c r="I14" s="71"/>
       <c r="J14" s="71"/>
       <c r="K14" s="71"/>
@@ -5196,44 +5442,41 @@
       <c r="Q14" s="71"/>
       <c r="R14" s="71"/>
       <c r="S14" s="71"/>
-      <c r="T14" s="71"/>
+      <c r="T14" s="72"/>
       <c r="U14" s="71"/>
       <c r="V14" s="71"/>
-      <c r="W14" s="71"/>
-      <c r="X14" s="71"/>
-      <c r="Y14" s="71"/>
-      <c r="Z14" s="71"/>
-      <c r="AA14" s="71"/>
+      <c r="W14" s="72"/>
+      <c r="X14" s="72"/>
+      <c r="Y14" s="72"/>
+      <c r="Z14" s="72"/>
+      <c r="AA14" s="72"/>
       <c r="AB14" s="71"/>
       <c r="AC14" s="71"/>
-      <c r="AD14" s="71"/>
-      <c r="AE14" s="71"/>
-      <c r="AF14" s="71" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG14" s="71" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH14" s="74"/>
+      <c r="AD14" s="72"/>
+      <c r="AE14" s="72"/>
+      <c r="AF14" s="72"/>
+      <c r="AG14" s="72"/>
+      <c r="AH14" s="72"/>
       <c r="AI14" s="71"/>
       <c r="AJ14" s="71"/>
-      <c r="AL14" s="71"/>
-      <c r="AM14" s="71"/>
-      <c r="AN14" s="71"/>
+      <c r="AK14" s="72"/>
+      <c r="AL14" s="72"/>
+      <c r="AM14" s="72"/>
+      <c r="AN14" s="72"/>
       <c r="AO14" s="72"/>
       <c r="AP14" s="71"/>
       <c r="AQ14" s="71"/>
       <c r="AR14" s="72"/>
       <c r="AS14" s="72"/>
       <c r="AT14" s="72"/>
-      <c r="AU14" s="71"/>
-      <c r="AV14" s="73"/>
+      <c r="AU14" s="72"/>
+      <c r="AV14" s="76"/>
       <c r="AW14" s="71"/>
       <c r="AX14" s="71"/>
-      <c r="AY14" s="71"/>
-      <c r="AZ14" s="71"/>
-      <c r="BA14" s="71"/>
-      <c r="BB14" s="71"/>
+      <c r="AY14" s="72"/>
+      <c r="AZ14" s="72"/>
+      <c r="BA14" s="72"/>
+      <c r="BB14" s="72"/>
       <c r="BC14" s="73"/>
       <c r="BD14" s="71"/>
       <c r="BE14" s="71"/>
@@ -5246,28 +5489,28 @@
       <c r="BL14" s="63"/>
       <c r="BM14" s="64"/>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="12.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C15" s="15"/>
       <c r="D15" s="15"/>
       <c r="E15" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="F15" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="F15" s="41" t="s">
-        <v>43</v>
-      </c>
       <c r="G15" s="65" t="n">
-        <f aca="false">Netzplan!J15</f>
-        <v>1</v>
+        <f aca="false">Netzplan!J13</f>
+        <v>2</v>
       </c>
       <c r="H15" s="66" t="n">
         <f aca="false">SUM(I15:BJ15)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" s="71"/>
       <c r="J15" s="71"/>
@@ -5290,22 +5533,25 @@
       <c r="AA15" s="71"/>
       <c r="AB15" s="71"/>
       <c r="AC15" s="71"/>
-      <c r="AD15" s="71"/>
-      <c r="AE15" s="71"/>
-      <c r="AF15" s="71"/>
+      <c r="AE15" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF15" s="72" t="n">
+        <v>1</v>
+      </c>
       <c r="AG15" s="71"/>
-      <c r="AH15" s="71" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH15" s="71"/>
       <c r="AI15" s="71"/>
       <c r="AJ15" s="71"/>
-      <c r="AL15" s="71"/>
-      <c r="AM15" s="74"/>
-      <c r="AO15" s="71"/>
+      <c r="AK15" s="72"/>
+      <c r="AL15" s="72"/>
+      <c r="AM15" s="72"/>
+      <c r="AN15" s="72"/>
+      <c r="AO15" s="72"/>
       <c r="AP15" s="71"/>
       <c r="AQ15" s="71"/>
-      <c r="AR15" s="74"/>
-      <c r="AS15" s="72"/>
+      <c r="AR15" s="71"/>
+      <c r="AS15" s="71"/>
       <c r="AT15" s="71"/>
       <c r="AU15" s="71"/>
       <c r="AV15" s="73"/>
@@ -5327,28 +5573,28 @@
       <c r="BL15" s="63"/>
       <c r="BM15" s="64"/>
     </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="12.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C16" s="15"/>
       <c r="D16" s="15"/>
       <c r="E16" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="F16" s="41" t="s">
-        <v>44</v>
-      </c>
       <c r="G16" s="65" t="n">
-        <f aca="false">Netzplan!J16</f>
-        <v>4</v>
+        <f aca="false">Netzplan!J14</f>
+        <v>2</v>
       </c>
       <c r="H16" s="66" t="n">
         <f aca="false">SUM(I16:BJ16)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I16" s="71"/>
       <c r="J16" s="71"/>
@@ -5373,36 +5619,30 @@
       <c r="AC16" s="71"/>
       <c r="AD16" s="71"/>
       <c r="AE16" s="71"/>
-      <c r="AF16" s="71"/>
-      <c r="AG16" s="71"/>
-      <c r="AH16" s="71"/>
+      <c r="AG16" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH16" s="71" t="n">
+        <v>1</v>
+      </c>
       <c r="AI16" s="71"/>
       <c r="AJ16" s="71"/>
-      <c r="AK16" s="71" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL16" s="71" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM16" s="74" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN16" s="74" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO16" s="74"/>
+      <c r="AL16" s="71"/>
+      <c r="AM16" s="71"/>
+      <c r="AN16" s="71"/>
+      <c r="AO16" s="72"/>
       <c r="AP16" s="71"/>
       <c r="AQ16" s="71"/>
-      <c r="AR16" s="71"/>
-      <c r="AS16" s="74"/>
-      <c r="AT16" s="71"/>
-      <c r="AU16" s="72"/>
+      <c r="AR16" s="72"/>
+      <c r="AS16" s="72"/>
+      <c r="AT16" s="72"/>
+      <c r="AU16" s="71"/>
       <c r="AV16" s="73"/>
       <c r="AW16" s="71"/>
       <c r="AX16" s="71"/>
-      <c r="AY16" s="72"/>
-      <c r="AZ16" s="72"/>
-      <c r="BA16" s="72"/>
+      <c r="AY16" s="71"/>
+      <c r="AZ16" s="71"/>
+      <c r="BA16" s="71"/>
       <c r="BB16" s="71"/>
       <c r="BC16" s="73"/>
       <c r="BD16" s="71"/>
@@ -5416,94 +5656,262 @@
       <c r="BL16" s="63"/>
       <c r="BM16" s="64"/>
     </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="45" t="s">
-        <v>60</v>
-      </c>
-      <c r="F17" s="46"/>
+    <row r="17" customFormat="false" ht="12.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="41" t="s">
+        <v>41</v>
+      </c>
+      <c r="F17" s="41" t="s">
+        <v>43</v>
+      </c>
       <c r="G17" s="65" t="n">
-        <f aca="false">Netzplan!J17</f>
+        <f aca="false">Netzplan!J15</f>
         <v>1</v>
       </c>
       <c r="H17" s="66" t="n">
         <f aca="false">SUM(I17:BJ17)</f>
         <v>1</v>
       </c>
-      <c r="I17" s="77"/>
-      <c r="J17" s="77"/>
-      <c r="K17" s="77"/>
-      <c r="L17" s="77"/>
-      <c r="M17" s="77"/>
-      <c r="N17" s="77"/>
-      <c r="O17" s="77"/>
-      <c r="P17" s="77"/>
-      <c r="Q17" s="77"/>
-      <c r="R17" s="77"/>
-      <c r="S17" s="77"/>
-      <c r="T17" s="77"/>
-      <c r="U17" s="77"/>
-      <c r="V17" s="77"/>
-      <c r="W17" s="77"/>
-      <c r="X17" s="77"/>
-      <c r="Y17" s="77"/>
-      <c r="Z17" s="77"/>
-      <c r="AA17" s="77"/>
-      <c r="AB17" s="77"/>
-      <c r="AC17" s="77"/>
-      <c r="AD17" s="77"/>
-      <c r="AE17" s="77"/>
-      <c r="AF17" s="77"/>
-      <c r="AG17" s="77"/>
-      <c r="AH17" s="77"/>
-      <c r="AI17" s="77"/>
-      <c r="AJ17" s="77"/>
-      <c r="AK17" s="77"/>
-      <c r="AL17" s="77"/>
-      <c r="AM17" s="77"/>
-      <c r="AN17" s="77"/>
-      <c r="AO17" s="77"/>
-      <c r="AP17" s="77"/>
-      <c r="AQ17" s="77"/>
-      <c r="AR17" s="77"/>
-      <c r="AS17" s="77"/>
-      <c r="AT17" s="77"/>
-      <c r="AU17" s="77"/>
-      <c r="AV17" s="78"/>
-      <c r="AW17" s="77"/>
-      <c r="AX17" s="77"/>
-      <c r="AY17" s="79" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ17" s="79"/>
-      <c r="BA17" s="77"/>
-      <c r="BB17" s="77"/>
-      <c r="BC17" s="78"/>
-      <c r="BD17" s="77"/>
-      <c r="BE17" s="77"/>
-      <c r="BF17" s="77"/>
-      <c r="BG17" s="77"/>
-      <c r="BH17" s="77"/>
-      <c r="BI17" s="78"/>
-      <c r="BJ17" s="80"/>
+      <c r="I17" s="71"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="71"/>
+      <c r="L17" s="71"/>
+      <c r="M17" s="71"/>
+      <c r="N17" s="71"/>
+      <c r="O17" s="71"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="71"/>
+      <c r="S17" s="71"/>
+      <c r="T17" s="71"/>
+      <c r="U17" s="71"/>
+      <c r="V17" s="71"/>
+      <c r="W17" s="71"/>
+      <c r="X17" s="71"/>
+      <c r="Y17" s="71"/>
+      <c r="Z17" s="71"/>
+      <c r="AA17" s="71"/>
+      <c r="AB17" s="71"/>
+      <c r="AC17" s="71"/>
+      <c r="AD17" s="71"/>
+      <c r="AE17" s="71"/>
+      <c r="AF17" s="71"/>
+      <c r="AG17" s="71"/>
+      <c r="AI17" s="71"/>
+      <c r="AJ17" s="71"/>
+      <c r="AL17" s="71"/>
+      <c r="AM17" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO17" s="71"/>
+      <c r="AP17" s="71"/>
+      <c r="AQ17" s="71"/>
+      <c r="AR17" s="74"/>
+      <c r="AS17" s="72"/>
+      <c r="AT17" s="71"/>
+      <c r="AU17" s="71"/>
+      <c r="AV17" s="73"/>
+      <c r="AW17" s="71"/>
+      <c r="AX17" s="71"/>
+      <c r="AY17" s="71"/>
+      <c r="AZ17" s="71"/>
+      <c r="BA17" s="71"/>
+      <c r="BB17" s="71"/>
+      <c r="BC17" s="73"/>
+      <c r="BD17" s="71"/>
+      <c r="BE17" s="71"/>
+      <c r="BF17" s="71"/>
+      <c r="BG17" s="71"/>
+      <c r="BH17" s="71"/>
+      <c r="BI17" s="73"/>
+      <c r="BJ17" s="74"/>
       <c r="BK17" s="62"/>
       <c r="BL17" s="63"/>
       <c r="BM17" s="64"/>
     </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>78</v>
+    <row r="18" customFormat="false" ht="12.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="F18" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G18" s="65" t="n">
+        <f aca="false">Netzplan!J16</f>
+        <v>4</v>
+      </c>
+      <c r="H18" s="66" t="n">
+        <f aca="false">SUM(I18:BJ18)</f>
+        <v>4</v>
+      </c>
+      <c r="I18" s="71"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="71"/>
+      <c r="L18" s="71"/>
+      <c r="M18" s="71"/>
+      <c r="N18" s="71"/>
+      <c r="O18" s="71"/>
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="71"/>
+      <c r="S18" s="71"/>
+      <c r="T18" s="71"/>
+      <c r="U18" s="71"/>
+      <c r="V18" s="71"/>
+      <c r="W18" s="71"/>
+      <c r="X18" s="71"/>
+      <c r="Y18" s="71"/>
+      <c r="Z18" s="71"/>
+      <c r="AA18" s="71"/>
+      <c r="AB18" s="71"/>
+      <c r="AC18" s="71"/>
+      <c r="AD18" s="71"/>
+      <c r="AE18" s="71"/>
+      <c r="AF18" s="71"/>
+      <c r="AG18" s="71"/>
+      <c r="AH18" s="71"/>
+      <c r="AI18" s="71"/>
+      <c r="AJ18" s="71"/>
+      <c r="AL18" s="71"/>
+      <c r="AM18" s="74"/>
+      <c r="AN18" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO18" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP18" s="71"/>
+      <c r="AQ18" s="71"/>
+      <c r="AR18" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS18" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT18" s="71"/>
+      <c r="AU18" s="72"/>
+      <c r="AV18" s="73"/>
+      <c r="AW18" s="71"/>
+      <c r="AX18" s="71"/>
+      <c r="AY18" s="72"/>
+      <c r="AZ18" s="72"/>
+      <c r="BA18" s="72"/>
+      <c r="BB18" s="71"/>
+      <c r="BC18" s="73"/>
+      <c r="BD18" s="71"/>
+      <c r="BE18" s="71"/>
+      <c r="BF18" s="71"/>
+      <c r="BG18" s="71"/>
+      <c r="BH18" s="71"/>
+      <c r="BI18" s="73"/>
+      <c r="BJ18" s="74"/>
+      <c r="BK18" s="62"/>
+      <c r="BL18" s="63"/>
+      <c r="BM18" s="64"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="45" t="s">
+        <v>60</v>
+      </c>
+      <c r="F19" s="46"/>
+      <c r="G19" s="65" t="n">
+        <f aca="false">Netzplan!J17</f>
+        <v>1</v>
+      </c>
+      <c r="H19" s="66" t="n">
+        <f aca="false">SUM(I19:BJ19)</f>
+        <v>1</v>
+      </c>
+      <c r="I19" s="77"/>
+      <c r="J19" s="77"/>
+      <c r="K19" s="77"/>
+      <c r="L19" s="77"/>
+      <c r="M19" s="77"/>
+      <c r="N19" s="77"/>
+      <c r="O19" s="77"/>
+      <c r="P19" s="77"/>
+      <c r="Q19" s="77"/>
+      <c r="R19" s="77"/>
+      <c r="S19" s="77"/>
+      <c r="T19" s="77"/>
+      <c r="U19" s="77"/>
+      <c r="V19" s="77"/>
+      <c r="W19" s="77"/>
+      <c r="X19" s="77"/>
+      <c r="Y19" s="77"/>
+      <c r="Z19" s="77"/>
+      <c r="AA19" s="77"/>
+      <c r="AB19" s="77"/>
+      <c r="AC19" s="77"/>
+      <c r="AD19" s="77"/>
+      <c r="AE19" s="77"/>
+      <c r="AF19" s="77"/>
+      <c r="AG19" s="77"/>
+      <c r="AH19" s="77"/>
+      <c r="AI19" s="77"/>
+      <c r="AJ19" s="77"/>
+      <c r="AK19" s="77"/>
+      <c r="AL19" s="77"/>
+      <c r="AM19" s="77"/>
+      <c r="AN19" s="77"/>
+      <c r="AO19" s="77"/>
+      <c r="AP19" s="77"/>
+      <c r="AQ19" s="77"/>
+      <c r="AR19" s="77"/>
+      <c r="AS19" s="77"/>
+      <c r="AT19" s="77"/>
+      <c r="AU19" s="77"/>
+      <c r="AV19" s="78"/>
+      <c r="AW19" s="77"/>
+      <c r="AX19" s="77"/>
+      <c r="AY19" s="79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ19" s="79"/>
+      <c r="BA19" s="77"/>
+      <c r="BB19" s="77"/>
+      <c r="BC19" s="78"/>
+      <c r="BD19" s="77"/>
+      <c r="BE19" s="77"/>
+      <c r="BF19" s="77"/>
+      <c r="BG19" s="77"/>
+      <c r="BH19" s="77"/>
+      <c r="BI19" s="78"/>
+      <c r="BJ19" s="80"/>
+      <c r="BK19" s="62"/>
+      <c r="BL19" s="63"/>
+      <c r="BM19" s="64"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="19">
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B3:D3"/>
@@ -5521,18 +5929,20 @@
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
   </mergeCells>
-  <conditionalFormatting sqref="I13:BF13 I10:AC12 AE10:BF11 I16:BF17 I14:AJ15 AL14:BF14 AL15:AM15 AO15:BF15 I1:BF9 AD12:BF12">
+  <conditionalFormatting sqref="I11:AC15 AE11:BF12 I19:BF19 AL16:BF16 AL17:AM17 AO17:BF17 I1:BF10 AD13:BF14 AE15:BF15 I16:AE16 AG16:AJ16 I17:AG17 I18:AJ18 AI17:AJ17 AL18:BF18">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>IF(OR(WEEKDAY(I$1)=7,WEEKDAY(I$1)=1),1,0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H17">
+  <conditionalFormatting sqref="H2:H19">
     <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>IF(H2&lt;&gt;G2,TRUE())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I13:BF13 I10:AC12 AE10:BF11 I16:BF17 I14:AJ15 AL14:BF14 AL15:AM15 AO15:BF15 I2:BF9 AD12:BF12">
+  <conditionalFormatting sqref="I11:AC15 AE11:BF12 I19:BF19 AL16:BF16 AL17:AM17 AO17:BF17 I2:BF10 AD13:BF14 AE15:BF15 I16:AE16 AG16:AJ16 I17:AG17 I18:AJ18 AI17:AJ17 AL18:BF18">
     <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>1</formula>
     </cfRule>
@@ -5544,5 +5954,6 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Übungen/Online_Shop.xlsx
+++ b/Übungen/Online_Shop.xlsx
@@ -5,12 +5,16 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="PSP" sheetId="1" state="visible" r:id="rId2"/>
     <sheet name="Netzplan" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="Gantt" sheetId="3" state="visible" r:id="rId4"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId5"/>
+  </externalReferences>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -21,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="79">
   <si>
     <t xml:space="preserve">Beispiel: Funktionsorientierter Projektstrukturplan</t>
   </si>
@@ -256,20 +260,24 @@
   </si>
   <si>
     <t xml:space="preserve">FAZ + D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gantt</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
     <numFmt numFmtId="166" formatCode="@"/>
     <numFmt numFmtId="167" formatCode="0.00\ %"/>
     <numFmt numFmtId="168" formatCode="General"/>
+    <numFmt numFmtId="169" formatCode="0\ %"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="13">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -328,8 +336,36 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF127622"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF55308D"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF8000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFDDDDDD"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -357,7 +393,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFAADCF7"/>
-        <bgColor rgb="FFCCCCFF"/>
+        <bgColor rgb="FFDDDDDD"/>
       </patternFill>
     </fill>
     <fill>
@@ -369,13 +405,19 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00A933"/>
-        <bgColor rgb="FF008000"/>
+        <bgColor rgb="FF008080"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF8000"/>
         <bgColor rgb="FFFF6600"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFEEEEEE"/>
       </patternFill>
     </fill>
   </fills>
@@ -499,7 +541,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="85">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -680,10 +722,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -754,6 +792,94 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="70" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="70" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="9" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="9" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -768,7 +894,7 @@
     <cellStyle name="KritischerPfad" xfId="21"/>
     <cellStyle name="Wochenende" xfId="22"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="4">
     <dxf>
       <font>
         <name val="Arial"/>
@@ -777,6 +903,48 @@
         <b val="1"/>
         <color rgb="FFFF0000"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="2"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF666666"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="2"/>
+        <b val="1"/>
+        <i val="0"/>
+        <color rgb="FFFFFFFF"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCC0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="2"/>
+        <color rgb="FFFFBF00"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFBF00"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <colors>
@@ -789,8 +957,8 @@
       <rgbColor rgb="FFFFFF00"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FFCC0000"/>
+      <rgbColor rgb="FF127622"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
@@ -804,7 +972,7 @@
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFDDDDDD"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -835,7 +1003,7 @@
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF55308D"/>
       <rgbColor rgb="FF333333"/>
     </indexedColors>
   </colors>
@@ -864,8 +1032,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="5488560" y="479520"/>
-          <a:ext cx="5545080" cy="0"/>
+          <a:off x="5493960" y="479520"/>
+          <a:ext cx="5554080" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -906,7 +1074,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5488200" y="488160"/>
+          <a:off x="5493240" y="488160"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -947,7 +1115,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5487480" y="488160"/>
+          <a:off x="5492520" y="488160"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -989,7 +1157,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5501520" y="1125360"/>
+          <a:off x="5507640" y="1125360"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1031,7 +1199,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5501520" y="1612800"/>
+          <a:off x="5507640" y="1612800"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1073,7 +1241,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5501520" y="2099880"/>
+          <a:off x="5507640" y="2099880"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1115,7 +1283,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5501520" y="2587320"/>
+          <a:off x="5507640" y="2587320"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1157,7 +1325,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8261640" y="324720"/>
+          <a:off x="8272080" y="324720"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1199,7 +1367,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8261640" y="487440"/>
+          <a:off x="8272080" y="487440"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1241,7 +1409,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8261640" y="1125360"/>
+          <a:off x="8272080" y="1125360"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1283,7 +1451,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8261640" y="1612800"/>
+          <a:off x="8272080" y="1612800"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1325,7 +1493,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8261640" y="2587320"/>
+          <a:off x="8272080" y="2587320"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1367,7 +1535,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8261640" y="3074400"/>
+          <a:off x="8272080" y="3074400"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1409,7 +1577,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8261640" y="4048920"/>
+          <a:off x="8272080" y="4048920"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1451,7 +1619,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8261640" y="5023440"/>
+          <a:off x="8272080" y="5023440"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1493,7 +1661,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11022480" y="487440"/>
+          <a:off x="11036520" y="487440"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1535,7 +1703,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11022480" y="1125360"/>
+          <a:off x="11036520" y="1125360"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1577,7 +1745,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11022480" y="1612800"/>
+          <a:off x="11036520" y="1612800"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1619,7 +1787,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11022480" y="2099880"/>
+          <a:off x="11036520" y="2099880"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1661,7 +1829,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8253000" y="3557520"/>
+          <a:off x="8261640" y="3557520"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1703,7 +1871,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8253000" y="4533480"/>
+          <a:off x="8261640" y="4533480"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1745,7 +1913,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8253000" y="2093760"/>
+          <a:off x="8261640" y="2093760"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1770,8 +1938,10 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</externalLink>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1780,7 +1950,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M41"/>
-  <sheetFormatPr defaultColWidth="13.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="13.07421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.77"/>
   </cols>
@@ -2322,7 +2492,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:BW35"/>
-  <sheetFormatPr defaultColWidth="11.8046875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.82421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="20" width="11.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.52"/>
@@ -3106,7 +3276,7 @@
         <f aca="false">AC11-AC8</f>
         <v>4</v>
       </c>
-      <c r="AC10" s="45" t="n">
+      <c r="AC10" s="37" t="n">
         <f aca="false">AL2-AC8</f>
         <v>1</v>
       </c>
@@ -3200,7 +3370,7 @@
         <v>19</v>
       </c>
       <c r="P12" s="41"/>
-      <c r="AA12" s="46"/>
+      <c r="AA12" s="45"/>
       <c r="AK12" s="41"/>
       <c r="BT12" s="41"/>
     </row>
@@ -3234,7 +3404,7 @@
         <v>2</v>
       </c>
       <c r="P13" s="41"/>
-      <c r="AA13" s="46"/>
+      <c r="AA13" s="45"/>
       <c r="AK13" s="41"/>
       <c r="BT13" s="41"/>
     </row>
@@ -3286,18 +3456,18 @@
         <f aca="false">V14+V16</f>
         <v>6</v>
       </c>
-      <c r="Y14" s="47"/>
-      <c r="Z14" s="47"/>
-      <c r="AA14" s="47"/>
-      <c r="AB14" s="47"/>
-      <c r="AC14" s="47"/>
-      <c r="AD14" s="47"/>
-      <c r="AE14" s="47"/>
-      <c r="AF14" s="47"/>
-      <c r="AG14" s="47"/>
-      <c r="AH14" s="47"/>
-      <c r="AI14" s="47"/>
-      <c r="AJ14" s="47"/>
+      <c r="Y14" s="46"/>
+      <c r="Z14" s="46"/>
+      <c r="AA14" s="46"/>
+      <c r="AB14" s="46"/>
+      <c r="AC14" s="46"/>
+      <c r="AD14" s="46"/>
+      <c r="AE14" s="46"/>
+      <c r="AF14" s="46"/>
+      <c r="AG14" s="46"/>
+      <c r="AH14" s="46"/>
+      <c r="AI14" s="46"/>
+      <c r="AJ14" s="46"/>
       <c r="AK14" s="41"/>
       <c r="AL14" s="30" t="n">
         <f aca="false">X14</f>
@@ -3350,8 +3520,8 @@
       </c>
       <c r="W15" s="36"/>
       <c r="X15" s="36"/>
-      <c r="AA15" s="46"/>
-      <c r="AK15" s="48"/>
+      <c r="AA15" s="45"/>
+      <c r="AK15" s="47"/>
       <c r="AL15" s="36" t="s">
         <v>17</v>
       </c>
@@ -3436,7 +3606,7 @@
         <f aca="false">AN17-AN14</f>
         <v>0</v>
       </c>
-      <c r="AN16" s="45" t="n">
+      <c r="AN16" s="37" t="n">
         <f aca="false">BU2-AN14</f>
         <v>0</v>
       </c>
@@ -3476,16 +3646,16 @@
       <c r="A17" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="49" t="s">
+      <c r="B17" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="49"/>
-      <c r="D17" s="49"/>
-      <c r="E17" s="50" t="s">
+      <c r="C17" s="48"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="51"/>
-      <c r="G17" s="52" t="n">
+      <c r="F17" s="50"/>
+      <c r="G17" s="51" t="n">
         <v>1</v>
       </c>
       <c r="H17" s="42" t="s">
@@ -3527,14 +3697,14 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="53" t="s">
+      <c r="A19" s="52" t="s">
         <v>61</v>
       </c>
-      <c r="B19" s="54" t="s">
+      <c r="B19" s="53" t="s">
         <v>62</v>
       </c>
-      <c r="C19" s="55"/>
-      <c r="D19" s="56" t="s">
+      <c r="C19" s="54"/>
+      <c r="D19" s="55" t="s">
         <v>63</v>
       </c>
     </row>
@@ -3557,19 +3727,19 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="57" t="s">
+      <c r="A22" s="56" t="s">
         <v>66</v>
       </c>
-      <c r="B22" s="58" t="s">
+      <c r="B22" s="57" t="s">
         <v>62</v>
       </c>
-      <c r="C22" s="59"/>
-      <c r="D22" s="60" t="s">
+      <c r="C22" s="58"/>
+      <c r="D22" s="59" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="61" t="s">
+      <c r="B24" s="60" t="s">
         <v>67</v>
       </c>
       <c r="C24" s="31"/>
@@ -3596,7 +3766,7 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="61" t="s">
+      <c r="B27" s="60" t="s">
         <v>73</v>
       </c>
       <c r="C27" s="31"/>
@@ -3608,58 +3778,58 @@
       <c r="A29" s="0" t="s">
         <v>67</v>
       </c>
-      <c r="B29" s="62" t="s">
+      <c r="B29" s="61" t="s">
         <v>75</v>
       </c>
-      <c r="C29" s="63" t="s">
+      <c r="C29" s="62" t="s">
         <v>76</v>
       </c>
-      <c r="D29" s="63"/>
+      <c r="D29" s="62"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="B30" s="62" t="s">
+      <c r="B30" s="61" t="s">
         <v>75</v>
       </c>
-      <c r="C30" s="63" t="s">
+      <c r="C30" s="62" t="s">
         <v>77</v>
       </c>
-      <c r="D30" s="63"/>
+      <c r="D30" s="62"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="62"/>
+      <c r="B31" s="61"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="B32" s="62" t="s">
+      <c r="B32" s="61" t="s">
         <v>75</v>
       </c>
-      <c r="C32" s="63" t="s">
+      <c r="C32" s="62" t="s">
         <v>77</v>
       </c>
-      <c r="D32" s="63"/>
+      <c r="D32" s="62"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
         <v>67</v>
       </c>
-      <c r="B33" s="62" t="s">
+      <c r="B33" s="61" t="s">
         <v>75</v>
       </c>
-      <c r="C33" s="63" t="s">
+      <c r="C33" s="62" t="s">
         <v>76</v>
       </c>
-      <c r="D33" s="63"/>
+      <c r="D33" s="62"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="62"/>
+      <c r="B34" s="61"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="62"/>
+      <c r="B35" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="39">
@@ -3715,6 +3885,1542 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>
   </headerFooter>
-  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:BM20"/>
+  <sheetFormatPr defaultColWidth="11.77734375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="1"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="5" min="5" style="0" width="16.2"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="6" min="6" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11.59"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="8" min="8" style="0" width="3.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="62" min="9" style="0" width="3.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="63" min="63" style="0" width="7.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="64" style="0" width="8.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="65" min="65" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1022" style="0" width="11.52"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="40.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" s="63" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1" s="63"/>
+      <c r="I1" s="64" t="n">
+        <v>44515</v>
+      </c>
+      <c r="J1" s="64" t="n">
+        <v>44516</v>
+      </c>
+      <c r="K1" s="64" t="n">
+        <v>44517</v>
+      </c>
+      <c r="L1" s="64" t="n">
+        <v>44518</v>
+      </c>
+      <c r="M1" s="64" t="n">
+        <v>44519</v>
+      </c>
+      <c r="N1" s="64" t="n">
+        <v>44520</v>
+      </c>
+      <c r="O1" s="64" t="n">
+        <v>44521</v>
+      </c>
+      <c r="P1" s="64" t="n">
+        <v>44522</v>
+      </c>
+      <c r="Q1" s="64" t="n">
+        <v>44523</v>
+      </c>
+      <c r="R1" s="64" t="n">
+        <v>44524</v>
+      </c>
+      <c r="S1" s="64" t="n">
+        <v>44525</v>
+      </c>
+      <c r="T1" s="64" t="n">
+        <v>44526</v>
+      </c>
+      <c r="U1" s="64" t="n">
+        <v>44527</v>
+      </c>
+      <c r="V1" s="64" t="n">
+        <v>44528</v>
+      </c>
+      <c r="W1" s="64" t="n">
+        <v>44529</v>
+      </c>
+      <c r="X1" s="64" t="n">
+        <v>44530</v>
+      </c>
+      <c r="Y1" s="64" t="n">
+        <v>44531</v>
+      </c>
+      <c r="Z1" s="64" t="n">
+        <v>44532</v>
+      </c>
+      <c r="AA1" s="64" t="n">
+        <v>44533</v>
+      </c>
+      <c r="AB1" s="64" t="n">
+        <v>44534</v>
+      </c>
+      <c r="AC1" s="64" t="n">
+        <v>44535</v>
+      </c>
+      <c r="AD1" s="64" t="n">
+        <v>44536</v>
+      </c>
+      <c r="AE1" s="64" t="n">
+        <v>44537</v>
+      </c>
+      <c r="AF1" s="64" t="n">
+        <v>44538</v>
+      </c>
+      <c r="AG1" s="64" t="n">
+        <v>44539</v>
+      </c>
+      <c r="AH1" s="64" t="n">
+        <v>44540</v>
+      </c>
+      <c r="AI1" s="64" t="n">
+        <v>44541</v>
+      </c>
+      <c r="AJ1" s="64" t="n">
+        <v>44542</v>
+      </c>
+      <c r="AK1" s="64" t="n">
+        <v>44543</v>
+      </c>
+      <c r="AL1" s="64" t="n">
+        <v>44544</v>
+      </c>
+      <c r="AM1" s="64" t="n">
+        <v>44545</v>
+      </c>
+      <c r="AN1" s="64" t="n">
+        <v>44546</v>
+      </c>
+      <c r="AO1" s="64" t="n">
+        <v>44547</v>
+      </c>
+      <c r="AP1" s="64" t="n">
+        <v>44548</v>
+      </c>
+      <c r="AQ1" s="64" t="n">
+        <v>44549</v>
+      </c>
+      <c r="AR1" s="64" t="n">
+        <v>44550</v>
+      </c>
+      <c r="AS1" s="64" t="n">
+        <v>44551</v>
+      </c>
+      <c r="AT1" s="64" t="n">
+        <v>44552</v>
+      </c>
+      <c r="AU1" s="64" t="n">
+        <v>44553</v>
+      </c>
+      <c r="AV1" s="65" t="n">
+        <v>44554</v>
+      </c>
+      <c r="AW1" s="64" t="n">
+        <v>44555</v>
+      </c>
+      <c r="AX1" s="64" t="n">
+        <v>44556</v>
+      </c>
+      <c r="AY1" s="64" t="n">
+        <v>44557</v>
+      </c>
+      <c r="AZ1" s="64" t="n">
+        <v>44558</v>
+      </c>
+      <c r="BA1" s="64" t="n">
+        <v>44559</v>
+      </c>
+      <c r="BB1" s="64" t="n">
+        <v>44560</v>
+      </c>
+      <c r="BC1" s="65" t="n">
+        <v>44561</v>
+      </c>
+      <c r="BD1" s="64" t="n">
+        <v>44562</v>
+      </c>
+      <c r="BE1" s="64" t="n">
+        <v>44563</v>
+      </c>
+      <c r="BF1" s="64" t="n">
+        <v>44564</v>
+      </c>
+      <c r="BG1" s="64" t="n">
+        <v>44565</v>
+      </c>
+      <c r="BH1" s="64" t="n">
+        <v>44566</v>
+      </c>
+      <c r="BI1" s="65" t="n">
+        <v>44567</v>
+      </c>
+      <c r="BJ1" s="64" t="n">
+        <v>44568</v>
+      </c>
+      <c r="BK1" s="66"/>
+      <c r="BL1" s="67"/>
+      <c r="BM1" s="68"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="G2" s="69" t="n">
+        <f aca="false">[1]Netzplan!J2</f>
+        <v>2</v>
+      </c>
+      <c r="H2" s="70" t="n">
+        <f aca="false">SUM(I2:BJ2)</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="71"/>
+      <c r="M2" s="71"/>
+      <c r="N2" s="72"/>
+      <c r="O2" s="72"/>
+      <c r="P2" s="72"/>
+      <c r="Q2" s="72"/>
+      <c r="R2" s="72"/>
+      <c r="S2" s="72"/>
+      <c r="T2" s="72"/>
+      <c r="U2" s="72"/>
+      <c r="V2" s="72"/>
+      <c r="W2" s="72"/>
+      <c r="X2" s="72"/>
+      <c r="Y2" s="72"/>
+      <c r="Z2" s="72"/>
+      <c r="AA2" s="72"/>
+      <c r="AB2" s="72"/>
+      <c r="AC2" s="72"/>
+      <c r="AD2" s="72"/>
+      <c r="AE2" s="72"/>
+      <c r="AF2" s="72"/>
+      <c r="AG2" s="72"/>
+      <c r="AH2" s="72"/>
+      <c r="AI2" s="72"/>
+      <c r="AJ2" s="72"/>
+      <c r="AK2" s="72"/>
+      <c r="AL2" s="72"/>
+      <c r="AM2" s="72"/>
+      <c r="AN2" s="72"/>
+      <c r="AO2" s="72"/>
+      <c r="AP2" s="72"/>
+      <c r="AQ2" s="72"/>
+      <c r="AR2" s="72"/>
+      <c r="AS2" s="72"/>
+      <c r="AT2" s="72"/>
+      <c r="AU2" s="72"/>
+      <c r="AV2" s="73"/>
+      <c r="AW2" s="72"/>
+      <c r="AX2" s="72"/>
+      <c r="AY2" s="72"/>
+      <c r="AZ2" s="72"/>
+      <c r="BA2" s="72"/>
+      <c r="BB2" s="72"/>
+      <c r="BC2" s="73"/>
+      <c r="BD2" s="72"/>
+      <c r="BE2" s="72"/>
+      <c r="BF2" s="72"/>
+      <c r="BG2" s="72"/>
+      <c r="BH2" s="72"/>
+      <c r="BI2" s="73"/>
+      <c r="BJ2" s="74"/>
+      <c r="BK2" s="66"/>
+      <c r="BL2" s="67"/>
+      <c r="BM2" s="68"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="G3" s="69" t="n">
+        <f aca="false">[1]Netzplan!J3</f>
+        <v>1</v>
+      </c>
+      <c r="H3" s="70" t="n">
+        <f aca="false">SUM(I3:BJ3)</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
+      <c r="K3" s="75"/>
+      <c r="L3" s="75"/>
+      <c r="M3" s="75"/>
+      <c r="N3" s="75"/>
+      <c r="O3" s="75"/>
+      <c r="P3" s="76"/>
+      <c r="Q3" s="75"/>
+      <c r="R3" s="75"/>
+      <c r="S3" s="75"/>
+      <c r="T3" s="75"/>
+      <c r="U3" s="75"/>
+      <c r="V3" s="75"/>
+      <c r="W3" s="75"/>
+      <c r="X3" s="75"/>
+      <c r="Y3" s="75"/>
+      <c r="Z3" s="75"/>
+      <c r="AA3" s="75"/>
+      <c r="AB3" s="75"/>
+      <c r="AC3" s="75"/>
+      <c r="AD3" s="75"/>
+      <c r="AE3" s="75"/>
+      <c r="AF3" s="75"/>
+      <c r="AG3" s="75"/>
+      <c r="AH3" s="75"/>
+      <c r="AI3" s="75"/>
+      <c r="AJ3" s="75"/>
+      <c r="AK3" s="75"/>
+      <c r="AL3" s="75"/>
+      <c r="AM3" s="75"/>
+      <c r="AN3" s="75"/>
+      <c r="AO3" s="75"/>
+      <c r="AP3" s="75"/>
+      <c r="AQ3" s="75"/>
+      <c r="AR3" s="75"/>
+      <c r="AS3" s="75"/>
+      <c r="AT3" s="75"/>
+      <c r="AU3" s="75"/>
+      <c r="AV3" s="77"/>
+      <c r="AW3" s="75"/>
+      <c r="AX3" s="75"/>
+      <c r="AY3" s="75"/>
+      <c r="AZ3" s="75"/>
+      <c r="BA3" s="75"/>
+      <c r="BB3" s="75"/>
+      <c r="BC3" s="77"/>
+      <c r="BD3" s="75"/>
+      <c r="BE3" s="75"/>
+      <c r="BF3" s="75"/>
+      <c r="BG3" s="75"/>
+      <c r="BH3" s="75"/>
+      <c r="BI3" s="77"/>
+      <c r="BJ3" s="78"/>
+      <c r="BK3" s="66"/>
+      <c r="BL3" s="67"/>
+      <c r="BM3" s="68"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="69" t="n">
+        <f aca="false">[1]Netzplan!J4</f>
+        <v>6</v>
+      </c>
+      <c r="H4" s="70" t="n">
+        <f aca="false">SUM(I4:BJ4)</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="75"/>
+      <c r="J4" s="75"/>
+      <c r="K4" s="75"/>
+      <c r="L4" s="75"/>
+      <c r="M4" s="75"/>
+      <c r="N4" s="75"/>
+      <c r="O4" s="75"/>
+      <c r="P4" s="75"/>
+      <c r="Q4" s="76"/>
+      <c r="R4" s="76"/>
+      <c r="S4" s="76"/>
+      <c r="T4" s="76"/>
+      <c r="U4" s="75"/>
+      <c r="V4" s="75"/>
+      <c r="W4" s="75"/>
+      <c r="X4" s="75"/>
+      <c r="Y4" s="75"/>
+      <c r="Z4" s="75"/>
+      <c r="AA4" s="75"/>
+      <c r="AB4" s="75"/>
+      <c r="AC4" s="75"/>
+      <c r="AD4" s="75"/>
+      <c r="AE4" s="75"/>
+      <c r="AF4" s="75"/>
+      <c r="AG4" s="75"/>
+      <c r="AH4" s="75"/>
+      <c r="AI4" s="75"/>
+      <c r="AJ4" s="75"/>
+      <c r="AK4" s="75"/>
+      <c r="AL4" s="75"/>
+      <c r="AM4" s="75"/>
+      <c r="AN4" s="75"/>
+      <c r="AO4" s="75"/>
+      <c r="AP4" s="75"/>
+      <c r="AQ4" s="75"/>
+      <c r="AR4" s="75"/>
+      <c r="AS4" s="75"/>
+      <c r="AT4" s="75"/>
+      <c r="AU4" s="75"/>
+      <c r="AV4" s="77"/>
+      <c r="AW4" s="75"/>
+      <c r="AX4" s="75"/>
+      <c r="AY4" s="75"/>
+      <c r="AZ4" s="75"/>
+      <c r="BA4" s="75"/>
+      <c r="BB4" s="75"/>
+      <c r="BC4" s="77"/>
+      <c r="BD4" s="75"/>
+      <c r="BE4" s="75"/>
+      <c r="BF4" s="75"/>
+      <c r="BG4" s="75"/>
+      <c r="BH4" s="75"/>
+      <c r="BI4" s="77"/>
+      <c r="BJ4" s="78"/>
+      <c r="BK4" s="66"/>
+      <c r="BL4" s="67"/>
+      <c r="BM4" s="68"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="69" t="n">
+        <f aca="false">[1]Netzplan!J5</f>
+        <v>2</v>
+      </c>
+      <c r="H5" s="70" t="n">
+        <f aca="false">SUM(I5:BJ5)</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="75"/>
+      <c r="J5" s="75"/>
+      <c r="K5" s="75"/>
+      <c r="L5" s="76"/>
+      <c r="M5" s="76"/>
+      <c r="N5" s="75"/>
+      <c r="O5" s="75"/>
+      <c r="P5" s="75"/>
+      <c r="Q5" s="76"/>
+      <c r="R5" s="76"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="75"/>
+      <c r="U5" s="75"/>
+      <c r="V5" s="75"/>
+      <c r="W5" s="75"/>
+      <c r="X5" s="75"/>
+      <c r="Y5" s="75"/>
+      <c r="Z5" s="75"/>
+      <c r="AA5" s="75"/>
+      <c r="AB5" s="75"/>
+      <c r="AC5" s="75"/>
+      <c r="AD5" s="75"/>
+      <c r="AE5" s="75"/>
+      <c r="AF5" s="75"/>
+      <c r="AG5" s="75"/>
+      <c r="AH5" s="75"/>
+      <c r="AI5" s="75"/>
+      <c r="AJ5" s="75"/>
+      <c r="AK5" s="75"/>
+      <c r="AL5" s="75"/>
+      <c r="AM5" s="75"/>
+      <c r="AN5" s="75"/>
+      <c r="AO5" s="75"/>
+      <c r="AP5" s="75"/>
+      <c r="AQ5" s="75"/>
+      <c r="AR5" s="75"/>
+      <c r="AS5" s="75"/>
+      <c r="AT5" s="75"/>
+      <c r="AU5" s="75"/>
+      <c r="AV5" s="77"/>
+      <c r="AW5" s="75"/>
+      <c r="AX5" s="75"/>
+      <c r="AY5" s="75"/>
+      <c r="AZ5" s="75"/>
+      <c r="BA5" s="75"/>
+      <c r="BB5" s="75"/>
+      <c r="BC5" s="77"/>
+      <c r="BD5" s="75"/>
+      <c r="BE5" s="75"/>
+      <c r="BF5" s="75"/>
+      <c r="BG5" s="75"/>
+      <c r="BH5" s="75"/>
+      <c r="BI5" s="77"/>
+      <c r="BJ5" s="78"/>
+      <c r="BK5" s="66"/>
+      <c r="BL5" s="67"/>
+      <c r="BM5" s="68"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="69" t="n">
+        <f aca="false">[1]Netzplan!J6</f>
+        <v>4</v>
+      </c>
+      <c r="H6" s="70" t="n">
+        <f aca="false">SUM(I6:BJ6)</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="75"/>
+      <c r="J6" s="75"/>
+      <c r="K6" s="75"/>
+      <c r="L6" s="75"/>
+      <c r="M6" s="75"/>
+      <c r="N6" s="75"/>
+      <c r="O6" s="75"/>
+      <c r="P6" s="76"/>
+      <c r="Q6" s="76"/>
+      <c r="R6" s="76"/>
+      <c r="S6" s="76"/>
+      <c r="T6" s="76"/>
+      <c r="U6" s="75"/>
+      <c r="V6" s="75"/>
+      <c r="W6" s="76"/>
+      <c r="X6" s="76"/>
+      <c r="Y6" s="76"/>
+      <c r="Z6" s="76"/>
+      <c r="AA6" s="79"/>
+      <c r="AB6" s="75"/>
+      <c r="AC6" s="75"/>
+      <c r="AD6" s="75"/>
+      <c r="AE6" s="75"/>
+      <c r="AF6" s="75"/>
+      <c r="AG6" s="75"/>
+      <c r="AH6" s="75"/>
+      <c r="AI6" s="75"/>
+      <c r="AJ6" s="75"/>
+      <c r="AK6" s="75"/>
+      <c r="AL6" s="75"/>
+      <c r="AM6" s="75"/>
+      <c r="AN6" s="75"/>
+      <c r="AO6" s="75"/>
+      <c r="AP6" s="75"/>
+      <c r="AQ6" s="75"/>
+      <c r="AR6" s="75"/>
+      <c r="AS6" s="75"/>
+      <c r="AT6" s="75"/>
+      <c r="AU6" s="75"/>
+      <c r="AV6" s="77"/>
+      <c r="AW6" s="75"/>
+      <c r="AX6" s="75"/>
+      <c r="AY6" s="75"/>
+      <c r="AZ6" s="75"/>
+      <c r="BA6" s="75"/>
+      <c r="BB6" s="75"/>
+      <c r="BC6" s="77"/>
+      <c r="BD6" s="75"/>
+      <c r="BE6" s="75"/>
+      <c r="BF6" s="75"/>
+      <c r="BG6" s="75"/>
+      <c r="BH6" s="75"/>
+      <c r="BI6" s="77"/>
+      <c r="BJ6" s="78"/>
+      <c r="BK6" s="66"/>
+      <c r="BL6" s="67"/>
+      <c r="BM6" s="68"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="69" t="n">
+        <f aca="false">[1]Netzplan!J7</f>
+        <v>1</v>
+      </c>
+      <c r="H7" s="70" t="n">
+        <f aca="false">SUM(I7:BJ7)</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="75"/>
+      <c r="J7" s="75"/>
+      <c r="K7" s="75"/>
+      <c r="L7" s="75"/>
+      <c r="M7" s="75"/>
+      <c r="N7" s="75"/>
+      <c r="O7" s="75"/>
+      <c r="P7" s="76"/>
+      <c r="Q7" s="75"/>
+      <c r="R7" s="75"/>
+      <c r="S7" s="75"/>
+      <c r="T7" s="75"/>
+      <c r="U7" s="75"/>
+      <c r="V7" s="75"/>
+      <c r="W7" s="75"/>
+      <c r="X7" s="75"/>
+      <c r="Y7" s="75"/>
+      <c r="Z7" s="75"/>
+      <c r="AA7" s="75"/>
+      <c r="AB7" s="75"/>
+      <c r="AC7" s="75"/>
+      <c r="AD7" s="75"/>
+      <c r="AE7" s="75"/>
+      <c r="AF7" s="75"/>
+      <c r="AG7" s="75"/>
+      <c r="AH7" s="75"/>
+      <c r="AI7" s="75"/>
+      <c r="AJ7" s="75"/>
+      <c r="AK7" s="75"/>
+      <c r="AL7" s="75"/>
+      <c r="AM7" s="75"/>
+      <c r="AN7" s="75"/>
+      <c r="AO7" s="75"/>
+      <c r="AP7" s="75"/>
+      <c r="AQ7" s="75"/>
+      <c r="AR7" s="75"/>
+      <c r="AS7" s="75"/>
+      <c r="AT7" s="75"/>
+      <c r="AU7" s="75"/>
+      <c r="AV7" s="77"/>
+      <c r="AW7" s="75"/>
+      <c r="AX7" s="75"/>
+      <c r="AY7" s="75"/>
+      <c r="AZ7" s="75"/>
+      <c r="BA7" s="75"/>
+      <c r="BB7" s="75"/>
+      <c r="BC7" s="77"/>
+      <c r="BD7" s="75"/>
+      <c r="BE7" s="75"/>
+      <c r="BF7" s="75"/>
+      <c r="BG7" s="75"/>
+      <c r="BH7" s="75"/>
+      <c r="BI7" s="77"/>
+      <c r="BJ7" s="78"/>
+      <c r="BK7" s="66"/>
+      <c r="BL7" s="67"/>
+      <c r="BM7" s="68"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="42" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8" s="69" t="n">
+        <f aca="false">[1]Netzplan!J8</f>
+        <v>6</v>
+      </c>
+      <c r="H8" s="70" t="n">
+        <f aca="false">SUM(I8:BJ8)</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="75"/>
+      <c r="J8" s="75"/>
+      <c r="K8" s="75"/>
+      <c r="L8" s="76"/>
+      <c r="M8" s="76"/>
+      <c r="N8" s="75"/>
+      <c r="O8" s="75"/>
+      <c r="P8" s="76"/>
+      <c r="Q8" s="76"/>
+      <c r="R8" s="76"/>
+      <c r="S8" s="76"/>
+      <c r="T8" s="75"/>
+      <c r="U8" s="75"/>
+      <c r="V8" s="75"/>
+      <c r="W8" s="75"/>
+      <c r="X8" s="75"/>
+      <c r="Y8" s="75"/>
+      <c r="Z8" s="75"/>
+      <c r="AA8" s="75"/>
+      <c r="AB8" s="75"/>
+      <c r="AC8" s="75"/>
+      <c r="AD8" s="75"/>
+      <c r="AE8" s="75"/>
+      <c r="AF8" s="75"/>
+      <c r="AG8" s="75"/>
+      <c r="AH8" s="75"/>
+      <c r="AI8" s="75"/>
+      <c r="AJ8" s="75"/>
+      <c r="AK8" s="75"/>
+      <c r="AL8" s="75"/>
+      <c r="AM8" s="75"/>
+      <c r="AN8" s="75"/>
+      <c r="AO8" s="75"/>
+      <c r="AP8" s="75"/>
+      <c r="AQ8" s="75"/>
+      <c r="AR8" s="75"/>
+      <c r="AS8" s="75"/>
+      <c r="AT8" s="75"/>
+      <c r="AU8" s="75"/>
+      <c r="AV8" s="77"/>
+      <c r="AW8" s="75"/>
+      <c r="AX8" s="75"/>
+      <c r="AY8" s="75"/>
+      <c r="AZ8" s="75"/>
+      <c r="BA8" s="75"/>
+      <c r="BB8" s="75"/>
+      <c r="BC8" s="77"/>
+      <c r="BD8" s="75"/>
+      <c r="BE8" s="75"/>
+      <c r="BF8" s="75"/>
+      <c r="BG8" s="75"/>
+      <c r="BH8" s="75"/>
+      <c r="BI8" s="77"/>
+      <c r="BJ8" s="78"/>
+      <c r="BK8" s="66"/>
+      <c r="BL8" s="67"/>
+      <c r="BM8" s="68"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="42" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="69" t="n">
+        <f aca="false">[1]Netzplan!J9</f>
+        <v>2</v>
+      </c>
+      <c r="H9" s="70" t="n">
+        <f aca="false">SUM(I9:BJ9)</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="75"/>
+      <c r="J9" s="75"/>
+      <c r="K9" s="75"/>
+      <c r="L9" s="75"/>
+      <c r="M9" s="75"/>
+      <c r="N9" s="75"/>
+      <c r="O9" s="75"/>
+      <c r="P9" s="75"/>
+      <c r="Q9" s="75"/>
+      <c r="R9" s="75"/>
+      <c r="S9" s="75"/>
+      <c r="T9" s="76"/>
+      <c r="U9" s="75"/>
+      <c r="V9" s="75"/>
+      <c r="W9" s="76"/>
+      <c r="X9" s="76"/>
+      <c r="Y9" s="76"/>
+      <c r="Z9" s="76"/>
+      <c r="AA9" s="78"/>
+      <c r="AB9" s="75"/>
+      <c r="AC9" s="75"/>
+      <c r="AD9" s="76"/>
+      <c r="AE9" s="75"/>
+      <c r="AF9" s="75"/>
+      <c r="AG9" s="75"/>
+      <c r="AH9" s="75"/>
+      <c r="AI9" s="75"/>
+      <c r="AJ9" s="75"/>
+      <c r="AK9" s="75"/>
+      <c r="AL9" s="75"/>
+      <c r="AM9" s="75"/>
+      <c r="AN9" s="75"/>
+      <c r="AO9" s="75"/>
+      <c r="AP9" s="75"/>
+      <c r="AQ9" s="75"/>
+      <c r="AR9" s="75"/>
+      <c r="AS9" s="75"/>
+      <c r="AT9" s="75"/>
+      <c r="AU9" s="75"/>
+      <c r="AV9" s="77"/>
+      <c r="AW9" s="75"/>
+      <c r="AX9" s="75"/>
+      <c r="AY9" s="75"/>
+      <c r="AZ9" s="75"/>
+      <c r="BA9" s="75"/>
+      <c r="BB9" s="75"/>
+      <c r="BC9" s="77"/>
+      <c r="BD9" s="75"/>
+      <c r="BE9" s="75"/>
+      <c r="BF9" s="75"/>
+      <c r="BG9" s="75"/>
+      <c r="BH9" s="75"/>
+      <c r="BI9" s="77"/>
+      <c r="BJ9" s="78"/>
+      <c r="BK9" s="66"/>
+      <c r="BL9" s="67"/>
+      <c r="BM9" s="68"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="69" t="n">
+        <f aca="false">[1]Netzplan!J10</f>
+        <v>2</v>
+      </c>
+      <c r="H10" s="70" t="n">
+        <f aca="false">SUM(I10:BJ10)</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="75"/>
+      <c r="J10" s="75"/>
+      <c r="K10" s="75"/>
+      <c r="L10" s="75"/>
+      <c r="M10" s="75"/>
+      <c r="N10" s="75"/>
+      <c r="O10" s="75"/>
+      <c r="P10" s="75"/>
+      <c r="Q10" s="75"/>
+      <c r="R10" s="75"/>
+      <c r="S10" s="75"/>
+      <c r="T10" s="75"/>
+      <c r="U10" s="75"/>
+      <c r="V10" s="75"/>
+      <c r="W10" s="75"/>
+      <c r="X10" s="76"/>
+      <c r="Y10" s="76"/>
+      <c r="Z10" s="75"/>
+      <c r="AA10" s="75"/>
+      <c r="AB10" s="75"/>
+      <c r="AC10" s="75"/>
+      <c r="AE10" s="78"/>
+      <c r="AF10" s="75"/>
+      <c r="AG10" s="75"/>
+      <c r="AH10" s="75"/>
+      <c r="AI10" s="75"/>
+      <c r="AJ10" s="75"/>
+      <c r="AK10" s="75"/>
+      <c r="AL10" s="75"/>
+      <c r="AM10" s="75"/>
+      <c r="AN10" s="75"/>
+      <c r="AO10" s="75"/>
+      <c r="AP10" s="75"/>
+      <c r="AQ10" s="75"/>
+      <c r="AR10" s="75"/>
+      <c r="AS10" s="75"/>
+      <c r="AT10" s="75"/>
+      <c r="AU10" s="75"/>
+      <c r="AV10" s="77"/>
+      <c r="AW10" s="75"/>
+      <c r="AX10" s="75"/>
+      <c r="AY10" s="75"/>
+      <c r="AZ10" s="75"/>
+      <c r="BA10" s="75"/>
+      <c r="BB10" s="75"/>
+      <c r="BC10" s="77"/>
+      <c r="BD10" s="75"/>
+      <c r="BE10" s="75"/>
+      <c r="BF10" s="75"/>
+      <c r="BG10" s="75"/>
+      <c r="BH10" s="75"/>
+      <c r="BI10" s="77"/>
+      <c r="BJ10" s="78"/>
+      <c r="BK10" s="66"/>
+      <c r="BL10" s="67"/>
+      <c r="BM10" s="68"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="69" t="n">
+        <f aca="false">[1]Netzplan!J11</f>
+        <v>2</v>
+      </c>
+      <c r="H11" s="70" t="n">
+        <f aca="false">SUM(I11:BJ11)</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="75"/>
+      <c r="J11" s="75"/>
+      <c r="K11" s="75"/>
+      <c r="L11" s="75"/>
+      <c r="M11" s="75"/>
+      <c r="N11" s="75"/>
+      <c r="O11" s="75"/>
+      <c r="P11" s="75"/>
+      <c r="Q11" s="75"/>
+      <c r="R11" s="75"/>
+      <c r="S11" s="75"/>
+      <c r="T11" s="75"/>
+      <c r="U11" s="75"/>
+      <c r="V11" s="75"/>
+      <c r="W11" s="75"/>
+      <c r="X11" s="75"/>
+      <c r="Y11" s="75"/>
+      <c r="Z11" s="76"/>
+      <c r="AA11" s="76"/>
+      <c r="AB11" s="75"/>
+      <c r="AC11" s="75"/>
+      <c r="AE11" s="78"/>
+      <c r="AF11" s="75"/>
+      <c r="AG11" s="76"/>
+      <c r="AH11" s="76"/>
+      <c r="AI11" s="75"/>
+      <c r="AJ11" s="75"/>
+      <c r="AK11" s="75"/>
+      <c r="AL11" s="75"/>
+      <c r="AM11" s="75"/>
+      <c r="AN11" s="75"/>
+      <c r="AO11" s="75"/>
+      <c r="AP11" s="75"/>
+      <c r="AQ11" s="75"/>
+      <c r="AR11" s="75"/>
+      <c r="AS11" s="75"/>
+      <c r="AT11" s="75"/>
+      <c r="AU11" s="75"/>
+      <c r="AV11" s="77"/>
+      <c r="AW11" s="75"/>
+      <c r="AX11" s="75"/>
+      <c r="AY11" s="75"/>
+      <c r="AZ11" s="75"/>
+      <c r="BA11" s="75"/>
+      <c r="BB11" s="75"/>
+      <c r="BC11" s="77"/>
+      <c r="BD11" s="75"/>
+      <c r="BE11" s="75"/>
+      <c r="BF11" s="75"/>
+      <c r="BG11" s="75"/>
+      <c r="BH11" s="75"/>
+      <c r="BI11" s="77"/>
+      <c r="BJ11" s="78"/>
+      <c r="BK11" s="66"/>
+      <c r="BL11" s="67"/>
+      <c r="BM11" s="68"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="69" t="n">
+        <f aca="false">[1]Netzplan!J12</f>
+        <v>20</v>
+      </c>
+      <c r="H12" s="70" t="n">
+        <f aca="false">SUM(I12:BJ12)</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="75"/>
+      <c r="J12" s="75"/>
+      <c r="K12" s="75"/>
+      <c r="L12" s="75"/>
+      <c r="M12" s="75"/>
+      <c r="N12" s="75"/>
+      <c r="O12" s="75"/>
+      <c r="P12" s="75"/>
+      <c r="Q12" s="75"/>
+      <c r="R12" s="75"/>
+      <c r="S12" s="75"/>
+      <c r="T12" s="76"/>
+      <c r="U12" s="75"/>
+      <c r="V12" s="75"/>
+      <c r="W12" s="76"/>
+      <c r="X12" s="76"/>
+      <c r="Y12" s="76"/>
+      <c r="Z12" s="76"/>
+      <c r="AA12" s="76"/>
+      <c r="AB12" s="75"/>
+      <c r="AC12" s="75"/>
+      <c r="AD12" s="76"/>
+      <c r="AE12" s="76"/>
+      <c r="AF12" s="76"/>
+      <c r="AG12" s="76"/>
+      <c r="AH12" s="76"/>
+      <c r="AI12" s="75"/>
+      <c r="AJ12" s="75"/>
+      <c r="AK12" s="76"/>
+      <c r="AL12" s="76"/>
+      <c r="AM12" s="76"/>
+      <c r="AN12" s="76"/>
+      <c r="AO12" s="76"/>
+      <c r="AP12" s="75"/>
+      <c r="AQ12" s="75"/>
+      <c r="AR12" s="76"/>
+      <c r="AS12" s="76"/>
+      <c r="AT12" s="76"/>
+      <c r="AU12" s="76"/>
+      <c r="AV12" s="80"/>
+      <c r="AW12" s="75"/>
+      <c r="AX12" s="75"/>
+      <c r="AY12" s="76"/>
+      <c r="AZ12" s="76"/>
+      <c r="BA12" s="76"/>
+      <c r="BB12" s="76"/>
+      <c r="BC12" s="77"/>
+      <c r="BD12" s="75"/>
+      <c r="BE12" s="75"/>
+      <c r="BF12" s="75"/>
+      <c r="BG12" s="75"/>
+      <c r="BH12" s="75"/>
+      <c r="BI12" s="77"/>
+      <c r="BJ12" s="78"/>
+      <c r="BK12" s="66"/>
+      <c r="BL12" s="67"/>
+      <c r="BM12" s="68"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="42" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" s="69" t="n">
+        <f aca="false">[1]Netzplan!J13</f>
+        <v>2</v>
+      </c>
+      <c r="H13" s="70" t="n">
+        <f aca="false">SUM(I13:BJ13)</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="75"/>
+      <c r="J13" s="75"/>
+      <c r="K13" s="75"/>
+      <c r="L13" s="75"/>
+      <c r="M13" s="75"/>
+      <c r="N13" s="75"/>
+      <c r="O13" s="75"/>
+      <c r="P13" s="75"/>
+      <c r="Q13" s="75"/>
+      <c r="R13" s="75"/>
+      <c r="S13" s="75"/>
+      <c r="T13" s="75"/>
+      <c r="U13" s="75"/>
+      <c r="V13" s="75"/>
+      <c r="W13" s="75"/>
+      <c r="X13" s="75"/>
+      <c r="Y13" s="75"/>
+      <c r="Z13" s="75"/>
+      <c r="AA13" s="75"/>
+      <c r="AB13" s="75"/>
+      <c r="AC13" s="75"/>
+      <c r="AE13" s="76"/>
+      <c r="AF13" s="76"/>
+      <c r="AG13" s="75"/>
+      <c r="AH13" s="75"/>
+      <c r="AI13" s="75"/>
+      <c r="AJ13" s="75"/>
+      <c r="AK13" s="76"/>
+      <c r="AL13" s="76"/>
+      <c r="AM13" s="76"/>
+      <c r="AN13" s="76"/>
+      <c r="AO13" s="76"/>
+      <c r="AP13" s="75"/>
+      <c r="AQ13" s="75"/>
+      <c r="AR13" s="75"/>
+      <c r="AS13" s="75"/>
+      <c r="AT13" s="75"/>
+      <c r="AU13" s="75"/>
+      <c r="AV13" s="77"/>
+      <c r="AW13" s="75"/>
+      <c r="AX13" s="75"/>
+      <c r="AY13" s="75"/>
+      <c r="AZ13" s="75"/>
+      <c r="BA13" s="75"/>
+      <c r="BB13" s="75"/>
+      <c r="BC13" s="77"/>
+      <c r="BD13" s="75"/>
+      <c r="BE13" s="75"/>
+      <c r="BF13" s="75"/>
+      <c r="BG13" s="75"/>
+      <c r="BH13" s="75"/>
+      <c r="BI13" s="77"/>
+      <c r="BJ13" s="78"/>
+      <c r="BK13" s="66"/>
+      <c r="BL13" s="67"/>
+      <c r="BM13" s="68"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" s="42" t="s">
+        <v>29</v>
+      </c>
+      <c r="G14" s="69" t="n">
+        <f aca="false">[1]Netzplan!J14</f>
+        <v>2</v>
+      </c>
+      <c r="H14" s="70" t="n">
+        <f aca="false">SUM(I14:BJ14)</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="75"/>
+      <c r="J14" s="75"/>
+      <c r="K14" s="75"/>
+      <c r="L14" s="75"/>
+      <c r="M14" s="75"/>
+      <c r="N14" s="75"/>
+      <c r="O14" s="75"/>
+      <c r="P14" s="75"/>
+      <c r="Q14" s="75"/>
+      <c r="R14" s="75"/>
+      <c r="S14" s="75"/>
+      <c r="T14" s="75"/>
+      <c r="U14" s="75"/>
+      <c r="V14" s="75"/>
+      <c r="W14" s="75"/>
+      <c r="X14" s="75"/>
+      <c r="Y14" s="75"/>
+      <c r="Z14" s="75"/>
+      <c r="AA14" s="75"/>
+      <c r="AB14" s="75"/>
+      <c r="AC14" s="75"/>
+      <c r="AD14" s="75"/>
+      <c r="AE14" s="75"/>
+      <c r="AG14" s="75"/>
+      <c r="AH14" s="75"/>
+      <c r="AI14" s="75"/>
+      <c r="AJ14" s="75"/>
+      <c r="AL14" s="75"/>
+      <c r="AM14" s="75"/>
+      <c r="AN14" s="75"/>
+      <c r="AO14" s="76"/>
+      <c r="AP14" s="75"/>
+      <c r="AQ14" s="75"/>
+      <c r="AR14" s="76"/>
+      <c r="AS14" s="76"/>
+      <c r="AT14" s="76"/>
+      <c r="AU14" s="75"/>
+      <c r="AV14" s="77"/>
+      <c r="AW14" s="75"/>
+      <c r="AX14" s="75"/>
+      <c r="AY14" s="75"/>
+      <c r="AZ14" s="75"/>
+      <c r="BA14" s="75"/>
+      <c r="BB14" s="75"/>
+      <c r="BC14" s="77"/>
+      <c r="BD14" s="75"/>
+      <c r="BE14" s="75"/>
+      <c r="BF14" s="75"/>
+      <c r="BG14" s="75"/>
+      <c r="BH14" s="75"/>
+      <c r="BI14" s="77"/>
+      <c r="BJ14" s="78"/>
+      <c r="BK14" s="66"/>
+      <c r="BL14" s="67"/>
+      <c r="BM14" s="68"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="42" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="G15" s="69" t="n">
+        <f aca="false">[1]Netzplan!J15</f>
+        <v>1</v>
+      </c>
+      <c r="H15" s="70" t="n">
+        <f aca="false">SUM(I15:BJ15)</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="75"/>
+      <c r="J15" s="75"/>
+      <c r="K15" s="75"/>
+      <c r="L15" s="75"/>
+      <c r="M15" s="75"/>
+      <c r="N15" s="75"/>
+      <c r="O15" s="75"/>
+      <c r="P15" s="75"/>
+      <c r="Q15" s="75"/>
+      <c r="R15" s="75"/>
+      <c r="S15" s="75"/>
+      <c r="T15" s="75"/>
+      <c r="U15" s="75"/>
+      <c r="V15" s="75"/>
+      <c r="W15" s="75"/>
+      <c r="X15" s="75"/>
+      <c r="Y15" s="75"/>
+      <c r="Z15" s="75"/>
+      <c r="AA15" s="75"/>
+      <c r="AB15" s="75"/>
+      <c r="AC15" s="75"/>
+      <c r="AD15" s="75"/>
+      <c r="AE15" s="75"/>
+      <c r="AF15" s="75"/>
+      <c r="AG15" s="75"/>
+      <c r="AI15" s="75"/>
+      <c r="AJ15" s="75"/>
+      <c r="AL15" s="75"/>
+      <c r="AM15" s="75"/>
+      <c r="AO15" s="75"/>
+      <c r="AP15" s="75"/>
+      <c r="AQ15" s="75"/>
+      <c r="AR15" s="78"/>
+      <c r="AS15" s="76"/>
+      <c r="AT15" s="75"/>
+      <c r="AU15" s="75"/>
+      <c r="AV15" s="77"/>
+      <c r="AW15" s="75"/>
+      <c r="AX15" s="75"/>
+      <c r="AY15" s="75"/>
+      <c r="AZ15" s="75"/>
+      <c r="BA15" s="75"/>
+      <c r="BB15" s="75"/>
+      <c r="BC15" s="77"/>
+      <c r="BD15" s="75"/>
+      <c r="BE15" s="75"/>
+      <c r="BF15" s="75"/>
+      <c r="BG15" s="75"/>
+      <c r="BH15" s="75"/>
+      <c r="BI15" s="77"/>
+      <c r="BJ15" s="78"/>
+      <c r="BK15" s="66"/>
+      <c r="BL15" s="67"/>
+      <c r="BM15" s="68"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="42" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="G16" s="69" t="n">
+        <f aca="false">[1]Netzplan!J16</f>
+        <v>4</v>
+      </c>
+      <c r="H16" s="70" t="n">
+        <f aca="false">SUM(I16:BJ16)</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="75"/>
+      <c r="J16" s="75"/>
+      <c r="K16" s="75"/>
+      <c r="L16" s="75"/>
+      <c r="M16" s="75"/>
+      <c r="N16" s="75"/>
+      <c r="O16" s="75"/>
+      <c r="P16" s="75"/>
+      <c r="Q16" s="75"/>
+      <c r="R16" s="75"/>
+      <c r="S16" s="75"/>
+      <c r="T16" s="75"/>
+      <c r="U16" s="75"/>
+      <c r="V16" s="75"/>
+      <c r="W16" s="75"/>
+      <c r="X16" s="75"/>
+      <c r="Y16" s="75"/>
+      <c r="Z16" s="75"/>
+      <c r="AA16" s="75"/>
+      <c r="AB16" s="75"/>
+      <c r="AC16" s="75"/>
+      <c r="AD16" s="75"/>
+      <c r="AE16" s="75"/>
+      <c r="AF16" s="75"/>
+      <c r="AG16" s="75"/>
+      <c r="AH16" s="75"/>
+      <c r="AI16" s="75"/>
+      <c r="AJ16" s="75"/>
+      <c r="AL16" s="75"/>
+      <c r="AM16" s="78"/>
+      <c r="AN16" s="78"/>
+      <c r="AO16" s="75"/>
+      <c r="AP16" s="75"/>
+      <c r="AQ16" s="75"/>
+      <c r="AR16" s="75"/>
+      <c r="AS16" s="75"/>
+      <c r="AT16" s="75"/>
+      <c r="AU16" s="76"/>
+      <c r="AV16" s="77"/>
+      <c r="AW16" s="75"/>
+      <c r="AX16" s="75"/>
+      <c r="AY16" s="76"/>
+      <c r="AZ16" s="76"/>
+      <c r="BA16" s="76"/>
+      <c r="BB16" s="75"/>
+      <c r="BC16" s="77"/>
+      <c r="BD16" s="75"/>
+      <c r="BE16" s="75"/>
+      <c r="BF16" s="75"/>
+      <c r="BG16" s="75"/>
+      <c r="BH16" s="75"/>
+      <c r="BI16" s="77"/>
+      <c r="BJ16" s="78"/>
+      <c r="BK16" s="66"/>
+      <c r="BL16" s="67"/>
+      <c r="BM16" s="68"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="49" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" s="50"/>
+      <c r="G17" s="69" t="n">
+        <f aca="false">[1]Netzplan!J17</f>
+        <v>1</v>
+      </c>
+      <c r="H17" s="70" t="n">
+        <f aca="false">SUM(I17:BJ17)</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="81"/>
+      <c r="J17" s="81"/>
+      <c r="K17" s="81"/>
+      <c r="L17" s="81"/>
+      <c r="M17" s="81"/>
+      <c r="N17" s="81"/>
+      <c r="O17" s="81"/>
+      <c r="P17" s="81"/>
+      <c r="Q17" s="81"/>
+      <c r="R17" s="81"/>
+      <c r="S17" s="81"/>
+      <c r="T17" s="81"/>
+      <c r="U17" s="81"/>
+      <c r="V17" s="81"/>
+      <c r="W17" s="81"/>
+      <c r="X17" s="81"/>
+      <c r="Y17" s="81"/>
+      <c r="Z17" s="81"/>
+      <c r="AA17" s="81"/>
+      <c r="AB17" s="81"/>
+      <c r="AC17" s="81"/>
+      <c r="AD17" s="81"/>
+      <c r="AE17" s="81"/>
+      <c r="AF17" s="81"/>
+      <c r="AG17" s="81"/>
+      <c r="AH17" s="81"/>
+      <c r="AI17" s="81"/>
+      <c r="AJ17" s="81"/>
+      <c r="AK17" s="81"/>
+      <c r="AL17" s="81"/>
+      <c r="AM17" s="81"/>
+      <c r="AN17" s="81"/>
+      <c r="AO17" s="81"/>
+      <c r="AP17" s="81"/>
+      <c r="AQ17" s="81"/>
+      <c r="AR17" s="81"/>
+      <c r="AS17" s="81"/>
+      <c r="AT17" s="81"/>
+      <c r="AU17" s="81"/>
+      <c r="AV17" s="82"/>
+      <c r="AW17" s="81"/>
+      <c r="AX17" s="81"/>
+      <c r="AY17" s="83"/>
+      <c r="AZ17" s="83"/>
+      <c r="BA17" s="81"/>
+      <c r="BB17" s="81"/>
+      <c r="BC17" s="82"/>
+      <c r="BD17" s="81"/>
+      <c r="BE17" s="81"/>
+      <c r="BF17" s="81"/>
+      <c r="BG17" s="81"/>
+      <c r="BH17" s="81"/>
+      <c r="BI17" s="82"/>
+      <c r="BJ17" s="84"/>
+      <c r="BK17" s="66"/>
+      <c r="BL17" s="67"/>
+      <c r="BM17" s="68"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
+        <v>78</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+  </mergeCells>
+  <conditionalFormatting sqref="I1:BF9 I10:AC13 AE10:BF11 I17:BF17 AL14:BF14 AL15:AM15 AO15:BF15 AD12:BF12 AE13:BF13 I14:AE14 AG14:AJ14 I15:AG15 I16:AJ16 AI15:AJ15 AL16:BF16">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>IF(OR(WEEKDAY(I$1)=7,WEEKDAY(I$1)=1),1,0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H2:H17">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>IF(H2&lt;&gt;G2,TRUE())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I10:AC13 AE10:BF11 I17:BF17 AL14:BF14 AL15:AM15 AO15:BF15 I2:BF9 AD12:BF12 AE13:BF13 I14:AE14 AG14:AJ14 I15:AG15 I16:AJ16 AI15:AJ15 AL16:BF16">
+    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
--- a/Übungen/Online_Shop.xlsx
+++ b/Übungen/Online_Shop.xlsx
@@ -12,9 +12,6 @@
     <sheet name="Netzplan" sheetId="2" state="visible" r:id="rId3"/>
     <sheet name="Gantt" sheetId="3" state="visible" r:id="rId4"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId5"/>
-  </externalReferences>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -25,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="82">
   <si>
     <t xml:space="preserve">Beispiel: Funktionsorientierter Projektstrukturplan</t>
   </si>
@@ -260,6 +257,15 @@
   </si>
   <si>
     <t xml:space="preserve">FAZ + D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projektbeginn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vorbereitung Datenbank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abschluss Entwicklung</t>
   </si>
   <si>
     <t xml:space="preserve">Gantt</t>
@@ -365,7 +371,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -411,13 +417,25 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF8000"/>
-        <bgColor rgb="FFFF6600"/>
+        <bgColor rgb="FFFF8080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF4000"/>
+        <bgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFEEEEEE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF808080"/>
+        <bgColor rgb="FF969696"/>
       </patternFill>
     </fill>
   </fills>
@@ -541,7 +559,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="90">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -818,6 +836,22 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -830,6 +864,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="10" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -846,7 +884,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -862,7 +900,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="11" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -874,7 +912,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="9" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="10" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -994,7 +1032,7 @@
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFBF00"/>
       <rgbColor rgb="FFFF8000"/>
-      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FFFF4000"/>
       <rgbColor rgb="FF666666"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
@@ -1938,10 +1976,344 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</externalLink>
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>63360</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>153360</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>198360</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>152640</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8001360" y="1802880"/>
+          <a:ext cx="135000" cy="162000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:rect l="l" t="t" r="r" b="b"/>
+          <a:pathLst>
+            <a:path w="21600" h="21600">
+              <a:moveTo>
+                <a:pt x="10800" y="0"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="21600" y="10800"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="10800" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="0" y="10800"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="10800" y="0"/>
+              </a:lnTo>
+              <a:close/>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="729fcf"/>
+        </a:solidFill>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>32400</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>153000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>167400</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>152640</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9490680" y="2615400"/>
+          <a:ext cx="135000" cy="162000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:rect l="l" t="t" r="r" b="b"/>
+          <a:pathLst>
+            <a:path w="21600" h="21600">
+              <a:moveTo>
+                <a:pt x="10800" y="0"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="21600" y="10800"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="10800" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="0" y="10800"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="10800" y="0"/>
+              </a:lnTo>
+              <a:close/>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="729fcf"/>
+        </a:solidFill>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>64800</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>5760</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>199800</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>5400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12309840" y="3119760"/>
+          <a:ext cx="135000" cy="162000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:rect l="l" t="t" r="r" b="b"/>
+          <a:pathLst>
+            <a:path w="21600" h="21600">
+              <a:moveTo>
+                <a:pt x="10800" y="0"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="21600" y="10800"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="10800" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="0" y="10800"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="10800" y="0"/>
+              </a:lnTo>
+              <a:close/>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="729fcf"/>
+        </a:solidFill>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>69480</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>3960</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>204480</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>3600</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13834800" y="3443040"/>
+          <a:ext cx="135000" cy="162000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:rect l="l" t="t" r="r" b="b"/>
+          <a:pathLst>
+            <a:path w="21600" h="21600">
+              <a:moveTo>
+                <a:pt x="10800" y="0"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="21600" y="10800"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="10800" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="0" y="10800"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="10800" y="0"/>
+              </a:lnTo>
+              <a:close/>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="729fcf"/>
+        </a:solidFill>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>53280</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>503640</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>188280</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>154800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4190760" y="503640"/>
+          <a:ext cx="135000" cy="162000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:rect l="l" t="t" r="r" b="b"/>
+          <a:pathLst>
+            <a:path w="21600" h="21600">
+              <a:moveTo>
+                <a:pt x="10800" y="0"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="21600" y="10800"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="10800" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="0" y="10800"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="10800" y="0"/>
+              </a:lnTo>
+              <a:close/>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="729fcf"/>
+        </a:solidFill>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3893,7 +4265,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM20"/>
+  <dimension ref="A1:BM23"/>
   <sheetFormatPr defaultColWidth="11.77734375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="1"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="5" min="5" style="0" width="16.2"/>
@@ -4093,252 +4465,246 @@
       <c r="BM1" s="68"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="G2" s="69" t="n">
-        <f aca="false">[1]Netzplan!J2</f>
-        <v>2</v>
-      </c>
-      <c r="H2" s="70" t="n">
-        <f aca="false">SUM(I2:BJ2)</f>
-        <v>0</v>
-      </c>
-      <c r="I2" s="71"/>
-      <c r="J2" s="71"/>
-      <c r="K2" s="71"/>
-      <c r="L2" s="71"/>
-      <c r="M2" s="71"/>
-      <c r="N2" s="72"/>
-      <c r="O2" s="72"/>
-      <c r="P2" s="72"/>
-      <c r="Q2" s="72"/>
-      <c r="R2" s="72"/>
-      <c r="S2" s="72"/>
-      <c r="T2" s="72"/>
-      <c r="U2" s="72"/>
-      <c r="V2" s="72"/>
-      <c r="W2" s="72"/>
-      <c r="X2" s="72"/>
-      <c r="Y2" s="72"/>
-      <c r="Z2" s="72"/>
-      <c r="AA2" s="72"/>
-      <c r="AB2" s="72"/>
-      <c r="AC2" s="72"/>
-      <c r="AD2" s="72"/>
-      <c r="AE2" s="72"/>
-      <c r="AF2" s="72"/>
-      <c r="AG2" s="72"/>
-      <c r="AH2" s="72"/>
-      <c r="AI2" s="72"/>
-      <c r="AJ2" s="72"/>
-      <c r="AK2" s="72"/>
-      <c r="AL2" s="72"/>
-      <c r="AM2" s="72"/>
-      <c r="AN2" s="72"/>
-      <c r="AO2" s="72"/>
-      <c r="AP2" s="72"/>
-      <c r="AQ2" s="72"/>
-      <c r="AR2" s="72"/>
-      <c r="AS2" s="72"/>
-      <c r="AT2" s="72"/>
-      <c r="AU2" s="72"/>
-      <c r="AV2" s="73"/>
-      <c r="AW2" s="72"/>
-      <c r="AX2" s="72"/>
-      <c r="AY2" s="72"/>
-      <c r="AZ2" s="72"/>
-      <c r="BA2" s="72"/>
-      <c r="BB2" s="72"/>
-      <c r="BC2" s="73"/>
-      <c r="BD2" s="72"/>
-      <c r="BE2" s="72"/>
-      <c r="BF2" s="72"/>
-      <c r="BG2" s="72"/>
-      <c r="BH2" s="72"/>
-      <c r="BI2" s="73"/>
-      <c r="BJ2" s="74"/>
+      <c r="A2" s="69"/>
+      <c r="B2" s="70" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="64"/>
+      <c r="L2" s="64"/>
+      <c r="M2" s="64"/>
+      <c r="N2" s="64"/>
+      <c r="O2" s="64"/>
+      <c r="P2" s="64"/>
+      <c r="Q2" s="64"/>
+      <c r="R2" s="64"/>
+      <c r="S2" s="64"/>
+      <c r="T2" s="64"/>
+      <c r="U2" s="64"/>
+      <c r="V2" s="64"/>
+      <c r="W2" s="64"/>
+      <c r="X2" s="64"/>
+      <c r="Y2" s="64"/>
+      <c r="Z2" s="64"/>
+      <c r="AA2" s="64"/>
+      <c r="AB2" s="64"/>
+      <c r="AC2" s="64"/>
+      <c r="AD2" s="64"/>
+      <c r="AE2" s="64"/>
+      <c r="AF2" s="64"/>
+      <c r="AG2" s="64"/>
+      <c r="AH2" s="64"/>
+      <c r="AI2" s="64"/>
+      <c r="AJ2" s="64"/>
+      <c r="AK2" s="64"/>
+      <c r="AL2" s="64"/>
+      <c r="AM2" s="64"/>
+      <c r="AN2" s="64"/>
+      <c r="AO2" s="64"/>
+      <c r="AP2" s="64"/>
+      <c r="AQ2" s="64"/>
+      <c r="AR2" s="64"/>
+      <c r="AS2" s="64"/>
+      <c r="AT2" s="64"/>
+      <c r="AU2" s="64"/>
+      <c r="AV2" s="65"/>
+      <c r="AW2" s="64"/>
+      <c r="AX2" s="64"/>
+      <c r="AY2" s="64"/>
+      <c r="AZ2" s="64"/>
+      <c r="BA2" s="64"/>
+      <c r="BB2" s="64"/>
+      <c r="BC2" s="65"/>
+      <c r="BD2" s="64"/>
+      <c r="BE2" s="64"/>
+      <c r="BF2" s="64"/>
+      <c r="BG2" s="64"/>
+      <c r="BH2" s="64"/>
+      <c r="BI2" s="65"/>
+      <c r="BJ2" s="64"/>
       <c r="BK2" s="66"/>
       <c r="BL2" s="67"/>
       <c r="BM2" s="68"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="33" t="s">
+      <c r="A3" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="33" t="s">
-        <v>54</v>
-      </c>
-      <c r="G3" s="69" t="n">
-        <f aca="false">[1]Netzplan!J3</f>
-        <v>1</v>
-      </c>
-      <c r="H3" s="70" t="n">
+      <c r="B3" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="G3" s="73" t="n">
+        <f aca="false">Netzplan!J2</f>
+        <v>2</v>
+      </c>
+      <c r="H3" s="74" t="n">
         <f aca="false">SUM(I3:BJ3)</f>
-        <v>0</v>
-      </c>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
-      <c r="K3" s="75"/>
-      <c r="L3" s="75"/>
-      <c r="M3" s="75"/>
-      <c r="N3" s="75"/>
-      <c r="O3" s="75"/>
-      <c r="P3" s="76"/>
-      <c r="Q3" s="75"/>
-      <c r="R3" s="75"/>
-      <c r="S3" s="75"/>
-      <c r="T3" s="75"/>
-      <c r="U3" s="75"/>
-      <c r="V3" s="75"/>
-      <c r="W3" s="75"/>
-      <c r="X3" s="75"/>
-      <c r="Y3" s="75"/>
-      <c r="Z3" s="75"/>
-      <c r="AA3" s="75"/>
-      <c r="AB3" s="75"/>
-      <c r="AC3" s="75"/>
-      <c r="AD3" s="75"/>
-      <c r="AE3" s="75"/>
-      <c r="AF3" s="75"/>
-      <c r="AG3" s="75"/>
-      <c r="AH3" s="75"/>
-      <c r="AI3" s="75"/>
-      <c r="AJ3" s="75"/>
-      <c r="AK3" s="75"/>
-      <c r="AL3" s="75"/>
-      <c r="AM3" s="75"/>
-      <c r="AN3" s="75"/>
-      <c r="AO3" s="75"/>
-      <c r="AP3" s="75"/>
-      <c r="AQ3" s="75"/>
-      <c r="AR3" s="75"/>
-      <c r="AS3" s="75"/>
-      <c r="AT3" s="75"/>
-      <c r="AU3" s="75"/>
-      <c r="AV3" s="77"/>
-      <c r="AW3" s="75"/>
-      <c r="AX3" s="75"/>
-      <c r="AY3" s="75"/>
-      <c r="AZ3" s="75"/>
-      <c r="BA3" s="75"/>
-      <c r="BB3" s="75"/>
-      <c r="BC3" s="77"/>
-      <c r="BD3" s="75"/>
-      <c r="BE3" s="75"/>
-      <c r="BF3" s="75"/>
-      <c r="BG3" s="75"/>
-      <c r="BH3" s="75"/>
-      <c r="BI3" s="77"/>
-      <c r="BJ3" s="78"/>
+        <v>2</v>
+      </c>
+      <c r="I3" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" s="76"/>
+      <c r="L3" s="76"/>
+      <c r="M3" s="76"/>
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="77"/>
+      <c r="Q3" s="77"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="77"/>
+      <c r="T3" s="77"/>
+      <c r="U3" s="77"/>
+      <c r="V3" s="77"/>
+      <c r="W3" s="77"/>
+      <c r="X3" s="77"/>
+      <c r="Y3" s="77"/>
+      <c r="Z3" s="77"/>
+      <c r="AA3" s="77"/>
+      <c r="AB3" s="77"/>
+      <c r="AC3" s="77"/>
+      <c r="AD3" s="77"/>
+      <c r="AE3" s="77"/>
+      <c r="AF3" s="77"/>
+      <c r="AG3" s="77"/>
+      <c r="AH3" s="77"/>
+      <c r="AI3" s="77"/>
+      <c r="AJ3" s="77"/>
+      <c r="AK3" s="77"/>
+      <c r="AL3" s="77"/>
+      <c r="AM3" s="77"/>
+      <c r="AN3" s="77"/>
+      <c r="AO3" s="77"/>
+      <c r="AP3" s="77"/>
+      <c r="AQ3" s="77"/>
+      <c r="AR3" s="77"/>
+      <c r="AS3" s="77"/>
+      <c r="AT3" s="77"/>
+      <c r="AU3" s="77"/>
+      <c r="AV3" s="78"/>
+      <c r="AW3" s="77"/>
+      <c r="AX3" s="77"/>
+      <c r="AY3" s="77"/>
+      <c r="AZ3" s="77"/>
+      <c r="BA3" s="77"/>
+      <c r="BB3" s="77"/>
+      <c r="BC3" s="78"/>
+      <c r="BD3" s="77"/>
+      <c r="BE3" s="77"/>
+      <c r="BF3" s="77"/>
+      <c r="BG3" s="77"/>
+      <c r="BH3" s="77"/>
+      <c r="BI3" s="78"/>
+      <c r="BJ3" s="79"/>
       <c r="BK3" s="66"/>
       <c r="BL3" s="67"/>
       <c r="BM3" s="68"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C4" s="15"/>
       <c r="D4" s="15"/>
       <c r="E4" s="33" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F4" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="G4" s="69" t="n">
-        <f aca="false">[1]Netzplan!J4</f>
-        <v>6</v>
-      </c>
-      <c r="H4" s="70" t="n">
+        <v>54</v>
+      </c>
+      <c r="G4" s="73" t="n">
+        <f aca="false">Netzplan!J3</f>
+        <v>1</v>
+      </c>
+      <c r="H4" s="74" t="n">
         <f aca="false">SUM(I4:BJ4)</f>
-        <v>0</v>
-      </c>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
-      <c r="K4" s="75"/>
-      <c r="L4" s="75"/>
-      <c r="M4" s="75"/>
-      <c r="N4" s="75"/>
-      <c r="O4" s="75"/>
-      <c r="P4" s="75"/>
-      <c r="Q4" s="76"/>
-      <c r="R4" s="76"/>
-      <c r="S4" s="76"/>
-      <c r="T4" s="76"/>
-      <c r="U4" s="75"/>
-      <c r="V4" s="75"/>
-      <c r="W4" s="75"/>
-      <c r="X4" s="75"/>
-      <c r="Y4" s="75"/>
-      <c r="Z4" s="75"/>
-      <c r="AA4" s="75"/>
-      <c r="AB4" s="75"/>
-      <c r="AC4" s="75"/>
-      <c r="AD4" s="75"/>
-      <c r="AE4" s="75"/>
-      <c r="AF4" s="75"/>
-      <c r="AG4" s="75"/>
-      <c r="AH4" s="75"/>
-      <c r="AI4" s="75"/>
-      <c r="AJ4" s="75"/>
-      <c r="AK4" s="75"/>
-      <c r="AL4" s="75"/>
-      <c r="AM4" s="75"/>
-      <c r="AN4" s="75"/>
-      <c r="AO4" s="75"/>
-      <c r="AP4" s="75"/>
-      <c r="AQ4" s="75"/>
-      <c r="AR4" s="75"/>
-      <c r="AS4" s="75"/>
-      <c r="AT4" s="75"/>
-      <c r="AU4" s="75"/>
-      <c r="AV4" s="77"/>
-      <c r="AW4" s="75"/>
-      <c r="AX4" s="75"/>
-      <c r="AY4" s="75"/>
-      <c r="AZ4" s="75"/>
-      <c r="BA4" s="75"/>
-      <c r="BB4" s="75"/>
-      <c r="BC4" s="77"/>
-      <c r="BD4" s="75"/>
-      <c r="BE4" s="75"/>
-      <c r="BF4" s="75"/>
-      <c r="BG4" s="75"/>
-      <c r="BH4" s="75"/>
-      <c r="BI4" s="77"/>
-      <c r="BJ4" s="78"/>
+        <v>1</v>
+      </c>
+      <c r="I4" s="80"/>
+      <c r="J4" s="80"/>
+      <c r="K4" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="80"/>
+      <c r="M4" s="80"/>
+      <c r="N4" s="80"/>
+      <c r="O4" s="80"/>
+      <c r="P4" s="81"/>
+      <c r="Q4" s="80"/>
+      <c r="R4" s="80"/>
+      <c r="S4" s="80"/>
+      <c r="T4" s="80"/>
+      <c r="U4" s="80"/>
+      <c r="V4" s="80"/>
+      <c r="W4" s="80"/>
+      <c r="X4" s="80"/>
+      <c r="Y4" s="80"/>
+      <c r="Z4" s="80"/>
+      <c r="AA4" s="80"/>
+      <c r="AB4" s="80"/>
+      <c r="AC4" s="80"/>
+      <c r="AD4" s="80"/>
+      <c r="AE4" s="80"/>
+      <c r="AF4" s="80"/>
+      <c r="AG4" s="80"/>
+      <c r="AH4" s="80"/>
+      <c r="AI4" s="80"/>
+      <c r="AJ4" s="80"/>
+      <c r="AK4" s="80"/>
+      <c r="AL4" s="80"/>
+      <c r="AM4" s="80"/>
+      <c r="AN4" s="80"/>
+      <c r="AO4" s="80"/>
+      <c r="AP4" s="80"/>
+      <c r="AQ4" s="80"/>
+      <c r="AR4" s="80"/>
+      <c r="AS4" s="80"/>
+      <c r="AT4" s="80"/>
+      <c r="AU4" s="80"/>
+      <c r="AV4" s="82"/>
+      <c r="AW4" s="80"/>
+      <c r="AX4" s="80"/>
+      <c r="AY4" s="80"/>
+      <c r="AZ4" s="80"/>
+      <c r="BA4" s="80"/>
+      <c r="BB4" s="80"/>
+      <c r="BC4" s="82"/>
+      <c r="BD4" s="80"/>
+      <c r="BE4" s="80"/>
+      <c r="BF4" s="80"/>
+      <c r="BG4" s="80"/>
+      <c r="BH4" s="80"/>
+      <c r="BI4" s="82"/>
+      <c r="BJ4" s="83"/>
       <c r="BK4" s="66"/>
       <c r="BL4" s="67"/>
       <c r="BM4" s="68"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C5" s="15"/>
       <c r="D5" s="15"/>
@@ -4346,1042 +4712,1355 @@
         <v>15</v>
       </c>
       <c r="F5" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="G5" s="69" t="n">
-        <f aca="false">[1]Netzplan!J5</f>
-        <v>2</v>
-      </c>
-      <c r="H5" s="70" t="n">
+        <v>33</v>
+      </c>
+      <c r="G5" s="73" t="n">
+        <f aca="false">Netzplan!J4</f>
+        <v>8</v>
+      </c>
+      <c r="H5" s="74" t="n">
         <f aca="false">SUM(I5:BJ5)</f>
-        <v>0</v>
-      </c>
-      <c r="I5" s="75"/>
-      <c r="J5" s="75"/>
-      <c r="K5" s="75"/>
-      <c r="L5" s="76"/>
-      <c r="M5" s="76"/>
-      <c r="N5" s="75"/>
-      <c r="O5" s="75"/>
-      <c r="P5" s="75"/>
-      <c r="Q5" s="76"/>
-      <c r="R5" s="76"/>
-      <c r="S5" s="79"/>
-      <c r="T5" s="75"/>
-      <c r="U5" s="75"/>
-      <c r="V5" s="75"/>
-      <c r="W5" s="75"/>
-      <c r="X5" s="75"/>
-      <c r="Y5" s="75"/>
-      <c r="Z5" s="75"/>
-      <c r="AA5" s="75"/>
-      <c r="AB5" s="75"/>
-      <c r="AC5" s="75"/>
-      <c r="AD5" s="75"/>
-      <c r="AE5" s="75"/>
-      <c r="AF5" s="75"/>
-      <c r="AG5" s="75"/>
-      <c r="AH5" s="75"/>
-      <c r="AI5" s="75"/>
-      <c r="AJ5" s="75"/>
-      <c r="AK5" s="75"/>
-      <c r="AL5" s="75"/>
-      <c r="AM5" s="75"/>
-      <c r="AN5" s="75"/>
-      <c r="AO5" s="75"/>
-      <c r="AP5" s="75"/>
-      <c r="AQ5" s="75"/>
-      <c r="AR5" s="75"/>
-      <c r="AS5" s="75"/>
-      <c r="AT5" s="75"/>
-      <c r="AU5" s="75"/>
-      <c r="AV5" s="77"/>
-      <c r="AW5" s="75"/>
-      <c r="AX5" s="75"/>
-      <c r="AY5" s="75"/>
-      <c r="AZ5" s="75"/>
-      <c r="BA5" s="75"/>
-      <c r="BB5" s="75"/>
-      <c r="BC5" s="77"/>
-      <c r="BD5" s="75"/>
-      <c r="BE5" s="75"/>
-      <c r="BF5" s="75"/>
-      <c r="BG5" s="75"/>
-      <c r="BH5" s="75"/>
-      <c r="BI5" s="77"/>
-      <c r="BJ5" s="78"/>
+        <v>8</v>
+      </c>
+      <c r="I5" s="80"/>
+      <c r="J5" s="80"/>
+      <c r="K5" s="80"/>
+      <c r="L5" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" s="80"/>
+      <c r="O5" s="80"/>
+      <c r="P5" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" s="80"/>
+      <c r="V5" s="80"/>
+      <c r="W5" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" s="80"/>
+      <c r="Y5" s="80"/>
+      <c r="Z5" s="80"/>
+      <c r="AA5" s="80"/>
+      <c r="AB5" s="80"/>
+      <c r="AC5" s="80"/>
+      <c r="AD5" s="80"/>
+      <c r="AE5" s="80"/>
+      <c r="AF5" s="80"/>
+      <c r="AG5" s="80"/>
+      <c r="AH5" s="80"/>
+      <c r="AI5" s="80"/>
+      <c r="AJ5" s="80"/>
+      <c r="AK5" s="80"/>
+      <c r="AL5" s="80"/>
+      <c r="AM5" s="80"/>
+      <c r="AN5" s="80"/>
+      <c r="AO5" s="80"/>
+      <c r="AP5" s="80"/>
+      <c r="AQ5" s="80"/>
+      <c r="AR5" s="80"/>
+      <c r="AS5" s="80"/>
+      <c r="AT5" s="80"/>
+      <c r="AU5" s="80"/>
+      <c r="AV5" s="82"/>
+      <c r="AW5" s="80"/>
+      <c r="AX5" s="80"/>
+      <c r="AY5" s="80"/>
+      <c r="AZ5" s="80"/>
+      <c r="BA5" s="80"/>
+      <c r="BB5" s="80"/>
+      <c r="BC5" s="82"/>
+      <c r="BD5" s="80"/>
+      <c r="BE5" s="80"/>
+      <c r="BF5" s="80"/>
+      <c r="BG5" s="80"/>
+      <c r="BH5" s="80"/>
+      <c r="BI5" s="82"/>
+      <c r="BJ5" s="83"/>
       <c r="BK5" s="66"/>
       <c r="BL5" s="67"/>
       <c r="BM5" s="68"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C6" s="15"/>
       <c r="D6" s="15"/>
-      <c r="E6" s="42" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="42" t="s">
-        <v>33</v>
-      </c>
-      <c r="G6" s="69" t="n">
-        <f aca="false">[1]Netzplan!J6</f>
-        <v>4</v>
-      </c>
-      <c r="H6" s="70" t="n">
+      <c r="E6" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="73" t="n">
+        <f aca="false">Netzplan!J5</f>
+        <v>2</v>
+      </c>
+      <c r="H6" s="74" t="n">
         <f aca="false">SUM(I6:BJ6)</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="75"/>
-      <c r="J6" s="75"/>
-      <c r="K6" s="75"/>
-      <c r="L6" s="75"/>
-      <c r="M6" s="75"/>
-      <c r="N6" s="75"/>
-      <c r="O6" s="75"/>
-      <c r="P6" s="76"/>
-      <c r="Q6" s="76"/>
-      <c r="R6" s="76"/>
-      <c r="S6" s="76"/>
-      <c r="T6" s="76"/>
-      <c r="U6" s="75"/>
-      <c r="V6" s="75"/>
-      <c r="W6" s="76"/>
-      <c r="X6" s="76"/>
-      <c r="Y6" s="76"/>
-      <c r="Z6" s="76"/>
-      <c r="AA6" s="79"/>
-      <c r="AB6" s="75"/>
-      <c r="AC6" s="75"/>
-      <c r="AD6" s="75"/>
-      <c r="AE6" s="75"/>
-      <c r="AF6" s="75"/>
-      <c r="AG6" s="75"/>
-      <c r="AH6" s="75"/>
-      <c r="AI6" s="75"/>
-      <c r="AJ6" s="75"/>
-      <c r="AK6" s="75"/>
-      <c r="AL6" s="75"/>
-      <c r="AM6" s="75"/>
-      <c r="AN6" s="75"/>
-      <c r="AO6" s="75"/>
-      <c r="AP6" s="75"/>
-      <c r="AQ6" s="75"/>
-      <c r="AR6" s="75"/>
-      <c r="AS6" s="75"/>
-      <c r="AT6" s="75"/>
-      <c r="AU6" s="75"/>
-      <c r="AV6" s="77"/>
-      <c r="AW6" s="75"/>
-      <c r="AX6" s="75"/>
-      <c r="AY6" s="75"/>
-      <c r="AZ6" s="75"/>
-      <c r="BA6" s="75"/>
-      <c r="BB6" s="75"/>
-      <c r="BC6" s="77"/>
-      <c r="BD6" s="75"/>
-      <c r="BE6" s="75"/>
-      <c r="BF6" s="75"/>
-      <c r="BG6" s="75"/>
-      <c r="BH6" s="75"/>
-      <c r="BI6" s="77"/>
-      <c r="BJ6" s="78"/>
+        <v>2</v>
+      </c>
+      <c r="I6" s="80"/>
+      <c r="J6" s="80"/>
+      <c r="K6" s="80"/>
+      <c r="L6" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" s="80"/>
+      <c r="O6" s="80"/>
+      <c r="P6" s="80"/>
+      <c r="Q6" s="81"/>
+      <c r="R6" s="81"/>
+      <c r="S6" s="84"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
+      <c r="V6" s="80"/>
+      <c r="W6" s="80"/>
+      <c r="X6" s="80"/>
+      <c r="Y6" s="80"/>
+      <c r="Z6" s="80"/>
+      <c r="AA6" s="80"/>
+      <c r="AB6" s="80"/>
+      <c r="AC6" s="80"/>
+      <c r="AD6" s="80"/>
+      <c r="AE6" s="80"/>
+      <c r="AF6" s="80"/>
+      <c r="AG6" s="80"/>
+      <c r="AH6" s="80"/>
+      <c r="AI6" s="80"/>
+      <c r="AJ6" s="80"/>
+      <c r="AK6" s="80"/>
+      <c r="AL6" s="80"/>
+      <c r="AM6" s="80"/>
+      <c r="AN6" s="80"/>
+      <c r="AO6" s="80"/>
+      <c r="AP6" s="80"/>
+      <c r="AQ6" s="80"/>
+      <c r="AR6" s="80"/>
+      <c r="AS6" s="80"/>
+      <c r="AT6" s="80"/>
+      <c r="AU6" s="80"/>
+      <c r="AV6" s="82"/>
+      <c r="AW6" s="80"/>
+      <c r="AX6" s="80"/>
+      <c r="AY6" s="80"/>
+      <c r="AZ6" s="80"/>
+      <c r="BA6" s="80"/>
+      <c r="BB6" s="80"/>
+      <c r="BC6" s="82"/>
+      <c r="BD6" s="80"/>
+      <c r="BE6" s="80"/>
+      <c r="BF6" s="80"/>
+      <c r="BG6" s="80"/>
+      <c r="BH6" s="80"/>
+      <c r="BI6" s="82"/>
+      <c r="BJ6" s="83"/>
       <c r="BK6" s="66"/>
       <c r="BL6" s="67"/>
       <c r="BM6" s="68"/>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="12.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C7" s="15"/>
       <c r="D7" s="15"/>
-      <c r="E7" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7" s="69" t="n">
-        <f aca="false">[1]Netzplan!J7</f>
-        <v>1</v>
-      </c>
-      <c r="H7" s="70" t="n">
+      <c r="E7" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="73" t="n">
+        <f aca="false">Netzplan!J6</f>
+        <v>5</v>
+      </c>
+      <c r="H7" s="74" t="n">
         <f aca="false">SUM(I7:BJ7)</f>
-        <v>0</v>
-      </c>
-      <c r="I7" s="75"/>
-      <c r="J7" s="75"/>
-      <c r="K7" s="75"/>
-      <c r="L7" s="75"/>
-      <c r="M7" s="75"/>
-      <c r="N7" s="75"/>
-      <c r="O7" s="75"/>
-      <c r="P7" s="76"/>
-      <c r="Q7" s="75"/>
-      <c r="R7" s="75"/>
-      <c r="S7" s="75"/>
-      <c r="T7" s="75"/>
-      <c r="U7" s="75"/>
-      <c r="V7" s="75"/>
-      <c r="W7" s="75"/>
-      <c r="X7" s="75"/>
-      <c r="Y7" s="75"/>
-      <c r="Z7" s="75"/>
-      <c r="AA7" s="75"/>
-      <c r="AB7" s="75"/>
-      <c r="AC7" s="75"/>
-      <c r="AD7" s="75"/>
-      <c r="AE7" s="75"/>
-      <c r="AF7" s="75"/>
-      <c r="AG7" s="75"/>
-      <c r="AH7" s="75"/>
-      <c r="AI7" s="75"/>
-      <c r="AJ7" s="75"/>
-      <c r="AK7" s="75"/>
-      <c r="AL7" s="75"/>
-      <c r="AM7" s="75"/>
-      <c r="AN7" s="75"/>
-      <c r="AO7" s="75"/>
-      <c r="AP7" s="75"/>
-      <c r="AQ7" s="75"/>
-      <c r="AR7" s="75"/>
-      <c r="AS7" s="75"/>
-      <c r="AT7" s="75"/>
-      <c r="AU7" s="75"/>
-      <c r="AV7" s="77"/>
-      <c r="AW7" s="75"/>
-      <c r="AX7" s="75"/>
-      <c r="AY7" s="75"/>
-      <c r="AZ7" s="75"/>
-      <c r="BA7" s="75"/>
-      <c r="BB7" s="75"/>
-      <c r="BC7" s="77"/>
-      <c r="BD7" s="75"/>
-      <c r="BE7" s="75"/>
-      <c r="BF7" s="75"/>
-      <c r="BG7" s="75"/>
-      <c r="BH7" s="75"/>
-      <c r="BI7" s="77"/>
-      <c r="BJ7" s="78"/>
+        <v>5</v>
+      </c>
+      <c r="I7" s="80"/>
+      <c r="J7" s="80"/>
+      <c r="K7" s="80"/>
+      <c r="L7" s="80"/>
+      <c r="M7" s="80"/>
+      <c r="N7" s="80"/>
+      <c r="O7" s="80"/>
+      <c r="P7" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" s="80"/>
+      <c r="V7" s="80"/>
+      <c r="W7" s="81"/>
+      <c r="X7" s="81"/>
+      <c r="Y7" s="81"/>
+      <c r="Z7" s="81"/>
+      <c r="AA7" s="84"/>
+      <c r="AB7" s="80"/>
+      <c r="AC7" s="80"/>
+      <c r="AD7" s="80"/>
+      <c r="AE7" s="80"/>
+      <c r="AF7" s="80"/>
+      <c r="AG7" s="80"/>
+      <c r="AH7" s="80"/>
+      <c r="AI7" s="80"/>
+      <c r="AJ7" s="80"/>
+      <c r="AK7" s="80"/>
+      <c r="AL7" s="80"/>
+      <c r="AM7" s="80"/>
+      <c r="AN7" s="80"/>
+      <c r="AO7" s="80"/>
+      <c r="AP7" s="80"/>
+      <c r="AQ7" s="80"/>
+      <c r="AR7" s="80"/>
+      <c r="AS7" s="80"/>
+      <c r="AT7" s="80"/>
+      <c r="AU7" s="80"/>
+      <c r="AV7" s="82"/>
+      <c r="AW7" s="80"/>
+      <c r="AX7" s="80"/>
+      <c r="AY7" s="80"/>
+      <c r="AZ7" s="80"/>
+      <c r="BA7" s="80"/>
+      <c r="BB7" s="80"/>
+      <c r="BC7" s="82"/>
+      <c r="BD7" s="80"/>
+      <c r="BE7" s="80"/>
+      <c r="BF7" s="80"/>
+      <c r="BG7" s="80"/>
+      <c r="BH7" s="80"/>
+      <c r="BI7" s="82"/>
+      <c r="BJ7" s="83"/>
       <c r="BK7" s="66"/>
       <c r="BL7" s="67"/>
       <c r="BM7" s="68"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C8" s="15"/>
       <c r="D8" s="15"/>
-      <c r="E8" s="42" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="42" t="s">
-        <v>57</v>
-      </c>
-      <c r="G8" s="69" t="n">
-        <f aca="false">[1]Netzplan!J8</f>
-        <v>6</v>
-      </c>
-      <c r="H8" s="70" t="n">
+      <c r="E8" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" s="73" t="n">
+        <f aca="false">Netzplan!J7</f>
+        <v>1</v>
+      </c>
+      <c r="H8" s="74" t="n">
         <f aca="false">SUM(I8:BJ8)</f>
-        <v>0</v>
-      </c>
-      <c r="I8" s="75"/>
-      <c r="J8" s="75"/>
-      <c r="K8" s="75"/>
-      <c r="L8" s="76"/>
-      <c r="M8" s="76"/>
-      <c r="N8" s="75"/>
-      <c r="O8" s="75"/>
-      <c r="P8" s="76"/>
-      <c r="Q8" s="76"/>
-      <c r="R8" s="76"/>
-      <c r="S8" s="76"/>
-      <c r="T8" s="75"/>
-      <c r="U8" s="75"/>
-      <c r="V8" s="75"/>
-      <c r="W8" s="75"/>
-      <c r="X8" s="75"/>
-      <c r="Y8" s="75"/>
-      <c r="Z8" s="75"/>
-      <c r="AA8" s="75"/>
-      <c r="AB8" s="75"/>
-      <c r="AC8" s="75"/>
-      <c r="AD8" s="75"/>
-      <c r="AE8" s="75"/>
-      <c r="AF8" s="75"/>
-      <c r="AG8" s="75"/>
-      <c r="AH8" s="75"/>
-      <c r="AI8" s="75"/>
-      <c r="AJ8" s="75"/>
-      <c r="AK8" s="75"/>
-      <c r="AL8" s="75"/>
-      <c r="AM8" s="75"/>
-      <c r="AN8" s="75"/>
-      <c r="AO8" s="75"/>
-      <c r="AP8" s="75"/>
-      <c r="AQ8" s="75"/>
-      <c r="AR8" s="75"/>
-      <c r="AS8" s="75"/>
-      <c r="AT8" s="75"/>
-      <c r="AU8" s="75"/>
-      <c r="AV8" s="77"/>
-      <c r="AW8" s="75"/>
-      <c r="AX8" s="75"/>
-      <c r="AY8" s="75"/>
-      <c r="AZ8" s="75"/>
-      <c r="BA8" s="75"/>
-      <c r="BB8" s="75"/>
-      <c r="BC8" s="77"/>
-      <c r="BD8" s="75"/>
-      <c r="BE8" s="75"/>
-      <c r="BF8" s="75"/>
-      <c r="BG8" s="75"/>
-      <c r="BH8" s="75"/>
-      <c r="BI8" s="77"/>
-      <c r="BJ8" s="78"/>
+        <v>1</v>
+      </c>
+      <c r="I8" s="80"/>
+      <c r="J8" s="80"/>
+      <c r="K8" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="80"/>
+      <c r="M8" s="80"/>
+      <c r="N8" s="80"/>
+      <c r="O8" s="80"/>
+      <c r="P8" s="81"/>
+      <c r="Q8" s="80"/>
+      <c r="R8" s="80"/>
+      <c r="S8" s="80"/>
+      <c r="T8" s="80"/>
+      <c r="U8" s="80"/>
+      <c r="V8" s="80"/>
+      <c r="W8" s="80"/>
+      <c r="X8" s="80"/>
+      <c r="Y8" s="80"/>
+      <c r="Z8" s="80"/>
+      <c r="AA8" s="80"/>
+      <c r="AB8" s="80"/>
+      <c r="AC8" s="80"/>
+      <c r="AD8" s="80"/>
+      <c r="AE8" s="80"/>
+      <c r="AF8" s="80"/>
+      <c r="AG8" s="80"/>
+      <c r="AH8" s="80"/>
+      <c r="AI8" s="80"/>
+      <c r="AJ8" s="80"/>
+      <c r="AK8" s="80"/>
+      <c r="AL8" s="80"/>
+      <c r="AM8" s="80"/>
+      <c r="AN8" s="80"/>
+      <c r="AO8" s="80"/>
+      <c r="AP8" s="80"/>
+      <c r="AQ8" s="80"/>
+      <c r="AR8" s="80"/>
+      <c r="AS8" s="80"/>
+      <c r="AT8" s="80"/>
+      <c r="AU8" s="80"/>
+      <c r="AV8" s="82"/>
+      <c r="AW8" s="80"/>
+      <c r="AX8" s="80"/>
+      <c r="AY8" s="80"/>
+      <c r="AZ8" s="80"/>
+      <c r="BA8" s="80"/>
+      <c r="BB8" s="80"/>
+      <c r="BC8" s="82"/>
+      <c r="BD8" s="80"/>
+      <c r="BE8" s="80"/>
+      <c r="BF8" s="80"/>
+      <c r="BG8" s="80"/>
+      <c r="BH8" s="80"/>
+      <c r="BI8" s="82"/>
+      <c r="BJ8" s="83"/>
       <c r="BK8" s="66"/>
       <c r="BL8" s="67"/>
       <c r="BM8" s="68"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C9" s="15"/>
       <c r="D9" s="15"/>
       <c r="E9" s="42" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="F9" s="42" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="69" t="n">
-        <f aca="false">[1]Netzplan!J9</f>
-        <v>2</v>
-      </c>
-      <c r="H9" s="70" t="n">
+        <v>57</v>
+      </c>
+      <c r="G9" s="73" t="n">
+        <f aca="false">Netzplan!J8</f>
+        <v>3</v>
+      </c>
+      <c r="H9" s="74" t="n">
         <f aca="false">SUM(I9:BJ9)</f>
-        <v>0</v>
-      </c>
-      <c r="I9" s="75"/>
-      <c r="J9" s="75"/>
-      <c r="K9" s="75"/>
-      <c r="L9" s="75"/>
-      <c r="M9" s="75"/>
-      <c r="N9" s="75"/>
-      <c r="O9" s="75"/>
-      <c r="P9" s="75"/>
-      <c r="Q9" s="75"/>
-      <c r="R9" s="75"/>
-      <c r="S9" s="75"/>
-      <c r="T9" s="76"/>
-      <c r="U9" s="75"/>
-      <c r="V9" s="75"/>
-      <c r="W9" s="76"/>
-      <c r="X9" s="76"/>
-      <c r="Y9" s="76"/>
-      <c r="Z9" s="76"/>
-      <c r="AA9" s="78"/>
-      <c r="AB9" s="75"/>
-      <c r="AC9" s="75"/>
-      <c r="AD9" s="76"/>
-      <c r="AE9" s="75"/>
-      <c r="AF9" s="75"/>
-      <c r="AG9" s="75"/>
-      <c r="AH9" s="75"/>
-      <c r="AI9" s="75"/>
-      <c r="AJ9" s="75"/>
-      <c r="AK9" s="75"/>
-      <c r="AL9" s="75"/>
-      <c r="AM9" s="75"/>
-      <c r="AN9" s="75"/>
-      <c r="AO9" s="75"/>
-      <c r="AP9" s="75"/>
-      <c r="AQ9" s="75"/>
-      <c r="AR9" s="75"/>
-      <c r="AS9" s="75"/>
-      <c r="AT9" s="75"/>
-      <c r="AU9" s="75"/>
-      <c r="AV9" s="77"/>
-      <c r="AW9" s="75"/>
-      <c r="AX9" s="75"/>
-      <c r="AY9" s="75"/>
-      <c r="AZ9" s="75"/>
-      <c r="BA9" s="75"/>
-      <c r="BB9" s="75"/>
-      <c r="BC9" s="77"/>
-      <c r="BD9" s="75"/>
-      <c r="BE9" s="75"/>
-      <c r="BF9" s="75"/>
-      <c r="BG9" s="75"/>
-      <c r="BH9" s="75"/>
-      <c r="BI9" s="77"/>
-      <c r="BJ9" s="78"/>
+        <v>3</v>
+      </c>
+      <c r="I9" s="80"/>
+      <c r="J9" s="80"/>
+      <c r="K9" s="80"/>
+      <c r="L9" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" s="80"/>
+      <c r="O9" s="80"/>
+      <c r="P9" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="81"/>
+      <c r="R9" s="81"/>
+      <c r="S9" s="81"/>
+      <c r="T9" s="80"/>
+      <c r="U9" s="80"/>
+      <c r="V9" s="80"/>
+      <c r="W9" s="80"/>
+      <c r="X9" s="80"/>
+      <c r="Y9" s="80"/>
+      <c r="Z9" s="80"/>
+      <c r="AA9" s="80"/>
+      <c r="AB9" s="80"/>
+      <c r="AC9" s="80"/>
+      <c r="AD9" s="80"/>
+      <c r="AE9" s="80"/>
+      <c r="AF9" s="80"/>
+      <c r="AG9" s="80"/>
+      <c r="AH9" s="80"/>
+      <c r="AI9" s="80"/>
+      <c r="AJ9" s="80"/>
+      <c r="AK9" s="80"/>
+      <c r="AL9" s="80"/>
+      <c r="AM9" s="80"/>
+      <c r="AN9" s="80"/>
+      <c r="AO9" s="80"/>
+      <c r="AP9" s="80"/>
+      <c r="AQ9" s="80"/>
+      <c r="AR9" s="80"/>
+      <c r="AS9" s="80"/>
+      <c r="AT9" s="80"/>
+      <c r="AU9" s="80"/>
+      <c r="AV9" s="82"/>
+      <c r="AW9" s="80"/>
+      <c r="AX9" s="80"/>
+      <c r="AY9" s="80"/>
+      <c r="AZ9" s="80"/>
+      <c r="BA9" s="80"/>
+      <c r="BB9" s="80"/>
+      <c r="BC9" s="82"/>
+      <c r="BD9" s="80"/>
+      <c r="BE9" s="80"/>
+      <c r="BF9" s="80"/>
+      <c r="BG9" s="80"/>
+      <c r="BH9" s="80"/>
+      <c r="BI9" s="82"/>
+      <c r="BJ9" s="83"/>
       <c r="BK9" s="66"/>
       <c r="BL9" s="67"/>
       <c r="BM9" s="68"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="42" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10" s="42" t="s">
-        <v>37</v>
-      </c>
-      <c r="G10" s="69" t="n">
-        <f aca="false">[1]Netzplan!J10</f>
-        <v>2</v>
-      </c>
-      <c r="H10" s="70" t="n">
-        <f aca="false">SUM(I10:BJ10)</f>
-        <v>0</v>
-      </c>
-      <c r="I10" s="75"/>
-      <c r="J10" s="75"/>
-      <c r="K10" s="75"/>
-      <c r="L10" s="75"/>
-      <c r="M10" s="75"/>
-      <c r="N10" s="75"/>
-      <c r="O10" s="75"/>
-      <c r="P10" s="75"/>
-      <c r="Q10" s="75"/>
-      <c r="R10" s="75"/>
-      <c r="S10" s="75"/>
-      <c r="T10" s="75"/>
-      <c r="U10" s="75"/>
-      <c r="V10" s="75"/>
-      <c r="W10" s="75"/>
-      <c r="X10" s="76"/>
-      <c r="Y10" s="76"/>
-      <c r="Z10" s="75"/>
-      <c r="AA10" s="75"/>
-      <c r="AB10" s="75"/>
-      <c r="AC10" s="75"/>
-      <c r="AE10" s="78"/>
-      <c r="AF10" s="75"/>
-      <c r="AG10" s="75"/>
-      <c r="AH10" s="75"/>
-      <c r="AI10" s="75"/>
-      <c r="AJ10" s="75"/>
-      <c r="AK10" s="75"/>
-      <c r="AL10" s="75"/>
-      <c r="AM10" s="75"/>
-      <c r="AN10" s="75"/>
-      <c r="AO10" s="75"/>
-      <c r="AP10" s="75"/>
-      <c r="AQ10" s="75"/>
-      <c r="AR10" s="75"/>
-      <c r="AS10" s="75"/>
-      <c r="AT10" s="75"/>
-      <c r="AU10" s="75"/>
-      <c r="AV10" s="77"/>
-      <c r="AW10" s="75"/>
-      <c r="AX10" s="75"/>
-      <c r="AY10" s="75"/>
-      <c r="AZ10" s="75"/>
-      <c r="BA10" s="75"/>
-      <c r="BB10" s="75"/>
-      <c r="BC10" s="77"/>
-      <c r="BD10" s="75"/>
-      <c r="BE10" s="75"/>
-      <c r="BF10" s="75"/>
-      <c r="BG10" s="75"/>
-      <c r="BH10" s="75"/>
-      <c r="BI10" s="77"/>
-      <c r="BJ10" s="78"/>
+      <c r="A10" s="14"/>
+      <c r="B10" s="43" t="s">
+        <v>79</v>
+      </c>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="73"/>
+      <c r="H10" s="74"/>
+      <c r="I10" s="80"/>
+      <c r="J10" s="80"/>
+      <c r="K10" s="80"/>
+      <c r="L10" s="81"/>
+      <c r="M10" s="81"/>
+      <c r="N10" s="80"/>
+      <c r="O10" s="80"/>
+      <c r="P10" s="81"/>
+      <c r="Q10" s="81"/>
+      <c r="R10" s="81"/>
+      <c r="S10" s="81"/>
+      <c r="T10" s="80"/>
+      <c r="U10" s="80"/>
+      <c r="V10" s="80"/>
+      <c r="W10" s="80"/>
+      <c r="X10" s="80"/>
+      <c r="Y10" s="80"/>
+      <c r="Z10" s="80"/>
+      <c r="AA10" s="80"/>
+      <c r="AB10" s="80"/>
+      <c r="AC10" s="80"/>
+      <c r="AD10" s="80"/>
+      <c r="AE10" s="80"/>
+      <c r="AF10" s="80"/>
+      <c r="AG10" s="80"/>
+      <c r="AH10" s="80"/>
+      <c r="AI10" s="80"/>
+      <c r="AJ10" s="80"/>
+      <c r="AK10" s="80"/>
+      <c r="AL10" s="80"/>
+      <c r="AM10" s="80"/>
+      <c r="AN10" s="80"/>
+      <c r="AO10" s="80"/>
+      <c r="AP10" s="80"/>
+      <c r="AQ10" s="80"/>
+      <c r="AR10" s="80"/>
+      <c r="AS10" s="80"/>
+      <c r="AT10" s="80"/>
+      <c r="AU10" s="80"/>
+      <c r="AV10" s="82"/>
+      <c r="AW10" s="80"/>
+      <c r="AX10" s="80"/>
+      <c r="AY10" s="80"/>
+      <c r="AZ10" s="80"/>
+      <c r="BA10" s="80"/>
+      <c r="BB10" s="80"/>
+      <c r="BC10" s="82"/>
+      <c r="BD10" s="80"/>
+      <c r="BE10" s="80"/>
+      <c r="BF10" s="80"/>
+      <c r="BG10" s="80"/>
+      <c r="BH10" s="80"/>
+      <c r="BI10" s="82"/>
+      <c r="BJ10" s="83"/>
       <c r="BK10" s="66"/>
       <c r="BL10" s="67"/>
       <c r="BM10" s="68"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C11" s="15"/>
       <c r="D11" s="15"/>
       <c r="E11" s="42" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="F11" s="42" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" s="69" t="n">
-        <f aca="false">[1]Netzplan!J11</f>
-        <v>2</v>
-      </c>
-      <c r="H11" s="70" t="n">
+      <c r="G11" s="73" t="n">
+        <f aca="false">Netzplan!J9</f>
+        <v>1</v>
+      </c>
+      <c r="H11" s="74" t="n">
         <f aca="false">SUM(I11:BJ11)</f>
-        <v>0</v>
-      </c>
-      <c r="I11" s="75"/>
-      <c r="J11" s="75"/>
-      <c r="K11" s="75"/>
-      <c r="L11" s="75"/>
-      <c r="M11" s="75"/>
-      <c r="N11" s="75"/>
-      <c r="O11" s="75"/>
-      <c r="P11" s="75"/>
-      <c r="Q11" s="75"/>
-      <c r="R11" s="75"/>
-      <c r="S11" s="75"/>
-      <c r="T11" s="75"/>
-      <c r="U11" s="75"/>
-      <c r="V11" s="75"/>
-      <c r="W11" s="75"/>
-      <c r="X11" s="75"/>
-      <c r="Y11" s="75"/>
-      <c r="Z11" s="76"/>
-      <c r="AA11" s="76"/>
-      <c r="AB11" s="75"/>
-      <c r="AC11" s="75"/>
-      <c r="AE11" s="78"/>
-      <c r="AF11" s="75"/>
-      <c r="AG11" s="76"/>
-      <c r="AH11" s="76"/>
-      <c r="AI11" s="75"/>
-      <c r="AJ11" s="75"/>
-      <c r="AK11" s="75"/>
-      <c r="AL11" s="75"/>
-      <c r="AM11" s="75"/>
-      <c r="AN11" s="75"/>
-      <c r="AO11" s="75"/>
-      <c r="AP11" s="75"/>
-      <c r="AQ11" s="75"/>
-      <c r="AR11" s="75"/>
-      <c r="AS11" s="75"/>
-      <c r="AT11" s="75"/>
-      <c r="AU11" s="75"/>
-      <c r="AV11" s="77"/>
-      <c r="AW11" s="75"/>
-      <c r="AX11" s="75"/>
-      <c r="AY11" s="75"/>
-      <c r="AZ11" s="75"/>
-      <c r="BA11" s="75"/>
-      <c r="BB11" s="75"/>
-      <c r="BC11" s="77"/>
-      <c r="BD11" s="75"/>
-      <c r="BE11" s="75"/>
-      <c r="BF11" s="75"/>
-      <c r="BG11" s="75"/>
-      <c r="BH11" s="75"/>
-      <c r="BI11" s="77"/>
-      <c r="BJ11" s="78"/>
+        <v>1</v>
+      </c>
+      <c r="I11" s="80"/>
+      <c r="J11" s="80"/>
+      <c r="K11" s="80"/>
+      <c r="L11" s="80"/>
+      <c r="M11" s="80"/>
+      <c r="N11" s="80"/>
+      <c r="O11" s="80"/>
+      <c r="P11" s="80"/>
+      <c r="Q11" s="80"/>
+      <c r="R11" s="80"/>
+      <c r="S11" s="80"/>
+      <c r="T11" s="81"/>
+      <c r="U11" s="80"/>
+      <c r="V11" s="80"/>
+      <c r="W11" s="81"/>
+      <c r="X11" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="81"/>
+      <c r="Z11" s="81"/>
+      <c r="AA11" s="83"/>
+      <c r="AB11" s="80"/>
+      <c r="AC11" s="80"/>
+      <c r="AD11" s="81"/>
+      <c r="AE11" s="80"/>
+      <c r="AF11" s="80"/>
+      <c r="AG11" s="80"/>
+      <c r="AH11" s="80"/>
+      <c r="AI11" s="80"/>
+      <c r="AJ11" s="80"/>
+      <c r="AK11" s="80"/>
+      <c r="AL11" s="80"/>
+      <c r="AM11" s="80"/>
+      <c r="AN11" s="80"/>
+      <c r="AO11" s="80"/>
+      <c r="AP11" s="80"/>
+      <c r="AQ11" s="80"/>
+      <c r="AR11" s="80"/>
+      <c r="AS11" s="80"/>
+      <c r="AT11" s="80"/>
+      <c r="AU11" s="80"/>
+      <c r="AV11" s="82"/>
+      <c r="AW11" s="80"/>
+      <c r="AX11" s="80"/>
+      <c r="AY11" s="80"/>
+      <c r="AZ11" s="80"/>
+      <c r="BA11" s="80"/>
+      <c r="BB11" s="80"/>
+      <c r="BC11" s="82"/>
+      <c r="BD11" s="80"/>
+      <c r="BE11" s="80"/>
+      <c r="BF11" s="80"/>
+      <c r="BG11" s="80"/>
+      <c r="BH11" s="80"/>
+      <c r="BI11" s="82"/>
+      <c r="BJ11" s="83"/>
       <c r="BK11" s="66"/>
       <c r="BL11" s="67"/>
       <c r="BM11" s="68"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="C12" s="15"/>
       <c r="D12" s="15"/>
       <c r="E12" s="42" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F12" s="42" t="s">
-        <v>44</v>
-      </c>
-      <c r="G12" s="69" t="n">
-        <f aca="false">[1]Netzplan!J12</f>
-        <v>20</v>
-      </c>
-      <c r="H12" s="70" t="n">
+        <v>37</v>
+      </c>
+      <c r="G12" s="73" t="n">
+        <f aca="false">Netzplan!J10</f>
+        <v>1</v>
+      </c>
+      <c r="H12" s="74" t="n">
         <f aca="false">SUM(I12:BJ12)</f>
-        <v>0</v>
-      </c>
-      <c r="I12" s="75"/>
-      <c r="J12" s="75"/>
-      <c r="K12" s="75"/>
-      <c r="L12" s="75"/>
-      <c r="M12" s="75"/>
-      <c r="N12" s="75"/>
-      <c r="O12" s="75"/>
-      <c r="P12" s="75"/>
-      <c r="Q12" s="75"/>
-      <c r="R12" s="75"/>
-      <c r="S12" s="75"/>
-      <c r="T12" s="76"/>
-      <c r="U12" s="75"/>
-      <c r="V12" s="75"/>
-      <c r="W12" s="76"/>
-      <c r="X12" s="76"/>
-      <c r="Y12" s="76"/>
-      <c r="Z12" s="76"/>
-      <c r="AA12" s="76"/>
-      <c r="AB12" s="75"/>
-      <c r="AC12" s="75"/>
-      <c r="AD12" s="76"/>
-      <c r="AE12" s="76"/>
-      <c r="AF12" s="76"/>
-      <c r="AG12" s="76"/>
-      <c r="AH12" s="76"/>
-      <c r="AI12" s="75"/>
-      <c r="AJ12" s="75"/>
-      <c r="AK12" s="76"/>
-      <c r="AL12" s="76"/>
-      <c r="AM12" s="76"/>
-      <c r="AN12" s="76"/>
-      <c r="AO12" s="76"/>
-      <c r="AP12" s="75"/>
-      <c r="AQ12" s="75"/>
-      <c r="AR12" s="76"/>
-      <c r="AS12" s="76"/>
-      <c r="AT12" s="76"/>
-      <c r="AU12" s="76"/>
-      <c r="AV12" s="80"/>
-      <c r="AW12" s="75"/>
-      <c r="AX12" s="75"/>
-      <c r="AY12" s="76"/>
-      <c r="AZ12" s="76"/>
-      <c r="BA12" s="76"/>
-      <c r="BB12" s="76"/>
-      <c r="BC12" s="77"/>
-      <c r="BD12" s="75"/>
-      <c r="BE12" s="75"/>
-      <c r="BF12" s="75"/>
-      <c r="BG12" s="75"/>
-      <c r="BH12" s="75"/>
-      <c r="BI12" s="77"/>
-      <c r="BJ12" s="78"/>
+        <v>1</v>
+      </c>
+      <c r="I12" s="80"/>
+      <c r="J12" s="80"/>
+      <c r="K12" s="80"/>
+      <c r="L12" s="80"/>
+      <c r="M12" s="80"/>
+      <c r="N12" s="80"/>
+      <c r="O12" s="80"/>
+      <c r="P12" s="80"/>
+      <c r="Q12" s="80"/>
+      <c r="R12" s="80"/>
+      <c r="S12" s="80"/>
+      <c r="T12" s="80"/>
+      <c r="U12" s="80"/>
+      <c r="V12" s="80"/>
+      <c r="W12" s="80"/>
+      <c r="X12" s="81"/>
+      <c r="Y12" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="80"/>
+      <c r="AA12" s="80"/>
+      <c r="AB12" s="80"/>
+      <c r="AC12" s="80"/>
+      <c r="AE12" s="83"/>
+      <c r="AF12" s="80"/>
+      <c r="AG12" s="80"/>
+      <c r="AH12" s="80"/>
+      <c r="AI12" s="80"/>
+      <c r="AJ12" s="80"/>
+      <c r="AK12" s="80"/>
+      <c r="AL12" s="80"/>
+      <c r="AM12" s="80"/>
+      <c r="AN12" s="80"/>
+      <c r="AO12" s="80"/>
+      <c r="AP12" s="80"/>
+      <c r="AQ12" s="80"/>
+      <c r="AR12" s="80"/>
+      <c r="AS12" s="80"/>
+      <c r="AT12" s="80"/>
+      <c r="AU12" s="80"/>
+      <c r="AV12" s="82"/>
+      <c r="AW12" s="80"/>
+      <c r="AX12" s="80"/>
+      <c r="AY12" s="80"/>
+      <c r="AZ12" s="80"/>
+      <c r="BA12" s="80"/>
+      <c r="BB12" s="80"/>
+      <c r="BC12" s="82"/>
+      <c r="BD12" s="80"/>
+      <c r="BE12" s="80"/>
+      <c r="BF12" s="80"/>
+      <c r="BG12" s="80"/>
+      <c r="BH12" s="80"/>
+      <c r="BI12" s="82"/>
+      <c r="BJ12" s="83"/>
       <c r="BK12" s="66"/>
       <c r="BL12" s="67"/>
       <c r="BM12" s="68"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="C13" s="15"/>
       <c r="D13" s="15"/>
       <c r="E13" s="42" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F13" s="42" t="s">
-        <v>41</v>
-      </c>
-      <c r="G13" s="69" t="n">
-        <f aca="false">[1]Netzplan!J13</f>
-        <v>2</v>
-      </c>
-      <c r="H13" s="70" t="n">
+        <v>23</v>
+      </c>
+      <c r="G13" s="73" t="n">
+        <f aca="false">Netzplan!J11</f>
+        <v>1</v>
+      </c>
+      <c r="H13" s="74" t="n">
         <f aca="false">SUM(I13:BJ13)</f>
-        <v>0</v>
-      </c>
-      <c r="I13" s="75"/>
-      <c r="J13" s="75"/>
-      <c r="K13" s="75"/>
-      <c r="L13" s="75"/>
-      <c r="M13" s="75"/>
-      <c r="N13" s="75"/>
-      <c r="O13" s="75"/>
-      <c r="P13" s="75"/>
-      <c r="Q13" s="75"/>
-      <c r="R13" s="75"/>
-      <c r="S13" s="75"/>
-      <c r="T13" s="75"/>
-      <c r="U13" s="75"/>
-      <c r="V13" s="75"/>
-      <c r="W13" s="75"/>
-      <c r="X13" s="75"/>
-      <c r="Y13" s="75"/>
-      <c r="Z13" s="75"/>
-      <c r="AA13" s="75"/>
-      <c r="AB13" s="75"/>
-      <c r="AC13" s="75"/>
-      <c r="AE13" s="76"/>
-      <c r="AF13" s="76"/>
-      <c r="AG13" s="75"/>
-      <c r="AH13" s="75"/>
-      <c r="AI13" s="75"/>
-      <c r="AJ13" s="75"/>
-      <c r="AK13" s="76"/>
-      <c r="AL13" s="76"/>
-      <c r="AM13" s="76"/>
-      <c r="AN13" s="76"/>
-      <c r="AO13" s="76"/>
-      <c r="AP13" s="75"/>
-      <c r="AQ13" s="75"/>
-      <c r="AR13" s="75"/>
-      <c r="AS13" s="75"/>
-      <c r="AT13" s="75"/>
-      <c r="AU13" s="75"/>
-      <c r="AV13" s="77"/>
-      <c r="AW13" s="75"/>
-      <c r="AX13" s="75"/>
-      <c r="AY13" s="75"/>
-      <c r="AZ13" s="75"/>
-      <c r="BA13" s="75"/>
-      <c r="BB13" s="75"/>
-      <c r="BC13" s="77"/>
-      <c r="BD13" s="75"/>
-      <c r="BE13" s="75"/>
-      <c r="BF13" s="75"/>
-      <c r="BG13" s="75"/>
-      <c r="BH13" s="75"/>
-      <c r="BI13" s="77"/>
-      <c r="BJ13" s="78"/>
+        <v>1</v>
+      </c>
+      <c r="I13" s="80"/>
+      <c r="J13" s="80"/>
+      <c r="K13" s="80"/>
+      <c r="L13" s="80"/>
+      <c r="M13" s="80"/>
+      <c r="N13" s="80"/>
+      <c r="O13" s="80"/>
+      <c r="P13" s="80"/>
+      <c r="Q13" s="80"/>
+      <c r="R13" s="80"/>
+      <c r="S13" s="80"/>
+      <c r="T13" s="80"/>
+      <c r="U13" s="80"/>
+      <c r="V13" s="80"/>
+      <c r="W13" s="80"/>
+      <c r="X13" s="80"/>
+      <c r="Y13" s="80"/>
+      <c r="Z13" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA13" s="81"/>
+      <c r="AB13" s="80"/>
+      <c r="AC13" s="80"/>
+      <c r="AE13" s="83"/>
+      <c r="AF13" s="80"/>
+      <c r="AG13" s="81"/>
+      <c r="AH13" s="81"/>
+      <c r="AI13" s="80"/>
+      <c r="AJ13" s="80"/>
+      <c r="AK13" s="80"/>
+      <c r="AL13" s="80"/>
+      <c r="AM13" s="80"/>
+      <c r="AN13" s="80"/>
+      <c r="AO13" s="80"/>
+      <c r="AP13" s="80"/>
+      <c r="AQ13" s="80"/>
+      <c r="AR13" s="80"/>
+      <c r="AS13" s="80"/>
+      <c r="AT13" s="80"/>
+      <c r="AU13" s="80"/>
+      <c r="AV13" s="82"/>
+      <c r="AW13" s="80"/>
+      <c r="AX13" s="80"/>
+      <c r="AY13" s="80"/>
+      <c r="AZ13" s="80"/>
+      <c r="BA13" s="80"/>
+      <c r="BB13" s="80"/>
+      <c r="BC13" s="82"/>
+      <c r="BD13" s="80"/>
+      <c r="BE13" s="80"/>
+      <c r="BF13" s="80"/>
+      <c r="BG13" s="80"/>
+      <c r="BH13" s="80"/>
+      <c r="BI13" s="82"/>
+      <c r="BJ13" s="83"/>
       <c r="BK13" s="66"/>
       <c r="BL13" s="67"/>
       <c r="BM13" s="68"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="C14" s="15"/>
       <c r="D14" s="15"/>
       <c r="E14" s="42" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F14" s="42" t="s">
-        <v>29</v>
-      </c>
-      <c r="G14" s="69" t="n">
-        <f aca="false">[1]Netzplan!J14</f>
-        <v>2</v>
-      </c>
-      <c r="H14" s="70" t="n">
+        <v>44</v>
+      </c>
+      <c r="G14" s="73" t="n">
+        <f aca="false">Netzplan!J12</f>
+        <v>19</v>
+      </c>
+      <c r="H14" s="74" t="n">
         <f aca="false">SUM(I14:BJ14)</f>
-        <v>0</v>
-      </c>
-      <c r="I14" s="75"/>
-      <c r="J14" s="75"/>
-      <c r="K14" s="75"/>
-      <c r="L14" s="75"/>
-      <c r="M14" s="75"/>
-      <c r="N14" s="75"/>
-      <c r="O14" s="75"/>
-      <c r="P14" s="75"/>
-      <c r="Q14" s="75"/>
-      <c r="R14" s="75"/>
-      <c r="S14" s="75"/>
-      <c r="T14" s="75"/>
-      <c r="U14" s="75"/>
-      <c r="V14" s="75"/>
-      <c r="W14" s="75"/>
-      <c r="X14" s="75"/>
-      <c r="Y14" s="75"/>
-      <c r="Z14" s="75"/>
-      <c r="AA14" s="75"/>
-      <c r="AB14" s="75"/>
-      <c r="AC14" s="75"/>
-      <c r="AD14" s="75"/>
-      <c r="AE14" s="75"/>
-      <c r="AG14" s="75"/>
-      <c r="AH14" s="75"/>
-      <c r="AI14" s="75"/>
-      <c r="AJ14" s="75"/>
-      <c r="AL14" s="75"/>
-      <c r="AM14" s="75"/>
-      <c r="AN14" s="75"/>
-      <c r="AO14" s="76"/>
-      <c r="AP14" s="75"/>
-      <c r="AQ14" s="75"/>
-      <c r="AR14" s="76"/>
-      <c r="AS14" s="76"/>
-      <c r="AT14" s="76"/>
-      <c r="AU14" s="75"/>
-      <c r="AV14" s="77"/>
-      <c r="AW14" s="75"/>
-      <c r="AX14" s="75"/>
-      <c r="AY14" s="75"/>
-      <c r="AZ14" s="75"/>
-      <c r="BA14" s="75"/>
-      <c r="BB14" s="75"/>
-      <c r="BC14" s="77"/>
-      <c r="BD14" s="75"/>
-      <c r="BE14" s="75"/>
-      <c r="BF14" s="75"/>
-      <c r="BG14" s="75"/>
-      <c r="BH14" s="75"/>
-      <c r="BI14" s="77"/>
-      <c r="BJ14" s="78"/>
+        <v>19</v>
+      </c>
+      <c r="I14" s="80"/>
+      <c r="J14" s="80"/>
+      <c r="K14" s="80"/>
+      <c r="L14" s="80"/>
+      <c r="M14" s="80"/>
+      <c r="N14" s="80"/>
+      <c r="O14" s="80"/>
+      <c r="P14" s="80"/>
+      <c r="Q14" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" s="80"/>
+      <c r="V14" s="80"/>
+      <c r="W14" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y14" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA14" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB14" s="80"/>
+      <c r="AC14" s="80"/>
+      <c r="AD14" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE14" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF14" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG14" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH14" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI14" s="80"/>
+      <c r="AJ14" s="80"/>
+      <c r="AK14" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL14" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM14" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN14" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO14" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP14" s="80"/>
+      <c r="AQ14" s="80"/>
+      <c r="AR14" s="80"/>
+      <c r="AS14" s="81"/>
+      <c r="AT14" s="81"/>
+      <c r="AU14" s="81"/>
+      <c r="AV14" s="85"/>
+      <c r="AW14" s="80"/>
+      <c r="AX14" s="80"/>
+      <c r="AY14" s="81"/>
+      <c r="AZ14" s="81"/>
+      <c r="BA14" s="81"/>
+      <c r="BB14" s="81"/>
+      <c r="BC14" s="82"/>
+      <c r="BD14" s="80"/>
+      <c r="BE14" s="80"/>
+      <c r="BF14" s="80"/>
+      <c r="BG14" s="80"/>
+      <c r="BH14" s="80"/>
+      <c r="BI14" s="82"/>
+      <c r="BJ14" s="83"/>
       <c r="BK14" s="66"/>
       <c r="BL14" s="67"/>
       <c r="BM14" s="68"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="42" t="s">
-        <v>41</v>
-      </c>
-      <c r="F15" s="42" t="s">
-        <v>43</v>
-      </c>
-      <c r="G15" s="69" t="n">
-        <f aca="false">[1]Netzplan!J15</f>
-        <v>1</v>
-      </c>
-      <c r="H15" s="70" t="n">
-        <f aca="false">SUM(I15:BJ15)</f>
-        <v>0</v>
-      </c>
-      <c r="I15" s="75"/>
-      <c r="J15" s="75"/>
-      <c r="K15" s="75"/>
-      <c r="L15" s="75"/>
-      <c r="M15" s="75"/>
-      <c r="N15" s="75"/>
-      <c r="O15" s="75"/>
-      <c r="P15" s="75"/>
-      <c r="Q15" s="75"/>
-      <c r="R15" s="75"/>
-      <c r="S15" s="75"/>
-      <c r="T15" s="75"/>
-      <c r="U15" s="75"/>
-      <c r="V15" s="75"/>
-      <c r="W15" s="75"/>
-      <c r="X15" s="75"/>
-      <c r="Y15" s="75"/>
-      <c r="Z15" s="75"/>
-      <c r="AA15" s="75"/>
-      <c r="AB15" s="75"/>
-      <c r="AC15" s="75"/>
-      <c r="AD15" s="75"/>
-      <c r="AE15" s="75"/>
-      <c r="AF15" s="75"/>
-      <c r="AG15" s="75"/>
-      <c r="AI15" s="75"/>
-      <c r="AJ15" s="75"/>
-      <c r="AL15" s="75"/>
-      <c r="AM15" s="75"/>
-      <c r="AO15" s="75"/>
-      <c r="AP15" s="75"/>
-      <c r="AQ15" s="75"/>
-      <c r="AR15" s="78"/>
-      <c r="AS15" s="76"/>
-      <c r="AT15" s="75"/>
-      <c r="AU15" s="75"/>
-      <c r="AV15" s="77"/>
-      <c r="AW15" s="75"/>
-      <c r="AX15" s="75"/>
-      <c r="AY15" s="75"/>
-      <c r="AZ15" s="75"/>
-      <c r="BA15" s="75"/>
-      <c r="BB15" s="75"/>
-      <c r="BC15" s="77"/>
-      <c r="BD15" s="75"/>
-      <c r="BE15" s="75"/>
-      <c r="BF15" s="75"/>
-      <c r="BG15" s="75"/>
-      <c r="BH15" s="75"/>
-      <c r="BI15" s="77"/>
-      <c r="BJ15" s="78"/>
+      <c r="A15" s="14"/>
+      <c r="B15" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="73"/>
+      <c r="H15" s="74"/>
+      <c r="I15" s="80"/>
+      <c r="J15" s="80"/>
+      <c r="K15" s="80"/>
+      <c r="L15" s="80"/>
+      <c r="M15" s="80"/>
+      <c r="N15" s="80"/>
+      <c r="O15" s="80"/>
+      <c r="P15" s="80"/>
+      <c r="Q15" s="81"/>
+      <c r="R15" s="81"/>
+      <c r="S15" s="81"/>
+      <c r="T15" s="81"/>
+      <c r="U15" s="80"/>
+      <c r="V15" s="80"/>
+      <c r="W15" s="80"/>
+      <c r="X15" s="81"/>
+      <c r="Y15" s="81"/>
+      <c r="Z15" s="81"/>
+      <c r="AA15" s="81"/>
+      <c r="AB15" s="80"/>
+      <c r="AC15" s="80"/>
+      <c r="AD15" s="80"/>
+      <c r="AE15" s="81"/>
+      <c r="AF15" s="81"/>
+      <c r="AG15" s="81"/>
+      <c r="AH15" s="81"/>
+      <c r="AI15" s="80"/>
+      <c r="AJ15" s="80"/>
+      <c r="AK15" s="80"/>
+      <c r="AL15" s="81"/>
+      <c r="AM15" s="81"/>
+      <c r="AN15" s="81"/>
+      <c r="AO15" s="81"/>
+      <c r="AP15" s="80"/>
+      <c r="AQ15" s="80"/>
+      <c r="AR15" s="80"/>
+      <c r="AS15" s="81"/>
+      <c r="AT15" s="81"/>
+      <c r="AU15" s="81"/>
+      <c r="AV15" s="85"/>
+      <c r="AW15" s="80"/>
+      <c r="AX15" s="80"/>
+      <c r="AY15" s="81"/>
+      <c r="AZ15" s="81"/>
+      <c r="BA15" s="81"/>
+      <c r="BB15" s="81"/>
+      <c r="BC15" s="82"/>
+      <c r="BD15" s="80"/>
+      <c r="BE15" s="80"/>
+      <c r="BF15" s="80"/>
+      <c r="BG15" s="80"/>
+      <c r="BH15" s="80"/>
+      <c r="BI15" s="82"/>
+      <c r="BJ15" s="83"/>
       <c r="BK15" s="66"/>
       <c r="BL15" s="67"/>
       <c r="BM15" s="68"/>
     </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="12.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="C16" s="15"/>
       <c r="D16" s="15"/>
       <c r="E16" s="42" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F16" s="42" t="s">
-        <v>44</v>
-      </c>
-      <c r="G16" s="69" t="n">
-        <f aca="false">[1]Netzplan!J16</f>
-        <v>4</v>
-      </c>
-      <c r="H16" s="70" t="n">
+        <v>41</v>
+      </c>
+      <c r="G16" s="73" t="n">
+        <f aca="false">Netzplan!J13</f>
+        <v>2</v>
+      </c>
+      <c r="H16" s="74" t="n">
         <f aca="false">SUM(I16:BJ16)</f>
-        <v>0</v>
-      </c>
-      <c r="I16" s="75"/>
-      <c r="J16" s="75"/>
-      <c r="K16" s="75"/>
-      <c r="L16" s="75"/>
-      <c r="M16" s="75"/>
-      <c r="N16" s="75"/>
-      <c r="O16" s="75"/>
-      <c r="P16" s="75"/>
-      <c r="Q16" s="75"/>
-      <c r="R16" s="75"/>
-      <c r="S16" s="75"/>
-      <c r="T16" s="75"/>
-      <c r="U16" s="75"/>
-      <c r="V16" s="75"/>
-      <c r="W16" s="75"/>
-      <c r="X16" s="75"/>
-      <c r="Y16" s="75"/>
-      <c r="Z16" s="75"/>
-      <c r="AA16" s="75"/>
-      <c r="AB16" s="75"/>
-      <c r="AC16" s="75"/>
-      <c r="AD16" s="75"/>
-      <c r="AE16" s="75"/>
-      <c r="AF16" s="75"/>
-      <c r="AG16" s="75"/>
-      <c r="AH16" s="75"/>
-      <c r="AI16" s="75"/>
-      <c r="AJ16" s="75"/>
-      <c r="AL16" s="75"/>
-      <c r="AM16" s="78"/>
-      <c r="AN16" s="78"/>
-      <c r="AO16" s="75"/>
-      <c r="AP16" s="75"/>
-      <c r="AQ16" s="75"/>
-      <c r="AR16" s="75"/>
-      <c r="AS16" s="75"/>
-      <c r="AT16" s="75"/>
-      <c r="AU16" s="76"/>
-      <c r="AV16" s="77"/>
-      <c r="AW16" s="75"/>
-      <c r="AX16" s="75"/>
-      <c r="AY16" s="76"/>
-      <c r="AZ16" s="76"/>
-      <c r="BA16" s="76"/>
-      <c r="BB16" s="75"/>
-      <c r="BC16" s="77"/>
-      <c r="BD16" s="75"/>
-      <c r="BE16" s="75"/>
-      <c r="BF16" s="75"/>
-      <c r="BG16" s="75"/>
-      <c r="BH16" s="75"/>
-      <c r="BI16" s="77"/>
-      <c r="BJ16" s="78"/>
+        <v>2</v>
+      </c>
+      <c r="I16" s="80"/>
+      <c r="J16" s="80"/>
+      <c r="K16" s="80"/>
+      <c r="L16" s="80"/>
+      <c r="M16" s="80"/>
+      <c r="N16" s="80"/>
+      <c r="O16" s="80"/>
+      <c r="P16" s="80"/>
+      <c r="Q16" s="80"/>
+      <c r="R16" s="80"/>
+      <c r="S16" s="80"/>
+      <c r="T16" s="80"/>
+      <c r="U16" s="80"/>
+      <c r="V16" s="80"/>
+      <c r="W16" s="80"/>
+      <c r="X16" s="80"/>
+      <c r="Y16" s="80"/>
+      <c r="Z16" s="80"/>
+      <c r="AB16" s="80"/>
+      <c r="AC16" s="80"/>
+      <c r="AD16" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE16" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF16" s="81"/>
+      <c r="AG16" s="80"/>
+      <c r="AH16" s="80"/>
+      <c r="AI16" s="80"/>
+      <c r="AJ16" s="80"/>
+      <c r="AK16" s="81"/>
+      <c r="AL16" s="81"/>
+      <c r="AM16" s="81"/>
+      <c r="AN16" s="81"/>
+      <c r="AO16" s="81"/>
+      <c r="AP16" s="80"/>
+      <c r="AQ16" s="80"/>
+      <c r="AR16" s="80"/>
+      <c r="AS16" s="80"/>
+      <c r="AT16" s="80"/>
+      <c r="AU16" s="80"/>
+      <c r="AV16" s="82"/>
+      <c r="AW16" s="80"/>
+      <c r="AX16" s="80"/>
+      <c r="AY16" s="80"/>
+      <c r="AZ16" s="80"/>
+      <c r="BA16" s="80"/>
+      <c r="BB16" s="80"/>
+      <c r="BC16" s="82"/>
+      <c r="BD16" s="80"/>
+      <c r="BE16" s="80"/>
+      <c r="BF16" s="80"/>
+      <c r="BG16" s="80"/>
+      <c r="BH16" s="80"/>
+      <c r="BI16" s="82"/>
+      <c r="BJ16" s="83"/>
       <c r="BK16" s="66"/>
       <c r="BL16" s="67"/>
       <c r="BM16" s="68"/>
     </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="49" t="s">
-        <v>60</v>
-      </c>
-      <c r="F17" s="50"/>
-      <c r="G17" s="69" t="n">
-        <f aca="false">[1]Netzplan!J17</f>
-        <v>1</v>
-      </c>
-      <c r="H17" s="70" t="n">
+    <row r="17" customFormat="false" ht="12.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17" s="42" t="s">
+        <v>29</v>
+      </c>
+      <c r="G17" s="73" t="n">
+        <f aca="false">Netzplan!J14</f>
+        <v>2</v>
+      </c>
+      <c r="H17" s="74" t="n">
         <f aca="false">SUM(I17:BJ17)</f>
-        <v>0</v>
-      </c>
-      <c r="I17" s="81"/>
-      <c r="J17" s="81"/>
-      <c r="K17" s="81"/>
-      <c r="L17" s="81"/>
-      <c r="M17" s="81"/>
-      <c r="N17" s="81"/>
-      <c r="O17" s="81"/>
-      <c r="P17" s="81"/>
-      <c r="Q17" s="81"/>
-      <c r="R17" s="81"/>
-      <c r="S17" s="81"/>
-      <c r="T17" s="81"/>
-      <c r="U17" s="81"/>
-      <c r="V17" s="81"/>
-      <c r="W17" s="81"/>
-      <c r="X17" s="81"/>
-      <c r="Y17" s="81"/>
-      <c r="Z17" s="81"/>
-      <c r="AA17" s="81"/>
-      <c r="AB17" s="81"/>
-      <c r="AC17" s="81"/>
-      <c r="AD17" s="81"/>
-      <c r="AE17" s="81"/>
-      <c r="AF17" s="81"/>
-      <c r="AG17" s="81"/>
-      <c r="AH17" s="81"/>
-      <c r="AI17" s="81"/>
-      <c r="AJ17" s="81"/>
-      <c r="AK17" s="81"/>
-      <c r="AL17" s="81"/>
-      <c r="AM17" s="81"/>
-      <c r="AN17" s="81"/>
+        <v>2</v>
+      </c>
+      <c r="I17" s="80"/>
+      <c r="J17" s="80"/>
+      <c r="K17" s="80"/>
+      <c r="L17" s="80"/>
+      <c r="M17" s="80"/>
+      <c r="N17" s="80"/>
+      <c r="O17" s="80"/>
+      <c r="P17" s="80"/>
+      <c r="Q17" s="80"/>
+      <c r="R17" s="80"/>
+      <c r="S17" s="80"/>
+      <c r="T17" s="80"/>
+      <c r="U17" s="80"/>
+      <c r="V17" s="80"/>
+      <c r="W17" s="80"/>
+      <c r="X17" s="80"/>
+      <c r="Y17" s="80"/>
+      <c r="Z17" s="80"/>
+      <c r="AA17" s="80"/>
+      <c r="AB17" s="80"/>
+      <c r="AC17" s="80"/>
+      <c r="AD17" s="80"/>
+      <c r="AF17" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG17" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH17" s="80"/>
+      <c r="AI17" s="80"/>
+      <c r="AJ17" s="80"/>
+      <c r="AL17" s="80"/>
+      <c r="AM17" s="80"/>
+      <c r="AN17" s="80"/>
       <c r="AO17" s="81"/>
-      <c r="AP17" s="81"/>
-      <c r="AQ17" s="81"/>
+      <c r="AP17" s="80"/>
+      <c r="AQ17" s="80"/>
       <c r="AR17" s="81"/>
       <c r="AS17" s="81"/>
       <c r="AT17" s="81"/>
-      <c r="AU17" s="81"/>
+      <c r="AU17" s="80"/>
       <c r="AV17" s="82"/>
-      <c r="AW17" s="81"/>
-      <c r="AX17" s="81"/>
-      <c r="AY17" s="83"/>
-      <c r="AZ17" s="83"/>
-      <c r="BA17" s="81"/>
-      <c r="BB17" s="81"/>
+      <c r="AW17" s="80"/>
+      <c r="AX17" s="80"/>
+      <c r="AY17" s="80"/>
+      <c r="AZ17" s="80"/>
+      <c r="BA17" s="80"/>
+      <c r="BB17" s="80"/>
       <c r="BC17" s="82"/>
-      <c r="BD17" s="81"/>
-      <c r="BE17" s="81"/>
-      <c r="BF17" s="81"/>
-      <c r="BG17" s="81"/>
-      <c r="BH17" s="81"/>
+      <c r="BD17" s="80"/>
+      <c r="BE17" s="80"/>
+      <c r="BF17" s="80"/>
+      <c r="BG17" s="80"/>
+      <c r="BH17" s="80"/>
       <c r="BI17" s="82"/>
-      <c r="BJ17" s="84"/>
+      <c r="BJ17" s="83"/>
       <c r="BK17" s="66"/>
       <c r="BL17" s="67"/>
       <c r="BM17" s="68"/>
     </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="42" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="G18" s="73" t="n">
+        <f aca="false">Netzplan!J15</f>
+        <v>1</v>
+      </c>
+      <c r="H18" s="74" t="n">
+        <f aca="false">SUM(I18:BJ18)</f>
+        <v>1</v>
+      </c>
+      <c r="I18" s="80"/>
+      <c r="J18" s="80"/>
+      <c r="K18" s="80"/>
+      <c r="L18" s="80"/>
+      <c r="M18" s="80"/>
+      <c r="N18" s="80"/>
+      <c r="O18" s="80"/>
+      <c r="P18" s="80"/>
+      <c r="Q18" s="80"/>
+      <c r="R18" s="80"/>
+      <c r="S18" s="80"/>
+      <c r="T18" s="80"/>
+      <c r="U18" s="80"/>
+      <c r="V18" s="80"/>
+      <c r="W18" s="80"/>
+      <c r="X18" s="80"/>
+      <c r="Y18" s="80"/>
+      <c r="Z18" s="80"/>
+      <c r="AA18" s="80"/>
+      <c r="AB18" s="80"/>
+      <c r="AC18" s="80"/>
+      <c r="AD18" s="80"/>
+      <c r="AE18" s="80"/>
+      <c r="AF18" s="80"/>
+      <c r="AI18" s="80"/>
+      <c r="AJ18" s="80"/>
+      <c r="AL18" s="80"/>
+      <c r="AM18" s="80"/>
+      <c r="AO18" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP18" s="80"/>
+      <c r="AQ18" s="80"/>
+      <c r="AR18" s="83"/>
+      <c r="AS18" s="81"/>
+      <c r="AT18" s="80"/>
+      <c r="AU18" s="80"/>
+      <c r="AV18" s="82"/>
+      <c r="AW18" s="80"/>
+      <c r="AX18" s="80"/>
+      <c r="AY18" s="80"/>
+      <c r="AZ18" s="80"/>
+      <c r="BA18" s="80"/>
+      <c r="BB18" s="80"/>
+      <c r="BC18" s="82"/>
+      <c r="BD18" s="80"/>
+      <c r="BE18" s="80"/>
+      <c r="BF18" s="80"/>
+      <c r="BG18" s="80"/>
+      <c r="BH18" s="80"/>
+      <c r="BI18" s="82"/>
+      <c r="BJ18" s="83"/>
+      <c r="BK18" s="66"/>
+      <c r="BL18" s="67"/>
+      <c r="BM18" s="68"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="42" t="s">
+        <v>29</v>
+      </c>
+      <c r="F19" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="G19" s="73" t="n">
+        <f aca="false">Netzplan!J16</f>
+        <v>3</v>
+      </c>
+      <c r="H19" s="74" t="n">
+        <f aca="false">SUM(I19:BJ19)</f>
+        <v>3</v>
+      </c>
+      <c r="I19" s="80"/>
+      <c r="J19" s="80"/>
+      <c r="K19" s="80"/>
+      <c r="L19" s="80"/>
+      <c r="M19" s="80"/>
+      <c r="N19" s="80"/>
+      <c r="O19" s="80"/>
+      <c r="P19" s="80"/>
+      <c r="Q19" s="80"/>
+      <c r="R19" s="80"/>
+      <c r="S19" s="80"/>
+      <c r="T19" s="80"/>
+      <c r="U19" s="80"/>
+      <c r="V19" s="80"/>
+      <c r="W19" s="80"/>
+      <c r="X19" s="80"/>
+      <c r="Y19" s="80"/>
+      <c r="Z19" s="80"/>
+      <c r="AA19" s="80"/>
+      <c r="AB19" s="80"/>
+      <c r="AC19" s="80"/>
+      <c r="AD19" s="80"/>
+      <c r="AE19" s="80"/>
+      <c r="AF19" s="80"/>
+      <c r="AG19" s="80"/>
+      <c r="AI19" s="80"/>
+      <c r="AJ19" s="80"/>
+      <c r="AO19" s="80"/>
+      <c r="AP19" s="80"/>
+      <c r="AQ19" s="80"/>
+      <c r="AR19" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS19" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT19" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU19" s="81"/>
+      <c r="AV19" s="82"/>
+      <c r="AW19" s="80"/>
+      <c r="AX19" s="80"/>
+      <c r="AY19" s="81"/>
+      <c r="AZ19" s="81"/>
+      <c r="BA19" s="81"/>
+      <c r="BB19" s="80"/>
+      <c r="BC19" s="82"/>
+      <c r="BD19" s="80"/>
+      <c r="BE19" s="80"/>
+      <c r="BF19" s="80"/>
+      <c r="BG19" s="80"/>
+      <c r="BH19" s="80"/>
+      <c r="BI19" s="82"/>
+      <c r="BJ19" s="83"/>
+      <c r="BK19" s="66"/>
+      <c r="BL19" s="67"/>
+      <c r="BM19" s="68"/>
+    </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>78</v>
+      <c r="A20" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="49" t="s">
+        <v>60</v>
+      </c>
+      <c r="F20" s="50"/>
+      <c r="G20" s="73" t="n">
+        <f aca="false">Netzplan!J17</f>
+        <v>1</v>
+      </c>
+      <c r="H20" s="74" t="n">
+        <f aca="false">SUM(I20:BJ20)</f>
+        <v>1</v>
+      </c>
+      <c r="I20" s="86"/>
+      <c r="J20" s="86"/>
+      <c r="K20" s="86"/>
+      <c r="L20" s="86"/>
+      <c r="M20" s="86"/>
+      <c r="N20" s="86"/>
+      <c r="O20" s="86"/>
+      <c r="P20" s="86"/>
+      <c r="Q20" s="86"/>
+      <c r="R20" s="86"/>
+      <c r="S20" s="86"/>
+      <c r="T20" s="86"/>
+      <c r="U20" s="86"/>
+      <c r="V20" s="86"/>
+      <c r="W20" s="86"/>
+      <c r="X20" s="86"/>
+      <c r="Y20" s="86"/>
+      <c r="Z20" s="86"/>
+      <c r="AA20" s="86"/>
+      <c r="AB20" s="86"/>
+      <c r="AC20" s="86"/>
+      <c r="AD20" s="86"/>
+      <c r="AE20" s="86"/>
+      <c r="AF20" s="86"/>
+      <c r="AG20" s="86"/>
+      <c r="AH20" s="86"/>
+      <c r="AI20" s="86"/>
+      <c r="AJ20" s="86"/>
+      <c r="AK20" s="86"/>
+      <c r="AL20" s="86"/>
+      <c r="AM20" s="86"/>
+      <c r="AN20" s="86"/>
+      <c r="AO20" s="86"/>
+      <c r="AP20" s="86"/>
+      <c r="AQ20" s="86"/>
+      <c r="AS20" s="86"/>
+      <c r="AT20" s="86"/>
+      <c r="AU20" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV20" s="87"/>
+      <c r="AW20" s="86"/>
+      <c r="AX20" s="86"/>
+      <c r="AY20" s="88"/>
+      <c r="AZ20" s="88"/>
+      <c r="BA20" s="86"/>
+      <c r="BB20" s="86"/>
+      <c r="BC20" s="87"/>
+      <c r="BD20" s="86"/>
+      <c r="BE20" s="86"/>
+      <c r="BF20" s="86"/>
+      <c r="BG20" s="86"/>
+      <c r="BH20" s="86"/>
+      <c r="BI20" s="87"/>
+      <c r="BJ20" s="89"/>
+      <c r="BK20" s="66"/>
+      <c r="BL20" s="67"/>
+      <c r="BM20" s="68"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="20">
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B3:D3"/>
@@ -5399,18 +6078,21 @@
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B20:D20"/>
   </mergeCells>
-  <conditionalFormatting sqref="I1:BF9 I10:AC13 AE10:BF11 I17:BF17 AL14:BF14 AL15:AM15 AO15:BF15 AD12:BF12 AE13:BF13 I14:AE14 AG14:AJ14 I15:AG15 I16:AJ16 AI15:AJ15 AL16:BF16">
+  <conditionalFormatting sqref="AE12:BF13 AL17:BF17 AO18:BF19 I19:AG19 AL18:AM18 I1:BF11 I12:AC15 AD14:BF15 I16:Z16 AB16:BF16 I17:AD17 AF17:AJ17 I18:AF19 AI18:AJ19 I20:AQ20 AS20:BF20">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>IF(OR(WEEKDAY(I$1)=7,WEEKDAY(I$1)=1),1,0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H17">
+  <conditionalFormatting sqref="H3:H20">
     <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
-      <formula>IF(H2&lt;&gt;G2,TRUE())</formula>
+      <formula>IF(H3&lt;&gt;G3,TRUE())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I10:AC13 AE10:BF11 I17:BF17 AL14:BF14 AL15:AM15 AO15:BF15 I2:BF9 AD12:BF12 AE13:BF13 I14:AE14 AG14:AJ14 I15:AG15 I16:AJ16 AI15:AJ15 AL16:BF16">
+  <conditionalFormatting sqref="AE12:BF13 AL17:BF17 AO18:BF19 I19:AG19 AL18:AM18 I3:BF11 I12:AC15 AD14:BF15 I16:Z16 AB16:BF16 I17:AD17 AF17:AJ17 I18:AF19 AI18:AJ19 I20:AQ20 AS20:BF20">
     <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>1</formula>
     </cfRule>
@@ -5422,5 +6104,6 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>